--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -218,12 +218,33 @@
   </si>
   <si>
     <t>Nº</t>
+  </si>
+  <si>
+    <t>Estonia Meistriliiga</t>
+  </si>
+  <si>
+    <t>2025</t>
+  </si>
+  <si>
+    <t>Tallinna FC Levadia</t>
+  </si>
+  <si>
+    <t>Harju Jalgpallikool</t>
+  </si>
+  <si>
+    <t>['8', '26', '48', '49', '63']</t>
+  </si>
+  <si>
+    <t>[]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -276,11 +297,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -575,7 +597,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP1"/>
+  <dimension ref="A1:BP2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -784,6 +806,212 @@
         <v>66</v>
       </c>
     </row>
+    <row r="2" spans="1:68">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>7828458</v>
+      </c>
+      <c r="C2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E2" s="2">
+        <v>45716.58333333334</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H2" t="s">
+        <v>71</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>5</v>
+      </c>
+      <c r="O2" t="s">
+        <v>72</v>
+      </c>
+      <c r="P2" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q2">
+        <v>1.73</v>
+      </c>
+      <c r="R2">
+        <v>2.63</v>
+      </c>
+      <c r="S2">
+        <v>7</v>
+      </c>
+      <c r="T2">
+        <v>1.22</v>
+      </c>
+      <c r="U2">
+        <v>3.75</v>
+      </c>
+      <c r="V2">
+        <v>2.05</v>
+      </c>
+      <c r="W2">
+        <v>1.7</v>
+      </c>
+      <c r="X2">
+        <v>4.2</v>
+      </c>
+      <c r="Y2">
+        <v>1.18</v>
+      </c>
+      <c r="Z2">
+        <v>1.18</v>
+      </c>
+      <c r="AA2">
+        <v>6.8</v>
+      </c>
+      <c r="AB2">
+        <v>13</v>
+      </c>
+      <c r="AC2">
+        <v>1.01</v>
+      </c>
+      <c r="AD2">
+        <v>17</v>
+      </c>
+      <c r="AE2">
+        <v>1.18</v>
+      </c>
+      <c r="AF2">
+        <v>4.5</v>
+      </c>
+      <c r="AG2">
+        <v>1.37</v>
+      </c>
+      <c r="AH2">
+        <v>2.85</v>
+      </c>
+      <c r="AI2">
+        <v>1.73</v>
+      </c>
+      <c r="AJ2">
+        <v>1.93</v>
+      </c>
+      <c r="AK2">
+        <v>1.02</v>
+      </c>
+      <c r="AL2">
+        <v>1.1</v>
+      </c>
+      <c r="AM2">
+        <v>3.5</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <v>3</v>
+      </c>
+      <c r="AQ2">
+        <v>0</v>
+      </c>
+      <c r="AR2">
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <v>0</v>
+      </c>
+      <c r="AU2">
+        <v>11</v>
+      </c>
+      <c r="AV2">
+        <v>2</v>
+      </c>
+      <c r="AW2">
+        <v>6</v>
+      </c>
+      <c r="AX2">
+        <v>4</v>
+      </c>
+      <c r="AY2">
+        <v>17</v>
+      </c>
+      <c r="AZ2">
+        <v>6</v>
+      </c>
+      <c r="BA2">
+        <v>11</v>
+      </c>
+      <c r="BB2">
+        <v>3</v>
+      </c>
+      <c r="BC2">
+        <v>14</v>
+      </c>
+      <c r="BD2">
+        <v>0</v>
+      </c>
+      <c r="BE2">
+        <v>0</v>
+      </c>
+      <c r="BF2">
+        <v>0</v>
+      </c>
+      <c r="BG2">
+        <v>0</v>
+      </c>
+      <c r="BH2">
+        <v>0</v>
+      </c>
+      <c r="BI2">
+        <v>0</v>
+      </c>
+      <c r="BJ2">
+        <v>0</v>
+      </c>
+      <c r="BK2">
+        <v>0</v>
+      </c>
+      <c r="BL2">
+        <v>0</v>
+      </c>
+      <c r="BM2">
+        <v>0</v>
+      </c>
+      <c r="BN2">
+        <v>0</v>
+      </c>
+      <c r="BO2">
+        <v>0</v>
+      </c>
+      <c r="BP2">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="81">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -229,13 +229,34 @@
     <t>Tallinna FC Levadia</t>
   </si>
   <si>
+    <t>Vaprus</t>
+  </si>
+  <si>
+    <t>Tallinna FC Flora</t>
+  </si>
+  <si>
     <t>Harju Jalgpallikool</t>
   </si>
   <si>
+    <t>Nõmme Kalju</t>
+  </si>
+  <si>
+    <t>Trans</t>
+  </si>
+  <si>
     <t>['8', '26', '48', '49', '63']</t>
   </si>
   <si>
     <t>[]</t>
+  </si>
+  <si>
+    <t>['43', '90+4']</t>
+  </si>
+  <si>
+    <t>['34', '59', '86']</t>
+  </si>
+  <si>
+    <t>['55', '57']</t>
   </si>
 </sst>
 </file>
@@ -597,7 +618,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP2"/>
+  <dimension ref="A1:BP4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -829,7 +850,7 @@
         <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I2">
         <v>2</v>
@@ -850,10 +871,10 @@
         <v>5</v>
       </c>
       <c r="O2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="P2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="Q2">
         <v>1.73</v>
@@ -1009,6 +1030,418 @@
         <v>0</v>
       </c>
       <c r="BP2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:68">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>7828459</v>
+      </c>
+      <c r="C3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E3" s="2">
+        <v>45717.3125</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H3" t="s">
+        <v>74</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>3</v>
+      </c>
+      <c r="N3">
+        <v>3</v>
+      </c>
+      <c r="O3" t="s">
+        <v>77</v>
+      </c>
+      <c r="P3" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q3">
+        <v>5</v>
+      </c>
+      <c r="R3">
+        <v>2.6</v>
+      </c>
+      <c r="S3">
+        <v>1.95</v>
+      </c>
+      <c r="T3">
+        <v>1.22</v>
+      </c>
+      <c r="U3">
+        <v>3.7</v>
+      </c>
+      <c r="V3">
+        <v>2.1</v>
+      </c>
+      <c r="W3">
+        <v>1.67</v>
+      </c>
+      <c r="X3">
+        <v>4.7</v>
+      </c>
+      <c r="Y3">
+        <v>1.14</v>
+      </c>
+      <c r="Z3">
+        <v>5.2</v>
+      </c>
+      <c r="AA3">
+        <v>4.3</v>
+      </c>
+      <c r="AB3">
+        <v>1.55</v>
+      </c>
+      <c r="AC3">
+        <v>1.01</v>
+      </c>
+      <c r="AD3">
+        <v>17</v>
+      </c>
+      <c r="AE3">
+        <v>1.07</v>
+      </c>
+      <c r="AF3">
+        <v>5.9</v>
+      </c>
+      <c r="AG3">
+        <v>1.43</v>
+      </c>
+      <c r="AH3">
+        <v>2.62</v>
+      </c>
+      <c r="AI3">
+        <v>1.53</v>
+      </c>
+      <c r="AJ3">
+        <v>2.25</v>
+      </c>
+      <c r="AK3">
+        <v>2.6</v>
+      </c>
+      <c r="AL3">
+        <v>1.14</v>
+      </c>
+      <c r="AM3">
+        <v>1.09</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <v>3</v>
+      </c>
+      <c r="AR3">
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <v>4</v>
+      </c>
+      <c r="AV3">
+        <v>10</v>
+      </c>
+      <c r="AW3">
+        <v>1</v>
+      </c>
+      <c r="AX3">
+        <v>19</v>
+      </c>
+      <c r="AY3">
+        <v>5</v>
+      </c>
+      <c r="AZ3">
+        <v>29</v>
+      </c>
+      <c r="BA3">
+        <v>2</v>
+      </c>
+      <c r="BB3">
+        <v>8</v>
+      </c>
+      <c r="BC3">
+        <v>10</v>
+      </c>
+      <c r="BD3">
+        <v>0</v>
+      </c>
+      <c r="BE3">
+        <v>0</v>
+      </c>
+      <c r="BF3">
+        <v>0</v>
+      </c>
+      <c r="BG3">
+        <v>0</v>
+      </c>
+      <c r="BH3">
+        <v>0</v>
+      </c>
+      <c r="BI3">
+        <v>0</v>
+      </c>
+      <c r="BJ3">
+        <v>0</v>
+      </c>
+      <c r="BK3">
+        <v>0</v>
+      </c>
+      <c r="BL3">
+        <v>0</v>
+      </c>
+      <c r="BM3">
+        <v>0</v>
+      </c>
+      <c r="BN3">
+        <v>0</v>
+      </c>
+      <c r="BO3">
+        <v>0</v>
+      </c>
+      <c r="BP3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:68">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>7828460</v>
+      </c>
+      <c r="C4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E4" s="2">
+        <v>45717.39583333334</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
+        <v>72</v>
+      </c>
+      <c r="H4" t="s">
+        <v>75</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
+      </c>
+      <c r="N4">
+        <v>4</v>
+      </c>
+      <c r="O4" t="s">
+        <v>78</v>
+      </c>
+      <c r="P4" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q4">
+        <v>2.2</v>
+      </c>
+      <c r="R4">
+        <v>2.4</v>
+      </c>
+      <c r="S4">
+        <v>4</v>
+      </c>
+      <c r="T4">
+        <v>1.25</v>
+      </c>
+      <c r="U4">
+        <v>3.55</v>
+      </c>
+      <c r="V4">
+        <v>2.15</v>
+      </c>
+      <c r="W4">
+        <v>1.62</v>
+      </c>
+      <c r="X4">
+        <v>5.05</v>
+      </c>
+      <c r="Y4">
+        <v>1.12</v>
+      </c>
+      <c r="Z4">
+        <v>1.7</v>
+      </c>
+      <c r="AA4">
+        <v>4.2</v>
+      </c>
+      <c r="AB4">
+        <v>4.1</v>
+      </c>
+      <c r="AC4">
+        <v>1.01</v>
+      </c>
+      <c r="AD4">
+        <v>15</v>
+      </c>
+      <c r="AE4">
+        <v>1.1</v>
+      </c>
+      <c r="AF4">
+        <v>5.05</v>
+      </c>
+      <c r="AG4">
+        <v>1.5</v>
+      </c>
+      <c r="AH4">
+        <v>2.41</v>
+      </c>
+      <c r="AI4">
+        <v>1.48</v>
+      </c>
+      <c r="AJ4">
+        <v>2.35</v>
+      </c>
+      <c r="AK4">
+        <v>1.18</v>
+      </c>
+      <c r="AL4">
+        <v>1.18</v>
+      </c>
+      <c r="AM4">
+        <v>2.1</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>1</v>
+      </c>
+      <c r="AQ4">
+        <v>1</v>
+      </c>
+      <c r="AR4">
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <v>5</v>
+      </c>
+      <c r="AV4">
+        <v>7</v>
+      </c>
+      <c r="AW4">
+        <v>5</v>
+      </c>
+      <c r="AX4">
+        <v>5</v>
+      </c>
+      <c r="AY4">
+        <v>10</v>
+      </c>
+      <c r="AZ4">
+        <v>12</v>
+      </c>
+      <c r="BA4">
+        <v>5</v>
+      </c>
+      <c r="BB4">
+        <v>8</v>
+      </c>
+      <c r="BC4">
+        <v>13</v>
+      </c>
+      <c r="BD4">
+        <v>0</v>
+      </c>
+      <c r="BE4">
+        <v>0</v>
+      </c>
+      <c r="BF4">
+        <v>0</v>
+      </c>
+      <c r="BG4">
+        <v>0</v>
+      </c>
+      <c r="BH4">
+        <v>0</v>
+      </c>
+      <c r="BI4">
+        <v>0</v>
+      </c>
+      <c r="BJ4">
+        <v>0</v>
+      </c>
+      <c r="BK4">
+        <v>0</v>
+      </c>
+      <c r="BL4">
+        <v>0</v>
+      </c>
+      <c r="BM4">
+        <v>0</v>
+      </c>
+      <c r="BN4">
+        <v>0</v>
+      </c>
+      <c r="BO4">
+        <v>0</v>
+      </c>
+      <c r="BP4">
         <v>0</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="89">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -235,6 +235,12 @@
     <t>Tallinna FC Flora</t>
   </si>
   <si>
+    <t>Kuressaare</t>
+  </si>
+  <si>
+    <t>Tallinna Kalev</t>
+  </si>
+  <si>
     <t>Harju Jalgpallikool</t>
   </si>
   <si>
@@ -244,6 +250,12 @@
     <t>Trans</t>
   </si>
   <si>
+    <t>Paide</t>
+  </si>
+  <si>
+    <t>Tammeka</t>
+  </si>
+  <si>
     <t>['8', '26', '48', '49', '63']</t>
   </si>
   <si>
@@ -253,10 +265,22 @@
     <t>['43', '90+4']</t>
   </si>
   <si>
+    <t>['90+3']</t>
+  </si>
+  <si>
+    <t>['69']</t>
+  </si>
+  <si>
     <t>['34', '59', '86']</t>
   </si>
   <si>
     <t>['55', '57']</t>
+  </si>
+  <si>
+    <t>['72', '90+4']</t>
+  </si>
+  <si>
+    <t>['36', '63']</t>
   </si>
 </sst>
 </file>
@@ -618,7 +642,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP4"/>
+  <dimension ref="A1:BP6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -850,7 +874,7 @@
         <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I2">
         <v>2</v>
@@ -871,10 +895,10 @@
         <v>5</v>
       </c>
       <c r="O2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="P2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="Q2">
         <v>1.73</v>
@@ -1056,7 +1080,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -1077,10 +1101,10 @@
         <v>3</v>
       </c>
       <c r="O3" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="P3" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -1262,7 +1286,7 @@
         <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I4">
         <v>1</v>
@@ -1283,10 +1307,10 @@
         <v>4</v>
       </c>
       <c r="O4" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="P4" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -1442,6 +1466,418 @@
         <v>0</v>
       </c>
       <c r="BP4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:68">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>7828461</v>
+      </c>
+      <c r="C5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="2">
+        <v>45718.3125</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
+        <v>73</v>
+      </c>
+      <c r="H5" t="s">
+        <v>78</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
+      </c>
+      <c r="N5">
+        <v>3</v>
+      </c>
+      <c r="O5" t="s">
+        <v>83</v>
+      </c>
+      <c r="P5" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q5">
+        <v>7</v>
+      </c>
+      <c r="R5">
+        <v>2.75</v>
+      </c>
+      <c r="S5">
+        <v>1.67</v>
+      </c>
+      <c r="T5">
+        <v>1.18</v>
+      </c>
+      <c r="U5">
+        <v>4.2</v>
+      </c>
+      <c r="V5">
+        <v>2.05</v>
+      </c>
+      <c r="W5">
+        <v>1.72</v>
+      </c>
+      <c r="X5">
+        <v>4.5</v>
+      </c>
+      <c r="Y5">
+        <v>1.16</v>
+      </c>
+      <c r="Z5">
+        <v>8.5</v>
+      </c>
+      <c r="AA5">
+        <v>5.8</v>
+      </c>
+      <c r="AB5">
+        <v>1.25</v>
+      </c>
+      <c r="AC5">
+        <v>1.01</v>
+      </c>
+      <c r="AD5">
+        <v>17</v>
+      </c>
+      <c r="AE5">
+        <v>1.06</v>
+      </c>
+      <c r="AF5">
+        <v>6.3</v>
+      </c>
+      <c r="AG5">
+        <v>1.37</v>
+      </c>
+      <c r="AH5">
+        <v>2.85</v>
+      </c>
+      <c r="AI5">
+        <v>1.72</v>
+      </c>
+      <c r="AJ5">
+        <v>1.95</v>
+      </c>
+      <c r="AK5">
+        <v>3.72</v>
+      </c>
+      <c r="AL5">
+        <v>1.09</v>
+      </c>
+      <c r="AM5">
+        <v>1.01</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>0</v>
+      </c>
+      <c r="AQ5">
+        <v>3</v>
+      </c>
+      <c r="AR5">
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <v>7</v>
+      </c>
+      <c r="AV5">
+        <v>9</v>
+      </c>
+      <c r="AW5">
+        <v>2</v>
+      </c>
+      <c r="AX5">
+        <v>6</v>
+      </c>
+      <c r="AY5">
+        <v>9</v>
+      </c>
+      <c r="AZ5">
+        <v>15</v>
+      </c>
+      <c r="BA5">
+        <v>4</v>
+      </c>
+      <c r="BB5">
+        <v>6</v>
+      </c>
+      <c r="BC5">
+        <v>10</v>
+      </c>
+      <c r="BD5">
+        <v>0</v>
+      </c>
+      <c r="BE5">
+        <v>0</v>
+      </c>
+      <c r="BF5">
+        <v>0</v>
+      </c>
+      <c r="BG5">
+        <v>0</v>
+      </c>
+      <c r="BH5">
+        <v>0</v>
+      </c>
+      <c r="BI5">
+        <v>0</v>
+      </c>
+      <c r="BJ5">
+        <v>0</v>
+      </c>
+      <c r="BK5">
+        <v>0</v>
+      </c>
+      <c r="BL5">
+        <v>0</v>
+      </c>
+      <c r="BM5">
+        <v>0</v>
+      </c>
+      <c r="BN5">
+        <v>0</v>
+      </c>
+      <c r="BO5">
+        <v>0</v>
+      </c>
+      <c r="BP5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:68">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>7828462</v>
+      </c>
+      <c r="C6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" s="2">
+        <v>45718.39583333334</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H6" t="s">
+        <v>79</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+      <c r="N6">
+        <v>3</v>
+      </c>
+      <c r="O6" t="s">
+        <v>84</v>
+      </c>
+      <c r="P6" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q6">
+        <v>4.33</v>
+      </c>
+      <c r="R6">
+        <v>2.4</v>
+      </c>
+      <c r="S6">
+        <v>2.2</v>
+      </c>
+      <c r="T6">
+        <v>1.27</v>
+      </c>
+      <c r="U6">
+        <v>3.34</v>
+      </c>
+      <c r="V6">
+        <v>2.33</v>
+      </c>
+      <c r="W6">
+        <v>1.56</v>
+      </c>
+      <c r="X6">
+        <v>5.15</v>
+      </c>
+      <c r="Y6">
+        <v>1.12</v>
+      </c>
+      <c r="Z6">
+        <v>3.6</v>
+      </c>
+      <c r="AA6">
+        <v>4.2</v>
+      </c>
+      <c r="AB6">
+        <v>1.75</v>
+      </c>
+      <c r="AC6">
+        <v>1.01</v>
+      </c>
+      <c r="AD6">
+        <v>15</v>
+      </c>
+      <c r="AE6">
+        <v>1.14</v>
+      </c>
+      <c r="AF6">
+        <v>4.35</v>
+      </c>
+      <c r="AG6">
+        <v>1.55</v>
+      </c>
+      <c r="AH6">
+        <v>2.2</v>
+      </c>
+      <c r="AI6">
+        <v>1.53</v>
+      </c>
+      <c r="AJ6">
+        <v>2.27</v>
+      </c>
+      <c r="AK6">
+        <v>1.92</v>
+      </c>
+      <c r="AL6">
+        <v>1.21</v>
+      </c>
+      <c r="AM6">
+        <v>1.21</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <v>3</v>
+      </c>
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <v>4</v>
+      </c>
+      <c r="AV6">
+        <v>14</v>
+      </c>
+      <c r="AW6">
+        <v>7</v>
+      </c>
+      <c r="AX6">
+        <v>8</v>
+      </c>
+      <c r="AY6">
+        <v>11</v>
+      </c>
+      <c r="AZ6">
+        <v>22</v>
+      </c>
+      <c r="BA6">
+        <v>8</v>
+      </c>
+      <c r="BB6">
+        <v>9</v>
+      </c>
+      <c r="BC6">
+        <v>17</v>
+      </c>
+      <c r="BD6">
+        <v>0</v>
+      </c>
+      <c r="BE6">
+        <v>0</v>
+      </c>
+      <c r="BF6">
+        <v>0</v>
+      </c>
+      <c r="BG6">
+        <v>0</v>
+      </c>
+      <c r="BH6">
+        <v>0</v>
+      </c>
+      <c r="BI6">
+        <v>0</v>
+      </c>
+      <c r="BJ6">
+        <v>0</v>
+      </c>
+      <c r="BK6">
+        <v>0</v>
+      </c>
+      <c r="BL6">
+        <v>0</v>
+      </c>
+      <c r="BM6">
+        <v>0</v>
+      </c>
+      <c r="BN6">
+        <v>0</v>
+      </c>
+      <c r="BO6">
+        <v>0</v>
+      </c>
+      <c r="BP6">
         <v>0</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="93">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -241,21 +241,21 @@
     <t>Tallinna Kalev</t>
   </si>
   <si>
+    <t>Tammeka</t>
+  </si>
+  <si>
+    <t>Trans</t>
+  </si>
+  <si>
     <t>Harju Jalgpallikool</t>
   </si>
   <si>
     <t>Nõmme Kalju</t>
   </si>
   <si>
-    <t>Trans</t>
-  </si>
-  <si>
     <t>Paide</t>
   </si>
   <si>
-    <t>Tammeka</t>
-  </si>
-  <si>
     <t>['8', '26', '48', '49', '63']</t>
   </si>
   <si>
@@ -271,6 +271,9 @@
     <t>['69']</t>
   </si>
   <si>
+    <t>['25', '72']</t>
+  </si>
+  <si>
     <t>['34', '59', '86']</t>
   </si>
   <si>
@@ -281,6 +284,15 @@
   </si>
   <si>
     <t>['36', '63']</t>
+  </si>
+  <si>
+    <t>['16']</t>
+  </si>
+  <si>
+    <t>['18', '44', '89']</t>
+  </si>
+  <si>
+    <t>['8', '90+6']</t>
   </si>
 </sst>
 </file>
@@ -642,7 +654,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP6"/>
+  <dimension ref="A1:BP9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -874,7 +886,7 @@
         <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I2">
         <v>2</v>
@@ -1080,7 +1092,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -1104,7 +1116,7 @@
         <v>81</v>
       </c>
       <c r="P3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -1286,7 +1298,7 @@
         <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I4">
         <v>1</v>
@@ -1310,7 +1322,7 @@
         <v>82</v>
       </c>
       <c r="P4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -1388,7 +1400,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AQ4">
         <v>1</v>
@@ -1492,7 +1504,7 @@
         <v>73</v>
       </c>
       <c r="H5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1516,7 +1528,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q5">
         <v>7</v>
@@ -1698,7 +1710,7 @@
         <v>74</v>
       </c>
       <c r="H6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -1722,7 +1734,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -1878,6 +1890,624 @@
         <v>0</v>
       </c>
       <c r="BP6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:68">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>7828463</v>
+      </c>
+      <c r="C7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45724.3125</v>
+      </c>
+      <c r="F7">
+        <v>2</v>
+      </c>
+      <c r="G7" t="s">
+        <v>72</v>
+      </c>
+      <c r="H7" t="s">
+        <v>71</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>1</v>
+      </c>
+      <c r="O7" t="s">
+        <v>81</v>
+      </c>
+      <c r="P7" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q7">
+        <v>1.83</v>
+      </c>
+      <c r="R7">
+        <v>2.5</v>
+      </c>
+      <c r="S7">
+        <v>6</v>
+      </c>
+      <c r="T7">
+        <v>1.22</v>
+      </c>
+      <c r="U7">
+        <v>3.65</v>
+      </c>
+      <c r="V7">
+        <v>2.27</v>
+      </c>
+      <c r="W7">
+        <v>1.59</v>
+      </c>
+      <c r="X7">
+        <v>5.3</v>
+      </c>
+      <c r="Y7">
+        <v>1.11</v>
+      </c>
+      <c r="Z7">
+        <v>1.24</v>
+      </c>
+      <c r="AA7">
+        <v>6.4</v>
+      </c>
+      <c r="AB7">
+        <v>9.6</v>
+      </c>
+      <c r="AC7">
+        <v>1.01</v>
+      </c>
+      <c r="AD7">
+        <v>13</v>
+      </c>
+      <c r="AE7">
+        <v>1.11</v>
+      </c>
+      <c r="AF7">
+        <v>5.5</v>
+      </c>
+      <c r="AG7">
+        <v>1.53</v>
+      </c>
+      <c r="AH7">
+        <v>2.25</v>
+      </c>
+      <c r="AI7">
+        <v>1.67</v>
+      </c>
+      <c r="AJ7">
+        <v>2.1</v>
+      </c>
+      <c r="AK7">
+        <v>1.04</v>
+      </c>
+      <c r="AL7">
+        <v>1.12</v>
+      </c>
+      <c r="AM7">
+        <v>3.02</v>
+      </c>
+      <c r="AN7">
+        <v>1</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>0.5</v>
+      </c>
+      <c r="AQ7">
+        <v>3</v>
+      </c>
+      <c r="AR7">
+        <v>1.43</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>1.43</v>
+      </c>
+      <c r="AU7">
+        <v>5</v>
+      </c>
+      <c r="AV7">
+        <v>4</v>
+      </c>
+      <c r="AW7">
+        <v>11</v>
+      </c>
+      <c r="AX7">
+        <v>3</v>
+      </c>
+      <c r="AY7">
+        <v>16</v>
+      </c>
+      <c r="AZ7">
+        <v>7</v>
+      </c>
+      <c r="BA7">
+        <v>10</v>
+      </c>
+      <c r="BB7">
+        <v>1</v>
+      </c>
+      <c r="BC7">
+        <v>11</v>
+      </c>
+      <c r="BD7">
+        <v>0</v>
+      </c>
+      <c r="BE7">
+        <v>0</v>
+      </c>
+      <c r="BF7">
+        <v>0</v>
+      </c>
+      <c r="BG7">
+        <v>0</v>
+      </c>
+      <c r="BH7">
+        <v>0</v>
+      </c>
+      <c r="BI7">
+        <v>0</v>
+      </c>
+      <c r="BJ7">
+        <v>0</v>
+      </c>
+      <c r="BK7">
+        <v>0</v>
+      </c>
+      <c r="BL7">
+        <v>0</v>
+      </c>
+      <c r="BM7">
+        <v>0</v>
+      </c>
+      <c r="BN7">
+        <v>0</v>
+      </c>
+      <c r="BO7">
+        <v>0</v>
+      </c>
+      <c r="BP7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:68">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>7828464</v>
+      </c>
+      <c r="C8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D8" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" s="2">
+        <v>45724.39583333334</v>
+      </c>
+      <c r="F8">
+        <v>2</v>
+      </c>
+      <c r="G8" t="s">
+        <v>75</v>
+      </c>
+      <c r="H8" t="s">
+        <v>70</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>2</v>
+      </c>
+      <c r="K8">
+        <v>3</v>
+      </c>
+      <c r="L8">
+        <v>2</v>
+      </c>
+      <c r="M8">
+        <v>3</v>
+      </c>
+      <c r="N8">
+        <v>5</v>
+      </c>
+      <c r="O8" t="s">
+        <v>85</v>
+      </c>
+      <c r="P8" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q8">
+        <v>8.5</v>
+      </c>
+      <c r="R8">
+        <v>2.5</v>
+      </c>
+      <c r="S8">
+        <v>1.73</v>
+      </c>
+      <c r="T8">
+        <v>1.28</v>
+      </c>
+      <c r="U8">
+        <v>3.34</v>
+      </c>
+      <c r="V8">
+        <v>2.41</v>
+      </c>
+      <c r="W8">
+        <v>1.5</v>
+      </c>
+      <c r="X8">
+        <v>5.6</v>
+      </c>
+      <c r="Y8">
+        <v>1.08</v>
+      </c>
+      <c r="Z8">
+        <v>14</v>
+      </c>
+      <c r="AA8">
+        <v>6.7</v>
+      </c>
+      <c r="AB8">
+        <v>1.18</v>
+      </c>
+      <c r="AC8">
+        <v>1.01</v>
+      </c>
+      <c r="AD8">
+        <v>13</v>
+      </c>
+      <c r="AE8">
+        <v>1.14</v>
+      </c>
+      <c r="AF8">
+        <v>4.8</v>
+      </c>
+      <c r="AG8">
+        <v>1.89</v>
+      </c>
+      <c r="AH8">
+        <v>1.84</v>
+      </c>
+      <c r="AI8">
+        <v>2.2</v>
+      </c>
+      <c r="AJ8">
+        <v>1.62</v>
+      </c>
+      <c r="AK8">
+        <v>3.96</v>
+      </c>
+      <c r="AL8">
+        <v>1.09</v>
+      </c>
+      <c r="AM8">
+        <v>1.03</v>
+      </c>
+      <c r="AN8">
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <v>0</v>
+      </c>
+      <c r="AQ8">
+        <v>3</v>
+      </c>
+      <c r="AR8">
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <v>6</v>
+      </c>
+      <c r="AV8">
+        <v>12</v>
+      </c>
+      <c r="AW8">
+        <v>1</v>
+      </c>
+      <c r="AX8">
+        <v>6</v>
+      </c>
+      <c r="AY8">
+        <v>7</v>
+      </c>
+      <c r="AZ8">
+        <v>18</v>
+      </c>
+      <c r="BA8">
+        <v>1</v>
+      </c>
+      <c r="BB8">
+        <v>10</v>
+      </c>
+      <c r="BC8">
+        <v>11</v>
+      </c>
+      <c r="BD8">
+        <v>0</v>
+      </c>
+      <c r="BE8">
+        <v>0</v>
+      </c>
+      <c r="BF8">
+        <v>0</v>
+      </c>
+      <c r="BG8">
+        <v>0</v>
+      </c>
+      <c r="BH8">
+        <v>0</v>
+      </c>
+      <c r="BI8">
+        <v>0</v>
+      </c>
+      <c r="BJ8">
+        <v>0</v>
+      </c>
+      <c r="BK8">
+        <v>0</v>
+      </c>
+      <c r="BL8">
+        <v>0</v>
+      </c>
+      <c r="BM8">
+        <v>0</v>
+      </c>
+      <c r="BN8">
+        <v>0</v>
+      </c>
+      <c r="BO8">
+        <v>0</v>
+      </c>
+      <c r="BP8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:68">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>7828465</v>
+      </c>
+      <c r="C9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9" s="2">
+        <v>45724.39583333334</v>
+      </c>
+      <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9" t="s">
+        <v>76</v>
+      </c>
+      <c r="H9" t="s">
+        <v>73</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>2</v>
+      </c>
+      <c r="N9">
+        <v>2</v>
+      </c>
+      <c r="O9" t="s">
+        <v>81</v>
+      </c>
+      <c r="P9" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q9">
+        <v>2</v>
+      </c>
+      <c r="R9">
+        <v>2.5</v>
+      </c>
+      <c r="S9">
+        <v>4.75</v>
+      </c>
+      <c r="T9">
+        <v>1.22</v>
+      </c>
+      <c r="U9">
+        <v>3.65</v>
+      </c>
+      <c r="V9">
+        <v>2.16</v>
+      </c>
+      <c r="W9">
+        <v>1.65</v>
+      </c>
+      <c r="X9">
+        <v>4.55</v>
+      </c>
+      <c r="Y9">
+        <v>1.15</v>
+      </c>
+      <c r="Z9">
+        <v>1.48</v>
+      </c>
+      <c r="AA9">
+        <v>4.4</v>
+      </c>
+      <c r="AB9">
+        <v>5.8</v>
+      </c>
+      <c r="AC9">
+        <v>1.01</v>
+      </c>
+      <c r="AD9">
+        <v>17</v>
+      </c>
+      <c r="AE9">
+        <v>1.11</v>
+      </c>
+      <c r="AF9">
+        <v>5.5</v>
+      </c>
+      <c r="AG9">
+        <v>1.48</v>
+      </c>
+      <c r="AH9">
+        <v>2.47</v>
+      </c>
+      <c r="AI9">
+        <v>1.57</v>
+      </c>
+      <c r="AJ9">
+        <v>2.25</v>
+      </c>
+      <c r="AK9">
+        <v>1.11</v>
+      </c>
+      <c r="AL9">
+        <v>1.15</v>
+      </c>
+      <c r="AM9">
+        <v>2.45</v>
+      </c>
+      <c r="AN9">
+        <v>0</v>
+      </c>
+      <c r="AO9">
+        <v>0</v>
+      </c>
+      <c r="AP9">
+        <v>0</v>
+      </c>
+      <c r="AQ9">
+        <v>3</v>
+      </c>
+      <c r="AR9">
+        <v>0</v>
+      </c>
+      <c r="AS9">
+        <v>0</v>
+      </c>
+      <c r="AT9">
+        <v>0</v>
+      </c>
+      <c r="AU9">
+        <v>3</v>
+      </c>
+      <c r="AV9">
+        <v>5</v>
+      </c>
+      <c r="AW9">
+        <v>9</v>
+      </c>
+      <c r="AX9">
+        <v>2</v>
+      </c>
+      <c r="AY9">
+        <v>12</v>
+      </c>
+      <c r="AZ9">
+        <v>7</v>
+      </c>
+      <c r="BA9">
+        <v>11</v>
+      </c>
+      <c r="BB9">
+        <v>2</v>
+      </c>
+      <c r="BC9">
+        <v>13</v>
+      </c>
+      <c r="BD9">
+        <v>0</v>
+      </c>
+      <c r="BE9">
+        <v>0</v>
+      </c>
+      <c r="BF9">
+        <v>0</v>
+      </c>
+      <c r="BG9">
+        <v>0</v>
+      </c>
+      <c r="BH9">
+        <v>0</v>
+      </c>
+      <c r="BI9">
+        <v>0</v>
+      </c>
+      <c r="BJ9">
+        <v>0</v>
+      </c>
+      <c r="BK9">
+        <v>0</v>
+      </c>
+      <c r="BL9">
+        <v>0</v>
+      </c>
+      <c r="BM9">
+        <v>0</v>
+      </c>
+      <c r="BN9">
+        <v>0</v>
+      </c>
+      <c r="BO9">
+        <v>0</v>
+      </c>
+      <c r="BP9">
         <v>0</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="95">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -250,12 +250,12 @@
     <t>Harju Jalgpallikool</t>
   </si>
   <si>
+    <t>Paide</t>
+  </si>
+  <si>
     <t>Nõmme Kalju</t>
   </si>
   <si>
-    <t>Paide</t>
-  </si>
-  <si>
     <t>['8', '26', '48', '49', '63']</t>
   </si>
   <si>
@@ -272,6 +272,12 @@
   </si>
   <si>
     <t>['25', '72']</t>
+  </si>
+  <si>
+    <t>['27', '30']</t>
+  </si>
+  <si>
+    <t>['49', '55', '76']</t>
   </si>
   <si>
     <t>['34', '59', '86']</t>
@@ -654,7 +660,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP9"/>
+  <dimension ref="A1:BP11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1092,7 +1098,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -1116,7 +1122,7 @@
         <v>81</v>
       </c>
       <c r="P3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -1197,7 +1203,7 @@
         <v>0</v>
       </c>
       <c r="AQ3">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1322,7 +1328,7 @@
         <v>82</v>
       </c>
       <c r="P4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -1504,7 +1510,7 @@
         <v>73</v>
       </c>
       <c r="H5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1528,7 +1534,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="Q5">
         <v>7</v>
@@ -1734,7 +1740,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -1940,7 +1946,7 @@
         <v>81</v>
       </c>
       <c r="P7" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="Q7">
         <v>1.83</v>
@@ -2146,7 +2152,7 @@
         <v>85</v>
       </c>
       <c r="P8" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="Q8">
         <v>8.5</v>
@@ -2352,7 +2358,7 @@
         <v>81</v>
       </c>
       <c r="P9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -2508,6 +2514,418 @@
         <v>0</v>
       </c>
       <c r="BP9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:68">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>7828466</v>
+      </c>
+      <c r="C10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" t="s">
+        <v>69</v>
+      </c>
+      <c r="E10" s="2">
+        <v>45725.3125</v>
+      </c>
+      <c r="F10">
+        <v>2</v>
+      </c>
+      <c r="G10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H10" t="s">
+        <v>74</v>
+      </c>
+      <c r="I10">
+        <v>2</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>2</v>
+      </c>
+      <c r="L10">
+        <v>2</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>2</v>
+      </c>
+      <c r="O10" t="s">
+        <v>86</v>
+      </c>
+      <c r="P10" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q10">
+        <v>2.4</v>
+      </c>
+      <c r="R10">
+        <v>2.38</v>
+      </c>
+      <c r="S10">
+        <v>3.6</v>
+      </c>
+      <c r="T10">
+        <v>1.25</v>
+      </c>
+      <c r="U10">
+        <v>3.42</v>
+      </c>
+      <c r="V10">
+        <v>2.28</v>
+      </c>
+      <c r="W10">
+        <v>1.54</v>
+      </c>
+      <c r="X10">
+        <v>5.1</v>
+      </c>
+      <c r="Y10">
+        <v>1.12</v>
+      </c>
+      <c r="Z10">
+        <v>1.91</v>
+      </c>
+      <c r="AA10">
+        <v>3.78</v>
+      </c>
+      <c r="AB10">
+        <v>3.56</v>
+      </c>
+      <c r="AC10">
+        <v>1.01</v>
+      </c>
+      <c r="AD10">
+        <v>13</v>
+      </c>
+      <c r="AE10">
+        <v>1.12</v>
+      </c>
+      <c r="AF10">
+        <v>4.65</v>
+      </c>
+      <c r="AG10">
+        <v>1.53</v>
+      </c>
+      <c r="AH10">
+        <v>2.25</v>
+      </c>
+      <c r="AI10">
+        <v>3.48</v>
+      </c>
+      <c r="AJ10">
+        <v>1.24</v>
+      </c>
+      <c r="AK10">
+        <v>1.26</v>
+      </c>
+      <c r="AL10">
+        <v>1.22</v>
+      </c>
+      <c r="AM10">
+        <v>1.81</v>
+      </c>
+      <c r="AN10">
+        <v>0</v>
+      </c>
+      <c r="AO10">
+        <v>0</v>
+      </c>
+      <c r="AP10">
+        <v>3</v>
+      </c>
+      <c r="AQ10">
+        <v>0</v>
+      </c>
+      <c r="AR10">
+        <v>0</v>
+      </c>
+      <c r="AS10">
+        <v>0</v>
+      </c>
+      <c r="AT10">
+        <v>0</v>
+      </c>
+      <c r="AU10">
+        <v>7</v>
+      </c>
+      <c r="AV10">
+        <v>2</v>
+      </c>
+      <c r="AW10">
+        <v>7</v>
+      </c>
+      <c r="AX10">
+        <v>11</v>
+      </c>
+      <c r="AY10">
+        <v>14</v>
+      </c>
+      <c r="AZ10">
+        <v>13</v>
+      </c>
+      <c r="BA10">
+        <v>6</v>
+      </c>
+      <c r="BB10">
+        <v>5</v>
+      </c>
+      <c r="BC10">
+        <v>11</v>
+      </c>
+      <c r="BD10">
+        <v>0</v>
+      </c>
+      <c r="BE10">
+        <v>0</v>
+      </c>
+      <c r="BF10">
+        <v>0</v>
+      </c>
+      <c r="BG10">
+        <v>0</v>
+      </c>
+      <c r="BH10">
+        <v>0</v>
+      </c>
+      <c r="BI10">
+        <v>0</v>
+      </c>
+      <c r="BJ10">
+        <v>0</v>
+      </c>
+      <c r="BK10">
+        <v>0</v>
+      </c>
+      <c r="BL10">
+        <v>0</v>
+      </c>
+      <c r="BM10">
+        <v>0</v>
+      </c>
+      <c r="BN10">
+        <v>0</v>
+      </c>
+      <c r="BO10">
+        <v>0</v>
+      </c>
+      <c r="BP10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:68">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>7828467</v>
+      </c>
+      <c r="C11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D11" t="s">
+        <v>69</v>
+      </c>
+      <c r="E11" s="2">
+        <v>45725.39583333334</v>
+      </c>
+      <c r="F11">
+        <v>2</v>
+      </c>
+      <c r="G11" t="s">
+        <v>78</v>
+      </c>
+      <c r="H11" t="s">
+        <v>79</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>3</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>3</v>
+      </c>
+      <c r="O11" t="s">
+        <v>87</v>
+      </c>
+      <c r="P11" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q11">
+        <v>2.75</v>
+      </c>
+      <c r="R11">
+        <v>2.38</v>
+      </c>
+      <c r="S11">
+        <v>3</v>
+      </c>
+      <c r="T11">
+        <v>1.24</v>
+      </c>
+      <c r="U11">
+        <v>3.48</v>
+      </c>
+      <c r="V11">
+        <v>2.25</v>
+      </c>
+      <c r="W11">
+        <v>1.6</v>
+      </c>
+      <c r="X11">
+        <v>4.9</v>
+      </c>
+      <c r="Y11">
+        <v>1.12</v>
+      </c>
+      <c r="Z11">
+        <v>2.34</v>
+      </c>
+      <c r="AA11">
+        <v>4</v>
+      </c>
+      <c r="AB11">
+        <v>2.55</v>
+      </c>
+      <c r="AC11">
+        <v>1.01</v>
+      </c>
+      <c r="AD11">
+        <v>13</v>
+      </c>
+      <c r="AE11">
+        <v>1.11</v>
+      </c>
+      <c r="AF11">
+        <v>5.5</v>
+      </c>
+      <c r="AG11">
+        <v>1.6</v>
+      </c>
+      <c r="AH11">
+        <v>2.15</v>
+      </c>
+      <c r="AI11">
+        <v>1.4</v>
+      </c>
+      <c r="AJ11">
+        <v>2.75</v>
+      </c>
+      <c r="AK11">
+        <v>1.44</v>
+      </c>
+      <c r="AL11">
+        <v>1.23</v>
+      </c>
+      <c r="AM11">
+        <v>1.51</v>
+      </c>
+      <c r="AN11">
+        <v>0</v>
+      </c>
+      <c r="AO11">
+        <v>3</v>
+      </c>
+      <c r="AP11">
+        <v>3</v>
+      </c>
+      <c r="AQ11">
+        <v>1.5</v>
+      </c>
+      <c r="AR11">
+        <v>0</v>
+      </c>
+      <c r="AS11">
+        <v>3.22</v>
+      </c>
+      <c r="AT11">
+        <v>3.22</v>
+      </c>
+      <c r="AU11">
+        <v>13</v>
+      </c>
+      <c r="AV11">
+        <v>5</v>
+      </c>
+      <c r="AW11">
+        <v>5</v>
+      </c>
+      <c r="AX11">
+        <v>10</v>
+      </c>
+      <c r="AY11">
+        <v>18</v>
+      </c>
+      <c r="AZ11">
+        <v>15</v>
+      </c>
+      <c r="BA11">
+        <v>7</v>
+      </c>
+      <c r="BB11">
+        <v>1</v>
+      </c>
+      <c r="BC11">
+        <v>8</v>
+      </c>
+      <c r="BD11">
+        <v>0</v>
+      </c>
+      <c r="BE11">
+        <v>0</v>
+      </c>
+      <c r="BF11">
+        <v>0</v>
+      </c>
+      <c r="BG11">
+        <v>0</v>
+      </c>
+      <c r="BH11">
+        <v>0</v>
+      </c>
+      <c r="BI11">
+        <v>0</v>
+      </c>
+      <c r="BJ11">
+        <v>0</v>
+      </c>
+      <c r="BK11">
+        <v>0</v>
+      </c>
+      <c r="BL11">
+        <v>0</v>
+      </c>
+      <c r="BM11">
+        <v>0</v>
+      </c>
+      <c r="BN11">
+        <v>0</v>
+      </c>
+      <c r="BO11">
+        <v>0</v>
+      </c>
+      <c r="BP11">
         <v>0</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="99">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -280,6 +280,12 @@
     <t>['49', '55', '76']</t>
   </si>
   <si>
+    <t>['10']</t>
+  </si>
+  <si>
+    <t>['40']</t>
+  </si>
+  <si>
     <t>['34', '59', '86']</t>
   </si>
   <si>
@@ -299,6 +305,12 @@
   </si>
   <si>
     <t>['8', '90+6']</t>
+  </si>
+  <si>
+    <t>['67', '90+1']</t>
+  </si>
+  <si>
+    <t>['25', '45+1', '47', '78']</t>
   </si>
 </sst>
 </file>
@@ -660,7 +672,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP11"/>
+  <dimension ref="A1:BP14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1122,7 +1134,7 @@
         <v>81</v>
       </c>
       <c r="P3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -1328,7 +1340,7 @@
         <v>82</v>
       </c>
       <c r="P4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -1534,7 +1546,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="Q5">
         <v>7</v>
@@ -1615,7 +1627,7 @@
         <v>0</v>
       </c>
       <c r="AQ5">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -1740,7 +1752,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -1946,7 +1958,7 @@
         <v>81</v>
       </c>
       <c r="P7" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="Q7">
         <v>1.83</v>
@@ -2152,7 +2164,7 @@
         <v>85</v>
       </c>
       <c r="P8" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="Q8">
         <v>8.5</v>
@@ -2358,7 +2370,7 @@
         <v>81</v>
       </c>
       <c r="P9" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -2436,7 +2448,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ9">
         <v>3</v>
@@ -2926,6 +2938,624 @@
         <v>0</v>
       </c>
       <c r="BP11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:68">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>7828468</v>
+      </c>
+      <c r="C12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E12" s="2">
+        <v>45731.3125</v>
+      </c>
+      <c r="F12">
+        <v>3</v>
+      </c>
+      <c r="G12" t="s">
+        <v>71</v>
+      </c>
+      <c r="H12" t="s">
+        <v>70</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+      <c r="M12">
+        <v>2</v>
+      </c>
+      <c r="N12">
+        <v>3</v>
+      </c>
+      <c r="O12" t="s">
+        <v>88</v>
+      </c>
+      <c r="P12" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q12">
+        <v>8</v>
+      </c>
+      <c r="R12">
+        <v>2.63</v>
+      </c>
+      <c r="S12">
+        <v>1.67</v>
+      </c>
+      <c r="T12">
+        <v>1.23</v>
+      </c>
+      <c r="U12">
+        <v>3.56</v>
+      </c>
+      <c r="V12">
+        <v>2.31</v>
+      </c>
+      <c r="W12">
+        <v>1.57</v>
+      </c>
+      <c r="X12">
+        <v>5.4</v>
+      </c>
+      <c r="Y12">
+        <v>1.1</v>
+      </c>
+      <c r="Z12">
+        <v>12</v>
+      </c>
+      <c r="AA12">
+        <v>7</v>
+      </c>
+      <c r="AB12">
+        <v>1.18</v>
+      </c>
+      <c r="AC12">
+        <v>1</v>
+      </c>
+      <c r="AD12">
+        <v>12</v>
+      </c>
+      <c r="AE12">
+        <v>1.11</v>
+      </c>
+      <c r="AF12">
+        <v>4.95</v>
+      </c>
+      <c r="AG12">
+        <v>1.53</v>
+      </c>
+      <c r="AH12">
+        <v>2.34</v>
+      </c>
+      <c r="AI12">
+        <v>2.19</v>
+      </c>
+      <c r="AJ12">
+        <v>1.57</v>
+      </c>
+      <c r="AK12">
+        <v>4.6</v>
+      </c>
+      <c r="AL12">
+        <v>1.07</v>
+      </c>
+      <c r="AM12">
+        <v>1.01</v>
+      </c>
+      <c r="AN12">
+        <v>0</v>
+      </c>
+      <c r="AO12">
+        <v>3</v>
+      </c>
+      <c r="AP12">
+        <v>0</v>
+      </c>
+      <c r="AQ12">
+        <v>3</v>
+      </c>
+      <c r="AR12">
+        <v>0.79</v>
+      </c>
+      <c r="AS12">
+        <v>2.51</v>
+      </c>
+      <c r="AT12">
+        <v>3.3</v>
+      </c>
+      <c r="AU12">
+        <v>3</v>
+      </c>
+      <c r="AV12">
+        <v>11</v>
+      </c>
+      <c r="AW12">
+        <v>2</v>
+      </c>
+      <c r="AX12">
+        <v>8</v>
+      </c>
+      <c r="AY12">
+        <v>5</v>
+      </c>
+      <c r="AZ12">
+        <v>19</v>
+      </c>
+      <c r="BA12">
+        <v>3</v>
+      </c>
+      <c r="BB12">
+        <v>9</v>
+      </c>
+      <c r="BC12">
+        <v>12</v>
+      </c>
+      <c r="BD12">
+        <v>0</v>
+      </c>
+      <c r="BE12">
+        <v>0</v>
+      </c>
+      <c r="BF12">
+        <v>0</v>
+      </c>
+      <c r="BG12">
+        <v>0</v>
+      </c>
+      <c r="BH12">
+        <v>0</v>
+      </c>
+      <c r="BI12">
+        <v>0</v>
+      </c>
+      <c r="BJ12">
+        <v>0</v>
+      </c>
+      <c r="BK12">
+        <v>0</v>
+      </c>
+      <c r="BL12">
+        <v>0</v>
+      </c>
+      <c r="BM12">
+        <v>0</v>
+      </c>
+      <c r="BN12">
+        <v>0</v>
+      </c>
+      <c r="BO12">
+        <v>0</v>
+      </c>
+      <c r="BP12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:68">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>7828470</v>
+      </c>
+      <c r="C13" t="s">
+        <v>68</v>
+      </c>
+      <c r="D13" t="s">
+        <v>69</v>
+      </c>
+      <c r="E13" s="2">
+        <v>45731.39583333334</v>
+      </c>
+      <c r="F13">
+        <v>3</v>
+      </c>
+      <c r="G13" t="s">
+        <v>74</v>
+      </c>
+      <c r="H13" t="s">
+        <v>72</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>2</v>
+      </c>
+      <c r="K13">
+        <v>2</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>4</v>
+      </c>
+      <c r="N13">
+        <v>4</v>
+      </c>
+      <c r="O13" t="s">
+        <v>81</v>
+      </c>
+      <c r="P13" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q13">
+        <v>5.5</v>
+      </c>
+      <c r="R13">
+        <v>2.5</v>
+      </c>
+      <c r="S13">
+        <v>1.83</v>
+      </c>
+      <c r="T13">
+        <v>1.24</v>
+      </c>
+      <c r="U13">
+        <v>3.48</v>
+      </c>
+      <c r="V13">
+        <v>2.23</v>
+      </c>
+      <c r="W13">
+        <v>1.61</v>
+      </c>
+      <c r="X13">
+        <v>4.75</v>
+      </c>
+      <c r="Y13">
+        <v>1.13</v>
+      </c>
+      <c r="Z13">
+        <v>9.5</v>
+      </c>
+      <c r="AA13">
+        <v>6</v>
+      </c>
+      <c r="AB13">
+        <v>1.25</v>
+      </c>
+      <c r="AC13">
+        <v>1.01</v>
+      </c>
+      <c r="AD13">
+        <v>17</v>
+      </c>
+      <c r="AE13">
+        <v>1.12</v>
+      </c>
+      <c r="AF13">
+        <v>4.7</v>
+      </c>
+      <c r="AG13">
+        <v>1.48</v>
+      </c>
+      <c r="AH13">
+        <v>2.47</v>
+      </c>
+      <c r="AI13">
+        <v>1.8</v>
+      </c>
+      <c r="AJ13">
+        <v>1.86</v>
+      </c>
+      <c r="AK13">
+        <v>3.14</v>
+      </c>
+      <c r="AL13">
+        <v>1.12</v>
+      </c>
+      <c r="AM13">
+        <v>1.04</v>
+      </c>
+      <c r="AN13">
+        <v>0</v>
+      </c>
+      <c r="AO13">
+        <v>0</v>
+      </c>
+      <c r="AP13">
+        <v>0</v>
+      </c>
+      <c r="AQ13">
+        <v>3</v>
+      </c>
+      <c r="AR13">
+        <v>1.42</v>
+      </c>
+      <c r="AS13">
+        <v>0</v>
+      </c>
+      <c r="AT13">
+        <v>1.42</v>
+      </c>
+      <c r="AU13">
+        <v>3</v>
+      </c>
+      <c r="AV13">
+        <v>12</v>
+      </c>
+      <c r="AW13">
+        <v>1</v>
+      </c>
+      <c r="AX13">
+        <v>9</v>
+      </c>
+      <c r="AY13">
+        <v>4</v>
+      </c>
+      <c r="AZ13">
+        <v>21</v>
+      </c>
+      <c r="BA13">
+        <v>8</v>
+      </c>
+      <c r="BB13">
+        <v>9</v>
+      </c>
+      <c r="BC13">
+        <v>17</v>
+      </c>
+      <c r="BD13">
+        <v>0</v>
+      </c>
+      <c r="BE13">
+        <v>0</v>
+      </c>
+      <c r="BF13">
+        <v>0</v>
+      </c>
+      <c r="BG13">
+        <v>0</v>
+      </c>
+      <c r="BH13">
+        <v>0</v>
+      </c>
+      <c r="BI13">
+        <v>0</v>
+      </c>
+      <c r="BJ13">
+        <v>0</v>
+      </c>
+      <c r="BK13">
+        <v>0</v>
+      </c>
+      <c r="BL13">
+        <v>0</v>
+      </c>
+      <c r="BM13">
+        <v>0</v>
+      </c>
+      <c r="BN13">
+        <v>0</v>
+      </c>
+      <c r="BO13">
+        <v>0</v>
+      </c>
+      <c r="BP13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:68">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>7828469</v>
+      </c>
+      <c r="C14" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" t="s">
+        <v>69</v>
+      </c>
+      <c r="E14" s="2">
+        <v>45731.39583333334</v>
+      </c>
+      <c r="F14">
+        <v>3</v>
+      </c>
+      <c r="G14" t="s">
+        <v>76</v>
+      </c>
+      <c r="H14" t="s">
+        <v>78</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>1</v>
+      </c>
+      <c r="O14" t="s">
+        <v>89</v>
+      </c>
+      <c r="P14" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q14">
+        <v>4.33</v>
+      </c>
+      <c r="R14">
+        <v>2.4</v>
+      </c>
+      <c r="S14">
+        <v>2.2</v>
+      </c>
+      <c r="T14">
+        <v>1.3</v>
+      </c>
+      <c r="U14">
+        <v>3.2</v>
+      </c>
+      <c r="V14">
+        <v>2.34</v>
+      </c>
+      <c r="W14">
+        <v>1.53</v>
+      </c>
+      <c r="X14">
+        <v>5.1</v>
+      </c>
+      <c r="Y14">
+        <v>1.1</v>
+      </c>
+      <c r="Z14">
+        <v>3.96</v>
+      </c>
+      <c r="AA14">
+        <v>3.93</v>
+      </c>
+      <c r="AB14">
+        <v>1.78</v>
+      </c>
+      <c r="AC14">
+        <v>1</v>
+      </c>
+      <c r="AD14">
+        <v>12</v>
+      </c>
+      <c r="AE14">
+        <v>1.15</v>
+      </c>
+      <c r="AF14">
+        <v>4.2</v>
+      </c>
+      <c r="AG14">
+        <v>1.55</v>
+      </c>
+      <c r="AH14">
+        <v>2.28</v>
+      </c>
+      <c r="AI14">
+        <v>1.61</v>
+      </c>
+      <c r="AJ14">
+        <v>2.12</v>
+      </c>
+      <c r="AK14">
+        <v>2.14</v>
+      </c>
+      <c r="AL14">
+        <v>1.21</v>
+      </c>
+      <c r="AM14">
+        <v>1.14</v>
+      </c>
+      <c r="AN14">
+        <v>0</v>
+      </c>
+      <c r="AO14">
+        <v>3</v>
+      </c>
+      <c r="AP14">
+        <v>1.5</v>
+      </c>
+      <c r="AQ14">
+        <v>1.5</v>
+      </c>
+      <c r="AR14">
+        <v>1.59</v>
+      </c>
+      <c r="AS14">
+        <v>2.21</v>
+      </c>
+      <c r="AT14">
+        <v>3.8</v>
+      </c>
+      <c r="AU14">
+        <v>4</v>
+      </c>
+      <c r="AV14">
+        <v>3</v>
+      </c>
+      <c r="AW14">
+        <v>3</v>
+      </c>
+      <c r="AX14">
+        <v>8</v>
+      </c>
+      <c r="AY14">
+        <v>7</v>
+      </c>
+      <c r="AZ14">
+        <v>11</v>
+      </c>
+      <c r="BA14">
+        <v>3</v>
+      </c>
+      <c r="BB14">
+        <v>3</v>
+      </c>
+      <c r="BC14">
+        <v>6</v>
+      </c>
+      <c r="BD14">
+        <v>0</v>
+      </c>
+      <c r="BE14">
+        <v>0</v>
+      </c>
+      <c r="BF14">
+        <v>0</v>
+      </c>
+      <c r="BG14">
+        <v>0</v>
+      </c>
+      <c r="BH14">
+        <v>0</v>
+      </c>
+      <c r="BI14">
+        <v>0</v>
+      </c>
+      <c r="BJ14">
+        <v>0</v>
+      </c>
+      <c r="BK14">
+        <v>0</v>
+      </c>
+      <c r="BL14">
+        <v>0</v>
+      </c>
+      <c r="BM14">
+        <v>0</v>
+      </c>
+      <c r="BN14">
+        <v>0</v>
+      </c>
+      <c r="BO14">
+        <v>0</v>
+      </c>
+      <c r="BP14">
         <v>0</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="103">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -286,6 +286,12 @@
     <t>['40']</t>
   </si>
   <si>
+    <t>['30']</t>
+  </si>
+  <si>
+    <t>['16', '75']</t>
+  </si>
+  <si>
     <t>['34', '59', '86']</t>
   </si>
   <si>
@@ -311,6 +317,12 @@
   </si>
   <si>
     <t>['25', '45+1', '47', '78']</t>
+  </si>
+  <si>
+    <t>['6', '90+1']</t>
+  </si>
+  <si>
+    <t>['42', '46']</t>
   </si>
 </sst>
 </file>
@@ -672,7 +684,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP14"/>
+  <dimension ref="A1:BP16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1009,7 +1021,7 @@
         <v>3</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1134,7 +1146,7 @@
         <v>81</v>
       </c>
       <c r="P3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -1340,7 +1352,7 @@
         <v>82</v>
       </c>
       <c r="P4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -1546,7 +1558,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="Q5">
         <v>7</v>
@@ -1752,7 +1764,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -1833,7 +1845,7 @@
         <v>0</v>
       </c>
       <c r="AQ6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -1958,7 +1970,7 @@
         <v>81</v>
       </c>
       <c r="P7" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="Q7">
         <v>1.83</v>
@@ -2164,7 +2176,7 @@
         <v>85</v>
       </c>
       <c r="P8" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="Q8">
         <v>8.5</v>
@@ -2370,7 +2382,7 @@
         <v>81</v>
       </c>
       <c r="P9" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -2988,7 +3000,7 @@
         <v>88</v>
       </c>
       <c r="P12" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="Q12">
         <v>8</v>
@@ -3194,7 +3206,7 @@
         <v>81</v>
       </c>
       <c r="P13" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="Q13">
         <v>5.5</v>
@@ -3556,6 +3568,418 @@
         <v>0</v>
       </c>
       <c r="BP14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:68">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>7828471</v>
+      </c>
+      <c r="C15" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" s="2">
+        <v>45732.3125</v>
+      </c>
+      <c r="F15">
+        <v>3</v>
+      </c>
+      <c r="G15" t="s">
+        <v>73</v>
+      </c>
+      <c r="H15" t="s">
+        <v>77</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="K15">
+        <v>2</v>
+      </c>
+      <c r="L15">
+        <v>1</v>
+      </c>
+      <c r="M15">
+        <v>2</v>
+      </c>
+      <c r="N15">
+        <v>3</v>
+      </c>
+      <c r="O15" t="s">
+        <v>90</v>
+      </c>
+      <c r="P15" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q15">
+        <v>2.5</v>
+      </c>
+      <c r="R15">
+        <v>2.38</v>
+      </c>
+      <c r="S15">
+        <v>3.5</v>
+      </c>
+      <c r="T15">
+        <v>1.28</v>
+      </c>
+      <c r="U15">
+        <v>3.34</v>
+      </c>
+      <c r="V15">
+        <v>2.46</v>
+      </c>
+      <c r="W15">
+        <v>1.48</v>
+      </c>
+      <c r="X15">
+        <v>6.05</v>
+      </c>
+      <c r="Y15">
+        <v>1.06</v>
+      </c>
+      <c r="Z15">
+        <v>1.73</v>
+      </c>
+      <c r="AA15">
+        <v>4</v>
+      </c>
+      <c r="AB15">
+        <v>4.1</v>
+      </c>
+      <c r="AC15">
+        <v>1.01</v>
+      </c>
+      <c r="AD15">
+        <v>11</v>
+      </c>
+      <c r="AE15">
+        <v>1.15</v>
+      </c>
+      <c r="AF15">
+        <v>4.3</v>
+      </c>
+      <c r="AG15">
+        <v>1.66</v>
+      </c>
+      <c r="AH15">
+        <v>2.09</v>
+      </c>
+      <c r="AI15">
+        <v>1.53</v>
+      </c>
+      <c r="AJ15">
+        <v>2.28</v>
+      </c>
+      <c r="AK15">
+        <v>1.34</v>
+      </c>
+      <c r="AL15">
+        <v>1.24</v>
+      </c>
+      <c r="AM15">
+        <v>1.62</v>
+      </c>
+      <c r="AN15">
+        <v>0</v>
+      </c>
+      <c r="AO15">
+        <v>0</v>
+      </c>
+      <c r="AP15">
+        <v>0</v>
+      </c>
+      <c r="AQ15">
+        <v>1.5</v>
+      </c>
+      <c r="AR15">
+        <v>1.37</v>
+      </c>
+      <c r="AS15">
+        <v>0.74</v>
+      </c>
+      <c r="AT15">
+        <v>2.11</v>
+      </c>
+      <c r="AU15">
+        <v>4</v>
+      </c>
+      <c r="AV15">
+        <v>7</v>
+      </c>
+      <c r="AW15">
+        <v>10</v>
+      </c>
+      <c r="AX15">
+        <v>7</v>
+      </c>
+      <c r="AY15">
+        <v>14</v>
+      </c>
+      <c r="AZ15">
+        <v>14</v>
+      </c>
+      <c r="BA15">
+        <v>4</v>
+      </c>
+      <c r="BB15">
+        <v>5</v>
+      </c>
+      <c r="BC15">
+        <v>9</v>
+      </c>
+      <c r="BD15">
+        <v>0</v>
+      </c>
+      <c r="BE15">
+        <v>0</v>
+      </c>
+      <c r="BF15">
+        <v>0</v>
+      </c>
+      <c r="BG15">
+        <v>0</v>
+      </c>
+      <c r="BH15">
+        <v>0</v>
+      </c>
+      <c r="BI15">
+        <v>0</v>
+      </c>
+      <c r="BJ15">
+        <v>0</v>
+      </c>
+      <c r="BK15">
+        <v>0</v>
+      </c>
+      <c r="BL15">
+        <v>0</v>
+      </c>
+      <c r="BM15">
+        <v>0</v>
+      </c>
+      <c r="BN15">
+        <v>0</v>
+      </c>
+      <c r="BO15">
+        <v>0</v>
+      </c>
+      <c r="BP15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:68">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>7828472</v>
+      </c>
+      <c r="C16" t="s">
+        <v>68</v>
+      </c>
+      <c r="D16" t="s">
+        <v>69</v>
+      </c>
+      <c r="E16" s="2">
+        <v>45732.39583333334</v>
+      </c>
+      <c r="F16">
+        <v>3</v>
+      </c>
+      <c r="G16" t="s">
+        <v>79</v>
+      </c>
+      <c r="H16" t="s">
+        <v>75</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+      <c r="K16">
+        <v>2</v>
+      </c>
+      <c r="L16">
+        <v>2</v>
+      </c>
+      <c r="M16">
+        <v>2</v>
+      </c>
+      <c r="N16">
+        <v>4</v>
+      </c>
+      <c r="O16" t="s">
+        <v>91</v>
+      </c>
+      <c r="P16" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q16">
+        <v>2.1</v>
+      </c>
+      <c r="R16">
+        <v>2.5</v>
+      </c>
+      <c r="S16">
+        <v>4.33</v>
+      </c>
+      <c r="T16">
+        <v>1.22</v>
+      </c>
+      <c r="U16">
+        <v>3.64</v>
+      </c>
+      <c r="V16">
+        <v>2.19</v>
+      </c>
+      <c r="W16">
+        <v>1.63</v>
+      </c>
+      <c r="X16">
+        <v>4.75</v>
+      </c>
+      <c r="Y16">
+        <v>1.13</v>
+      </c>
+      <c r="Z16">
+        <v>1.54</v>
+      </c>
+      <c r="AA16">
+        <v>4.4</v>
+      </c>
+      <c r="AB16">
+        <v>5.1</v>
+      </c>
+      <c r="AC16">
+        <v>1.01</v>
+      </c>
+      <c r="AD16">
+        <v>15</v>
+      </c>
+      <c r="AE16">
+        <v>1.1</v>
+      </c>
+      <c r="AF16">
+        <v>5</v>
+      </c>
+      <c r="AG16">
+        <v>1.48</v>
+      </c>
+      <c r="AH16">
+        <v>2.47</v>
+      </c>
+      <c r="AI16">
+        <v>1.52</v>
+      </c>
+      <c r="AJ16">
+        <v>2.3</v>
+      </c>
+      <c r="AK16">
+        <v>1.14</v>
+      </c>
+      <c r="AL16">
+        <v>1.17</v>
+      </c>
+      <c r="AM16">
+        <v>2.24</v>
+      </c>
+      <c r="AN16">
+        <v>0</v>
+      </c>
+      <c r="AO16">
+        <v>3</v>
+      </c>
+      <c r="AP16">
+        <v>1</v>
+      </c>
+      <c r="AQ16">
+        <v>2</v>
+      </c>
+      <c r="AR16">
+        <v>0</v>
+      </c>
+      <c r="AS16">
+        <v>2.84</v>
+      </c>
+      <c r="AT16">
+        <v>2.84</v>
+      </c>
+      <c r="AU16">
+        <v>12</v>
+      </c>
+      <c r="AV16">
+        <v>5</v>
+      </c>
+      <c r="AW16">
+        <v>21</v>
+      </c>
+      <c r="AX16">
+        <v>9</v>
+      </c>
+      <c r="AY16">
+        <v>33</v>
+      </c>
+      <c r="AZ16">
+        <v>14</v>
+      </c>
+      <c r="BA16">
+        <v>9</v>
+      </c>
+      <c r="BB16">
+        <v>3</v>
+      </c>
+      <c r="BC16">
+        <v>12</v>
+      </c>
+      <c r="BD16">
+        <v>0</v>
+      </c>
+      <c r="BE16">
+        <v>0</v>
+      </c>
+      <c r="BF16">
+        <v>0</v>
+      </c>
+      <c r="BG16">
+        <v>0</v>
+      </c>
+      <c r="BH16">
+        <v>0</v>
+      </c>
+      <c r="BI16">
+        <v>0</v>
+      </c>
+      <c r="BJ16">
+        <v>0</v>
+      </c>
+      <c r="BK16">
+        <v>0</v>
+      </c>
+      <c r="BL16">
+        <v>0</v>
+      </c>
+      <c r="BM16">
+        <v>0</v>
+      </c>
+      <c r="BN16">
+        <v>0</v>
+      </c>
+      <c r="BO16">
+        <v>0</v>
+      </c>
+      <c r="BP16">
         <v>0</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
@@ -3164,7 +3164,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>7828470</v>
+        <v>7828469</v>
       </c>
       <c r="C13" t="s">
         <v>68</v>
@@ -3179,151 +3179,151 @@
         <v>3</v>
       </c>
       <c r="G13" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H13" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>1</v>
+      </c>
+      <c r="O13" t="s">
+        <v>89</v>
+      </c>
+      <c r="P13" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q13">
+        <v>4.33</v>
+      </c>
+      <c r="R13">
+        <v>2.4</v>
+      </c>
+      <c r="S13">
+        <v>2.2</v>
+      </c>
+      <c r="T13">
+        <v>1.3</v>
+      </c>
+      <c r="U13">
+        <v>3.2</v>
+      </c>
+      <c r="V13">
+        <v>2.34</v>
+      </c>
+      <c r="W13">
+        <v>1.53</v>
+      </c>
+      <c r="X13">
+        <v>5.1</v>
+      </c>
+      <c r="Y13">
+        <v>1.1</v>
+      </c>
+      <c r="Z13">
+        <v>3.96</v>
+      </c>
+      <c r="AA13">
+        <v>3.93</v>
+      </c>
+      <c r="AB13">
+        <v>1.78</v>
+      </c>
+      <c r="AC13">
+        <v>1</v>
+      </c>
+      <c r="AD13">
+        <v>12</v>
+      </c>
+      <c r="AE13">
+        <v>1.15</v>
+      </c>
+      <c r="AF13">
+        <v>4.2</v>
+      </c>
+      <c r="AG13">
+        <v>1.55</v>
+      </c>
+      <c r="AH13">
+        <v>2.28</v>
+      </c>
+      <c r="AI13">
+        <v>1.61</v>
+      </c>
+      <c r="AJ13">
+        <v>2.12</v>
+      </c>
+      <c r="AK13">
+        <v>2.14</v>
+      </c>
+      <c r="AL13">
+        <v>1.21</v>
+      </c>
+      <c r="AM13">
+        <v>1.14</v>
+      </c>
+      <c r="AN13">
+        <v>0</v>
+      </c>
+      <c r="AO13">
+        <v>3</v>
+      </c>
+      <c r="AP13">
+        <v>1.5</v>
+      </c>
+      <c r="AQ13">
+        <v>1.5</v>
+      </c>
+      <c r="AR13">
+        <v>1.59</v>
+      </c>
+      <c r="AS13">
+        <v>2.21</v>
+      </c>
+      <c r="AT13">
+        <v>3.8</v>
+      </c>
+      <c r="AU13">
         <v>4</v>
       </c>
-      <c r="N13">
-        <v>4</v>
-      </c>
-      <c r="O13" t="s">
-        <v>81</v>
-      </c>
-      <c r="P13" t="s">
-        <v>100</v>
-      </c>
-      <c r="Q13">
-        <v>5.5</v>
-      </c>
-      <c r="R13">
-        <v>2.5</v>
-      </c>
-      <c r="S13">
-        <v>1.83</v>
-      </c>
-      <c r="T13">
-        <v>1.24</v>
-      </c>
-      <c r="U13">
-        <v>3.48</v>
-      </c>
-      <c r="V13">
-        <v>2.23</v>
-      </c>
-      <c r="W13">
-        <v>1.61</v>
-      </c>
-      <c r="X13">
-        <v>4.75</v>
-      </c>
-      <c r="Y13">
-        <v>1.13</v>
-      </c>
-      <c r="Z13">
-        <v>9.5</v>
-      </c>
-      <c r="AA13">
+      <c r="AV13">
+        <v>3</v>
+      </c>
+      <c r="AW13">
+        <v>3</v>
+      </c>
+      <c r="AX13">
+        <v>8</v>
+      </c>
+      <c r="AY13">
+        <v>7</v>
+      </c>
+      <c r="AZ13">
+        <v>11</v>
+      </c>
+      <c r="BA13">
+        <v>3</v>
+      </c>
+      <c r="BB13">
+        <v>3</v>
+      </c>
+      <c r="BC13">
         <v>6</v>
-      </c>
-      <c r="AB13">
-        <v>1.25</v>
-      </c>
-      <c r="AC13">
-        <v>1.01</v>
-      </c>
-      <c r="AD13">
-        <v>17</v>
-      </c>
-      <c r="AE13">
-        <v>1.12</v>
-      </c>
-      <c r="AF13">
-        <v>4.7</v>
-      </c>
-      <c r="AG13">
-        <v>1.48</v>
-      </c>
-      <c r="AH13">
-        <v>2.47</v>
-      </c>
-      <c r="AI13">
-        <v>1.8</v>
-      </c>
-      <c r="AJ13">
-        <v>1.86</v>
-      </c>
-      <c r="AK13">
-        <v>3.14</v>
-      </c>
-      <c r="AL13">
-        <v>1.12</v>
-      </c>
-      <c r="AM13">
-        <v>1.04</v>
-      </c>
-      <c r="AN13">
-        <v>0</v>
-      </c>
-      <c r="AO13">
-        <v>0</v>
-      </c>
-      <c r="AP13">
-        <v>0</v>
-      </c>
-      <c r="AQ13">
-        <v>3</v>
-      </c>
-      <c r="AR13">
-        <v>1.42</v>
-      </c>
-      <c r="AS13">
-        <v>0</v>
-      </c>
-      <c r="AT13">
-        <v>1.42</v>
-      </c>
-      <c r="AU13">
-        <v>3</v>
-      </c>
-      <c r="AV13">
-        <v>12</v>
-      </c>
-      <c r="AW13">
-        <v>1</v>
-      </c>
-      <c r="AX13">
-        <v>9</v>
-      </c>
-      <c r="AY13">
-        <v>4</v>
-      </c>
-      <c r="AZ13">
-        <v>21</v>
-      </c>
-      <c r="BA13">
-        <v>8</v>
-      </c>
-      <c r="BB13">
-        <v>9</v>
-      </c>
-      <c r="BC13">
-        <v>17</v>
       </c>
       <c r="BD13">
         <v>0</v>
@@ -3370,7 +3370,7 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>7828469</v>
+        <v>7828470</v>
       </c>
       <c r="C14" t="s">
         <v>68</v>
@@ -3385,151 +3385,151 @@
         <v>3</v>
       </c>
       <c r="G14" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H14" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="I14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O14" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="P14" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="Q14">
-        <v>4.33</v>
+        <v>5.5</v>
       </c>
       <c r="R14">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S14">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="T14">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="U14">
-        <v>3.2</v>
+        <v>3.48</v>
       </c>
       <c r="V14">
-        <v>2.34</v>
+        <v>2.23</v>
       </c>
       <c r="W14">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="X14">
-        <v>5.1</v>
+        <v>4.75</v>
       </c>
       <c r="Y14">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z14">
-        <v>3.96</v>
+        <v>9.5</v>
       </c>
       <c r="AA14">
-        <v>3.93</v>
+        <v>6</v>
       </c>
       <c r="AB14">
-        <v>1.78</v>
+        <v>1.25</v>
       </c>
       <c r="AC14">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AD14">
+        <v>17</v>
+      </c>
+      <c r="AE14">
+        <v>1.12</v>
+      </c>
+      <c r="AF14">
+        <v>4.7</v>
+      </c>
+      <c r="AG14">
+        <v>1.48</v>
+      </c>
+      <c r="AH14">
+        <v>2.47</v>
+      </c>
+      <c r="AI14">
+        <v>1.8</v>
+      </c>
+      <c r="AJ14">
+        <v>1.86</v>
+      </c>
+      <c r="AK14">
+        <v>3.14</v>
+      </c>
+      <c r="AL14">
+        <v>1.12</v>
+      </c>
+      <c r="AM14">
+        <v>1.04</v>
+      </c>
+      <c r="AN14">
+        <v>0</v>
+      </c>
+      <c r="AO14">
+        <v>0</v>
+      </c>
+      <c r="AP14">
+        <v>0</v>
+      </c>
+      <c r="AQ14">
+        <v>3</v>
+      </c>
+      <c r="AR14">
+        <v>1.42</v>
+      </c>
+      <c r="AS14">
+        <v>0</v>
+      </c>
+      <c r="AT14">
+        <v>1.42</v>
+      </c>
+      <c r="AU14">
+        <v>3</v>
+      </c>
+      <c r="AV14">
         <v>12</v>
       </c>
-      <c r="AE14">
-        <v>1.15</v>
-      </c>
-      <c r="AF14">
-        <v>4.2</v>
-      </c>
-      <c r="AG14">
-        <v>1.55</v>
-      </c>
-      <c r="AH14">
-        <v>2.28</v>
-      </c>
-      <c r="AI14">
-        <v>1.61</v>
-      </c>
-      <c r="AJ14">
-        <v>2.12</v>
-      </c>
-      <c r="AK14">
-        <v>2.14</v>
-      </c>
-      <c r="AL14">
-        <v>1.21</v>
-      </c>
-      <c r="AM14">
-        <v>1.14</v>
-      </c>
-      <c r="AN14">
-        <v>0</v>
-      </c>
-      <c r="AO14">
-        <v>3</v>
-      </c>
-      <c r="AP14">
-        <v>1.5</v>
-      </c>
-      <c r="AQ14">
-        <v>1.5</v>
-      </c>
-      <c r="AR14">
-        <v>1.59</v>
-      </c>
-      <c r="AS14">
-        <v>2.21</v>
-      </c>
-      <c r="AT14">
-        <v>3.8</v>
-      </c>
-      <c r="AU14">
+      <c r="AW14">
+        <v>1</v>
+      </c>
+      <c r="AX14">
+        <v>9</v>
+      </c>
+      <c r="AY14">
         <v>4</v>
       </c>
-      <c r="AV14">
-        <v>3</v>
-      </c>
-      <c r="AW14">
-        <v>3</v>
-      </c>
-      <c r="AX14">
+      <c r="AZ14">
+        <v>21</v>
+      </c>
+      <c r="BA14">
         <v>8</v>
       </c>
-      <c r="AY14">
-        <v>7</v>
-      </c>
-      <c r="AZ14">
-        <v>11</v>
-      </c>
-      <c r="BA14">
-        <v>3</v>
-      </c>
       <c r="BB14">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="BC14">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="BD14">
         <v>0</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="106">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -292,6 +292,9 @@
     <t>['16', '75']</t>
   </si>
   <si>
+    <t>['2', '60', '64', '77', '90+2']</t>
+  </si>
+  <si>
     <t>['34', '59', '86']</t>
   </si>
   <si>
@@ -323,6 +326,12 @@
   </si>
   <si>
     <t>['42', '46']</t>
+  </si>
+  <si>
+    <t>['1', '34', '36', '47', '90']</t>
+  </si>
+  <si>
+    <t>['17', '37', '90']</t>
   </si>
 </sst>
 </file>
@@ -684,7 +693,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP16"/>
+  <dimension ref="A1:BP19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1146,7 +1155,7 @@
         <v>81</v>
       </c>
       <c r="P3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -1352,7 +1361,7 @@
         <v>82</v>
       </c>
       <c r="P4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -1430,10 +1439,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1558,7 +1567,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q5">
         <v>7</v>
@@ -1764,7 +1773,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -1970,7 +1979,7 @@
         <v>81</v>
       </c>
       <c r="P7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q7">
         <v>1.83</v>
@@ -2048,7 +2057,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ7">
         <v>3</v>
@@ -2176,7 +2185,7 @@
         <v>85</v>
       </c>
       <c r="P8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q8">
         <v>8.5</v>
@@ -2382,7 +2391,7 @@
         <v>81</v>
       </c>
       <c r="P9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -2463,7 +2472,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ9">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -2666,7 +2675,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AQ10">
         <v>0</v>
@@ -3000,7 +3009,7 @@
         <v>88</v>
       </c>
       <c r="P12" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q12">
         <v>8</v>
@@ -3412,7 +3421,7 @@
         <v>81</v>
       </c>
       <c r="P14" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q14">
         <v>5.5</v>
@@ -3618,7 +3627,7 @@
         <v>90</v>
       </c>
       <c r="P15" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q15">
         <v>2.5</v>
@@ -3824,7 +3833,7 @@
         <v>91</v>
       </c>
       <c r="P16" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Q16">
         <v>2.1</v>
@@ -3980,6 +3989,624 @@
         <v>0</v>
       </c>
       <c r="BP16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:68">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>7828473</v>
+      </c>
+      <c r="C17" t="s">
+        <v>68</v>
+      </c>
+      <c r="D17" t="s">
+        <v>69</v>
+      </c>
+      <c r="E17" s="2">
+        <v>45745.3125</v>
+      </c>
+      <c r="F17">
+        <v>4</v>
+      </c>
+      <c r="G17" t="s">
+        <v>75</v>
+      </c>
+      <c r="H17" t="s">
+        <v>71</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>3</v>
+      </c>
+      <c r="K17">
+        <v>3</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>5</v>
+      </c>
+      <c r="N17">
+        <v>5</v>
+      </c>
+      <c r="O17" t="s">
+        <v>81</v>
+      </c>
+      <c r="P17" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q17">
+        <v>2.38</v>
+      </c>
+      <c r="R17">
+        <v>2.25</v>
+      </c>
+      <c r="S17">
+        <v>4.33</v>
+      </c>
+      <c r="T17">
+        <v>1.33</v>
+      </c>
+      <c r="U17">
+        <v>3.04</v>
+      </c>
+      <c r="V17">
+        <v>2.62</v>
+      </c>
+      <c r="W17">
+        <v>1.43</v>
+      </c>
+      <c r="X17">
+        <v>6.5</v>
+      </c>
+      <c r="Y17">
+        <v>1.05</v>
+      </c>
+      <c r="Z17">
+        <v>1.81</v>
+      </c>
+      <c r="AA17">
+        <v>4.2</v>
+      </c>
+      <c r="AB17">
+        <v>3.58</v>
+      </c>
+      <c r="AC17">
+        <v>1.01</v>
+      </c>
+      <c r="AD17">
+        <v>11</v>
+      </c>
+      <c r="AE17">
+        <v>1.2</v>
+      </c>
+      <c r="AF17">
+        <v>3.7</v>
+      </c>
+      <c r="AG17">
+        <v>1.76</v>
+      </c>
+      <c r="AH17">
+        <v>1.94</v>
+      </c>
+      <c r="AI17">
+        <v>1.68</v>
+      </c>
+      <c r="AJ17">
+        <v>2.01</v>
+      </c>
+      <c r="AK17">
+        <v>1.2</v>
+      </c>
+      <c r="AL17">
+        <v>1.23</v>
+      </c>
+      <c r="AM17">
+        <v>1.9</v>
+      </c>
+      <c r="AN17">
+        <v>0</v>
+      </c>
+      <c r="AO17">
+        <v>3</v>
+      </c>
+      <c r="AP17">
+        <v>0</v>
+      </c>
+      <c r="AQ17">
+        <v>3</v>
+      </c>
+      <c r="AR17">
+        <v>1.11</v>
+      </c>
+      <c r="AS17">
+        <v>0.89</v>
+      </c>
+      <c r="AT17">
+        <v>2</v>
+      </c>
+      <c r="AU17">
+        <v>2</v>
+      </c>
+      <c r="AV17">
+        <v>10</v>
+      </c>
+      <c r="AW17">
+        <v>6</v>
+      </c>
+      <c r="AX17">
+        <v>11</v>
+      </c>
+      <c r="AY17">
+        <v>8</v>
+      </c>
+      <c r="AZ17">
+        <v>21</v>
+      </c>
+      <c r="BA17">
+        <v>4</v>
+      </c>
+      <c r="BB17">
+        <v>7</v>
+      </c>
+      <c r="BC17">
+        <v>11</v>
+      </c>
+      <c r="BD17">
+        <v>0</v>
+      </c>
+      <c r="BE17">
+        <v>0</v>
+      </c>
+      <c r="BF17">
+        <v>0</v>
+      </c>
+      <c r="BG17">
+        <v>0</v>
+      </c>
+      <c r="BH17">
+        <v>0</v>
+      </c>
+      <c r="BI17">
+        <v>0</v>
+      </c>
+      <c r="BJ17">
+        <v>0</v>
+      </c>
+      <c r="BK17">
+        <v>0</v>
+      </c>
+      <c r="BL17">
+        <v>0</v>
+      </c>
+      <c r="BM17">
+        <v>0</v>
+      </c>
+      <c r="BN17">
+        <v>0</v>
+      </c>
+      <c r="BO17">
+        <v>0</v>
+      </c>
+      <c r="BP17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:68">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>7828474</v>
+      </c>
+      <c r="C18" t="s">
+        <v>68</v>
+      </c>
+      <c r="D18" t="s">
+        <v>69</v>
+      </c>
+      <c r="E18" s="2">
+        <v>45745.39583333334</v>
+      </c>
+      <c r="F18">
+        <v>4</v>
+      </c>
+      <c r="G18" t="s">
+        <v>77</v>
+      </c>
+      <c r="H18" t="s">
+        <v>76</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>2</v>
+      </c>
+      <c r="K18">
+        <v>2</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>3</v>
+      </c>
+      <c r="N18">
+        <v>3</v>
+      </c>
+      <c r="O18" t="s">
+        <v>81</v>
+      </c>
+      <c r="P18" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q18">
+        <v>3.4</v>
+      </c>
+      <c r="R18">
+        <v>2.3</v>
+      </c>
+      <c r="S18">
+        <v>2.6</v>
+      </c>
+      <c r="T18">
+        <v>1.27</v>
+      </c>
+      <c r="U18">
+        <v>3.4</v>
+      </c>
+      <c r="V18">
+        <v>2.36</v>
+      </c>
+      <c r="W18">
+        <v>1.52</v>
+      </c>
+      <c r="X18">
+        <v>5.5</v>
+      </c>
+      <c r="Y18">
+        <v>1.08</v>
+      </c>
+      <c r="Z18">
+        <v>2.43</v>
+      </c>
+      <c r="AA18">
+        <v>3.76</v>
+      </c>
+      <c r="AB18">
+        <v>2.54</v>
+      </c>
+      <c r="AC18">
+        <v>1.01</v>
+      </c>
+      <c r="AD18">
+        <v>13</v>
+      </c>
+      <c r="AE18">
+        <v>1.14</v>
+      </c>
+      <c r="AF18">
+        <v>4.4</v>
+      </c>
+      <c r="AG18">
+        <v>1.57</v>
+      </c>
+      <c r="AH18">
+        <v>2.15</v>
+      </c>
+      <c r="AI18">
+        <v>1.5</v>
+      </c>
+      <c r="AJ18">
+        <v>2.34</v>
+      </c>
+      <c r="AK18">
+        <v>1.64</v>
+      </c>
+      <c r="AL18">
+        <v>1.24</v>
+      </c>
+      <c r="AM18">
+        <v>1.33</v>
+      </c>
+      <c r="AN18">
+        <v>3</v>
+      </c>
+      <c r="AO18">
+        <v>1</v>
+      </c>
+      <c r="AP18">
+        <v>1.5</v>
+      </c>
+      <c r="AQ18">
+        <v>2</v>
+      </c>
+      <c r="AR18">
+        <v>1.67</v>
+      </c>
+      <c r="AS18">
+        <v>1.68</v>
+      </c>
+      <c r="AT18">
+        <v>3.35</v>
+      </c>
+      <c r="AU18">
+        <v>4</v>
+      </c>
+      <c r="AV18">
+        <v>11</v>
+      </c>
+      <c r="AW18">
+        <v>1</v>
+      </c>
+      <c r="AX18">
+        <v>6</v>
+      </c>
+      <c r="AY18">
+        <v>5</v>
+      </c>
+      <c r="AZ18">
+        <v>17</v>
+      </c>
+      <c r="BA18">
+        <v>1</v>
+      </c>
+      <c r="BB18">
+        <v>7</v>
+      </c>
+      <c r="BC18">
+        <v>8</v>
+      </c>
+      <c r="BD18">
+        <v>0</v>
+      </c>
+      <c r="BE18">
+        <v>0</v>
+      </c>
+      <c r="BF18">
+        <v>0</v>
+      </c>
+      <c r="BG18">
+        <v>0</v>
+      </c>
+      <c r="BH18">
+        <v>0</v>
+      </c>
+      <c r="BI18">
+        <v>0</v>
+      </c>
+      <c r="BJ18">
+        <v>0</v>
+      </c>
+      <c r="BK18">
+        <v>0</v>
+      </c>
+      <c r="BL18">
+        <v>0</v>
+      </c>
+      <c r="BM18">
+        <v>0</v>
+      </c>
+      <c r="BN18">
+        <v>0</v>
+      </c>
+      <c r="BO18">
+        <v>0</v>
+      </c>
+      <c r="BP18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:68">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>7828475</v>
+      </c>
+      <c r="C19" t="s">
+        <v>68</v>
+      </c>
+      <c r="D19" t="s">
+        <v>69</v>
+      </c>
+      <c r="E19" s="2">
+        <v>45745.5</v>
+      </c>
+      <c r="F19">
+        <v>4</v>
+      </c>
+      <c r="G19" t="s">
+        <v>72</v>
+      </c>
+      <c r="H19" t="s">
+        <v>73</v>
+      </c>
+      <c r="I19">
+        <v>1</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>1</v>
+      </c>
+      <c r="L19">
+        <v>5</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>5</v>
+      </c>
+      <c r="O19" t="s">
+        <v>92</v>
+      </c>
+      <c r="P19" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q19">
+        <v>1.62</v>
+      </c>
+      <c r="R19">
+        <v>2.63</v>
+      </c>
+      <c r="S19">
+        <v>8</v>
+      </c>
+      <c r="T19">
+        <v>1.25</v>
+      </c>
+      <c r="U19">
+        <v>3.42</v>
+      </c>
+      <c r="V19">
+        <v>2.19</v>
+      </c>
+      <c r="W19">
+        <v>1.63</v>
+      </c>
+      <c r="X19">
+        <v>4.7</v>
+      </c>
+      <c r="Y19">
+        <v>1.14</v>
+      </c>
+      <c r="Z19">
+        <v>1.25</v>
+      </c>
+      <c r="AA19">
+        <v>6</v>
+      </c>
+      <c r="AB19">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC19">
+        <v>1.01</v>
+      </c>
+      <c r="AD19">
+        <v>17</v>
+      </c>
+      <c r="AE19">
+        <v>1.1</v>
+      </c>
+      <c r="AF19">
+        <v>5</v>
+      </c>
+      <c r="AG19">
+        <v>1.5</v>
+      </c>
+      <c r="AH19">
+        <v>2.5</v>
+      </c>
+      <c r="AI19">
+        <v>1.97</v>
+      </c>
+      <c r="AJ19">
+        <v>1.71</v>
+      </c>
+      <c r="AK19">
+        <v>1</v>
+      </c>
+      <c r="AL19">
+        <v>1.1</v>
+      </c>
+      <c r="AM19">
+        <v>3.92</v>
+      </c>
+      <c r="AN19">
+        <v>0.5</v>
+      </c>
+      <c r="AO19">
+        <v>3</v>
+      </c>
+      <c r="AP19">
+        <v>1.33</v>
+      </c>
+      <c r="AQ19">
+        <v>1.5</v>
+      </c>
+      <c r="AR19">
+        <v>1.56</v>
+      </c>
+      <c r="AS19">
+        <v>1.12</v>
+      </c>
+      <c r="AT19">
+        <v>2.68</v>
+      </c>
+      <c r="AU19">
+        <v>12</v>
+      </c>
+      <c r="AV19">
+        <v>4</v>
+      </c>
+      <c r="AW19">
+        <v>9</v>
+      </c>
+      <c r="AX19">
+        <v>2</v>
+      </c>
+      <c r="AY19">
+        <v>21</v>
+      </c>
+      <c r="AZ19">
+        <v>6</v>
+      </c>
+      <c r="BA19">
+        <v>10</v>
+      </c>
+      <c r="BB19">
+        <v>4</v>
+      </c>
+      <c r="BC19">
+        <v>14</v>
+      </c>
+      <c r="BD19">
+        <v>0</v>
+      </c>
+      <c r="BE19">
+        <v>0</v>
+      </c>
+      <c r="BF19">
+        <v>0</v>
+      </c>
+      <c r="BG19">
+        <v>0</v>
+      </c>
+      <c r="BH19">
+        <v>0</v>
+      </c>
+      <c r="BI19">
+        <v>0</v>
+      </c>
+      <c r="BJ19">
+        <v>0</v>
+      </c>
+      <c r="BK19">
+        <v>0</v>
+      </c>
+      <c r="BL19">
+        <v>0</v>
+      </c>
+      <c r="BM19">
+        <v>0</v>
+      </c>
+      <c r="BN19">
+        <v>0</v>
+      </c>
+      <c r="BO19">
+        <v>0</v>
+      </c>
+      <c r="BP19">
         <v>0</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="109">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -295,6 +295,12 @@
     <t>['2', '60', '64', '77', '90+2']</t>
   </si>
   <si>
+    <t>['3', '31', '33', '48', '73']</t>
+  </si>
+  <si>
+    <t>['35', '43']</t>
+  </si>
+  <si>
     <t>['34', '59', '86']</t>
   </si>
   <si>
@@ -332,6 +338,9 @@
   </si>
   <si>
     <t>['17', '37', '90']</t>
+  </si>
+  <si>
+    <t>['86']</t>
   </si>
 </sst>
 </file>
@@ -693,7 +702,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP19"/>
+  <dimension ref="A1:BP21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1155,7 +1164,7 @@
         <v>81</v>
       </c>
       <c r="P3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -1236,7 +1245,7 @@
         <v>0</v>
       </c>
       <c r="AQ3">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1361,7 +1370,7 @@
         <v>82</v>
       </c>
       <c r="P4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -1567,7 +1576,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="Q5">
         <v>7</v>
@@ -1773,7 +1782,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -1979,7 +1988,7 @@
         <v>81</v>
       </c>
       <c r="P7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="Q7">
         <v>1.83</v>
@@ -2185,7 +2194,7 @@
         <v>85</v>
       </c>
       <c r="P8" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="Q8">
         <v>8.5</v>
@@ -2391,7 +2400,7 @@
         <v>81</v>
       </c>
       <c r="P9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -2884,7 +2893,7 @@
         <v>3</v>
       </c>
       <c r="AQ11">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3009,7 +3018,7 @@
         <v>88</v>
       </c>
       <c r="P12" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="Q12">
         <v>8</v>
@@ -3421,7 +3430,7 @@
         <v>81</v>
       </c>
       <c r="P14" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="Q14">
         <v>5.5</v>
@@ -3627,7 +3636,7 @@
         <v>90</v>
       </c>
       <c r="P15" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="Q15">
         <v>2.5</v>
@@ -3833,7 +3842,7 @@
         <v>91</v>
       </c>
       <c r="P16" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="Q16">
         <v>2.1</v>
@@ -4039,7 +4048,7 @@
         <v>81</v>
       </c>
       <c r="P17" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="Q17">
         <v>2.38</v>
@@ -4245,7 +4254,7 @@
         <v>81</v>
       </c>
       <c r="P18" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="Q18">
         <v>3.4</v>
@@ -4607,6 +4616,418 @@
         <v>0</v>
       </c>
       <c r="BP19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:68">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>7828476</v>
+      </c>
+      <c r="C20" t="s">
+        <v>68</v>
+      </c>
+      <c r="D20" t="s">
+        <v>69</v>
+      </c>
+      <c r="E20" s="2">
+        <v>45746.27083333334</v>
+      </c>
+      <c r="F20">
+        <v>4</v>
+      </c>
+      <c r="G20" t="s">
+        <v>78</v>
+      </c>
+      <c r="H20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I20">
+        <v>3</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>3</v>
+      </c>
+      <c r="L20">
+        <v>5</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>5</v>
+      </c>
+      <c r="O20" t="s">
+        <v>93</v>
+      </c>
+      <c r="P20" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q20">
+        <v>1.53</v>
+      </c>
+      <c r="R20">
+        <v>2.75</v>
+      </c>
+      <c r="S20">
+        <v>11</v>
+      </c>
+      <c r="T20">
+        <v>1.33</v>
+      </c>
+      <c r="U20">
+        <v>3.04</v>
+      </c>
+      <c r="V20">
+        <v>2.27</v>
+      </c>
+      <c r="W20">
+        <v>1.56</v>
+      </c>
+      <c r="X20">
+        <v>4.7</v>
+      </c>
+      <c r="Y20">
+        <v>1.12</v>
+      </c>
+      <c r="Z20">
+        <v>1.18</v>
+      </c>
+      <c r="AA20">
+        <v>6.6</v>
+      </c>
+      <c r="AB20">
+        <v>14</v>
+      </c>
+      <c r="AC20">
+        <v>1.01</v>
+      </c>
+      <c r="AD20">
+        <v>17</v>
+      </c>
+      <c r="AE20">
+        <v>1.14</v>
+      </c>
+      <c r="AF20">
+        <v>4.4</v>
+      </c>
+      <c r="AG20">
+        <v>1.35</v>
+      </c>
+      <c r="AH20">
+        <v>2.94</v>
+      </c>
+      <c r="AI20">
+        <v>2.57</v>
+      </c>
+      <c r="AJ20">
+        <v>1.42</v>
+      </c>
+      <c r="AK20">
+        <v>1.01</v>
+      </c>
+      <c r="AL20">
+        <v>1.08</v>
+      </c>
+      <c r="AM20">
+        <v>4.8</v>
+      </c>
+      <c r="AN20">
+        <v>3</v>
+      </c>
+      <c r="AO20">
+        <v>0</v>
+      </c>
+      <c r="AP20">
+        <v>3</v>
+      </c>
+      <c r="AQ20">
+        <v>0</v>
+      </c>
+      <c r="AR20">
+        <v>2.45</v>
+      </c>
+      <c r="AS20">
+        <v>1.67</v>
+      </c>
+      <c r="AT20">
+        <v>4.12</v>
+      </c>
+      <c r="AU20">
+        <v>14</v>
+      </c>
+      <c r="AV20">
+        <v>5</v>
+      </c>
+      <c r="AW20">
+        <v>19</v>
+      </c>
+      <c r="AX20">
+        <v>4</v>
+      </c>
+      <c r="AY20">
+        <v>33</v>
+      </c>
+      <c r="AZ20">
+        <v>9</v>
+      </c>
+      <c r="BA20">
+        <v>9</v>
+      </c>
+      <c r="BB20">
+        <v>5</v>
+      </c>
+      <c r="BC20">
+        <v>14</v>
+      </c>
+      <c r="BD20">
+        <v>0</v>
+      </c>
+      <c r="BE20">
+        <v>0</v>
+      </c>
+      <c r="BF20">
+        <v>0</v>
+      </c>
+      <c r="BG20">
+        <v>0</v>
+      </c>
+      <c r="BH20">
+        <v>0</v>
+      </c>
+      <c r="BI20">
+        <v>0</v>
+      </c>
+      <c r="BJ20">
+        <v>0</v>
+      </c>
+      <c r="BK20">
+        <v>0</v>
+      </c>
+      <c r="BL20">
+        <v>0</v>
+      </c>
+      <c r="BM20">
+        <v>0</v>
+      </c>
+      <c r="BN20">
+        <v>0</v>
+      </c>
+      <c r="BO20">
+        <v>0</v>
+      </c>
+      <c r="BP20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:68">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>7828477</v>
+      </c>
+      <c r="C21" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" t="s">
+        <v>69</v>
+      </c>
+      <c r="E21" s="2">
+        <v>45746.35416666666</v>
+      </c>
+      <c r="F21">
+        <v>4</v>
+      </c>
+      <c r="G21" t="s">
+        <v>70</v>
+      </c>
+      <c r="H21" t="s">
+        <v>79</v>
+      </c>
+      <c r="I21">
+        <v>2</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>2</v>
+      </c>
+      <c r="L21">
+        <v>2</v>
+      </c>
+      <c r="M21">
+        <v>1</v>
+      </c>
+      <c r="N21">
+        <v>3</v>
+      </c>
+      <c r="O21" t="s">
+        <v>94</v>
+      </c>
+      <c r="P21" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q21">
+        <v>1.91</v>
+      </c>
+      <c r="R21">
+        <v>2.5</v>
+      </c>
+      <c r="S21">
+        <v>5.5</v>
+      </c>
+      <c r="T21">
+        <v>1.22</v>
+      </c>
+      <c r="U21">
+        <v>3.64</v>
+      </c>
+      <c r="V21">
+        <v>2.25</v>
+      </c>
+      <c r="W21">
+        <v>1.6</v>
+      </c>
+      <c r="X21">
+        <v>5.05</v>
+      </c>
+      <c r="Y21">
+        <v>1.12</v>
+      </c>
+      <c r="Z21">
+        <v>1.45</v>
+      </c>
+      <c r="AA21">
+        <v>4.6</v>
+      </c>
+      <c r="AB21">
+        <v>6.2</v>
+      </c>
+      <c r="AC21">
+        <v>1.01</v>
+      </c>
+      <c r="AD21">
+        <v>13</v>
+      </c>
+      <c r="AE21">
+        <v>1.1</v>
+      </c>
+      <c r="AF21">
+        <v>5</v>
+      </c>
+      <c r="AG21">
+        <v>1.57</v>
+      </c>
+      <c r="AH21">
+        <v>2.25</v>
+      </c>
+      <c r="AI21">
+        <v>1.67</v>
+      </c>
+      <c r="AJ21">
+        <v>2.03</v>
+      </c>
+      <c r="AK21">
+        <v>1.07</v>
+      </c>
+      <c r="AL21">
+        <v>1.14</v>
+      </c>
+      <c r="AM21">
+        <v>2.75</v>
+      </c>
+      <c r="AN21">
+        <v>3</v>
+      </c>
+      <c r="AO21">
+        <v>1.5</v>
+      </c>
+      <c r="AP21">
+        <v>3</v>
+      </c>
+      <c r="AQ21">
+        <v>1</v>
+      </c>
+      <c r="AR21">
+        <v>2.18</v>
+      </c>
+      <c r="AS21">
+        <v>2.42</v>
+      </c>
+      <c r="AT21">
+        <v>4.6</v>
+      </c>
+      <c r="AU21">
+        <v>10</v>
+      </c>
+      <c r="AV21">
+        <v>5</v>
+      </c>
+      <c r="AW21">
+        <v>14</v>
+      </c>
+      <c r="AX21">
+        <v>6</v>
+      </c>
+      <c r="AY21">
+        <v>24</v>
+      </c>
+      <c r="AZ21">
+        <v>11</v>
+      </c>
+      <c r="BA21">
+        <v>12</v>
+      </c>
+      <c r="BB21">
+        <v>4</v>
+      </c>
+      <c r="BC21">
+        <v>16</v>
+      </c>
+      <c r="BD21">
+        <v>0</v>
+      </c>
+      <c r="BE21">
+        <v>0</v>
+      </c>
+      <c r="BF21">
+        <v>0</v>
+      </c>
+      <c r="BG21">
+        <v>0</v>
+      </c>
+      <c r="BH21">
+        <v>0</v>
+      </c>
+      <c r="BI21">
+        <v>0</v>
+      </c>
+      <c r="BJ21">
+        <v>0</v>
+      </c>
+      <c r="BK21">
+        <v>0</v>
+      </c>
+      <c r="BL21">
+        <v>0</v>
+      </c>
+      <c r="BM21">
+        <v>0</v>
+      </c>
+      <c r="BN21">
+        <v>0</v>
+      </c>
+      <c r="BO21">
+        <v>0</v>
+      </c>
+      <c r="BP21">
         <v>0</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="117">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -301,6 +301,18 @@
     <t>['35', '43']</t>
   </si>
   <si>
+    <t>['62']</t>
+  </si>
+  <si>
+    <t>['55']</t>
+  </si>
+  <si>
+    <t>['45+1']</t>
+  </si>
+  <si>
+    <t>['9', '50', '80', '90+3']</t>
+  </si>
+  <si>
     <t>['34', '59', '86']</t>
   </si>
   <si>
@@ -341,6 +353,18 @@
   </si>
   <si>
     <t>['86']</t>
+  </si>
+  <si>
+    <t>['74']</t>
+  </si>
+  <si>
+    <t>['84', '90+3']</t>
+  </si>
+  <si>
+    <t>['68']</t>
+  </si>
+  <si>
+    <t>['2']</t>
   </si>
 </sst>
 </file>
@@ -702,7 +726,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP21"/>
+  <dimension ref="A1:BP26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1039,7 +1063,7 @@
         <v>3</v>
       </c>
       <c r="AQ2">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1164,7 +1188,7 @@
         <v>81</v>
       </c>
       <c r="P3" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -1242,7 +1266,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ3">
         <v>1</v>
@@ -1370,7 +1394,7 @@
         <v>82</v>
       </c>
       <c r="P4" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -1576,7 +1600,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="Q5">
         <v>7</v>
@@ -1782,7 +1806,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -1860,10 +1884,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ6">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -1988,7 +2012,7 @@
         <v>81</v>
       </c>
       <c r="P7" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="Q7">
         <v>1.83</v>
@@ -2194,7 +2218,7 @@
         <v>85</v>
       </c>
       <c r="P8" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="Q8">
         <v>8.5</v>
@@ -2400,7 +2424,7 @@
         <v>81</v>
       </c>
       <c r="P9" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -2478,10 +2502,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AQ9">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3018,7 +3042,7 @@
         <v>88</v>
       </c>
       <c r="P12" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="Q12">
         <v>8</v>
@@ -3096,7 +3120,7 @@
         <v>3</v>
       </c>
       <c r="AP12">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ12">
         <v>3</v>
@@ -3302,7 +3326,7 @@
         <v>3</v>
       </c>
       <c r="AP13">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AQ13">
         <v>1.5</v>
@@ -3430,7 +3454,7 @@
         <v>81</v>
       </c>
       <c r="P14" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="Q14">
         <v>5.5</v>
@@ -3508,7 +3532,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ14">
         <v>3</v>
@@ -3636,7 +3660,7 @@
         <v>90</v>
       </c>
       <c r="P15" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="Q15">
         <v>2.5</v>
@@ -3717,7 +3741,7 @@
         <v>0</v>
       </c>
       <c r="AQ15">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR15">
         <v>1.37</v>
@@ -3842,7 +3866,7 @@
         <v>91</v>
       </c>
       <c r="P16" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="Q16">
         <v>2.1</v>
@@ -3920,10 +3944,10 @@
         <v>3</v>
       </c>
       <c r="AP16">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AQ16">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4048,7 +4072,7 @@
         <v>81</v>
       </c>
       <c r="P17" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="Q17">
         <v>2.38</v>
@@ -4254,7 +4278,7 @@
         <v>81</v>
       </c>
       <c r="P18" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="Q18">
         <v>3.4</v>
@@ -4541,7 +4565,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ19">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AR19">
         <v>1.56</v>
@@ -4872,7 +4896,7 @@
         <v>94</v>
       </c>
       <c r="P21" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="Q21">
         <v>1.91</v>
@@ -5028,6 +5052,1036 @@
         <v>0</v>
       </c>
       <c r="BP21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:68">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>7828478</v>
+      </c>
+      <c r="C22" t="s">
+        <v>68</v>
+      </c>
+      <c r="D22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E22" s="2">
+        <v>45752.27083333334</v>
+      </c>
+      <c r="F22">
+        <v>5</v>
+      </c>
+      <c r="G22" t="s">
+        <v>78</v>
+      </c>
+      <c r="H22" t="s">
+        <v>75</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>1</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>1</v>
+      </c>
+      <c r="O22" t="s">
+        <v>95</v>
+      </c>
+      <c r="P22" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q22">
+        <v>1.73</v>
+      </c>
+      <c r="R22">
+        <v>2.5</v>
+      </c>
+      <c r="S22">
+        <v>7.5</v>
+      </c>
+      <c r="T22">
+        <v>1.29</v>
+      </c>
+      <c r="U22">
+        <v>3.3</v>
+      </c>
+      <c r="V22">
+        <v>2.25</v>
+      </c>
+      <c r="W22">
+        <v>1.57</v>
+      </c>
+      <c r="X22">
+        <v>5.75</v>
+      </c>
+      <c r="Y22">
+        <v>1.07</v>
+      </c>
+      <c r="Z22">
+        <v>1.3</v>
+      </c>
+      <c r="AA22">
+        <v>5</v>
+      </c>
+      <c r="AB22">
+        <v>9.6</v>
+      </c>
+      <c r="AC22">
+        <v>1.01</v>
+      </c>
+      <c r="AD22">
+        <v>15</v>
+      </c>
+      <c r="AE22">
+        <v>1.2</v>
+      </c>
+      <c r="AF22">
+        <v>4.33</v>
+      </c>
+      <c r="AG22">
+        <v>1.61</v>
+      </c>
+      <c r="AH22">
+        <v>2.1</v>
+      </c>
+      <c r="AI22">
+        <v>2.05</v>
+      </c>
+      <c r="AJ22">
+        <v>1.68</v>
+      </c>
+      <c r="AK22">
+        <v>1.06</v>
+      </c>
+      <c r="AL22">
+        <v>1.15</v>
+      </c>
+      <c r="AM22">
+        <v>3.5</v>
+      </c>
+      <c r="AN22">
+        <v>3</v>
+      </c>
+      <c r="AO22">
+        <v>2</v>
+      </c>
+      <c r="AP22">
+        <v>3</v>
+      </c>
+      <c r="AQ22">
+        <v>1.33</v>
+      </c>
+      <c r="AR22">
+        <v>3.01</v>
+      </c>
+      <c r="AS22">
+        <v>2.22</v>
+      </c>
+      <c r="AT22">
+        <v>5.23</v>
+      </c>
+      <c r="AU22">
+        <v>7</v>
+      </c>
+      <c r="AV22">
+        <v>3</v>
+      </c>
+      <c r="AW22">
+        <v>10</v>
+      </c>
+      <c r="AX22">
+        <v>5</v>
+      </c>
+      <c r="AY22">
+        <v>17</v>
+      </c>
+      <c r="AZ22">
+        <v>8</v>
+      </c>
+      <c r="BA22">
+        <v>9</v>
+      </c>
+      <c r="BB22">
+        <v>3</v>
+      </c>
+      <c r="BC22">
+        <v>12</v>
+      </c>
+      <c r="BD22">
+        <v>0</v>
+      </c>
+      <c r="BE22">
+        <v>0</v>
+      </c>
+      <c r="BF22">
+        <v>0</v>
+      </c>
+      <c r="BG22">
+        <v>0</v>
+      </c>
+      <c r="BH22">
+        <v>0</v>
+      </c>
+      <c r="BI22">
+        <v>0</v>
+      </c>
+      <c r="BJ22">
+        <v>0</v>
+      </c>
+      <c r="BK22">
+        <v>0</v>
+      </c>
+      <c r="BL22">
+        <v>0</v>
+      </c>
+      <c r="BM22">
+        <v>0</v>
+      </c>
+      <c r="BN22">
+        <v>0</v>
+      </c>
+      <c r="BO22">
+        <v>0</v>
+      </c>
+      <c r="BP22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:68">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>7828480</v>
+      </c>
+      <c r="C23" t="s">
+        <v>68</v>
+      </c>
+      <c r="D23" t="s">
+        <v>69</v>
+      </c>
+      <c r="E23" s="2">
+        <v>45752.35416666666</v>
+      </c>
+      <c r="F23">
+        <v>5</v>
+      </c>
+      <c r="G23" t="s">
+        <v>76</v>
+      </c>
+      <c r="H23" t="s">
+        <v>70</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>1</v>
+      </c>
+      <c r="N23">
+        <v>1</v>
+      </c>
+      <c r="O23" t="s">
+        <v>81</v>
+      </c>
+      <c r="P23" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q23">
+        <v>5.5</v>
+      </c>
+      <c r="R23">
+        <v>2.4</v>
+      </c>
+      <c r="S23">
+        <v>1.95</v>
+      </c>
+      <c r="T23">
+        <v>1.31</v>
+      </c>
+      <c r="U23">
+        <v>3.1</v>
+      </c>
+      <c r="V23">
+        <v>2.3</v>
+      </c>
+      <c r="W23">
+        <v>1.55</v>
+      </c>
+      <c r="X23">
+        <v>5</v>
+      </c>
+      <c r="Y23">
+        <v>1.15</v>
+      </c>
+      <c r="Z23">
+        <v>6.6</v>
+      </c>
+      <c r="AA23">
+        <v>4.3</v>
+      </c>
+      <c r="AB23">
+        <v>1.46</v>
+      </c>
+      <c r="AC23">
+        <v>1.02</v>
+      </c>
+      <c r="AD23">
+        <v>13</v>
+      </c>
+      <c r="AE23">
+        <v>1.22</v>
+      </c>
+      <c r="AF23">
+        <v>4</v>
+      </c>
+      <c r="AG23">
+        <v>1.65</v>
+      </c>
+      <c r="AH23">
+        <v>2.05</v>
+      </c>
+      <c r="AI23">
+        <v>1.7</v>
+      </c>
+      <c r="AJ23">
+        <v>2</v>
+      </c>
+      <c r="AK23">
+        <v>2.45</v>
+      </c>
+      <c r="AL23">
+        <v>1.23</v>
+      </c>
+      <c r="AM23">
+        <v>1.12</v>
+      </c>
+      <c r="AN23">
+        <v>1.5</v>
+      </c>
+      <c r="AO23">
+        <v>3</v>
+      </c>
+      <c r="AP23">
+        <v>1</v>
+      </c>
+      <c r="AQ23">
+        <v>3</v>
+      </c>
+      <c r="AR23">
+        <v>1.34</v>
+      </c>
+      <c r="AS23">
+        <v>2.41</v>
+      </c>
+      <c r="AT23">
+        <v>3.75</v>
+      </c>
+      <c r="AU23">
+        <v>6</v>
+      </c>
+      <c r="AV23">
+        <v>5</v>
+      </c>
+      <c r="AW23">
+        <v>4</v>
+      </c>
+      <c r="AX23">
+        <v>5</v>
+      </c>
+      <c r="AY23">
+        <v>10</v>
+      </c>
+      <c r="AZ23">
+        <v>10</v>
+      </c>
+      <c r="BA23">
+        <v>2</v>
+      </c>
+      <c r="BB23">
+        <v>1</v>
+      </c>
+      <c r="BC23">
+        <v>3</v>
+      </c>
+      <c r="BD23">
+        <v>0</v>
+      </c>
+      <c r="BE23">
+        <v>0</v>
+      </c>
+      <c r="BF23">
+        <v>0</v>
+      </c>
+      <c r="BG23">
+        <v>0</v>
+      </c>
+      <c r="BH23">
+        <v>0</v>
+      </c>
+      <c r="BI23">
+        <v>0</v>
+      </c>
+      <c r="BJ23">
+        <v>0</v>
+      </c>
+      <c r="BK23">
+        <v>0</v>
+      </c>
+      <c r="BL23">
+        <v>0</v>
+      </c>
+      <c r="BM23">
+        <v>0</v>
+      </c>
+      <c r="BN23">
+        <v>0</v>
+      </c>
+      <c r="BO23">
+        <v>0</v>
+      </c>
+      <c r="BP23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:68">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>7828479</v>
+      </c>
+      <c r="C24" t="s">
+        <v>68</v>
+      </c>
+      <c r="D24" t="s">
+        <v>69</v>
+      </c>
+      <c r="E24" s="2">
+        <v>45752.35416666666</v>
+      </c>
+      <c r="F24">
+        <v>5</v>
+      </c>
+      <c r="G24" t="s">
+        <v>79</v>
+      </c>
+      <c r="H24" t="s">
+        <v>72</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>1</v>
+      </c>
+      <c r="M24">
+        <v>2</v>
+      </c>
+      <c r="N24">
+        <v>3</v>
+      </c>
+      <c r="O24" t="s">
+        <v>96</v>
+      </c>
+      <c r="P24" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q24">
+        <v>3.1</v>
+      </c>
+      <c r="R24">
+        <v>2.38</v>
+      </c>
+      <c r="S24">
+        <v>2.75</v>
+      </c>
+      <c r="T24">
+        <v>1.29</v>
+      </c>
+      <c r="U24">
+        <v>3.25</v>
+      </c>
+      <c r="V24">
+        <v>2.35</v>
+      </c>
+      <c r="W24">
+        <v>1.52</v>
+      </c>
+      <c r="X24">
+        <v>5.8</v>
+      </c>
+      <c r="Y24">
+        <v>1.12</v>
+      </c>
+      <c r="Z24">
+        <v>2.74</v>
+      </c>
+      <c r="AA24">
+        <v>3.73</v>
+      </c>
+      <c r="AB24">
+        <v>2.29</v>
+      </c>
+      <c r="AC24">
+        <v>1.03</v>
+      </c>
+      <c r="AD24">
+        <v>12</v>
+      </c>
+      <c r="AE24">
+        <v>1.2</v>
+      </c>
+      <c r="AF24">
+        <v>4.2</v>
+      </c>
+      <c r="AG24">
+        <v>1.55</v>
+      </c>
+      <c r="AH24">
+        <v>2.2</v>
+      </c>
+      <c r="AI24">
+        <v>1.55</v>
+      </c>
+      <c r="AJ24">
+        <v>2.25</v>
+      </c>
+      <c r="AK24">
+        <v>1.57</v>
+      </c>
+      <c r="AL24">
+        <v>1.27</v>
+      </c>
+      <c r="AM24">
+        <v>1.43</v>
+      </c>
+      <c r="AN24">
+        <v>1</v>
+      </c>
+      <c r="AO24">
+        <v>3</v>
+      </c>
+      <c r="AP24">
+        <v>0.5</v>
+      </c>
+      <c r="AQ24">
+        <v>3</v>
+      </c>
+      <c r="AR24">
+        <v>3.56</v>
+      </c>
+      <c r="AS24">
+        <v>2.95</v>
+      </c>
+      <c r="AT24">
+        <v>6.51</v>
+      </c>
+      <c r="AU24">
+        <v>9</v>
+      </c>
+      <c r="AV24">
+        <v>11</v>
+      </c>
+      <c r="AW24">
+        <v>4</v>
+      </c>
+      <c r="AX24">
+        <v>6</v>
+      </c>
+      <c r="AY24">
+        <v>13</v>
+      </c>
+      <c r="AZ24">
+        <v>17</v>
+      </c>
+      <c r="BA24">
+        <v>5</v>
+      </c>
+      <c r="BB24">
+        <v>7</v>
+      </c>
+      <c r="BC24">
+        <v>12</v>
+      </c>
+      <c r="BD24">
+        <v>0</v>
+      </c>
+      <c r="BE24">
+        <v>0</v>
+      </c>
+      <c r="BF24">
+        <v>0</v>
+      </c>
+      <c r="BG24">
+        <v>0</v>
+      </c>
+      <c r="BH24">
+        <v>0</v>
+      </c>
+      <c r="BI24">
+        <v>0</v>
+      </c>
+      <c r="BJ24">
+        <v>0</v>
+      </c>
+      <c r="BK24">
+        <v>0</v>
+      </c>
+      <c r="BL24">
+        <v>0</v>
+      </c>
+      <c r="BM24">
+        <v>0</v>
+      </c>
+      <c r="BN24">
+        <v>0</v>
+      </c>
+      <c r="BO24">
+        <v>0</v>
+      </c>
+      <c r="BP24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:68">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>7828481</v>
+      </c>
+      <c r="C25" t="s">
+        <v>68</v>
+      </c>
+      <c r="D25" t="s">
+        <v>69</v>
+      </c>
+      <c r="E25" s="2">
+        <v>45752.45833333334</v>
+      </c>
+      <c r="F25">
+        <v>5</v>
+      </c>
+      <c r="G25" t="s">
+        <v>71</v>
+      </c>
+      <c r="H25" t="s">
+        <v>77</v>
+      </c>
+      <c r="I25">
+        <v>1</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>1</v>
+      </c>
+      <c r="L25">
+        <v>1</v>
+      </c>
+      <c r="M25">
+        <v>1</v>
+      </c>
+      <c r="N25">
+        <v>2</v>
+      </c>
+      <c r="O25" t="s">
+        <v>97</v>
+      </c>
+      <c r="P25" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q25">
+        <v>2.38</v>
+      </c>
+      <c r="R25">
+        <v>2.3</v>
+      </c>
+      <c r="S25">
+        <v>4</v>
+      </c>
+      <c r="T25">
+        <v>1.32</v>
+      </c>
+      <c r="U25">
+        <v>3.1</v>
+      </c>
+      <c r="V25">
+        <v>2.4</v>
+      </c>
+      <c r="W25">
+        <v>1.49</v>
+      </c>
+      <c r="X25">
+        <v>5.7</v>
+      </c>
+      <c r="Y25">
+        <v>1.08</v>
+      </c>
+      <c r="Z25">
+        <v>1.86</v>
+      </c>
+      <c r="AA25">
+        <v>3.53</v>
+      </c>
+      <c r="AB25">
+        <v>4</v>
+      </c>
+      <c r="AC25">
+        <v>1.04</v>
+      </c>
+      <c r="AD25">
+        <v>11</v>
+      </c>
+      <c r="AE25">
+        <v>1.22</v>
+      </c>
+      <c r="AF25">
+        <v>3.95</v>
+      </c>
+      <c r="AG25">
+        <v>1.67</v>
+      </c>
+      <c r="AH25">
+        <v>2</v>
+      </c>
+      <c r="AI25">
+        <v>1.58</v>
+      </c>
+      <c r="AJ25">
+        <v>2.2</v>
+      </c>
+      <c r="AK25">
+        <v>1.32</v>
+      </c>
+      <c r="AL25">
+        <v>1.27</v>
+      </c>
+      <c r="AM25">
+        <v>1.71</v>
+      </c>
+      <c r="AN25">
+        <v>0</v>
+      </c>
+      <c r="AO25">
+        <v>1.5</v>
+      </c>
+      <c r="AP25">
+        <v>0.33</v>
+      </c>
+      <c r="AQ25">
+        <v>1.33</v>
+      </c>
+      <c r="AR25">
+        <v>0.71</v>
+      </c>
+      <c r="AS25">
+        <v>1.28</v>
+      </c>
+      <c r="AT25">
+        <v>1.99</v>
+      </c>
+      <c r="AU25">
+        <v>4</v>
+      </c>
+      <c r="AV25">
+        <v>4</v>
+      </c>
+      <c r="AW25">
+        <v>4</v>
+      </c>
+      <c r="AX25">
+        <v>7</v>
+      </c>
+      <c r="AY25">
+        <v>8</v>
+      </c>
+      <c r="AZ25">
+        <v>11</v>
+      </c>
+      <c r="BA25">
+        <v>7</v>
+      </c>
+      <c r="BB25">
+        <v>4</v>
+      </c>
+      <c r="BC25">
+        <v>11</v>
+      </c>
+      <c r="BD25">
+        <v>0</v>
+      </c>
+      <c r="BE25">
+        <v>0</v>
+      </c>
+      <c r="BF25">
+        <v>0</v>
+      </c>
+      <c r="BG25">
+        <v>0</v>
+      </c>
+      <c r="BH25">
+        <v>0</v>
+      </c>
+      <c r="BI25">
+        <v>0</v>
+      </c>
+      <c r="BJ25">
+        <v>0</v>
+      </c>
+      <c r="BK25">
+        <v>0</v>
+      </c>
+      <c r="BL25">
+        <v>0</v>
+      </c>
+      <c r="BM25">
+        <v>0</v>
+      </c>
+      <c r="BN25">
+        <v>0</v>
+      </c>
+      <c r="BO25">
+        <v>0</v>
+      </c>
+      <c r="BP25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:68">
+      <c r="A26" s="1">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>7828482</v>
+      </c>
+      <c r="C26" t="s">
+        <v>68</v>
+      </c>
+      <c r="D26" t="s">
+        <v>69</v>
+      </c>
+      <c r="E26" s="2">
+        <v>45752.54166666666</v>
+      </c>
+      <c r="F26">
+        <v>5</v>
+      </c>
+      <c r="G26" t="s">
+        <v>74</v>
+      </c>
+      <c r="H26" t="s">
+        <v>73</v>
+      </c>
+      <c r="I26">
+        <v>1</v>
+      </c>
+      <c r="J26">
+        <v>1</v>
+      </c>
+      <c r="K26">
+        <v>2</v>
+      </c>
+      <c r="L26">
+        <v>4</v>
+      </c>
+      <c r="M26">
+        <v>1</v>
+      </c>
+      <c r="N26">
+        <v>5</v>
+      </c>
+      <c r="O26" t="s">
+        <v>98</v>
+      </c>
+      <c r="P26" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q26">
+        <v>3.1</v>
+      </c>
+      <c r="R26">
+        <v>2.38</v>
+      </c>
+      <c r="S26">
+        <v>2.63</v>
+      </c>
+      <c r="T26">
+        <v>1.3</v>
+      </c>
+      <c r="U26">
+        <v>3.2</v>
+      </c>
+      <c r="V26">
+        <v>2.3</v>
+      </c>
+      <c r="W26">
+        <v>1.53</v>
+      </c>
+      <c r="X26">
+        <v>5.5</v>
+      </c>
+      <c r="Y26">
+        <v>1.12</v>
+      </c>
+      <c r="Z26">
+        <v>2.96</v>
+      </c>
+      <c r="AA26">
+        <v>3.55</v>
+      </c>
+      <c r="AB26">
+        <v>2.22</v>
+      </c>
+      <c r="AC26">
+        <v>1.03</v>
+      </c>
+      <c r="AD26">
+        <v>12</v>
+      </c>
+      <c r="AE26">
+        <v>1.2</v>
+      </c>
+      <c r="AF26">
+        <v>4.2</v>
+      </c>
+      <c r="AG26">
+        <v>1.62</v>
+      </c>
+      <c r="AH26">
+        <v>2.16</v>
+      </c>
+      <c r="AI26">
+        <v>1.55</v>
+      </c>
+      <c r="AJ26">
+        <v>2.3</v>
+      </c>
+      <c r="AK26">
+        <v>1.57</v>
+      </c>
+      <c r="AL26">
+        <v>1.28</v>
+      </c>
+      <c r="AM26">
+        <v>1.41</v>
+      </c>
+      <c r="AN26">
+        <v>0</v>
+      </c>
+      <c r="AO26">
+        <v>1.5</v>
+      </c>
+      <c r="AP26">
+        <v>1</v>
+      </c>
+      <c r="AQ26">
+        <v>1</v>
+      </c>
+      <c r="AR26">
+        <v>1.15</v>
+      </c>
+      <c r="AS26">
+        <v>0.99</v>
+      </c>
+      <c r="AT26">
+        <v>2.14</v>
+      </c>
+      <c r="AU26">
+        <v>13</v>
+      </c>
+      <c r="AV26">
+        <v>2</v>
+      </c>
+      <c r="AW26">
+        <v>11</v>
+      </c>
+      <c r="AX26">
+        <v>5</v>
+      </c>
+      <c r="AY26">
+        <v>24</v>
+      </c>
+      <c r="AZ26">
+        <v>7</v>
+      </c>
+      <c r="BA26">
+        <v>14</v>
+      </c>
+      <c r="BB26">
+        <v>5</v>
+      </c>
+      <c r="BC26">
+        <v>19</v>
+      </c>
+      <c r="BD26">
+        <v>0</v>
+      </c>
+      <c r="BE26">
+        <v>0</v>
+      </c>
+      <c r="BF26">
+        <v>0</v>
+      </c>
+      <c r="BG26">
+        <v>0</v>
+      </c>
+      <c r="BH26">
+        <v>0</v>
+      </c>
+      <c r="BI26">
+        <v>0</v>
+      </c>
+      <c r="BJ26">
+        <v>0</v>
+      </c>
+      <c r="BK26">
+        <v>0</v>
+      </c>
+      <c r="BL26">
+        <v>0</v>
+      </c>
+      <c r="BM26">
+        <v>0</v>
+      </c>
+      <c r="BN26">
+        <v>0</v>
+      </c>
+      <c r="BO26">
+        <v>0</v>
+      </c>
+      <c r="BP26">
         <v>0</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="122">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -313,6 +313,15 @@
     <t>['9', '50', '80', '90+3']</t>
   </si>
   <si>
+    <t>['75']</t>
+  </si>
+  <si>
+    <t>['80', '90+3']</t>
+  </si>
+  <si>
+    <t>['27']</t>
+  </si>
+  <si>
     <t>['34', '59', '86']</t>
   </si>
   <si>
@@ -365,6 +374,12 @@
   </si>
   <si>
     <t>['2']</t>
+  </si>
+  <si>
+    <t>['29']</t>
+  </si>
+  <si>
+    <t>['42', '47']</t>
   </si>
 </sst>
 </file>
@@ -726,7 +741,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP26"/>
+  <dimension ref="A1:BP29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1188,7 +1203,7 @@
         <v>81</v>
       </c>
       <c r="P3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -1394,7 +1409,7 @@
         <v>82</v>
       </c>
       <c r="P4" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -1600,7 +1615,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="Q5">
         <v>7</v>
@@ -1806,7 +1821,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2012,7 +2027,7 @@
         <v>81</v>
       </c>
       <c r="P7" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="Q7">
         <v>1.83</v>
@@ -2218,7 +2233,7 @@
         <v>85</v>
       </c>
       <c r="P8" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="Q8">
         <v>8.5</v>
@@ -2424,7 +2439,7 @@
         <v>81</v>
       </c>
       <c r="P9" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -2502,10 +2517,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AQ9">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3042,7 +3057,7 @@
         <v>88</v>
       </c>
       <c r="P12" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="Q12">
         <v>8</v>
@@ -3326,7 +3341,7 @@
         <v>3</v>
       </c>
       <c r="AP13">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AQ13">
         <v>1.5</v>
@@ -3454,7 +3469,7 @@
         <v>81</v>
       </c>
       <c r="P14" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="Q14">
         <v>5.5</v>
@@ -3660,7 +3675,7 @@
         <v>90</v>
       </c>
       <c r="P15" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="Q15">
         <v>2.5</v>
@@ -3866,7 +3881,7 @@
         <v>91</v>
       </c>
       <c r="P16" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="Q16">
         <v>2.1</v>
@@ -4072,7 +4087,7 @@
         <v>81</v>
       </c>
       <c r="P17" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="Q17">
         <v>2.38</v>
@@ -4278,7 +4293,7 @@
         <v>81</v>
       </c>
       <c r="P18" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="Q18">
         <v>3.4</v>
@@ -4565,7 +4580,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ19">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AR19">
         <v>1.56</v>
@@ -4896,7 +4911,7 @@
         <v>94</v>
       </c>
       <c r="P21" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="Q21">
         <v>1.91</v>
@@ -5308,7 +5323,7 @@
         <v>81</v>
       </c>
       <c r="P23" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="Q23">
         <v>5.5</v>
@@ -5386,7 +5401,7 @@
         <v>3</v>
       </c>
       <c r="AP23">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AQ23">
         <v>3</v>
@@ -5514,7 +5529,7 @@
         <v>96</v>
       </c>
       <c r="P24" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="Q24">
         <v>3.1</v>
@@ -5720,7 +5735,7 @@
         <v>97</v>
       </c>
       <c r="P25" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="Q25">
         <v>2.38</v>
@@ -5926,7 +5941,7 @@
         <v>98</v>
       </c>
       <c r="P26" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="Q26">
         <v>3.1</v>
@@ -6007,7 +6022,7 @@
         <v>1</v>
       </c>
       <c r="AQ26">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AR26">
         <v>1.15</v>
@@ -6082,6 +6097,624 @@
         <v>0</v>
       </c>
       <c r="BP26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:68">
+      <c r="A27" s="1">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>7828484</v>
+      </c>
+      <c r="C27" t="s">
+        <v>68</v>
+      </c>
+      <c r="D27" t="s">
+        <v>69</v>
+      </c>
+      <c r="E27" s="2">
+        <v>45755.47916666666</v>
+      </c>
+      <c r="F27">
+        <v>6</v>
+      </c>
+      <c r="G27" t="s">
+        <v>76</v>
+      </c>
+      <c r="H27" t="s">
+        <v>74</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>1</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27">
+        <v>1</v>
+      </c>
+      <c r="O27" t="s">
+        <v>99</v>
+      </c>
+      <c r="P27" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q27">
+        <v>1.7</v>
+      </c>
+      <c r="R27">
+        <v>2.6</v>
+      </c>
+      <c r="S27">
+        <v>5.5</v>
+      </c>
+      <c r="T27">
+        <v>1.25</v>
+      </c>
+      <c r="U27">
+        <v>3.42</v>
+      </c>
+      <c r="V27">
+        <v>2.25</v>
+      </c>
+      <c r="W27">
+        <v>1.58</v>
+      </c>
+      <c r="X27">
+        <v>4.75</v>
+      </c>
+      <c r="Y27">
+        <v>1.15</v>
+      </c>
+      <c r="Z27">
+        <v>1.45</v>
+      </c>
+      <c r="AA27">
+        <v>4.3</v>
+      </c>
+      <c r="AB27">
+        <v>5.75</v>
+      </c>
+      <c r="AC27">
+        <v>1.01</v>
+      </c>
+      <c r="AD27">
+        <v>12</v>
+      </c>
+      <c r="AE27">
+        <v>1.11</v>
+      </c>
+      <c r="AF27">
+        <v>5</v>
+      </c>
+      <c r="AG27">
+        <v>1.47</v>
+      </c>
+      <c r="AH27">
+        <v>2.35</v>
+      </c>
+      <c r="AI27">
+        <v>1.65</v>
+      </c>
+      <c r="AJ27">
+        <v>2.05</v>
+      </c>
+      <c r="AK27">
+        <v>1.18</v>
+      </c>
+      <c r="AL27">
+        <v>1.17</v>
+      </c>
+      <c r="AM27">
+        <v>2.75</v>
+      </c>
+      <c r="AN27">
+        <v>1</v>
+      </c>
+      <c r="AO27">
+        <v>0</v>
+      </c>
+      <c r="AP27">
+        <v>1.5</v>
+      </c>
+      <c r="AQ27">
+        <v>0</v>
+      </c>
+      <c r="AR27">
+        <v>1.38</v>
+      </c>
+      <c r="AS27">
+        <v>1.42</v>
+      </c>
+      <c r="AT27">
+        <v>2.8</v>
+      </c>
+      <c r="AU27">
+        <v>5</v>
+      </c>
+      <c r="AV27">
+        <v>2</v>
+      </c>
+      <c r="AW27">
+        <v>5</v>
+      </c>
+      <c r="AX27">
+        <v>3</v>
+      </c>
+      <c r="AY27">
+        <v>10</v>
+      </c>
+      <c r="AZ27">
+        <v>5</v>
+      </c>
+      <c r="BA27">
+        <v>7</v>
+      </c>
+      <c r="BB27">
+        <v>2</v>
+      </c>
+      <c r="BC27">
+        <v>9</v>
+      </c>
+      <c r="BD27">
+        <v>0</v>
+      </c>
+      <c r="BE27">
+        <v>0</v>
+      </c>
+      <c r="BF27">
+        <v>0</v>
+      </c>
+      <c r="BG27">
+        <v>0</v>
+      </c>
+      <c r="BH27">
+        <v>0</v>
+      </c>
+      <c r="BI27">
+        <v>0</v>
+      </c>
+      <c r="BJ27">
+        <v>0</v>
+      </c>
+      <c r="BK27">
+        <v>0</v>
+      </c>
+      <c r="BL27">
+        <v>0</v>
+      </c>
+      <c r="BM27">
+        <v>0</v>
+      </c>
+      <c r="BN27">
+        <v>0</v>
+      </c>
+      <c r="BO27">
+        <v>0</v>
+      </c>
+      <c r="BP27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:68">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>7828483</v>
+      </c>
+      <c r="C28" t="s">
+        <v>68</v>
+      </c>
+      <c r="D28" t="s">
+        <v>69</v>
+      </c>
+      <c r="E28" s="2">
+        <v>45755.5</v>
+      </c>
+      <c r="F28">
+        <v>6</v>
+      </c>
+      <c r="G28" t="s">
+        <v>70</v>
+      </c>
+      <c r="H28" t="s">
+        <v>73</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>1</v>
+      </c>
+      <c r="K28">
+        <v>1</v>
+      </c>
+      <c r="L28">
+        <v>2</v>
+      </c>
+      <c r="M28">
+        <v>1</v>
+      </c>
+      <c r="N28">
+        <v>3</v>
+      </c>
+      <c r="O28" t="s">
+        <v>100</v>
+      </c>
+      <c r="P28" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q28">
+        <v>1.3</v>
+      </c>
+      <c r="R28">
+        <v>3.55</v>
+      </c>
+      <c r="S28">
+        <v>15</v>
+      </c>
+      <c r="T28">
+        <v>1.21</v>
+      </c>
+      <c r="U28">
+        <v>4</v>
+      </c>
+      <c r="V28">
+        <v>1.95</v>
+      </c>
+      <c r="W28">
+        <v>1.97</v>
+      </c>
+      <c r="X28">
+        <v>3.74</v>
+      </c>
+      <c r="Y28">
+        <v>1.21</v>
+      </c>
+      <c r="Z28">
+        <v>1.05</v>
+      </c>
+      <c r="AA28">
+        <v>11</v>
+      </c>
+      <c r="AB28">
+        <v>28</v>
+      </c>
+      <c r="AC28">
+        <v>1.01</v>
+      </c>
+      <c r="AD28">
+        <v>29</v>
+      </c>
+      <c r="AE28">
+        <v>1.04</v>
+      </c>
+      <c r="AF28">
+        <v>7.8</v>
+      </c>
+      <c r="AG28">
+        <v>1.29</v>
+      </c>
+      <c r="AH28">
+        <v>2.88</v>
+      </c>
+      <c r="AI28">
+        <v>2.62</v>
+      </c>
+      <c r="AJ28">
+        <v>1.42</v>
+      </c>
+      <c r="AK28">
+        <v>1.01</v>
+      </c>
+      <c r="AL28">
+        <v>1.07</v>
+      </c>
+      <c r="AM28">
+        <v>9</v>
+      </c>
+      <c r="AN28">
+        <v>3</v>
+      </c>
+      <c r="AO28">
+        <v>1</v>
+      </c>
+      <c r="AP28">
+        <v>3</v>
+      </c>
+      <c r="AQ28">
+        <v>0.75</v>
+      </c>
+      <c r="AR28">
+        <v>2.38</v>
+      </c>
+      <c r="AS28">
+        <v>0.98</v>
+      </c>
+      <c r="AT28">
+        <v>3.36</v>
+      </c>
+      <c r="AU28">
+        <v>17</v>
+      </c>
+      <c r="AV28">
+        <v>2</v>
+      </c>
+      <c r="AW28">
+        <v>14</v>
+      </c>
+      <c r="AX28">
+        <v>1</v>
+      </c>
+      <c r="AY28">
+        <v>31</v>
+      </c>
+      <c r="AZ28">
+        <v>3</v>
+      </c>
+      <c r="BA28">
+        <v>15</v>
+      </c>
+      <c r="BB28">
+        <v>2</v>
+      </c>
+      <c r="BC28">
+        <v>17</v>
+      </c>
+      <c r="BD28">
+        <v>0</v>
+      </c>
+      <c r="BE28">
+        <v>0</v>
+      </c>
+      <c r="BF28">
+        <v>0</v>
+      </c>
+      <c r="BG28">
+        <v>0</v>
+      </c>
+      <c r="BH28">
+        <v>0</v>
+      </c>
+      <c r="BI28">
+        <v>0</v>
+      </c>
+      <c r="BJ28">
+        <v>0</v>
+      </c>
+      <c r="BK28">
+        <v>0</v>
+      </c>
+      <c r="BL28">
+        <v>0</v>
+      </c>
+      <c r="BM28">
+        <v>0</v>
+      </c>
+      <c r="BN28">
+        <v>0</v>
+      </c>
+      <c r="BO28">
+        <v>0</v>
+      </c>
+      <c r="BP28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:68">
+      <c r="A29" s="1">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <v>7828485</v>
+      </c>
+      <c r="C29" t="s">
+        <v>68</v>
+      </c>
+      <c r="D29" t="s">
+        <v>69</v>
+      </c>
+      <c r="E29" s="2">
+        <v>45755.54166666666</v>
+      </c>
+      <c r="F29">
+        <v>6</v>
+      </c>
+      <c r="G29" t="s">
+        <v>75</v>
+      </c>
+      <c r="H29" t="s">
+        <v>72</v>
+      </c>
+      <c r="I29">
+        <v>1</v>
+      </c>
+      <c r="J29">
+        <v>1</v>
+      </c>
+      <c r="K29">
+        <v>2</v>
+      </c>
+      <c r="L29">
+        <v>1</v>
+      </c>
+      <c r="M29">
+        <v>2</v>
+      </c>
+      <c r="N29">
+        <v>3</v>
+      </c>
+      <c r="O29" t="s">
+        <v>101</v>
+      </c>
+      <c r="P29" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q29">
+        <v>5</v>
+      </c>
+      <c r="R29">
+        <v>2.25</v>
+      </c>
+      <c r="S29">
+        <v>1.95</v>
+      </c>
+      <c r="T29">
+        <v>1.25</v>
+      </c>
+      <c r="U29">
+        <v>3.8</v>
+      </c>
+      <c r="V29">
+        <v>2.33</v>
+      </c>
+      <c r="W29">
+        <v>1.57</v>
+      </c>
+      <c r="X29">
+        <v>5.5</v>
+      </c>
+      <c r="Y29">
+        <v>1.15</v>
+      </c>
+      <c r="Z29">
+        <v>5</v>
+      </c>
+      <c r="AA29">
+        <v>4</v>
+      </c>
+      <c r="AB29">
+        <v>1.46</v>
+      </c>
+      <c r="AC29">
+        <v>1</v>
+      </c>
+      <c r="AD29">
+        <v>12</v>
+      </c>
+      <c r="AE29">
+        <v>1.13</v>
+      </c>
+      <c r="AF29">
+        <v>4.9</v>
+      </c>
+      <c r="AG29">
+        <v>1.57</v>
+      </c>
+      <c r="AH29">
+        <v>2.32</v>
+      </c>
+      <c r="AI29">
+        <v>1.62</v>
+      </c>
+      <c r="AJ29">
+        <v>2.18</v>
+      </c>
+      <c r="AK29">
+        <v>1.19</v>
+      </c>
+      <c r="AL29">
+        <v>1.23</v>
+      </c>
+      <c r="AM29">
+        <v>1.11</v>
+      </c>
+      <c r="AN29">
+        <v>0</v>
+      </c>
+      <c r="AO29">
+        <v>3</v>
+      </c>
+      <c r="AP29">
+        <v>0</v>
+      </c>
+      <c r="AQ29">
+        <v>3</v>
+      </c>
+      <c r="AR29">
+        <v>1.01</v>
+      </c>
+      <c r="AS29">
+        <v>2.68</v>
+      </c>
+      <c r="AT29">
+        <v>3.69</v>
+      </c>
+      <c r="AU29">
+        <v>3</v>
+      </c>
+      <c r="AV29">
+        <v>10</v>
+      </c>
+      <c r="AW29">
+        <v>5</v>
+      </c>
+      <c r="AX29">
+        <v>12</v>
+      </c>
+      <c r="AY29">
+        <v>8</v>
+      </c>
+      <c r="AZ29">
+        <v>22</v>
+      </c>
+      <c r="BA29">
+        <v>3</v>
+      </c>
+      <c r="BB29">
+        <v>16</v>
+      </c>
+      <c r="BC29">
+        <v>19</v>
+      </c>
+      <c r="BD29">
+        <v>0</v>
+      </c>
+      <c r="BE29">
+        <v>0</v>
+      </c>
+      <c r="BF29">
+        <v>0</v>
+      </c>
+      <c r="BG29">
+        <v>0</v>
+      </c>
+      <c r="BH29">
+        <v>0</v>
+      </c>
+      <c r="BI29">
+        <v>0</v>
+      </c>
+      <c r="BJ29">
+        <v>0</v>
+      </c>
+      <c r="BK29">
+        <v>0</v>
+      </c>
+      <c r="BL29">
+        <v>0</v>
+      </c>
+      <c r="BM29">
+        <v>0</v>
+      </c>
+      <c r="BN29">
+        <v>0</v>
+      </c>
+      <c r="BO29">
+        <v>0</v>
+      </c>
+      <c r="BP29">
         <v>0</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="123">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -320,6 +320,9 @@
   </si>
   <si>
     <t>['27']</t>
+  </si>
+  <si>
+    <t>['4', '9', '16']</t>
   </si>
   <si>
     <t>['34', '59', '86']</t>
@@ -741,7 +744,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP29"/>
+  <dimension ref="A1:BP30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1078,7 +1081,7 @@
         <v>3</v>
       </c>
       <c r="AQ2">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1203,7 +1206,7 @@
         <v>81</v>
       </c>
       <c r="P3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -1409,7 +1412,7 @@
         <v>82</v>
       </c>
       <c r="P4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -1615,7 +1618,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q5">
         <v>7</v>
@@ -1821,7 +1824,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2027,7 +2030,7 @@
         <v>81</v>
       </c>
       <c r="P7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q7">
         <v>1.83</v>
@@ -2233,7 +2236,7 @@
         <v>85</v>
       </c>
       <c r="P8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q8">
         <v>8.5</v>
@@ -2439,7 +2442,7 @@
         <v>81</v>
       </c>
       <c r="P9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -3057,7 +3060,7 @@
         <v>88</v>
       </c>
       <c r="P12" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q12">
         <v>8</v>
@@ -3469,7 +3472,7 @@
         <v>81</v>
       </c>
       <c r="P14" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q14">
         <v>5.5</v>
@@ -3675,7 +3678,7 @@
         <v>90</v>
       </c>
       <c r="P15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q15">
         <v>2.5</v>
@@ -3756,7 +3759,7 @@
         <v>0</v>
       </c>
       <c r="AQ15">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AR15">
         <v>1.37</v>
@@ -3881,7 +3884,7 @@
         <v>91</v>
       </c>
       <c r="P16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q16">
         <v>2.1</v>
@@ -3959,7 +3962,7 @@
         <v>3</v>
       </c>
       <c r="AP16">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ16">
         <v>1.33</v>
@@ -4087,7 +4090,7 @@
         <v>81</v>
       </c>
       <c r="P17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q17">
         <v>2.38</v>
@@ -4293,7 +4296,7 @@
         <v>81</v>
       </c>
       <c r="P18" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Q18">
         <v>3.4</v>
@@ -4911,7 +4914,7 @@
         <v>94</v>
       </c>
       <c r="P21" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q21">
         <v>1.91</v>
@@ -5323,7 +5326,7 @@
         <v>81</v>
       </c>
       <c r="P23" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q23">
         <v>5.5</v>
@@ -5529,7 +5532,7 @@
         <v>96</v>
       </c>
       <c r="P24" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q24">
         <v>3.1</v>
@@ -5607,7 +5610,7 @@
         <v>3</v>
       </c>
       <c r="AP24">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ24">
         <v>3</v>
@@ -5735,7 +5738,7 @@
         <v>97</v>
       </c>
       <c r="P25" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q25">
         <v>2.38</v>
@@ -5816,7 +5819,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ25">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AR25">
         <v>0.71</v>
@@ -5941,7 +5944,7 @@
         <v>98</v>
       </c>
       <c r="P26" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q26">
         <v>3.1</v>
@@ -6353,7 +6356,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q28">
         <v>1.3</v>
@@ -6559,7 +6562,7 @@
         <v>101</v>
       </c>
       <c r="P29" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q29">
         <v>5</v>
@@ -6715,6 +6718,212 @@
         <v>0</v>
       </c>
       <c r="BP29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:68">
+      <c r="A30" s="1">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>7828486</v>
+      </c>
+      <c r="C30" t="s">
+        <v>68</v>
+      </c>
+      <c r="D30" t="s">
+        <v>69</v>
+      </c>
+      <c r="E30" s="2">
+        <v>45756.5</v>
+      </c>
+      <c r="F30">
+        <v>6</v>
+      </c>
+      <c r="G30" t="s">
+        <v>79</v>
+      </c>
+      <c r="H30" t="s">
+        <v>77</v>
+      </c>
+      <c r="I30">
+        <v>3</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>3</v>
+      </c>
+      <c r="L30">
+        <v>3</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30">
+        <v>3</v>
+      </c>
+      <c r="O30" t="s">
+        <v>102</v>
+      </c>
+      <c r="P30" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q30">
+        <v>1.8</v>
+      </c>
+      <c r="R30">
+        <v>2.75</v>
+      </c>
+      <c r="S30">
+        <v>5.8</v>
+      </c>
+      <c r="T30">
+        <v>1.22</v>
+      </c>
+      <c r="U30">
+        <v>3.8</v>
+      </c>
+      <c r="V30">
+        <v>2.1</v>
+      </c>
+      <c r="W30">
+        <v>1.7</v>
+      </c>
+      <c r="X30">
+        <v>4.33</v>
+      </c>
+      <c r="Y30">
+        <v>1.18</v>
+      </c>
+      <c r="Z30">
+        <v>1.4</v>
+      </c>
+      <c r="AA30">
+        <v>4.6</v>
+      </c>
+      <c r="AB30">
+        <v>6</v>
+      </c>
+      <c r="AC30">
+        <v>1.02</v>
+      </c>
+      <c r="AD30">
+        <v>10</v>
+      </c>
+      <c r="AE30">
+        <v>1.09</v>
+      </c>
+      <c r="AF30">
+        <v>6.25</v>
+      </c>
+      <c r="AG30">
+        <v>1.42</v>
+      </c>
+      <c r="AH30">
+        <v>2.62</v>
+      </c>
+      <c r="AI30">
+        <v>1.6</v>
+      </c>
+      <c r="AJ30">
+        <v>2.1</v>
+      </c>
+      <c r="AK30">
+        <v>1.12</v>
+      </c>
+      <c r="AL30">
+        <v>1.19</v>
+      </c>
+      <c r="AM30">
+        <v>2.85</v>
+      </c>
+      <c r="AN30">
+        <v>0.5</v>
+      </c>
+      <c r="AO30">
+        <v>1.33</v>
+      </c>
+      <c r="AP30">
+        <v>1.33</v>
+      </c>
+      <c r="AQ30">
+        <v>1</v>
+      </c>
+      <c r="AR30">
+        <v>2.7</v>
+      </c>
+      <c r="AS30">
+        <v>1.3</v>
+      </c>
+      <c r="AT30">
+        <v>4</v>
+      </c>
+      <c r="AU30">
+        <v>5</v>
+      </c>
+      <c r="AV30">
+        <v>3</v>
+      </c>
+      <c r="AW30">
+        <v>7</v>
+      </c>
+      <c r="AX30">
+        <v>5</v>
+      </c>
+      <c r="AY30">
+        <v>12</v>
+      </c>
+      <c r="AZ30">
+        <v>8</v>
+      </c>
+      <c r="BA30">
+        <v>3</v>
+      </c>
+      <c r="BB30">
+        <v>4</v>
+      </c>
+      <c r="BC30">
+        <v>7</v>
+      </c>
+      <c r="BD30">
+        <v>0</v>
+      </c>
+      <c r="BE30">
+        <v>0</v>
+      </c>
+      <c r="BF30">
+        <v>0</v>
+      </c>
+      <c r="BG30">
+        <v>0</v>
+      </c>
+      <c r="BH30">
+        <v>0</v>
+      </c>
+      <c r="BI30">
+        <v>0</v>
+      </c>
+      <c r="BJ30">
+        <v>0</v>
+      </c>
+      <c r="BK30">
+        <v>0</v>
+      </c>
+      <c r="BL30">
+        <v>0</v>
+      </c>
+      <c r="BM30">
+        <v>0</v>
+      </c>
+      <c r="BN30">
+        <v>0</v>
+      </c>
+      <c r="BO30">
+        <v>0</v>
+      </c>
+      <c r="BP30">
         <v>0</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="124">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -323,6 +323,9 @@
   </si>
   <si>
     <t>['4', '9', '16']</t>
+  </si>
+  <si>
+    <t>['5']</t>
   </si>
   <si>
     <t>['34', '59', '86']</t>
@@ -744,7 +747,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP30"/>
+  <dimension ref="A1:BP31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1206,7 +1209,7 @@
         <v>81</v>
       </c>
       <c r="P3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -1412,7 +1415,7 @@
         <v>82</v>
       </c>
       <c r="P4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -1618,7 +1621,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q5">
         <v>7</v>
@@ -1824,7 +1827,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2030,7 +2033,7 @@
         <v>81</v>
       </c>
       <c r="P7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q7">
         <v>1.83</v>
@@ -2111,7 +2114,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR7">
         <v>1.43</v>
@@ -2236,7 +2239,7 @@
         <v>85</v>
       </c>
       <c r="P8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q8">
         <v>8.5</v>
@@ -2442,7 +2445,7 @@
         <v>81</v>
       </c>
       <c r="P9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -3060,7 +3063,7 @@
         <v>88</v>
       </c>
       <c r="P12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q12">
         <v>8</v>
@@ -3472,7 +3475,7 @@
         <v>81</v>
       </c>
       <c r="P14" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q14">
         <v>5.5</v>
@@ -3678,7 +3681,7 @@
         <v>90</v>
       </c>
       <c r="P15" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q15">
         <v>2.5</v>
@@ -3884,7 +3887,7 @@
         <v>91</v>
       </c>
       <c r="P16" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q16">
         <v>2.1</v>
@@ -4090,7 +4093,7 @@
         <v>81</v>
       </c>
       <c r="P17" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Q17">
         <v>2.38</v>
@@ -4171,7 +4174,7 @@
         <v>0</v>
       </c>
       <c r="AQ17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR17">
         <v>1.11</v>
@@ -4296,7 +4299,7 @@
         <v>81</v>
       </c>
       <c r="P18" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q18">
         <v>3.4</v>
@@ -4914,7 +4917,7 @@
         <v>94</v>
       </c>
       <c r="P21" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q21">
         <v>1.91</v>
@@ -5326,7 +5329,7 @@
         <v>81</v>
       </c>
       <c r="P23" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q23">
         <v>5.5</v>
@@ -5532,7 +5535,7 @@
         <v>96</v>
       </c>
       <c r="P24" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q24">
         <v>3.1</v>
@@ -5738,7 +5741,7 @@
         <v>97</v>
       </c>
       <c r="P25" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q25">
         <v>2.38</v>
@@ -5944,7 +5947,7 @@
         <v>98</v>
       </c>
       <c r="P26" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q26">
         <v>3.1</v>
@@ -6356,7 +6359,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q28">
         <v>1.3</v>
@@ -6562,7 +6565,7 @@
         <v>101</v>
       </c>
       <c r="P29" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q29">
         <v>5</v>
@@ -6924,6 +6927,212 @@
         <v>0</v>
       </c>
       <c r="BP30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:68">
+      <c r="A31" s="1">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>7828487</v>
+      </c>
+      <c r="C31" t="s">
+        <v>68</v>
+      </c>
+      <c r="D31" t="s">
+        <v>69</v>
+      </c>
+      <c r="E31" s="2">
+        <v>45756.54166666666</v>
+      </c>
+      <c r="F31">
+        <v>6</v>
+      </c>
+      <c r="G31" t="s">
+        <v>78</v>
+      </c>
+      <c r="H31" t="s">
+        <v>71</v>
+      </c>
+      <c r="I31">
+        <v>1</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>1</v>
+      </c>
+      <c r="L31">
+        <v>1</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31">
+        <v>1</v>
+      </c>
+      <c r="O31" t="s">
+        <v>103</v>
+      </c>
+      <c r="P31" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q31">
+        <v>1.68</v>
+      </c>
+      <c r="R31">
+        <v>2.49</v>
+      </c>
+      <c r="S31">
+        <v>6.5</v>
+      </c>
+      <c r="T31">
+        <v>1.2</v>
+      </c>
+      <c r="U31">
+        <v>3.8</v>
+      </c>
+      <c r="V31">
+        <v>2.3</v>
+      </c>
+      <c r="W31">
+        <v>1.6</v>
+      </c>
+      <c r="X31">
+        <v>4.4</v>
+      </c>
+      <c r="Y31">
+        <v>1.15</v>
+      </c>
+      <c r="Z31">
+        <v>1.29</v>
+      </c>
+      <c r="AA31">
+        <v>5</v>
+      </c>
+      <c r="AB31">
+        <v>7.8</v>
+      </c>
+      <c r="AC31">
+        <v>1.03</v>
+      </c>
+      <c r="AD31">
+        <v>14</v>
+      </c>
+      <c r="AE31">
+        <v>1.13</v>
+      </c>
+      <c r="AF31">
+        <v>4.75</v>
+      </c>
+      <c r="AG31">
+        <v>1.55</v>
+      </c>
+      <c r="AH31">
+        <v>2.32</v>
+      </c>
+      <c r="AI31">
+        <v>2</v>
+      </c>
+      <c r="AJ31">
+        <v>1.73</v>
+      </c>
+      <c r="AK31">
+        <v>1.15</v>
+      </c>
+      <c r="AL31">
+        <v>1.19</v>
+      </c>
+      <c r="AM31">
+        <v>3.4</v>
+      </c>
+      <c r="AN31">
+        <v>3</v>
+      </c>
+      <c r="AO31">
+        <v>3</v>
+      </c>
+      <c r="AP31">
+        <v>3</v>
+      </c>
+      <c r="AQ31">
+        <v>2</v>
+      </c>
+      <c r="AR31">
+        <v>2.69</v>
+      </c>
+      <c r="AS31">
+        <v>1.67</v>
+      </c>
+      <c r="AT31">
+        <v>4.36</v>
+      </c>
+      <c r="AU31">
+        <v>5</v>
+      </c>
+      <c r="AV31">
+        <v>2</v>
+      </c>
+      <c r="AW31">
+        <v>6</v>
+      </c>
+      <c r="AX31">
+        <v>8</v>
+      </c>
+      <c r="AY31">
+        <v>11</v>
+      </c>
+      <c r="AZ31">
+        <v>10</v>
+      </c>
+      <c r="BA31">
+        <v>5</v>
+      </c>
+      <c r="BB31">
+        <v>3</v>
+      </c>
+      <c r="BC31">
+        <v>8</v>
+      </c>
+      <c r="BD31">
+        <v>0</v>
+      </c>
+      <c r="BE31">
+        <v>0</v>
+      </c>
+      <c r="BF31">
+        <v>0</v>
+      </c>
+      <c r="BG31">
+        <v>0</v>
+      </c>
+      <c r="BH31">
+        <v>0</v>
+      </c>
+      <c r="BI31">
+        <v>0</v>
+      </c>
+      <c r="BJ31">
+        <v>0</v>
+      </c>
+      <c r="BK31">
+        <v>0</v>
+      </c>
+      <c r="BL31">
+        <v>0</v>
+      </c>
+      <c r="BM31">
+        <v>0</v>
+      </c>
+      <c r="BN31">
+        <v>0</v>
+      </c>
+      <c r="BO31">
+        <v>0</v>
+      </c>
+      <c r="BP31">
         <v>0</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="192">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -427,6 +427,9 @@
     <t>['26', '59']</t>
   </si>
   <si>
+    <t>['36', '44']</t>
+  </si>
+  <si>
     <t>['34', '59', '86']</t>
   </si>
   <si>
@@ -581,6 +584,12 @@
   </si>
   <si>
     <t>['24']</t>
+  </si>
+  <si>
+    <t>['90+4']</t>
+  </si>
+  <si>
+    <t>['3', '41', '69']</t>
   </si>
 </sst>
 </file>
@@ -942,7 +951,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP76"/>
+  <dimension ref="A1:BP78"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1279,7 +1288,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ2">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1404,7 +1413,7 @@
         <v>81</v>
       </c>
       <c r="P3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -1610,7 +1619,7 @@
         <v>82</v>
       </c>
       <c r="P4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -1816,7 +1825,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q5">
         <v>7</v>
@@ -2022,7 +2031,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2100,7 +2109,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AQ6">
         <v>0.5</v>
@@ -2228,7 +2237,7 @@
         <v>81</v>
       </c>
       <c r="P7" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q7">
         <v>1.83</v>
@@ -2309,7 +2318,7 @@
         <v>2</v>
       </c>
       <c r="AQ7">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AR7">
         <v>1.43</v>
@@ -2434,7 +2443,7 @@
         <v>85</v>
       </c>
       <c r="P8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q8">
         <v>8.5</v>
@@ -2512,7 +2521,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="AQ8">
         <v>1.88</v>
@@ -2640,7 +2649,7 @@
         <v>81</v>
       </c>
       <c r="P9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -3258,7 +3267,7 @@
         <v>88</v>
       </c>
       <c r="P12" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q12">
         <v>8</v>
@@ -3670,7 +3679,7 @@
         <v>81</v>
       </c>
       <c r="P14" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q14">
         <v>5.5</v>
@@ -3748,7 +3757,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AQ14">
         <v>2.71</v>
@@ -3876,7 +3885,7 @@
         <v>90</v>
       </c>
       <c r="P15" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q15">
         <v>2.5</v>
@@ -3957,7 +3966,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ15">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR15">
         <v>1.37</v>
@@ -4082,7 +4091,7 @@
         <v>91</v>
       </c>
       <c r="P16" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q16">
         <v>2.1</v>
@@ -4288,7 +4297,7 @@
         <v>81</v>
       </c>
       <c r="P17" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q17">
         <v>2.38</v>
@@ -4366,10 +4375,10 @@
         <v>3</v>
       </c>
       <c r="AP17">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="AQ17">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AR17">
         <v>1.11</v>
@@ -4494,7 +4503,7 @@
         <v>81</v>
       </c>
       <c r="P18" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q18">
         <v>3.4</v>
@@ -5112,7 +5121,7 @@
         <v>94</v>
       </c>
       <c r="P21" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q21">
         <v>1.91</v>
@@ -5524,7 +5533,7 @@
         <v>81</v>
       </c>
       <c r="P23" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q23">
         <v>5.5</v>
@@ -5730,7 +5739,7 @@
         <v>96</v>
       </c>
       <c r="P24" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q24">
         <v>3.1</v>
@@ -5936,7 +5945,7 @@
         <v>97</v>
       </c>
       <c r="P25" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q25">
         <v>2.38</v>
@@ -6017,7 +6026,7 @@
         <v>1</v>
       </c>
       <c r="AQ25">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR25">
         <v>0.71</v>
@@ -6142,7 +6151,7 @@
         <v>98</v>
       </c>
       <c r="P26" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q26">
         <v>3.1</v>
@@ -6220,7 +6229,7 @@
         <v>1.5</v>
       </c>
       <c r="AP26">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AQ26">
         <v>0.5</v>
@@ -6554,7 +6563,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q28">
         <v>1.3</v>
@@ -6760,7 +6769,7 @@
         <v>101</v>
       </c>
       <c r="P29" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q29">
         <v>5</v>
@@ -6838,7 +6847,7 @@
         <v>3</v>
       </c>
       <c r="AP29">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="AQ29">
         <v>2.71</v>
@@ -7047,7 +7056,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ30">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR30">
         <v>2.7</v>
@@ -7253,7 +7262,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ31">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AR31">
         <v>2.69</v>
@@ -7378,7 +7387,7 @@
         <v>81</v>
       </c>
       <c r="P32" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q32">
         <v>6</v>
@@ -7584,7 +7593,7 @@
         <v>104</v>
       </c>
       <c r="P33" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q33">
         <v>8.449999999999999</v>
@@ -7996,7 +8005,7 @@
         <v>105</v>
       </c>
       <c r="P35" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q35">
         <v>2.2</v>
@@ -8202,7 +8211,7 @@
         <v>106</v>
       </c>
       <c r="P36" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q36">
         <v>4.25</v>
@@ -8280,7 +8289,7 @@
         <v>2</v>
       </c>
       <c r="AP36">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="AQ36">
         <v>2.29</v>
@@ -8695,7 +8704,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ38">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AR38">
         <v>1.47</v>
@@ -8820,7 +8829,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q39">
         <v>3.2</v>
@@ -9026,7 +9035,7 @@
         <v>81</v>
       </c>
       <c r="P40" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q40">
         <v>12</v>
@@ -9104,7 +9113,7 @@
         <v>3</v>
       </c>
       <c r="AP40">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AQ40">
         <v>1.88</v>
@@ -9232,7 +9241,7 @@
         <v>110</v>
       </c>
       <c r="P41" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q41">
         <v>3.77</v>
@@ -9516,7 +9525,7 @@
         <v>0.75</v>
       </c>
       <c r="AP42">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="AQ42">
         <v>0.5</v>
@@ -9644,7 +9653,7 @@
         <v>112</v>
       </c>
       <c r="P43" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q43">
         <v>1.35</v>
@@ -9850,7 +9859,7 @@
         <v>113</v>
       </c>
       <c r="P44" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q44">
         <v>1.66</v>
@@ -9931,7 +9940,7 @@
         <v>2</v>
       </c>
       <c r="AQ44">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR44">
         <v>1.77</v>
@@ -10056,7 +10065,7 @@
         <v>114</v>
       </c>
       <c r="P45" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q45">
         <v>4.75</v>
@@ -10262,7 +10271,7 @@
         <v>115</v>
       </c>
       <c r="P46" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q46">
         <v>5.2</v>
@@ -10468,7 +10477,7 @@
         <v>81</v>
       </c>
       <c r="P47" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q47">
         <v>2.35</v>
@@ -10549,7 +10558,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ47">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AR47">
         <v>1.51</v>
@@ -10752,7 +10761,7 @@
         <v>1.5</v>
       </c>
       <c r="AP48">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AQ48">
         <v>1.29</v>
@@ -11086,7 +11095,7 @@
         <v>117</v>
       </c>
       <c r="P50" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q50">
         <v>2.62</v>
@@ -11292,7 +11301,7 @@
         <v>118</v>
       </c>
       <c r="P51" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q51">
         <v>4.55</v>
@@ -11498,7 +11507,7 @@
         <v>81</v>
       </c>
       <c r="P52" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q52">
         <v>6.5</v>
@@ -11704,7 +11713,7 @@
         <v>119</v>
       </c>
       <c r="P53" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q53">
         <v>3.35</v>
@@ -11782,10 +11791,10 @@
         <v>0.8</v>
       </c>
       <c r="AP53">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AQ53">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR53">
         <v>1.56</v>
@@ -12322,7 +12331,7 @@
         <v>122</v>
       </c>
       <c r="P56" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q56">
         <v>1.56</v>
@@ -12528,7 +12537,7 @@
         <v>81</v>
       </c>
       <c r="P57" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q57">
         <v>5.25</v>
@@ -12940,7 +12949,7 @@
         <v>81</v>
       </c>
       <c r="P59" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -13018,7 +13027,7 @@
         <v>2</v>
       </c>
       <c r="AP59">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="AQ59">
         <v>2.25</v>
@@ -13146,7 +13155,7 @@
         <v>124</v>
       </c>
       <c r="P60" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q60">
         <v>2.25</v>
@@ -13352,7 +13361,7 @@
         <v>125</v>
       </c>
       <c r="P61" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q61">
         <v>2.27</v>
@@ -13433,7 +13442,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ61">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AR61">
         <v>1.64</v>
@@ -13558,7 +13567,7 @@
         <v>126</v>
       </c>
       <c r="P62" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q62">
         <v>2.4</v>
@@ -13764,7 +13773,7 @@
         <v>127</v>
       </c>
       <c r="P63" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q63">
         <v>1.64</v>
@@ -13845,7 +13854,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ63">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR63">
         <v>2.27</v>
@@ -14382,7 +14391,7 @@
         <v>130</v>
       </c>
       <c r="P66" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q66">
         <v>4.35</v>
@@ -14460,7 +14469,7 @@
         <v>2</v>
       </c>
       <c r="AP66">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AQ66">
         <v>2.29</v>
@@ -14666,7 +14675,7 @@
         <v>0.17</v>
       </c>
       <c r="AP67">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="AQ67">
         <v>0.14</v>
@@ -14794,7 +14803,7 @@
         <v>132</v>
       </c>
       <c r="P68" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q68">
         <v>9</v>
@@ -15000,7 +15009,7 @@
         <v>133</v>
       </c>
       <c r="P69" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q69">
         <v>1.91</v>
@@ -15081,7 +15090,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ69">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR69">
         <v>1.66</v>
@@ -15206,7 +15215,7 @@
         <v>81</v>
       </c>
       <c r="P70" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q70">
         <v>2.35</v>
@@ -15412,7 +15421,7 @@
         <v>134</v>
       </c>
       <c r="P71" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q71">
         <v>1.55</v>
@@ -15493,7 +15502,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ71">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AR71">
         <v>2.37</v>
@@ -15618,7 +15627,7 @@
         <v>135</v>
       </c>
       <c r="P72" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q72">
         <v>1.46</v>
@@ -15824,7 +15833,7 @@
         <v>81</v>
       </c>
       <c r="P73" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q73">
         <v>8.5</v>
@@ -16030,7 +16039,7 @@
         <v>81</v>
       </c>
       <c r="P74" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q74">
         <v>2.2</v>
@@ -16236,7 +16245,7 @@
         <v>136</v>
       </c>
       <c r="P75" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q75">
         <v>2.3</v>
@@ -16442,7 +16451,7 @@
         <v>81</v>
       </c>
       <c r="P76" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q76">
         <v>8.949999999999999</v>
@@ -16520,7 +16529,7 @@
         <v>2.14</v>
       </c>
       <c r="AP76">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AQ76">
         <v>2.25</v>
@@ -16599,6 +16608,418 @@
       </c>
       <c r="BP76">
         <v>1.8</v>
+      </c>
+    </row>
+    <row r="77" spans="1:68">
+      <c r="A77" s="1">
+        <v>76</v>
+      </c>
+      <c r="B77">
+        <v>7828533</v>
+      </c>
+      <c r="C77" t="s">
+        <v>68</v>
+      </c>
+      <c r="D77" t="s">
+        <v>69</v>
+      </c>
+      <c r="E77" s="2">
+        <v>45821.54166666666</v>
+      </c>
+      <c r="F77">
+        <v>0</v>
+      </c>
+      <c r="G77" t="s">
+        <v>75</v>
+      </c>
+      <c r="H77" t="s">
+        <v>77</v>
+      </c>
+      <c r="I77">
+        <v>2</v>
+      </c>
+      <c r="J77">
+        <v>0</v>
+      </c>
+      <c r="K77">
+        <v>2</v>
+      </c>
+      <c r="L77">
+        <v>2</v>
+      </c>
+      <c r="M77">
+        <v>1</v>
+      </c>
+      <c r="N77">
+        <v>3</v>
+      </c>
+      <c r="O77" t="s">
+        <v>137</v>
+      </c>
+      <c r="P77" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q77">
+        <v>2.94</v>
+      </c>
+      <c r="R77">
+        <v>2.26</v>
+      </c>
+      <c r="S77">
+        <v>3.1</v>
+      </c>
+      <c r="T77">
+        <v>1.29</v>
+      </c>
+      <c r="U77">
+        <v>3.3</v>
+      </c>
+      <c r="V77">
+        <v>2.15</v>
+      </c>
+      <c r="W77">
+        <v>1.6</v>
+      </c>
+      <c r="X77">
+        <v>5.3</v>
+      </c>
+      <c r="Y77">
+        <v>1.1</v>
+      </c>
+      <c r="Z77">
+        <v>2.4</v>
+      </c>
+      <c r="AA77">
+        <v>3.45</v>
+      </c>
+      <c r="AB77">
+        <v>2.42</v>
+      </c>
+      <c r="AC77">
+        <v>1.03</v>
+      </c>
+      <c r="AD77">
+        <v>15</v>
+      </c>
+      <c r="AE77">
+        <v>1.13</v>
+      </c>
+      <c r="AF77">
+        <v>4.75</v>
+      </c>
+      <c r="AG77">
+        <v>1.55</v>
+      </c>
+      <c r="AH77">
+        <v>2.3</v>
+      </c>
+      <c r="AI77">
+        <v>1.5</v>
+      </c>
+      <c r="AJ77">
+        <v>2.4</v>
+      </c>
+      <c r="AK77">
+        <v>1.3</v>
+      </c>
+      <c r="AL77">
+        <v>1.22</v>
+      </c>
+      <c r="AM77">
+        <v>1.5</v>
+      </c>
+      <c r="AN77">
+        <v>0.86</v>
+      </c>
+      <c r="AO77">
+        <v>1</v>
+      </c>
+      <c r="AP77">
+        <v>1.13</v>
+      </c>
+      <c r="AQ77">
+        <v>0.89</v>
+      </c>
+      <c r="AR77">
+        <v>1.36</v>
+      </c>
+      <c r="AS77">
+        <v>1.27</v>
+      </c>
+      <c r="AT77">
+        <v>2.63</v>
+      </c>
+      <c r="AU77">
+        <v>11</v>
+      </c>
+      <c r="AV77">
+        <v>11</v>
+      </c>
+      <c r="AW77">
+        <v>9</v>
+      </c>
+      <c r="AX77">
+        <v>7</v>
+      </c>
+      <c r="AY77">
+        <v>20</v>
+      </c>
+      <c r="AZ77">
+        <v>18</v>
+      </c>
+      <c r="BA77">
+        <v>6</v>
+      </c>
+      <c r="BB77">
+        <v>3</v>
+      </c>
+      <c r="BC77">
+        <v>9</v>
+      </c>
+      <c r="BD77">
+        <v>0</v>
+      </c>
+      <c r="BE77">
+        <v>0</v>
+      </c>
+      <c r="BF77">
+        <v>0</v>
+      </c>
+      <c r="BG77">
+        <v>0</v>
+      </c>
+      <c r="BH77">
+        <v>0</v>
+      </c>
+      <c r="BI77">
+        <v>0</v>
+      </c>
+      <c r="BJ77">
+        <v>0</v>
+      </c>
+      <c r="BK77">
+        <v>0</v>
+      </c>
+      <c r="BL77">
+        <v>0</v>
+      </c>
+      <c r="BM77">
+        <v>0</v>
+      </c>
+      <c r="BN77">
+        <v>0</v>
+      </c>
+      <c r="BO77">
+        <v>0</v>
+      </c>
+      <c r="BP77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:68">
+      <c r="A78" s="1">
+        <v>77</v>
+      </c>
+      <c r="B78">
+        <v>7828534</v>
+      </c>
+      <c r="C78" t="s">
+        <v>68</v>
+      </c>
+      <c r="D78" t="s">
+        <v>69</v>
+      </c>
+      <c r="E78" s="2">
+        <v>45822.35416666666</v>
+      </c>
+      <c r="F78">
+        <v>0</v>
+      </c>
+      <c r="G78" t="s">
+        <v>74</v>
+      </c>
+      <c r="H78" t="s">
+        <v>71</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>2</v>
+      </c>
+      <c r="K78">
+        <v>2</v>
+      </c>
+      <c r="L78">
+        <v>0</v>
+      </c>
+      <c r="M78">
+        <v>3</v>
+      </c>
+      <c r="N78">
+        <v>3</v>
+      </c>
+      <c r="O78" t="s">
+        <v>81</v>
+      </c>
+      <c r="P78" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q78">
+        <v>4.83</v>
+      </c>
+      <c r="R78">
+        <v>2.28</v>
+      </c>
+      <c r="S78">
+        <v>2.06</v>
+      </c>
+      <c r="T78">
+        <v>1.3</v>
+      </c>
+      <c r="U78">
+        <v>3.3</v>
+      </c>
+      <c r="V78">
+        <v>2.45</v>
+      </c>
+      <c r="W78">
+        <v>1.5</v>
+      </c>
+      <c r="X78">
+        <v>5</v>
+      </c>
+      <c r="Y78">
+        <v>1.12</v>
+      </c>
+      <c r="Z78">
+        <v>4.4</v>
+      </c>
+      <c r="AA78">
+        <v>3.75</v>
+      </c>
+      <c r="AB78">
+        <v>1.61</v>
+      </c>
+      <c r="AC78">
+        <v>1</v>
+      </c>
+      <c r="AD78">
+        <v>13</v>
+      </c>
+      <c r="AE78">
+        <v>1.2</v>
+      </c>
+      <c r="AF78">
+        <v>4.4</v>
+      </c>
+      <c r="AG78">
+        <v>1.65</v>
+      </c>
+      <c r="AH78">
+        <v>2.25</v>
+      </c>
+      <c r="AI78">
+        <v>1.62</v>
+      </c>
+      <c r="AJ78">
+        <v>2.2</v>
+      </c>
+      <c r="AK78">
+        <v>1.24</v>
+      </c>
+      <c r="AL78">
+        <v>1.21</v>
+      </c>
+      <c r="AM78">
+        <v>1.19</v>
+      </c>
+      <c r="AN78">
+        <v>0.75</v>
+      </c>
+      <c r="AO78">
+        <v>1.43</v>
+      </c>
+      <c r="AP78">
+        <v>0.67</v>
+      </c>
+      <c r="AQ78">
+        <v>1.63</v>
+      </c>
+      <c r="AR78">
+        <v>1.49</v>
+      </c>
+      <c r="AS78">
+        <v>1.4</v>
+      </c>
+      <c r="AT78">
+        <v>2.89</v>
+      </c>
+      <c r="AU78">
+        <v>5</v>
+      </c>
+      <c r="AV78">
+        <v>10</v>
+      </c>
+      <c r="AW78">
+        <v>8</v>
+      </c>
+      <c r="AX78">
+        <v>10</v>
+      </c>
+      <c r="AY78">
+        <v>13</v>
+      </c>
+      <c r="AZ78">
+        <v>20</v>
+      </c>
+      <c r="BA78">
+        <v>1</v>
+      </c>
+      <c r="BB78">
+        <v>7</v>
+      </c>
+      <c r="BC78">
+        <v>8</v>
+      </c>
+      <c r="BD78">
+        <v>0</v>
+      </c>
+      <c r="BE78">
+        <v>0</v>
+      </c>
+      <c r="BF78">
+        <v>0</v>
+      </c>
+      <c r="BG78">
+        <v>0</v>
+      </c>
+      <c r="BH78">
+        <v>0</v>
+      </c>
+      <c r="BI78">
+        <v>0</v>
+      </c>
+      <c r="BJ78">
+        <v>0</v>
+      </c>
+      <c r="BK78">
+        <v>0</v>
+      </c>
+      <c r="BL78">
+        <v>0</v>
+      </c>
+      <c r="BM78">
+        <v>0</v>
+      </c>
+      <c r="BN78">
+        <v>0</v>
+      </c>
+      <c r="BO78">
+        <v>0</v>
+      </c>
+      <c r="BP78">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="195">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -430,6 +430,9 @@
     <t>['36', '44']</t>
   </si>
   <si>
+    <t>['53']</t>
+  </si>
+  <si>
     <t>['34', '59', '86']</t>
   </si>
   <si>
@@ -590,6 +593,12 @@
   </si>
   <si>
     <t>['3', '41', '69']</t>
+  </si>
+  <si>
+    <t>['45+5', '59']</t>
+  </si>
+  <si>
+    <t>['22', '31']</t>
   </si>
 </sst>
 </file>
@@ -951,7 +960,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP78"/>
+  <dimension ref="A1:BP80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1413,7 +1422,7 @@
         <v>81</v>
       </c>
       <c r="P3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -1619,7 +1628,7 @@
         <v>82</v>
       </c>
       <c r="P4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -1825,7 +1834,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q5">
         <v>7</v>
@@ -1903,7 +1912,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ5">
         <v>1.29</v>
@@ -2031,7 +2040,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2237,7 +2246,7 @@
         <v>81</v>
       </c>
       <c r="P7" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q7">
         <v>1.83</v>
@@ -2443,7 +2452,7 @@
         <v>85</v>
       </c>
       <c r="P8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q8">
         <v>8.5</v>
@@ -2524,7 +2533,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ8">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2649,7 +2658,7 @@
         <v>81</v>
       </c>
       <c r="P9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -3139,7 +3148,7 @@
         <v>3</v>
       </c>
       <c r="AP11">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AQ11">
         <v>2.25</v>
@@ -3267,7 +3276,7 @@
         <v>88</v>
       </c>
       <c r="P12" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q12">
         <v>8</v>
@@ -3348,7 +3357,7 @@
         <v>1</v>
       </c>
       <c r="AQ12">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AR12">
         <v>0.79</v>
@@ -3679,7 +3688,7 @@
         <v>81</v>
       </c>
       <c r="P14" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q14">
         <v>5.5</v>
@@ -3760,7 +3769,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ14">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AR14">
         <v>1.42</v>
@@ -3885,7 +3894,7 @@
         <v>90</v>
       </c>
       <c r="P15" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q15">
         <v>2.5</v>
@@ -3963,7 +3972,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ15">
         <v>0.89</v>
@@ -4091,7 +4100,7 @@
         <v>91</v>
       </c>
       <c r="P16" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q16">
         <v>2.1</v>
@@ -4297,7 +4306,7 @@
         <v>81</v>
       </c>
       <c r="P17" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q17">
         <v>2.38</v>
@@ -4503,7 +4512,7 @@
         <v>81</v>
       </c>
       <c r="P18" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q18">
         <v>3.4</v>
@@ -4993,7 +5002,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AQ20">
         <v>0.14</v>
@@ -5121,7 +5130,7 @@
         <v>94</v>
       </c>
       <c r="P21" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q21">
         <v>1.91</v>
@@ -5405,7 +5414,7 @@
         <v>2</v>
       </c>
       <c r="AP22">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AQ22">
         <v>0.5</v>
@@ -5533,7 +5542,7 @@
         <v>81</v>
       </c>
       <c r="P23" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q23">
         <v>5.5</v>
@@ -5614,7 +5623,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ23">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AR23">
         <v>1.34</v>
@@ -5739,7 +5748,7 @@
         <v>96</v>
       </c>
       <c r="P24" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q24">
         <v>3.1</v>
@@ -5820,7 +5829,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ24">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AR24">
         <v>3.56</v>
@@ -5945,7 +5954,7 @@
         <v>97</v>
       </c>
       <c r="P25" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q25">
         <v>2.38</v>
@@ -6151,7 +6160,7 @@
         <v>98</v>
       </c>
       <c r="P26" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q26">
         <v>3.1</v>
@@ -6563,7 +6572,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q28">
         <v>1.3</v>
@@ -6769,7 +6778,7 @@
         <v>101</v>
       </c>
       <c r="P29" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q29">
         <v>5</v>
@@ -6850,7 +6859,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ29">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AR29">
         <v>1.01</v>
@@ -7259,7 +7268,7 @@
         <v>3</v>
       </c>
       <c r="AP31">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AQ31">
         <v>1.63</v>
@@ -7387,7 +7396,7 @@
         <v>81</v>
       </c>
       <c r="P32" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q32">
         <v>6</v>
@@ -7465,7 +7474,7 @@
         <v>1</v>
       </c>
       <c r="AP32">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ32">
         <v>2.25</v>
@@ -7593,7 +7602,7 @@
         <v>104</v>
       </c>
       <c r="P33" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q33">
         <v>8.449999999999999</v>
@@ -7880,7 +7889,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ34">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AR34">
         <v>2.81</v>
@@ -8005,7 +8014,7 @@
         <v>105</v>
       </c>
       <c r="P35" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q35">
         <v>2.2</v>
@@ -8211,7 +8220,7 @@
         <v>106</v>
       </c>
       <c r="P36" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q36">
         <v>4.25</v>
@@ -8701,7 +8710,7 @@
         <v>2</v>
       </c>
       <c r="AP38">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ38">
         <v>1.63</v>
@@ -8829,7 +8838,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q39">
         <v>3.2</v>
@@ -9035,7 +9044,7 @@
         <v>81</v>
       </c>
       <c r="P40" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q40">
         <v>12</v>
@@ -9116,7 +9125,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ40">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AR40">
         <v>1.8</v>
@@ -9241,7 +9250,7 @@
         <v>110</v>
       </c>
       <c r="P41" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q41">
         <v>3.77</v>
@@ -9653,7 +9662,7 @@
         <v>112</v>
       </c>
       <c r="P43" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q43">
         <v>1.35</v>
@@ -9859,7 +9868,7 @@
         <v>113</v>
       </c>
       <c r="P44" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q44">
         <v>1.66</v>
@@ -10065,7 +10074,7 @@
         <v>114</v>
       </c>
       <c r="P45" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q45">
         <v>4.75</v>
@@ -10271,7 +10280,7 @@
         <v>115</v>
       </c>
       <c r="P46" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q46">
         <v>5.2</v>
@@ -10349,10 +10358,10 @@
         <v>3</v>
       </c>
       <c r="AP46">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AQ46">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AR46">
         <v>2.34</v>
@@ -10477,7 +10486,7 @@
         <v>81</v>
       </c>
       <c r="P47" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q47">
         <v>2.35</v>
@@ -11095,7 +11104,7 @@
         <v>117</v>
       </c>
       <c r="P50" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q50">
         <v>2.62</v>
@@ -11301,7 +11310,7 @@
         <v>118</v>
       </c>
       <c r="P51" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q51">
         <v>4.55</v>
@@ -11379,7 +11388,7 @@
         <v>2.5</v>
       </c>
       <c r="AP51">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ51">
         <v>2.29</v>
@@ -11507,7 +11516,7 @@
         <v>81</v>
       </c>
       <c r="P52" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q52">
         <v>6.5</v>
@@ -11588,7 +11597,7 @@
         <v>1</v>
       </c>
       <c r="AQ52">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AR52">
         <v>1.16</v>
@@ -11713,7 +11722,7 @@
         <v>119</v>
       </c>
       <c r="P53" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q53">
         <v>3.35</v>
@@ -12206,7 +12215,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ55">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AR55">
         <v>2.3</v>
@@ -12331,7 +12340,7 @@
         <v>122</v>
       </c>
       <c r="P56" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q56">
         <v>1.56</v>
@@ -12409,7 +12418,7 @@
         <v>0.6</v>
       </c>
       <c r="AP56">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AQ56">
         <v>0.5</v>
@@ -12537,7 +12546,7 @@
         <v>81</v>
       </c>
       <c r="P57" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q57">
         <v>5.25</v>
@@ -12618,7 +12627,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ57">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AR57">
         <v>1.43</v>
@@ -12821,7 +12830,7 @@
         <v>0.2</v>
       </c>
       <c r="AP58">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ58">
         <v>0.14</v>
@@ -12949,7 +12958,7 @@
         <v>81</v>
       </c>
       <c r="P59" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -13155,7 +13164,7 @@
         <v>124</v>
       </c>
       <c r="P60" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q60">
         <v>2.25</v>
@@ -13361,7 +13370,7 @@
         <v>125</v>
       </c>
       <c r="P61" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q61">
         <v>2.27</v>
@@ -13567,7 +13576,7 @@
         <v>126</v>
       </c>
       <c r="P62" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q62">
         <v>2.4</v>
@@ -13773,7 +13782,7 @@
         <v>127</v>
       </c>
       <c r="P63" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q63">
         <v>1.64</v>
@@ -13851,7 +13860,7 @@
         <v>1.17</v>
       </c>
       <c r="AP63">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AQ63">
         <v>0.89</v>
@@ -14060,7 +14069,7 @@
         <v>2</v>
       </c>
       <c r="AQ64">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AR64">
         <v>1.9</v>
@@ -14391,7 +14400,7 @@
         <v>130</v>
       </c>
       <c r="P66" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q66">
         <v>4.35</v>
@@ -14803,7 +14812,7 @@
         <v>132</v>
       </c>
       <c r="P68" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q68">
         <v>9</v>
@@ -14881,10 +14890,10 @@
         <v>2.67</v>
       </c>
       <c r="AP68">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ68">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AR68">
         <v>1.52</v>
@@ -15009,7 +15018,7 @@
         <v>133</v>
       </c>
       <c r="P69" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q69">
         <v>1.91</v>
@@ -15215,7 +15224,7 @@
         <v>81</v>
       </c>
       <c r="P70" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q70">
         <v>2.35</v>
@@ -15421,7 +15430,7 @@
         <v>134</v>
       </c>
       <c r="P71" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q71">
         <v>1.55</v>
@@ -15627,7 +15636,7 @@
         <v>135</v>
       </c>
       <c r="P72" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q72">
         <v>1.46</v>
@@ -15833,7 +15842,7 @@
         <v>81</v>
       </c>
       <c r="P73" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q73">
         <v>8.5</v>
@@ -15914,7 +15923,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ73">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AR73">
         <v>1.33</v>
@@ -16039,7 +16048,7 @@
         <v>81</v>
       </c>
       <c r="P74" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q74">
         <v>2.2</v>
@@ -16117,7 +16126,7 @@
         <v>2.17</v>
       </c>
       <c r="AP74">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AQ74">
         <v>2.29</v>
@@ -16245,7 +16254,7 @@
         <v>136</v>
       </c>
       <c r="P75" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q75">
         <v>2.3</v>
@@ -16451,7 +16460,7 @@
         <v>81</v>
       </c>
       <c r="P76" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q76">
         <v>8.949999999999999</v>
@@ -16657,7 +16666,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q77">
         <v>2.94</v>
@@ -16863,7 +16872,7 @@
         <v>81</v>
       </c>
       <c r="P78" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q78">
         <v>4.83</v>
@@ -17019,6 +17028,418 @@
         <v>0</v>
       </c>
       <c r="BP78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:68">
+      <c r="A79" s="1">
+        <v>78</v>
+      </c>
+      <c r="B79">
+        <v>7828535</v>
+      </c>
+      <c r="C79" t="s">
+        <v>68</v>
+      </c>
+      <c r="D79" t="s">
+        <v>69</v>
+      </c>
+      <c r="E79" s="2">
+        <v>45822.45833333334</v>
+      </c>
+      <c r="F79">
+        <v>0</v>
+      </c>
+      <c r="G79" t="s">
+        <v>73</v>
+      </c>
+      <c r="H79" t="s">
+        <v>70</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>1</v>
+      </c>
+      <c r="K79">
+        <v>1</v>
+      </c>
+      <c r="L79">
+        <v>1</v>
+      </c>
+      <c r="M79">
+        <v>2</v>
+      </c>
+      <c r="N79">
+        <v>3</v>
+      </c>
+      <c r="O79" t="s">
+        <v>138</v>
+      </c>
+      <c r="P79" t="s">
+        <v>193</v>
+      </c>
+      <c r="Q79">
+        <v>10</v>
+      </c>
+      <c r="R79">
+        <v>3.27</v>
+      </c>
+      <c r="S79">
+        <v>1.42</v>
+      </c>
+      <c r="T79">
+        <v>1.2</v>
+      </c>
+      <c r="U79">
+        <v>4.25</v>
+      </c>
+      <c r="V79">
+        <v>2.03</v>
+      </c>
+      <c r="W79">
+        <v>1.77</v>
+      </c>
+      <c r="X79">
+        <v>3.6</v>
+      </c>
+      <c r="Y79">
+        <v>1.22</v>
+      </c>
+      <c r="Z79">
+        <v>10</v>
+      </c>
+      <c r="AA79">
+        <v>6.5</v>
+      </c>
+      <c r="AB79">
+        <v>1.15</v>
+      </c>
+      <c r="AC79">
+        <v>1.01</v>
+      </c>
+      <c r="AD79">
+        <v>23</v>
+      </c>
+      <c r="AE79">
+        <v>1.09</v>
+      </c>
+      <c r="AF79">
+        <v>6.5</v>
+      </c>
+      <c r="AG79">
+        <v>1.33</v>
+      </c>
+      <c r="AH79">
+        <v>3.25</v>
+      </c>
+      <c r="AI79">
+        <v>1.88</v>
+      </c>
+      <c r="AJ79">
+        <v>1.73</v>
+      </c>
+      <c r="AK79">
+        <v>1.08</v>
+      </c>
+      <c r="AL79">
+        <v>1.04</v>
+      </c>
+      <c r="AM79">
+        <v>1.03</v>
+      </c>
+      <c r="AN79">
+        <v>1.29</v>
+      </c>
+      <c r="AO79">
+        <v>1.88</v>
+      </c>
+      <c r="AP79">
+        <v>1.13</v>
+      </c>
+      <c r="AQ79">
+        <v>2</v>
+      </c>
+      <c r="AR79">
+        <v>1.48</v>
+      </c>
+      <c r="AS79">
+        <v>2.33</v>
+      </c>
+      <c r="AT79">
+        <v>3.81</v>
+      </c>
+      <c r="AU79">
+        <v>9</v>
+      </c>
+      <c r="AV79">
+        <v>11</v>
+      </c>
+      <c r="AW79">
+        <v>5</v>
+      </c>
+      <c r="AX79">
+        <v>17</v>
+      </c>
+      <c r="AY79">
+        <v>14</v>
+      </c>
+      <c r="AZ79">
+        <v>28</v>
+      </c>
+      <c r="BA79">
+        <v>1</v>
+      </c>
+      <c r="BB79">
+        <v>8</v>
+      </c>
+      <c r="BC79">
+        <v>9</v>
+      </c>
+      <c r="BD79">
+        <v>0</v>
+      </c>
+      <c r="BE79">
+        <v>0</v>
+      </c>
+      <c r="BF79">
+        <v>0</v>
+      </c>
+      <c r="BG79">
+        <v>0</v>
+      </c>
+      <c r="BH79">
+        <v>0</v>
+      </c>
+      <c r="BI79">
+        <v>0</v>
+      </c>
+      <c r="BJ79">
+        <v>0</v>
+      </c>
+      <c r="BK79">
+        <v>0</v>
+      </c>
+      <c r="BL79">
+        <v>0</v>
+      </c>
+      <c r="BM79">
+        <v>0</v>
+      </c>
+      <c r="BN79">
+        <v>0</v>
+      </c>
+      <c r="BO79">
+        <v>0</v>
+      </c>
+      <c r="BP79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:68">
+      <c r="A80" s="1">
+        <v>79</v>
+      </c>
+      <c r="B80">
+        <v>7828536</v>
+      </c>
+      <c r="C80" t="s">
+        <v>68</v>
+      </c>
+      <c r="D80" t="s">
+        <v>69</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45823.35416666666</v>
+      </c>
+      <c r="F80">
+        <v>0</v>
+      </c>
+      <c r="G80" t="s">
+        <v>78</v>
+      </c>
+      <c r="H80" t="s">
+        <v>72</v>
+      </c>
+      <c r="I80">
+        <v>1</v>
+      </c>
+      <c r="J80">
+        <v>2</v>
+      </c>
+      <c r="K80">
+        <v>3</v>
+      </c>
+      <c r="L80">
+        <v>1</v>
+      </c>
+      <c r="M80">
+        <v>2</v>
+      </c>
+      <c r="N80">
+        <v>3</v>
+      </c>
+      <c r="O80" t="s">
+        <v>106</v>
+      </c>
+      <c r="P80" t="s">
+        <v>194</v>
+      </c>
+      <c r="Q80">
+        <v>4.33</v>
+      </c>
+      <c r="R80">
+        <v>2.08</v>
+      </c>
+      <c r="S80">
+        <v>2.05</v>
+      </c>
+      <c r="T80">
+        <v>1.32</v>
+      </c>
+      <c r="U80">
+        <v>2.88</v>
+      </c>
+      <c r="V80">
+        <v>2.7</v>
+      </c>
+      <c r="W80">
+        <v>1.38</v>
+      </c>
+      <c r="X80">
+        <v>7.2</v>
+      </c>
+      <c r="Y80">
+        <v>1.05</v>
+      </c>
+      <c r="Z80">
+        <v>3.8</v>
+      </c>
+      <c r="AA80">
+        <v>3.3</v>
+      </c>
+      <c r="AB80">
+        <v>1.86</v>
+      </c>
+      <c r="AC80">
+        <v>1.02</v>
+      </c>
+      <c r="AD80">
+        <v>10</v>
+      </c>
+      <c r="AE80">
+        <v>1.29</v>
+      </c>
+      <c r="AF80">
+        <v>3.4</v>
+      </c>
+      <c r="AG80">
+        <v>1.91</v>
+      </c>
+      <c r="AH80">
+        <v>1.83</v>
+      </c>
+      <c r="AI80">
+        <v>1.84</v>
+      </c>
+      <c r="AJ80">
+        <v>1.95</v>
+      </c>
+      <c r="AK80">
+        <v>1.96</v>
+      </c>
+      <c r="AL80">
+        <v>0</v>
+      </c>
+      <c r="AM80">
+        <v>1.12</v>
+      </c>
+      <c r="AN80">
+        <v>2.13</v>
+      </c>
+      <c r="AO80">
+        <v>2.71</v>
+      </c>
+      <c r="AP80">
+        <v>1.89</v>
+      </c>
+      <c r="AQ80">
+        <v>2.75</v>
+      </c>
+      <c r="AR80">
+        <v>2.07</v>
+      </c>
+      <c r="AS80">
+        <v>2.16</v>
+      </c>
+      <c r="AT80">
+        <v>4.23</v>
+      </c>
+      <c r="AU80">
+        <v>-1</v>
+      </c>
+      <c r="AV80">
+        <v>-1</v>
+      </c>
+      <c r="AW80">
+        <v>-1</v>
+      </c>
+      <c r="AX80">
+        <v>-1</v>
+      </c>
+      <c r="AY80">
+        <v>-1</v>
+      </c>
+      <c r="AZ80">
+        <v>-1</v>
+      </c>
+      <c r="BA80">
+        <v>-1</v>
+      </c>
+      <c r="BB80">
+        <v>-1</v>
+      </c>
+      <c r="BC80">
+        <v>-1</v>
+      </c>
+      <c r="BD80">
+        <v>0</v>
+      </c>
+      <c r="BE80">
+        <v>0</v>
+      </c>
+      <c r="BF80">
+        <v>0</v>
+      </c>
+      <c r="BG80">
+        <v>0</v>
+      </c>
+      <c r="BH80">
+        <v>0</v>
+      </c>
+      <c r="BI80">
+        <v>0</v>
+      </c>
+      <c r="BJ80">
+        <v>0</v>
+      </c>
+      <c r="BK80">
+        <v>0</v>
+      </c>
+      <c r="BL80">
+        <v>0</v>
+      </c>
+      <c r="BM80">
+        <v>0</v>
+      </c>
+      <c r="BN80">
+        <v>0</v>
+      </c>
+      <c r="BO80">
+        <v>0</v>
+      </c>
+      <c r="BP80">
         <v>0</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="196">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -431,6 +431,9 @@
   </si>
   <si>
     <t>['53']</t>
+  </si>
+  <si>
+    <t>['67', '71']</t>
   </si>
   <si>
     <t>['34', '59', '86']</t>
@@ -960,7 +963,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP80"/>
+  <dimension ref="A1:BP81"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1422,7 +1425,7 @@
         <v>81</v>
       </c>
       <c r="P3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -1628,7 +1631,7 @@
         <v>82</v>
       </c>
       <c r="P4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -1709,7 +1712,7 @@
         <v>2</v>
       </c>
       <c r="AQ4">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1834,7 +1837,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q5">
         <v>7</v>
@@ -2040,7 +2043,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2246,7 +2249,7 @@
         <v>81</v>
       </c>
       <c r="P7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q7">
         <v>1.83</v>
@@ -2452,7 +2455,7 @@
         <v>85</v>
       </c>
       <c r="P8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q8">
         <v>8.5</v>
@@ -2658,7 +2661,7 @@
         <v>81</v>
       </c>
       <c r="P9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -3276,7 +3279,7 @@
         <v>88</v>
       </c>
       <c r="P12" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q12">
         <v>8</v>
@@ -3688,7 +3691,7 @@
         <v>81</v>
       </c>
       <c r="P14" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q14">
         <v>5.5</v>
@@ -3894,7 +3897,7 @@
         <v>90</v>
       </c>
       <c r="P15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q15">
         <v>2.5</v>
@@ -4100,7 +4103,7 @@
         <v>91</v>
       </c>
       <c r="P16" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q16">
         <v>2.1</v>
@@ -4178,7 +4181,7 @@
         <v>3</v>
       </c>
       <c r="AP16">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ16">
         <v>0.5</v>
@@ -4306,7 +4309,7 @@
         <v>81</v>
       </c>
       <c r="P17" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q17">
         <v>2.38</v>
@@ -4512,7 +4515,7 @@
         <v>81</v>
       </c>
       <c r="P18" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q18">
         <v>3.4</v>
@@ -4593,7 +4596,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ18">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AR18">
         <v>1.67</v>
@@ -5130,7 +5133,7 @@
         <v>94</v>
       </c>
       <c r="P21" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q21">
         <v>1.91</v>
@@ -5542,7 +5545,7 @@
         <v>81</v>
       </c>
       <c r="P23" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q23">
         <v>5.5</v>
@@ -5748,7 +5751,7 @@
         <v>96</v>
       </c>
       <c r="P24" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q24">
         <v>3.1</v>
@@ -5826,7 +5829,7 @@
         <v>3</v>
       </c>
       <c r="AP24">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ24">
         <v>2.75</v>
@@ -5954,7 +5957,7 @@
         <v>97</v>
       </c>
       <c r="P25" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q25">
         <v>2.38</v>
@@ -6160,7 +6163,7 @@
         <v>98</v>
       </c>
       <c r="P26" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q26">
         <v>3.1</v>
@@ -6572,7 +6575,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q28">
         <v>1.3</v>
@@ -6778,7 +6781,7 @@
         <v>101</v>
       </c>
       <c r="P29" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q29">
         <v>5</v>
@@ -7062,7 +7065,7 @@
         <v>1.33</v>
       </c>
       <c r="AP30">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ30">
         <v>0.89</v>
@@ -7396,7 +7399,7 @@
         <v>81</v>
       </c>
       <c r="P32" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q32">
         <v>6</v>
@@ -7602,7 +7605,7 @@
         <v>104</v>
       </c>
       <c r="P33" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q33">
         <v>8.449999999999999</v>
@@ -8014,7 +8017,7 @@
         <v>105</v>
       </c>
       <c r="P35" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q35">
         <v>2.2</v>
@@ -8220,7 +8223,7 @@
         <v>106</v>
       </c>
       <c r="P36" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q36">
         <v>4.25</v>
@@ -8301,7 +8304,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ36">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AR36">
         <v>0.99</v>
@@ -8838,7 +8841,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q39">
         <v>3.2</v>
@@ -9044,7 +9047,7 @@
         <v>81</v>
       </c>
       <c r="P40" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q40">
         <v>12</v>
@@ -9250,7 +9253,7 @@
         <v>110</v>
       </c>
       <c r="P41" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q41">
         <v>3.77</v>
@@ -9662,7 +9665,7 @@
         <v>112</v>
       </c>
       <c r="P43" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q43">
         <v>1.35</v>
@@ -9740,7 +9743,7 @@
         <v>0.25</v>
       </c>
       <c r="AP43">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ43">
         <v>0.14</v>
@@ -9868,7 +9871,7 @@
         <v>113</v>
       </c>
       <c r="P44" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q44">
         <v>1.66</v>
@@ -10074,7 +10077,7 @@
         <v>114</v>
       </c>
       <c r="P45" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q45">
         <v>4.75</v>
@@ -10155,7 +10158,7 @@
         <v>1</v>
       </c>
       <c r="AQ45">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AR45">
         <v>1.06</v>
@@ -10280,7 +10283,7 @@
         <v>115</v>
       </c>
       <c r="P46" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q46">
         <v>5.2</v>
@@ -10486,7 +10489,7 @@
         <v>81</v>
       </c>
       <c r="P47" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q47">
         <v>2.35</v>
@@ -11104,7 +11107,7 @@
         <v>117</v>
       </c>
       <c r="P50" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q50">
         <v>2.62</v>
@@ -11310,7 +11313,7 @@
         <v>118</v>
       </c>
       <c r="P51" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q51">
         <v>4.55</v>
@@ -11391,7 +11394,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ51">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AR51">
         <v>1.64</v>
@@ -11516,7 +11519,7 @@
         <v>81</v>
       </c>
       <c r="P52" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q52">
         <v>6.5</v>
@@ -11722,7 +11725,7 @@
         <v>119</v>
       </c>
       <c r="P53" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q53">
         <v>3.35</v>
@@ -12212,7 +12215,7 @@
         <v>2.4</v>
       </c>
       <c r="AP55">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ55">
         <v>2</v>
@@ -12340,7 +12343,7 @@
         <v>122</v>
       </c>
       <c r="P56" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q56">
         <v>1.56</v>
@@ -12546,7 +12549,7 @@
         <v>81</v>
       </c>
       <c r="P57" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q57">
         <v>5.25</v>
@@ -12958,7 +12961,7 @@
         <v>81</v>
       </c>
       <c r="P59" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -13164,7 +13167,7 @@
         <v>124</v>
       </c>
       <c r="P60" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q60">
         <v>2.25</v>
@@ -13370,7 +13373,7 @@
         <v>125</v>
       </c>
       <c r="P61" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q61">
         <v>2.27</v>
@@ -13576,7 +13579,7 @@
         <v>126</v>
       </c>
       <c r="P62" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q62">
         <v>2.4</v>
@@ -13782,7 +13785,7 @@
         <v>127</v>
       </c>
       <c r="P63" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q63">
         <v>1.64</v>
@@ -14272,7 +14275,7 @@
         <v>0.67</v>
       </c>
       <c r="AP65">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ65">
         <v>0.5</v>
@@ -14400,7 +14403,7 @@
         <v>130</v>
       </c>
       <c r="P66" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q66">
         <v>4.35</v>
@@ -14481,7 +14484,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ66">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AR66">
         <v>1.52</v>
@@ -14812,7 +14815,7 @@
         <v>132</v>
       </c>
       <c r="P68" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q68">
         <v>9</v>
@@ -15018,7 +15021,7 @@
         <v>133</v>
       </c>
       <c r="P69" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q69">
         <v>1.91</v>
@@ -15224,7 +15227,7 @@
         <v>81</v>
       </c>
       <c r="P70" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q70">
         <v>2.35</v>
@@ -15302,7 +15305,7 @@
         <v>1</v>
       </c>
       <c r="AP70">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ70">
         <v>1.29</v>
@@ -15430,7 +15433,7 @@
         <v>134</v>
       </c>
       <c r="P71" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q71">
         <v>1.55</v>
@@ -15636,7 +15639,7 @@
         <v>135</v>
       </c>
       <c r="P72" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q72">
         <v>1.46</v>
@@ -15842,7 +15845,7 @@
         <v>81</v>
       </c>
       <c r="P73" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q73">
         <v>8.5</v>
@@ -16048,7 +16051,7 @@
         <v>81</v>
       </c>
       <c r="P74" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q74">
         <v>2.2</v>
@@ -16129,7 +16132,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ74">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AR74">
         <v>2.22</v>
@@ -16254,7 +16257,7 @@
         <v>136</v>
       </c>
       <c r="P75" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q75">
         <v>2.3</v>
@@ -16460,7 +16463,7 @@
         <v>81</v>
       </c>
       <c r="P76" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q76">
         <v>8.949999999999999</v>
@@ -16666,7 +16669,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q77">
         <v>2.94</v>
@@ -16872,7 +16875,7 @@
         <v>81</v>
       </c>
       <c r="P78" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q78">
         <v>4.83</v>
@@ -17078,7 +17081,7 @@
         <v>138</v>
       </c>
       <c r="P79" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q79">
         <v>10</v>
@@ -17284,7 +17287,7 @@
         <v>106</v>
       </c>
       <c r="P80" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q80">
         <v>4.33</v>
@@ -17440,6 +17443,212 @@
         <v>0</v>
       </c>
       <c r="BP80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:68">
+      <c r="A81" s="1">
+        <v>80</v>
+      </c>
+      <c r="B81">
+        <v>7828537</v>
+      </c>
+      <c r="C81" t="s">
+        <v>68</v>
+      </c>
+      <c r="D81" t="s">
+        <v>69</v>
+      </c>
+      <c r="E81" s="2">
+        <v>45823.45833333334</v>
+      </c>
+      <c r="F81">
+        <v>0</v>
+      </c>
+      <c r="G81" t="s">
+        <v>79</v>
+      </c>
+      <c r="H81" t="s">
+        <v>76</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>0</v>
+      </c>
+      <c r="K81">
+        <v>0</v>
+      </c>
+      <c r="L81">
+        <v>2</v>
+      </c>
+      <c r="M81">
+        <v>0</v>
+      </c>
+      <c r="N81">
+        <v>2</v>
+      </c>
+      <c r="O81" t="s">
+        <v>139</v>
+      </c>
+      <c r="P81" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q81">
+        <v>2.2</v>
+      </c>
+      <c r="R81">
+        <v>2.35</v>
+      </c>
+      <c r="S81">
+        <v>4.6</v>
+      </c>
+      <c r="T81">
+        <v>1.29</v>
+      </c>
+      <c r="U81">
+        <v>3.34</v>
+      </c>
+      <c r="V81">
+        <v>2.44</v>
+      </c>
+      <c r="W81">
+        <v>1.55</v>
+      </c>
+      <c r="X81">
+        <v>5.5</v>
+      </c>
+      <c r="Y81">
+        <v>1.09</v>
+      </c>
+      <c r="Z81">
+        <v>1.84</v>
+      </c>
+      <c r="AA81">
+        <v>3.76</v>
+      </c>
+      <c r="AB81">
+        <v>3.23</v>
+      </c>
+      <c r="AC81">
+        <v>1.01</v>
+      </c>
+      <c r="AD81">
+        <v>13</v>
+      </c>
+      <c r="AE81">
+        <v>1.2</v>
+      </c>
+      <c r="AF81">
+        <v>4.2</v>
+      </c>
+      <c r="AG81">
+        <v>1.55</v>
+      </c>
+      <c r="AH81">
+        <v>2.2</v>
+      </c>
+      <c r="AI81">
+        <v>1.65</v>
+      </c>
+      <c r="AJ81">
+        <v>2.15</v>
+      </c>
+      <c r="AK81">
+        <v>1.25</v>
+      </c>
+      <c r="AL81">
+        <v>1.25</v>
+      </c>
+      <c r="AM81">
+        <v>2.15</v>
+      </c>
+      <c r="AN81">
+        <v>1.86</v>
+      </c>
+      <c r="AO81">
+        <v>2.29</v>
+      </c>
+      <c r="AP81">
+        <v>2</v>
+      </c>
+      <c r="AQ81">
+        <v>2</v>
+      </c>
+      <c r="AR81">
+        <v>1.99</v>
+      </c>
+      <c r="AS81">
+        <v>1.82</v>
+      </c>
+      <c r="AT81">
+        <v>3.81</v>
+      </c>
+      <c r="AU81">
+        <v>9</v>
+      </c>
+      <c r="AV81">
+        <v>5</v>
+      </c>
+      <c r="AW81">
+        <v>7</v>
+      </c>
+      <c r="AX81">
+        <v>10</v>
+      </c>
+      <c r="AY81">
+        <v>16</v>
+      </c>
+      <c r="AZ81">
+        <v>15</v>
+      </c>
+      <c r="BA81">
+        <v>9</v>
+      </c>
+      <c r="BB81">
+        <v>11</v>
+      </c>
+      <c r="BC81">
+        <v>20</v>
+      </c>
+      <c r="BD81">
+        <v>0</v>
+      </c>
+      <c r="BE81">
+        <v>0</v>
+      </c>
+      <c r="BF81">
+        <v>0</v>
+      </c>
+      <c r="BG81">
+        <v>0</v>
+      </c>
+      <c r="BH81">
+        <v>0</v>
+      </c>
+      <c r="BI81">
+        <v>0</v>
+      </c>
+      <c r="BJ81">
+        <v>0</v>
+      </c>
+      <c r="BK81">
+        <v>0</v>
+      </c>
+      <c r="BL81">
+        <v>0</v>
+      </c>
+      <c r="BM81">
+        <v>0</v>
+      </c>
+      <c r="BN81">
+        <v>0</v>
+      </c>
+      <c r="BO81">
+        <v>0</v>
+      </c>
+      <c r="BP81">
         <v>0</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
@@ -433,7 +433,7 @@
     <t>['53']</t>
   </si>
   <si>
-    <t>['67', '71']</t>
+    <t>['68', '72']</t>
   </si>
   <si>
     <t>['34', '59', '86']</t>
@@ -17380,31 +17380,31 @@
         <v>4.23</v>
       </c>
       <c r="AU80">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AV80">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AW80">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AX80">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AY80">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AZ80">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="BA80">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BB80">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BC80">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="BD80">
         <v>0</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="202">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -436,6 +436,15 @@
     <t>['68', '72']</t>
   </si>
   <si>
+    <t>['31', '8']</t>
+  </si>
+  <si>
+    <t>['25', '21', '88', '84']</t>
+  </si>
+  <si>
+    <t>['81']</t>
+  </si>
+  <si>
     <t>['34', '59', '86']</t>
   </si>
   <si>
@@ -602,6 +611,15 @@
   </si>
   <si>
     <t>['22', '31']</t>
+  </si>
+  <si>
+    <t>['45', '38', '90+9']</t>
+  </si>
+  <si>
+    <t>['88', '48']</t>
+  </si>
+  <si>
+    <t>['33', '45+1']</t>
   </si>
 </sst>
 </file>
@@ -963,7 +981,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP81"/>
+  <dimension ref="A1:BP86"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1297,10 +1315,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AQ2">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1425,7 +1443,7 @@
         <v>81</v>
       </c>
       <c r="P3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -1503,7 +1521,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AQ3">
         <v>2.25</v>
@@ -1631,7 +1649,7 @@
         <v>82</v>
       </c>
       <c r="P4" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -1837,7 +1855,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="Q5">
         <v>7</v>
@@ -1915,10 +1933,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ5">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2043,7 +2061,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2124,7 +2142,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ6">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2249,7 +2267,7 @@
         <v>81</v>
       </c>
       <c r="P7" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="Q7">
         <v>1.83</v>
@@ -2455,7 +2473,7 @@
         <v>85</v>
       </c>
       <c r="P8" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="Q8">
         <v>8.5</v>
@@ -2661,7 +2679,7 @@
         <v>81</v>
       </c>
       <c r="P9" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -2739,7 +2757,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ9">
         <v>0.5</v>
@@ -2948,7 +2966,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ10">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3279,7 +3297,7 @@
         <v>88</v>
       </c>
       <c r="P12" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="Q12">
         <v>8</v>
@@ -3357,7 +3375,7 @@
         <v>3</v>
       </c>
       <c r="AP12">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AQ12">
         <v>2</v>
@@ -3563,10 +3581,10 @@
         <v>3</v>
       </c>
       <c r="AP13">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ13">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AR13">
         <v>1.59</v>
@@ -3691,7 +3709,7 @@
         <v>81</v>
       </c>
       <c r="P14" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="Q14">
         <v>5.5</v>
@@ -3772,7 +3790,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ14">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AR14">
         <v>1.42</v>
@@ -3897,7 +3915,7 @@
         <v>90</v>
       </c>
       <c r="P15" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="Q15">
         <v>2.5</v>
@@ -3975,10 +3993,10 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ15">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR15">
         <v>1.37</v>
@@ -4103,7 +4121,7 @@
         <v>91</v>
       </c>
       <c r="P16" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="Q16">
         <v>2.1</v>
@@ -4181,10 +4199,10 @@
         <v>3</v>
       </c>
       <c r="AP16">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ16">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4309,7 +4327,7 @@
         <v>81</v>
       </c>
       <c r="P17" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="Q17">
         <v>2.38</v>
@@ -4515,7 +4533,7 @@
         <v>81</v>
       </c>
       <c r="P18" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="Q18">
         <v>3.4</v>
@@ -5008,7 +5026,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ20">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AR20">
         <v>2.45</v>
@@ -5133,7 +5151,7 @@
         <v>94</v>
       </c>
       <c r="P21" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="Q21">
         <v>1.91</v>
@@ -5211,7 +5229,7 @@
         <v>1.5</v>
       </c>
       <c r="AP21">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AQ21">
         <v>2.25</v>
@@ -5420,7 +5438,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ22">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="AR22">
         <v>3.01</v>
@@ -5545,7 +5563,7 @@
         <v>81</v>
       </c>
       <c r="P23" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="Q23">
         <v>5.5</v>
@@ -5623,7 +5641,7 @@
         <v>3</v>
       </c>
       <c r="AP23">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ23">
         <v>2</v>
@@ -5751,7 +5769,7 @@
         <v>96</v>
       </c>
       <c r="P24" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="Q24">
         <v>3.1</v>
@@ -5829,10 +5847,10 @@
         <v>3</v>
       </c>
       <c r="AP24">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ24">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AR24">
         <v>3.56</v>
@@ -5957,7 +5975,7 @@
         <v>97</v>
       </c>
       <c r="P25" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="Q25">
         <v>2.38</v>
@@ -6035,10 +6053,10 @@
         <v>1.5</v>
       </c>
       <c r="AP25">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AQ25">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR25">
         <v>0.71</v>
@@ -6163,7 +6181,7 @@
         <v>98</v>
       </c>
       <c r="P26" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="Q26">
         <v>3.1</v>
@@ -6447,10 +6465,10 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ27">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AR27">
         <v>1.38</v>
@@ -6575,7 +6593,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="Q28">
         <v>1.3</v>
@@ -6653,7 +6671,7 @@
         <v>1</v>
       </c>
       <c r="AP28">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AQ28">
         <v>0.5</v>
@@ -6781,7 +6799,7 @@
         <v>101</v>
       </c>
       <c r="P29" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="Q29">
         <v>5</v>
@@ -6862,7 +6880,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ29">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AR29">
         <v>1.01</v>
@@ -7065,10 +7083,10 @@
         <v>1.33</v>
       </c>
       <c r="AP30">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ30">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR30">
         <v>2.7</v>
@@ -7399,7 +7417,7 @@
         <v>81</v>
       </c>
       <c r="P32" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="Q32">
         <v>6</v>
@@ -7477,7 +7495,7 @@
         <v>1</v>
       </c>
       <c r="AP32">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ32">
         <v>2.25</v>
@@ -7605,7 +7623,7 @@
         <v>104</v>
       </c>
       <c r="P33" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="Q33">
         <v>8.449999999999999</v>
@@ -7686,7 +7704,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ33">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AR33">
         <v>1.28</v>
@@ -7889,10 +7907,10 @@
         <v>3</v>
       </c>
       <c r="AP34">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AQ34">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AR34">
         <v>2.81</v>
@@ -8017,7 +8035,7 @@
         <v>105</v>
       </c>
       <c r="P35" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="Q35">
         <v>2.2</v>
@@ -8095,10 +8113,10 @@
         <v>0</v>
       </c>
       <c r="AP35">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AQ35">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AR35">
         <v>0.88</v>
@@ -8223,7 +8241,7 @@
         <v>106</v>
       </c>
       <c r="P36" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="Q36">
         <v>4.25</v>
@@ -8510,7 +8528,7 @@
         <v>2</v>
       </c>
       <c r="AQ37">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AR37">
         <v>1.88</v>
@@ -8713,7 +8731,7 @@
         <v>2</v>
       </c>
       <c r="AP38">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ38">
         <v>1.63</v>
@@ -8841,7 +8859,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="Q39">
         <v>3.2</v>
@@ -8922,7 +8940,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ39">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="AR39">
         <v>1.2</v>
@@ -9047,7 +9065,7 @@
         <v>81</v>
       </c>
       <c r="P40" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="Q40">
         <v>12</v>
@@ -9253,7 +9271,7 @@
         <v>110</v>
       </c>
       <c r="P41" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="Q41">
         <v>3.77</v>
@@ -9331,7 +9349,7 @@
         <v>1.5</v>
       </c>
       <c r="AP41">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ41">
         <v>2.25</v>
@@ -9665,7 +9683,7 @@
         <v>112</v>
       </c>
       <c r="P43" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="Q43">
         <v>1.35</v>
@@ -9743,10 +9761,10 @@
         <v>0.25</v>
       </c>
       <c r="AP43">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ43">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AR43">
         <v>2.31</v>
@@ -9871,7 +9889,7 @@
         <v>113</v>
       </c>
       <c r="P44" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="Q44">
         <v>1.66</v>
@@ -9952,7 +9970,7 @@
         <v>2</v>
       </c>
       <c r="AQ44">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR44">
         <v>1.77</v>
@@ -10077,7 +10095,7 @@
         <v>114</v>
       </c>
       <c r="P45" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="Q45">
         <v>4.75</v>
@@ -10155,7 +10173,7 @@
         <v>2.33</v>
       </c>
       <c r="AP45">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AQ45">
         <v>2</v>
@@ -10283,7 +10301,7 @@
         <v>115</v>
       </c>
       <c r="P46" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="Q46">
         <v>5.2</v>
@@ -10489,7 +10507,7 @@
         <v>81</v>
       </c>
       <c r="P47" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="Q47">
         <v>2.35</v>
@@ -10776,7 +10794,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ48">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AR48">
         <v>1.68</v>
@@ -10979,10 +10997,10 @@
         <v>1</v>
       </c>
       <c r="AP49">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AQ49">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="AR49">
         <v>2.61</v>
@@ -11107,7 +11125,7 @@
         <v>117</v>
       </c>
       <c r="P50" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="Q50">
         <v>2.62</v>
@@ -11313,7 +11331,7 @@
         <v>118</v>
       </c>
       <c r="P51" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="Q51">
         <v>4.55</v>
@@ -11391,7 +11409,7 @@
         <v>2.5</v>
       </c>
       <c r="AP51">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ51">
         <v>2</v>
@@ -11519,7 +11537,7 @@
         <v>81</v>
       </c>
       <c r="P52" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="Q52">
         <v>6.5</v>
@@ -11597,10 +11615,10 @@
         <v>2.5</v>
       </c>
       <c r="AP52">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AQ52">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AR52">
         <v>1.16</v>
@@ -11725,7 +11743,7 @@
         <v>119</v>
       </c>
       <c r="P53" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="Q53">
         <v>3.35</v>
@@ -11806,7 +11824,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ53">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR53">
         <v>1.56</v>
@@ -12009,10 +12027,10 @@
         <v>0.8</v>
       </c>
       <c r="AP54">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ54">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="AR54">
         <v>1.43</v>
@@ -12215,7 +12233,7 @@
         <v>2.4</v>
       </c>
       <c r="AP55">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ55">
         <v>2</v>
@@ -12343,7 +12361,7 @@
         <v>122</v>
       </c>
       <c r="P56" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="Q56">
         <v>1.56</v>
@@ -12549,7 +12567,7 @@
         <v>81</v>
       </c>
       <c r="P57" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="Q57">
         <v>5.25</v>
@@ -12630,7 +12648,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ57">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AR57">
         <v>1.43</v>
@@ -12833,10 +12851,10 @@
         <v>0.2</v>
       </c>
       <c r="AP58">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ58">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AR58">
         <v>1.57</v>
@@ -12961,7 +12979,7 @@
         <v>81</v>
       </c>
       <c r="P59" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -13167,7 +13185,7 @@
         <v>124</v>
       </c>
       <c r="P60" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="Q60">
         <v>2.25</v>
@@ -13245,10 +13263,10 @@
         <v>1.2</v>
       </c>
       <c r="AP60">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AQ60">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AR60">
         <v>2.68</v>
@@ -13373,7 +13391,7 @@
         <v>125</v>
       </c>
       <c r="P61" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="Q61">
         <v>2.27</v>
@@ -13451,7 +13469,7 @@
         <v>1.8</v>
       </c>
       <c r="AP61">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ61">
         <v>1.63</v>
@@ -13579,7 +13597,7 @@
         <v>126</v>
       </c>
       <c r="P62" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="Q62">
         <v>2.4</v>
@@ -13657,10 +13675,10 @@
         <v>0.67</v>
       </c>
       <c r="AP62">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AQ62">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="AR62">
         <v>1.18</v>
@@ -13785,7 +13803,7 @@
         <v>127</v>
       </c>
       <c r="P63" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="Q63">
         <v>1.64</v>
@@ -13866,7 +13884,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ63">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR63">
         <v>2.27</v>
@@ -14275,7 +14293,7 @@
         <v>0.67</v>
       </c>
       <c r="AP65">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ65">
         <v>0.5</v>
@@ -14403,7 +14421,7 @@
         <v>130</v>
       </c>
       <c r="P66" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Q66">
         <v>4.35</v>
@@ -14690,7 +14708,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ67">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AR67">
         <v>1.07</v>
@@ -14815,7 +14833,7 @@
         <v>132</v>
       </c>
       <c r="P68" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="Q68">
         <v>9</v>
@@ -14893,10 +14911,10 @@
         <v>2.67</v>
       </c>
       <c r="AP68">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ68">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AR68">
         <v>1.52</v>
@@ -15021,7 +15039,7 @@
         <v>133</v>
       </c>
       <c r="P69" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="Q69">
         <v>1.91</v>
@@ -15099,10 +15117,10 @@
         <v>1.14</v>
       </c>
       <c r="AP69">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ69">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR69">
         <v>1.66</v>
@@ -15227,7 +15245,7 @@
         <v>81</v>
       </c>
       <c r="P70" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Q70">
         <v>2.35</v>
@@ -15305,10 +15323,10 @@
         <v>1</v>
       </c>
       <c r="AP70">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ70">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AR70">
         <v>2.19</v>
@@ -15433,7 +15451,7 @@
         <v>134</v>
       </c>
       <c r="P71" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="Q71">
         <v>1.55</v>
@@ -15511,7 +15529,7 @@
         <v>1.5</v>
       </c>
       <c r="AP71">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AQ71">
         <v>1.63</v>
@@ -15639,7 +15657,7 @@
         <v>135</v>
       </c>
       <c r="P72" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q72">
         <v>1.46</v>
@@ -15720,7 +15738,7 @@
         <v>2</v>
       </c>
       <c r="AQ72">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="AR72">
         <v>1.73</v>
@@ -15845,7 +15863,7 @@
         <v>81</v>
       </c>
       <c r="P73" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q73">
         <v>8.5</v>
@@ -16051,7 +16069,7 @@
         <v>81</v>
       </c>
       <c r="P74" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q74">
         <v>2.2</v>
@@ -16257,7 +16275,7 @@
         <v>136</v>
       </c>
       <c r="P75" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q75">
         <v>2.3</v>
@@ -16335,7 +16353,7 @@
         <v>0.57</v>
       </c>
       <c r="AP75">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AQ75">
         <v>0.5</v>
@@ -16463,7 +16481,7 @@
         <v>81</v>
       </c>
       <c r="P76" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q76">
         <v>8.949999999999999</v>
@@ -16669,7 +16687,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q77">
         <v>2.94</v>
@@ -16750,7 +16768,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ77">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR77">
         <v>1.36</v>
@@ -16875,7 +16893,7 @@
         <v>81</v>
       </c>
       <c r="P78" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q78">
         <v>4.83</v>
@@ -17081,7 +17099,7 @@
         <v>138</v>
       </c>
       <c r="P79" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q79">
         <v>10</v>
@@ -17159,7 +17177,7 @@
         <v>1.88</v>
       </c>
       <c r="AP79">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ79">
         <v>2</v>
@@ -17287,7 +17305,7 @@
         <v>106</v>
       </c>
       <c r="P80" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q80">
         <v>4.33</v>
@@ -17368,7 +17386,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ80">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AR80">
         <v>2.07</v>
@@ -17571,7 +17589,7 @@
         <v>2.29</v>
       </c>
       <c r="AP81">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ81">
         <v>2</v>
@@ -17586,22 +17604,22 @@
         <v>3.81</v>
       </c>
       <c r="AU81">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AV81">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW81">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AX81">
+        <v>4</v>
+      </c>
+      <c r="AY81">
         <v>10</v>
       </c>
-      <c r="AY81">
-        <v>16</v>
-      </c>
       <c r="AZ81">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="BA81">
         <v>9</v>
@@ -17649,6 +17667,1036 @@
         <v>0</v>
       </c>
       <c r="BP81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:68">
+      <c r="A82" s="1">
+        <v>81</v>
+      </c>
+      <c r="B82">
+        <v>7828538</v>
+      </c>
+      <c r="C82" t="s">
+        <v>68</v>
+      </c>
+      <c r="D82" t="s">
+        <v>69</v>
+      </c>
+      <c r="E82" s="2">
+        <v>45825.5</v>
+      </c>
+      <c r="F82">
+        <v>0</v>
+      </c>
+      <c r="G82" t="s">
+        <v>73</v>
+      </c>
+      <c r="H82" t="s">
+        <v>75</v>
+      </c>
+      <c r="I82">
+        <v>2</v>
+      </c>
+      <c r="J82">
+        <v>2</v>
+      </c>
+      <c r="K82">
+        <v>4</v>
+      </c>
+      <c r="L82">
+        <v>2</v>
+      </c>
+      <c r="M82">
+        <v>3</v>
+      </c>
+      <c r="N82">
+        <v>5</v>
+      </c>
+      <c r="O82" t="s">
+        <v>140</v>
+      </c>
+      <c r="P82" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q82">
+        <v>2.54</v>
+      </c>
+      <c r="R82">
+        <v>2.34</v>
+      </c>
+      <c r="S82">
+        <v>3.3</v>
+      </c>
+      <c r="T82">
+        <v>1.2</v>
+      </c>
+      <c r="U82">
+        <v>3.8</v>
+      </c>
+      <c r="V82">
+        <v>2.19</v>
+      </c>
+      <c r="W82">
+        <v>1.65</v>
+      </c>
+      <c r="X82">
+        <v>4.1</v>
+      </c>
+      <c r="Y82">
+        <v>1.17</v>
+      </c>
+      <c r="Z82">
+        <v>2.1</v>
+      </c>
+      <c r="AA82">
+        <v>3.5</v>
+      </c>
+      <c r="AB82">
+        <v>2.75</v>
+      </c>
+      <c r="AC82">
+        <v>1.01</v>
+      </c>
+      <c r="AD82">
+        <v>14.7</v>
+      </c>
+      <c r="AE82">
+        <v>1.15</v>
+      </c>
+      <c r="AF82">
+        <v>5</v>
+      </c>
+      <c r="AG82">
+        <v>1.45</v>
+      </c>
+      <c r="AH82">
+        <v>2.45</v>
+      </c>
+      <c r="AI82">
+        <v>1.4</v>
+      </c>
+      <c r="AJ82">
+        <v>2.7</v>
+      </c>
+      <c r="AK82">
+        <v>1.29</v>
+      </c>
+      <c r="AL82">
+        <v>1.25</v>
+      </c>
+      <c r="AM82">
+        <v>1.67</v>
+      </c>
+      <c r="AN82">
+        <v>1.13</v>
+      </c>
+      <c r="AO82">
+        <v>0.5</v>
+      </c>
+      <c r="AP82">
+        <v>1</v>
+      </c>
+      <c r="AQ82">
+        <v>0.78</v>
+      </c>
+      <c r="AR82">
+        <v>1.51</v>
+      </c>
+      <c r="AS82">
+        <v>1.22</v>
+      </c>
+      <c r="AT82">
+        <v>2.73</v>
+      </c>
+      <c r="AU82">
+        <v>7</v>
+      </c>
+      <c r="AV82">
+        <v>12</v>
+      </c>
+      <c r="AW82">
+        <v>11</v>
+      </c>
+      <c r="AX82">
+        <v>9</v>
+      </c>
+      <c r="AY82">
+        <v>18</v>
+      </c>
+      <c r="AZ82">
+        <v>21</v>
+      </c>
+      <c r="BA82">
+        <v>13</v>
+      </c>
+      <c r="BB82">
+        <v>6</v>
+      </c>
+      <c r="BC82">
+        <v>19</v>
+      </c>
+      <c r="BD82">
+        <v>0</v>
+      </c>
+      <c r="BE82">
+        <v>0</v>
+      </c>
+      <c r="BF82">
+        <v>0</v>
+      </c>
+      <c r="BG82">
+        <v>0</v>
+      </c>
+      <c r="BH82">
+        <v>0</v>
+      </c>
+      <c r="BI82">
+        <v>0</v>
+      </c>
+      <c r="BJ82">
+        <v>0</v>
+      </c>
+      <c r="BK82">
+        <v>0</v>
+      </c>
+      <c r="BL82">
+        <v>0</v>
+      </c>
+      <c r="BM82">
+        <v>0</v>
+      </c>
+      <c r="BN82">
+        <v>0</v>
+      </c>
+      <c r="BO82">
+        <v>0</v>
+      </c>
+      <c r="BP82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:68">
+      <c r="A83" s="1">
+        <v>82</v>
+      </c>
+      <c r="B83">
+        <v>7828539</v>
+      </c>
+      <c r="C83" t="s">
+        <v>68</v>
+      </c>
+      <c r="D83" t="s">
+        <v>69</v>
+      </c>
+      <c r="E83" s="2">
+        <v>45826.5</v>
+      </c>
+      <c r="F83">
+        <v>0</v>
+      </c>
+      <c r="G83" t="s">
+        <v>76</v>
+      </c>
+      <c r="H83" t="s">
+        <v>72</v>
+      </c>
+      <c r="I83">
+        <v>1</v>
+      </c>
+      <c r="J83">
+        <v>0</v>
+      </c>
+      <c r="K83">
+        <v>1</v>
+      </c>
+      <c r="L83">
+        <v>1</v>
+      </c>
+      <c r="M83">
+        <v>2</v>
+      </c>
+      <c r="N83">
+        <v>3</v>
+      </c>
+      <c r="O83" t="s">
+        <v>119</v>
+      </c>
+      <c r="P83" t="s">
+        <v>200</v>
+      </c>
+      <c r="Q83">
+        <v>3.8</v>
+      </c>
+      <c r="R83">
+        <v>2.37</v>
+      </c>
+      <c r="S83">
+        <v>2.6</v>
+      </c>
+      <c r="T83">
+        <v>1.31</v>
+      </c>
+      <c r="U83">
+        <v>3.1</v>
+      </c>
+      <c r="V83">
+        <v>2.46</v>
+      </c>
+      <c r="W83">
+        <v>1.48</v>
+      </c>
+      <c r="X83">
+        <v>5.85</v>
+      </c>
+      <c r="Y83">
+        <v>1.07</v>
+      </c>
+      <c r="Z83">
+        <v>3.1</v>
+      </c>
+      <c r="AA83">
+        <v>3.74</v>
+      </c>
+      <c r="AB83">
+        <v>1.98</v>
+      </c>
+      <c r="AC83">
+        <v>1.04</v>
+      </c>
+      <c r="AD83">
+        <v>13</v>
+      </c>
+      <c r="AE83">
+        <v>1.16</v>
+      </c>
+      <c r="AF83">
+        <v>4.15</v>
+      </c>
+      <c r="AG83">
+        <v>1.66</v>
+      </c>
+      <c r="AH83">
+        <v>1.92</v>
+      </c>
+      <c r="AI83">
+        <v>1.62</v>
+      </c>
+      <c r="AJ83">
+        <v>2.25</v>
+      </c>
+      <c r="AK83">
+        <v>1.68</v>
+      </c>
+      <c r="AL83">
+        <v>1.25</v>
+      </c>
+      <c r="AM83">
+        <v>1.3</v>
+      </c>
+      <c r="AN83">
+        <v>1.88</v>
+      </c>
+      <c r="AO83">
+        <v>2.75</v>
+      </c>
+      <c r="AP83">
+        <v>1.67</v>
+      </c>
+      <c r="AQ83">
+        <v>2.78</v>
+      </c>
+      <c r="AR83">
+        <v>1.83</v>
+      </c>
+      <c r="AS83">
+        <v>2.07</v>
+      </c>
+      <c r="AT83">
+        <v>3.9</v>
+      </c>
+      <c r="AU83">
+        <v>5</v>
+      </c>
+      <c r="AV83">
+        <v>6</v>
+      </c>
+      <c r="AW83">
+        <v>5</v>
+      </c>
+      <c r="AX83">
+        <v>9</v>
+      </c>
+      <c r="AY83">
+        <v>10</v>
+      </c>
+      <c r="AZ83">
+        <v>15</v>
+      </c>
+      <c r="BA83">
+        <v>8</v>
+      </c>
+      <c r="BB83">
+        <v>5</v>
+      </c>
+      <c r="BC83">
+        <v>13</v>
+      </c>
+      <c r="BD83">
+        <v>0</v>
+      </c>
+      <c r="BE83">
+        <v>0</v>
+      </c>
+      <c r="BF83">
+        <v>0</v>
+      </c>
+      <c r="BG83">
+        <v>0</v>
+      </c>
+      <c r="BH83">
+        <v>0</v>
+      </c>
+      <c r="BI83">
+        <v>0</v>
+      </c>
+      <c r="BJ83">
+        <v>0</v>
+      </c>
+      <c r="BK83">
+        <v>0</v>
+      </c>
+      <c r="BL83">
+        <v>0</v>
+      </c>
+      <c r="BM83">
+        <v>0</v>
+      </c>
+      <c r="BN83">
+        <v>0</v>
+      </c>
+      <c r="BO83">
+        <v>0</v>
+      </c>
+      <c r="BP83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:68">
+      <c r="A84" s="1">
+        <v>83</v>
+      </c>
+      <c r="B84">
+        <v>7828540</v>
+      </c>
+      <c r="C84" t="s">
+        <v>68</v>
+      </c>
+      <c r="D84" t="s">
+        <v>69</v>
+      </c>
+      <c r="E84" s="2">
+        <v>45826.5</v>
+      </c>
+      <c r="F84">
+        <v>0</v>
+      </c>
+      <c r="G84" t="s">
+        <v>70</v>
+      </c>
+      <c r="H84" t="s">
+        <v>74</v>
+      </c>
+      <c r="I84">
+        <v>2</v>
+      </c>
+      <c r="J84">
+        <v>0</v>
+      </c>
+      <c r="K84">
+        <v>2</v>
+      </c>
+      <c r="L84">
+        <v>4</v>
+      </c>
+      <c r="M84">
+        <v>0</v>
+      </c>
+      <c r="N84">
+        <v>4</v>
+      </c>
+      <c r="O84" t="s">
+        <v>141</v>
+      </c>
+      <c r="P84" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q84">
+        <v>1.25</v>
+      </c>
+      <c r="R84">
+        <v>4.75</v>
+      </c>
+      <c r="S84">
+        <v>17</v>
+      </c>
+      <c r="T84">
+        <v>1.08</v>
+      </c>
+      <c r="U84">
+        <v>5.35</v>
+      </c>
+      <c r="V84">
+        <v>1.51</v>
+      </c>
+      <c r="W84">
+        <v>2.37</v>
+      </c>
+      <c r="X84">
+        <v>2.55</v>
+      </c>
+      <c r="Y84">
+        <v>1.46</v>
+      </c>
+      <c r="Z84">
+        <v>1.02</v>
+      </c>
+      <c r="AA84">
+        <v>21.03</v>
+      </c>
+      <c r="AB84">
+        <v>51</v>
+      </c>
+      <c r="AC84">
+        <v>1.01</v>
+      </c>
+      <c r="AD84">
+        <v>41</v>
+      </c>
+      <c r="AE84">
+        <v>1.02</v>
+      </c>
+      <c r="AF84">
+        <v>10</v>
+      </c>
+      <c r="AG84">
+        <v>1.13</v>
+      </c>
+      <c r="AH84">
+        <v>4.8</v>
+      </c>
+      <c r="AI84">
+        <v>2.23</v>
+      </c>
+      <c r="AJ84">
+        <v>1.51</v>
+      </c>
+      <c r="AK84">
+        <v>1.02</v>
+      </c>
+      <c r="AL84">
+        <v>1.01</v>
+      </c>
+      <c r="AM84">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="AN84">
+        <v>2.43</v>
+      </c>
+      <c r="AO84">
+        <v>0.14</v>
+      </c>
+      <c r="AP84">
+        <v>2.5</v>
+      </c>
+      <c r="AQ84">
+        <v>0.13</v>
+      </c>
+      <c r="AR84">
+        <v>2.37</v>
+      </c>
+      <c r="AS84">
+        <v>1.59</v>
+      </c>
+      <c r="AT84">
+        <v>3.96</v>
+      </c>
+      <c r="AU84">
+        <v>14</v>
+      </c>
+      <c r="AV84">
+        <v>4</v>
+      </c>
+      <c r="AW84">
+        <v>9</v>
+      </c>
+      <c r="AX84">
+        <v>4</v>
+      </c>
+      <c r="AY84">
+        <v>23</v>
+      </c>
+      <c r="AZ84">
+        <v>8</v>
+      </c>
+      <c r="BA84">
+        <v>10</v>
+      </c>
+      <c r="BB84">
+        <v>2</v>
+      </c>
+      <c r="BC84">
+        <v>12</v>
+      </c>
+      <c r="BD84">
+        <v>0</v>
+      </c>
+      <c r="BE84">
+        <v>0</v>
+      </c>
+      <c r="BF84">
+        <v>0</v>
+      </c>
+      <c r="BG84">
+        <v>0</v>
+      </c>
+      <c r="BH84">
+        <v>0</v>
+      </c>
+      <c r="BI84">
+        <v>0</v>
+      </c>
+      <c r="BJ84">
+        <v>0</v>
+      </c>
+      <c r="BK84">
+        <v>0</v>
+      </c>
+      <c r="BL84">
+        <v>0</v>
+      </c>
+      <c r="BM84">
+        <v>0</v>
+      </c>
+      <c r="BN84">
+        <v>0</v>
+      </c>
+      <c r="BO84">
+        <v>0</v>
+      </c>
+      <c r="BP84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:68">
+      <c r="A85" s="1">
+        <v>84</v>
+      </c>
+      <c r="B85">
+        <v>7828541</v>
+      </c>
+      <c r="C85" t="s">
+        <v>68</v>
+      </c>
+      <c r="D85" t="s">
+        <v>69</v>
+      </c>
+      <c r="E85" s="2">
+        <v>45826.54166666666</v>
+      </c>
+      <c r="F85">
+        <v>0</v>
+      </c>
+      <c r="G85" t="s">
+        <v>71</v>
+      </c>
+      <c r="H85" t="s">
+        <v>78</v>
+      </c>
+      <c r="I85">
+        <v>1</v>
+      </c>
+      <c r="J85">
+        <v>2</v>
+      </c>
+      <c r="K85">
+        <v>3</v>
+      </c>
+      <c r="L85">
+        <v>1</v>
+      </c>
+      <c r="M85">
+        <v>2</v>
+      </c>
+      <c r="N85">
+        <v>3</v>
+      </c>
+      <c r="O85" t="s">
+        <v>108</v>
+      </c>
+      <c r="P85" t="s">
+        <v>201</v>
+      </c>
+      <c r="Q85">
+        <v>4.37</v>
+      </c>
+      <c r="R85">
+        <v>2.35</v>
+      </c>
+      <c r="S85">
+        <v>2.17</v>
+      </c>
+      <c r="T85">
+        <v>1.32</v>
+      </c>
+      <c r="U85">
+        <v>3.12</v>
+      </c>
+      <c r="V85">
+        <v>2.4</v>
+      </c>
+      <c r="W85">
+        <v>1.51</v>
+      </c>
+      <c r="X85">
+        <v>5.95</v>
+      </c>
+      <c r="Y85">
+        <v>1.12</v>
+      </c>
+      <c r="Z85">
+        <v>4.55</v>
+      </c>
+      <c r="AA85">
+        <v>3.98</v>
+      </c>
+      <c r="AB85">
+        <v>1.55</v>
+      </c>
+      <c r="AC85">
+        <v>1.03</v>
+      </c>
+      <c r="AD85">
+        <v>11</v>
+      </c>
+      <c r="AE85">
+        <v>1.22</v>
+      </c>
+      <c r="AF85">
+        <v>4.4</v>
+      </c>
+      <c r="AG85">
+        <v>1.68</v>
+      </c>
+      <c r="AH85">
+        <v>2.1</v>
+      </c>
+      <c r="AI85">
+        <v>1.78</v>
+      </c>
+      <c r="AJ85">
+        <v>1.89</v>
+      </c>
+      <c r="AK85">
+        <v>2.4</v>
+      </c>
+      <c r="AL85">
+        <v>1.22</v>
+      </c>
+      <c r="AM85">
+        <v>1.11</v>
+      </c>
+      <c r="AN85">
+        <v>1</v>
+      </c>
+      <c r="AO85">
+        <v>1.29</v>
+      </c>
+      <c r="AP85">
+        <v>0.89</v>
+      </c>
+      <c r="AQ85">
+        <v>1.5</v>
+      </c>
+      <c r="AR85">
+        <v>1.4</v>
+      </c>
+      <c r="AS85">
+        <v>1.95</v>
+      </c>
+      <c r="AT85">
+        <v>3.35</v>
+      </c>
+      <c r="AU85">
+        <v>6</v>
+      </c>
+      <c r="AV85">
+        <v>7</v>
+      </c>
+      <c r="AW85">
+        <v>2</v>
+      </c>
+      <c r="AX85">
+        <v>7</v>
+      </c>
+      <c r="AY85">
+        <v>8</v>
+      </c>
+      <c r="AZ85">
+        <v>14</v>
+      </c>
+      <c r="BA85">
+        <v>4</v>
+      </c>
+      <c r="BB85">
+        <v>9</v>
+      </c>
+      <c r="BC85">
+        <v>13</v>
+      </c>
+      <c r="BD85">
+        <v>0</v>
+      </c>
+      <c r="BE85">
+        <v>0</v>
+      </c>
+      <c r="BF85">
+        <v>0</v>
+      </c>
+      <c r="BG85">
+        <v>0</v>
+      </c>
+      <c r="BH85">
+        <v>0</v>
+      </c>
+      <c r="BI85">
+        <v>0</v>
+      </c>
+      <c r="BJ85">
+        <v>0</v>
+      </c>
+      <c r="BK85">
+        <v>0</v>
+      </c>
+      <c r="BL85">
+        <v>0</v>
+      </c>
+      <c r="BM85">
+        <v>0</v>
+      </c>
+      <c r="BN85">
+        <v>0</v>
+      </c>
+      <c r="BO85">
+        <v>0</v>
+      </c>
+      <c r="BP85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:68">
+      <c r="A86" s="1">
+        <v>85</v>
+      </c>
+      <c r="B86">
+        <v>7828542</v>
+      </c>
+      <c r="C86" t="s">
+        <v>68</v>
+      </c>
+      <c r="D86" t="s">
+        <v>69</v>
+      </c>
+      <c r="E86" s="2">
+        <v>45826.58333333334</v>
+      </c>
+      <c r="F86">
+        <v>0</v>
+      </c>
+      <c r="G86" t="s">
+        <v>79</v>
+      </c>
+      <c r="H86" t="s">
+        <v>77</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>0</v>
+      </c>
+      <c r="K86">
+        <v>0</v>
+      </c>
+      <c r="L86">
+        <v>1</v>
+      </c>
+      <c r="M86">
+        <v>0</v>
+      </c>
+      <c r="N86">
+        <v>1</v>
+      </c>
+      <c r="O86" t="s">
+        <v>142</v>
+      </c>
+      <c r="P86" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q86">
+        <v>1.77</v>
+      </c>
+      <c r="R86">
+        <v>2.64</v>
+      </c>
+      <c r="S86">
+        <v>6.74</v>
+      </c>
+      <c r="T86">
+        <v>1.16</v>
+      </c>
+      <c r="U86">
+        <v>4</v>
+      </c>
+      <c r="V86">
+        <v>1.95</v>
+      </c>
+      <c r="W86">
+        <v>1.73</v>
+      </c>
+      <c r="X86">
+        <v>4.2</v>
+      </c>
+      <c r="Y86">
+        <v>1.22</v>
+      </c>
+      <c r="Z86">
+        <v>1.29</v>
+      </c>
+      <c r="AA86">
+        <v>5</v>
+      </c>
+      <c r="AB86">
+        <v>6.5</v>
+      </c>
+      <c r="AC86">
+        <v>1.02</v>
+      </c>
+      <c r="AD86">
+        <v>19</v>
+      </c>
+      <c r="AE86">
+        <v>1.11</v>
+      </c>
+      <c r="AF86">
+        <v>5.8</v>
+      </c>
+      <c r="AG86">
+        <v>1.36</v>
+      </c>
+      <c r="AH86">
+        <v>2.76</v>
+      </c>
+      <c r="AI86">
+        <v>1.62</v>
+      </c>
+      <c r="AJ86">
+        <v>1.97</v>
+      </c>
+      <c r="AK86">
+        <v>1.02</v>
+      </c>
+      <c r="AL86">
+        <v>1.21</v>
+      </c>
+      <c r="AM86">
+        <v>3.2</v>
+      </c>
+      <c r="AN86">
+        <v>2</v>
+      </c>
+      <c r="AO86">
+        <v>0.89</v>
+      </c>
+      <c r="AP86">
+        <v>2.11</v>
+      </c>
+      <c r="AQ86">
+        <v>0.8</v>
+      </c>
+      <c r="AR86">
+        <v>1.93</v>
+      </c>
+      <c r="AS86">
+        <v>1.38</v>
+      </c>
+      <c r="AT86">
+        <v>3.31</v>
+      </c>
+      <c r="AU86">
+        <v>8</v>
+      </c>
+      <c r="AV86">
+        <v>3</v>
+      </c>
+      <c r="AW86">
+        <v>17</v>
+      </c>
+      <c r="AX86">
+        <v>5</v>
+      </c>
+      <c r="AY86">
+        <v>25</v>
+      </c>
+      <c r="AZ86">
+        <v>8</v>
+      </c>
+      <c r="BA86">
+        <v>15</v>
+      </c>
+      <c r="BB86">
+        <v>1</v>
+      </c>
+      <c r="BC86">
+        <v>16</v>
+      </c>
+      <c r="BD86">
+        <v>0</v>
+      </c>
+      <c r="BE86">
+        <v>0</v>
+      </c>
+      <c r="BF86">
+        <v>0</v>
+      </c>
+      <c r="BG86">
+        <v>0</v>
+      </c>
+      <c r="BH86">
+        <v>0</v>
+      </c>
+      <c r="BI86">
+        <v>0</v>
+      </c>
+      <c r="BJ86">
+        <v>0</v>
+      </c>
+      <c r="BK86">
+        <v>0</v>
+      </c>
+      <c r="BL86">
+        <v>0</v>
+      </c>
+      <c r="BM86">
+        <v>0</v>
+      </c>
+      <c r="BN86">
+        <v>0</v>
+      </c>
+      <c r="BO86">
+        <v>0</v>
+      </c>
+      <c r="BP86">
         <v>0</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
@@ -439,6 +439,9 @@
     <t>['31', '8']</t>
   </si>
   <si>
+    <t>['16']</t>
+  </si>
+  <si>
     <t>['25', '21', '88', '84']</t>
   </si>
   <si>
@@ -455,9 +458,6 @@
   </si>
   <si>
     <t>['36', '63']</t>
-  </si>
-  <si>
-    <t>['16']</t>
   </si>
   <si>
     <t>['18', '44', '89']</t>
@@ -1443,7 +1443,7 @@
         <v>81</v>
       </c>
       <c r="P3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -1649,7 +1649,7 @@
         <v>82</v>
       </c>
       <c r="P4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -1855,7 +1855,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q5">
         <v>7</v>
@@ -2061,7 +2061,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2267,7 +2267,7 @@
         <v>81</v>
       </c>
       <c r="P7" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="Q7">
         <v>1.83</v>
@@ -17920,7 +17920,7 @@
         <v>3</v>
       </c>
       <c r="O83" t="s">
-        <v>119</v>
+        <v>141</v>
       </c>
       <c r="P83" t="s">
         <v>200</v>
@@ -18126,7 +18126,7 @@
         <v>4</v>
       </c>
       <c r="O84" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P84" t="s">
         <v>81</v>
@@ -18538,7 +18538,7 @@
         <v>1</v>
       </c>
       <c r="O86" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P86" t="s">
         <v>81</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
@@ -445,7 +445,7 @@
     <t>['25', '21', '88', '84']</t>
   </si>
   <si>
-    <t>['81']</t>
+    <t>['80']</t>
   </si>
   <si>
     <t>['34', '59', '86']</t>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="205">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -439,15 +439,21 @@
     <t>['31', '8']</t>
   </si>
   <si>
+    <t>['25', '21', '88', '84']</t>
+  </si>
+  <si>
     <t>['16']</t>
   </si>
   <si>
-    <t>['25', '21', '88', '84']</t>
-  </si>
-  <si>
     <t>['80']</t>
   </si>
   <si>
+    <t>['16', '39', '58']</t>
+  </si>
+  <si>
+    <t>['50', '68']</t>
+  </si>
+  <si>
     <t>['34', '59', '86']</t>
   </si>
   <si>
@@ -610,9 +616,6 @@
     <t>['45+5', '59']</t>
   </si>
   <si>
-    <t>['22', '31']</t>
-  </si>
-  <si>
     <t>['45', '38', '90+9']</t>
   </si>
   <si>
@@ -620,6 +623,12 @@
   </si>
   <si>
     <t>['33', '45+1']</t>
+  </si>
+  <si>
+    <t>['56']</t>
+  </si>
+  <si>
+    <t>['83']</t>
   </si>
 </sst>
 </file>
@@ -981,7 +990,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP86"/>
+  <dimension ref="A1:BP87"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1315,7 +1324,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AQ2">
         <v>0.8</v>
@@ -1443,7 +1452,7 @@
         <v>81</v>
       </c>
       <c r="P3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -1524,7 +1533,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ3">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1649,7 +1658,7 @@
         <v>82</v>
       </c>
       <c r="P4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -1855,7 +1864,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="Q5">
         <v>7</v>
@@ -2061,7 +2070,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2267,7 +2276,7 @@
         <v>81</v>
       </c>
       <c r="P7" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q7">
         <v>1.83</v>
@@ -2473,7 +2482,7 @@
         <v>85</v>
       </c>
       <c r="P8" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="Q8">
         <v>8.5</v>
@@ -2679,7 +2688,7 @@
         <v>81</v>
       </c>
       <c r="P9" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -3169,10 +3178,10 @@
         <v>3</v>
       </c>
       <c r="AP11">
-        <v>1.89</v>
+        <v>2.22</v>
       </c>
       <c r="AQ11">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3297,7 +3306,7 @@
         <v>88</v>
       </c>
       <c r="P12" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="Q12">
         <v>8</v>
@@ -3709,7 +3718,7 @@
         <v>81</v>
       </c>
       <c r="P14" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="Q14">
         <v>5.5</v>
@@ -3790,7 +3799,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ14">
-        <v>2.78</v>
+        <v>2.44</v>
       </c>
       <c r="AR14">
         <v>1.42</v>
@@ -3915,7 +3924,7 @@
         <v>90</v>
       </c>
       <c r="P15" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="Q15">
         <v>2.5</v>
@@ -4121,7 +4130,7 @@
         <v>91</v>
       </c>
       <c r="P16" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="Q16">
         <v>2.1</v>
@@ -4327,7 +4336,7 @@
         <v>81</v>
       </c>
       <c r="P17" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="Q17">
         <v>2.38</v>
@@ -4533,7 +4542,7 @@
         <v>81</v>
       </c>
       <c r="P18" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="Q18">
         <v>3.4</v>
@@ -5023,7 +5032,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.89</v>
+        <v>2.22</v>
       </c>
       <c r="AQ20">
         <v>0.13</v>
@@ -5151,7 +5160,7 @@
         <v>94</v>
       </c>
       <c r="P21" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="Q21">
         <v>1.91</v>
@@ -5229,10 +5238,10 @@
         <v>1.5</v>
       </c>
       <c r="AP21">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AQ21">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AR21">
         <v>2.18</v>
@@ -5435,7 +5444,7 @@
         <v>2</v>
       </c>
       <c r="AP22">
-        <v>1.89</v>
+        <v>2.22</v>
       </c>
       <c r="AQ22">
         <v>0.78</v>
@@ -5563,7 +5572,7 @@
         <v>81</v>
       </c>
       <c r="P23" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q23">
         <v>5.5</v>
@@ -5769,7 +5778,7 @@
         <v>96</v>
       </c>
       <c r="P24" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Q24">
         <v>3.1</v>
@@ -5850,7 +5859,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ24">
-        <v>2.78</v>
+        <v>2.44</v>
       </c>
       <c r="AR24">
         <v>3.56</v>
@@ -5975,7 +5984,7 @@
         <v>97</v>
       </c>
       <c r="P25" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q25">
         <v>2.38</v>
@@ -6181,7 +6190,7 @@
         <v>98</v>
       </c>
       <c r="P26" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q26">
         <v>3.1</v>
@@ -6593,7 +6602,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q28">
         <v>1.3</v>
@@ -6671,7 +6680,7 @@
         <v>1</v>
       </c>
       <c r="AP28">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AQ28">
         <v>0.5</v>
@@ -6799,7 +6808,7 @@
         <v>101</v>
       </c>
       <c r="P29" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q29">
         <v>5</v>
@@ -6880,7 +6889,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ29">
-        <v>2.78</v>
+        <v>2.44</v>
       </c>
       <c r="AR29">
         <v>1.01</v>
@@ -7289,7 +7298,7 @@
         <v>3</v>
       </c>
       <c r="AP31">
-        <v>1.89</v>
+        <v>2.22</v>
       </c>
       <c r="AQ31">
         <v>1.63</v>
@@ -7417,7 +7426,7 @@
         <v>81</v>
       </c>
       <c r="P32" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q32">
         <v>6</v>
@@ -7498,7 +7507,7 @@
         <v>1</v>
       </c>
       <c r="AQ32">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AR32">
         <v>1.48</v>
@@ -7623,7 +7632,7 @@
         <v>104</v>
       </c>
       <c r="P33" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q33">
         <v>8.449999999999999</v>
@@ -7907,10 +7916,10 @@
         <v>3</v>
       </c>
       <c r="AP34">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AQ34">
-        <v>2.78</v>
+        <v>2.44</v>
       </c>
       <c r="AR34">
         <v>2.81</v>
@@ -8035,7 +8044,7 @@
         <v>105</v>
       </c>
       <c r="P35" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q35">
         <v>2.2</v>
@@ -8241,7 +8250,7 @@
         <v>106</v>
       </c>
       <c r="P36" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q36">
         <v>4.25</v>
@@ -8859,7 +8868,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q39">
         <v>3.2</v>
@@ -9065,7 +9074,7 @@
         <v>81</v>
       </c>
       <c r="P40" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q40">
         <v>12</v>
@@ -9271,7 +9280,7 @@
         <v>110</v>
       </c>
       <c r="P41" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q41">
         <v>3.77</v>
@@ -9352,7 +9361,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ41">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AR41">
         <v>1.43</v>
@@ -9683,7 +9692,7 @@
         <v>112</v>
       </c>
       <c r="P43" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q43">
         <v>1.35</v>
@@ -9889,7 +9898,7 @@
         <v>113</v>
       </c>
       <c r="P44" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q44">
         <v>1.66</v>
@@ -10095,7 +10104,7 @@
         <v>114</v>
       </c>
       <c r="P45" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q45">
         <v>4.75</v>
@@ -10301,7 +10310,7 @@
         <v>115</v>
       </c>
       <c r="P46" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q46">
         <v>5.2</v>
@@ -10379,7 +10388,7 @@
         <v>3</v>
       </c>
       <c r="AP46">
-        <v>1.89</v>
+        <v>2.22</v>
       </c>
       <c r="AQ46">
         <v>2</v>
@@ -10507,7 +10516,7 @@
         <v>81</v>
       </c>
       <c r="P47" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q47">
         <v>2.35</v>
@@ -10997,7 +11006,7 @@
         <v>1</v>
       </c>
       <c r="AP49">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AQ49">
         <v>0.78</v>
@@ -11125,7 +11134,7 @@
         <v>117</v>
       </c>
       <c r="P50" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q50">
         <v>2.62</v>
@@ -11206,7 +11215,7 @@
         <v>2</v>
       </c>
       <c r="AQ50">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AR50">
         <v>1.94</v>
@@ -11331,7 +11340,7 @@
         <v>118</v>
       </c>
       <c r="P51" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q51">
         <v>4.55</v>
@@ -11537,7 +11546,7 @@
         <v>81</v>
       </c>
       <c r="P52" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q52">
         <v>6.5</v>
@@ -11618,7 +11627,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ52">
-        <v>2.78</v>
+        <v>2.44</v>
       </c>
       <c r="AR52">
         <v>1.16</v>
@@ -11743,7 +11752,7 @@
         <v>119</v>
       </c>
       <c r="P53" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q53">
         <v>3.35</v>
@@ -12361,7 +12370,7 @@
         <v>122</v>
       </c>
       <c r="P56" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q56">
         <v>1.56</v>
@@ -12439,7 +12448,7 @@
         <v>0.6</v>
       </c>
       <c r="AP56">
-        <v>1.89</v>
+        <v>2.22</v>
       </c>
       <c r="AQ56">
         <v>0.5</v>
@@ -12567,7 +12576,7 @@
         <v>81</v>
       </c>
       <c r="P57" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q57">
         <v>5.25</v>
@@ -12648,7 +12657,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ57">
-        <v>2.78</v>
+        <v>2.44</v>
       </c>
       <c r="AR57">
         <v>1.43</v>
@@ -12979,7 +12988,7 @@
         <v>81</v>
       </c>
       <c r="P59" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -13060,7 +13069,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ59">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AR59">
         <v>1.1</v>
@@ -13185,7 +13194,7 @@
         <v>124</v>
       </c>
       <c r="P60" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q60">
         <v>2.25</v>
@@ -13263,7 +13272,7 @@
         <v>1.2</v>
       </c>
       <c r="AP60">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AQ60">
         <v>1.5</v>
@@ -13391,7 +13400,7 @@
         <v>125</v>
       </c>
       <c r="P61" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q61">
         <v>2.27</v>
@@ -13597,7 +13606,7 @@
         <v>126</v>
       </c>
       <c r="P62" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q62">
         <v>2.4</v>
@@ -13803,7 +13812,7 @@
         <v>127</v>
       </c>
       <c r="P63" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q63">
         <v>1.64</v>
@@ -13881,7 +13890,7 @@
         <v>1.17</v>
       </c>
       <c r="AP63">
-        <v>1.89</v>
+        <v>2.22</v>
       </c>
       <c r="AQ63">
         <v>0.8</v>
@@ -14421,7 +14430,7 @@
         <v>130</v>
       </c>
       <c r="P66" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q66">
         <v>4.35</v>
@@ -14833,7 +14842,7 @@
         <v>132</v>
       </c>
       <c r="P68" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q68">
         <v>9</v>
@@ -14914,7 +14923,7 @@
         <v>1</v>
       </c>
       <c r="AQ68">
-        <v>2.78</v>
+        <v>2.44</v>
       </c>
       <c r="AR68">
         <v>1.52</v>
@@ -15039,7 +15048,7 @@
         <v>133</v>
       </c>
       <c r="P69" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q69">
         <v>1.91</v>
@@ -15245,7 +15254,7 @@
         <v>81</v>
       </c>
       <c r="P70" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q70">
         <v>2.35</v>
@@ -15451,7 +15460,7 @@
         <v>134</v>
       </c>
       <c r="P71" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q71">
         <v>1.55</v>
@@ -15529,7 +15538,7 @@
         <v>1.5</v>
       </c>
       <c r="AP71">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AQ71">
         <v>1.63</v>
@@ -15657,7 +15666,7 @@
         <v>135</v>
       </c>
       <c r="P72" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q72">
         <v>1.46</v>
@@ -15863,7 +15872,7 @@
         <v>81</v>
       </c>
       <c r="P73" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q73">
         <v>8.5</v>
@@ -16069,7 +16078,7 @@
         <v>81</v>
       </c>
       <c r="P74" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q74">
         <v>2.2</v>
@@ -16147,7 +16156,7 @@
         <v>2.17</v>
       </c>
       <c r="AP74">
-        <v>1.89</v>
+        <v>2.22</v>
       </c>
       <c r="AQ74">
         <v>2</v>
@@ -16275,7 +16284,7 @@
         <v>136</v>
       </c>
       <c r="P75" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q75">
         <v>2.3</v>
@@ -16481,7 +16490,7 @@
         <v>81</v>
       </c>
       <c r="P76" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q76">
         <v>8.949999999999999</v>
@@ -16562,7 +16571,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ76">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AR76">
         <v>1.51</v>
@@ -16687,7 +16696,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q77">
         <v>2.94</v>
@@ -16893,7 +16902,7 @@
         <v>81</v>
       </c>
       <c r="P78" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q78">
         <v>4.83</v>
@@ -17099,7 +17108,7 @@
         <v>138</v>
       </c>
       <c r="P79" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q79">
         <v>10</v>
@@ -17263,7 +17272,7 @@
         <v>79</v>
       </c>
       <c r="B80">
-        <v>7828536</v>
+        <v>7828537</v>
       </c>
       <c r="C80" t="s">
         <v>68</v>
@@ -17272,157 +17281,157 @@
         <v>69</v>
       </c>
       <c r="E80" s="2">
-        <v>45823.35416666666</v>
+        <v>45823.45833333334</v>
       </c>
       <c r="F80">
         <v>0</v>
       </c>
       <c r="G80" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H80" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="I80">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J80">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K80">
+        <v>0</v>
+      </c>
+      <c r="L80">
+        <v>2</v>
+      </c>
+      <c r="M80">
+        <v>0</v>
+      </c>
+      <c r="N80">
+        <v>2</v>
+      </c>
+      <c r="O80" t="s">
+        <v>139</v>
+      </c>
+      <c r="P80" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q80">
+        <v>2.2</v>
+      </c>
+      <c r="R80">
+        <v>2.35</v>
+      </c>
+      <c r="S80">
+        <v>4.6</v>
+      </c>
+      <c r="T80">
+        <v>1.29</v>
+      </c>
+      <c r="U80">
+        <v>3.34</v>
+      </c>
+      <c r="V80">
+        <v>2.44</v>
+      </c>
+      <c r="W80">
+        <v>1.55</v>
+      </c>
+      <c r="X80">
+        <v>5.5</v>
+      </c>
+      <c r="Y80">
+        <v>1.09</v>
+      </c>
+      <c r="Z80">
+        <v>1.84</v>
+      </c>
+      <c r="AA80">
+        <v>3.76</v>
+      </c>
+      <c r="AB80">
+        <v>3.23</v>
+      </c>
+      <c r="AC80">
+        <v>1.01</v>
+      </c>
+      <c r="AD80">
+        <v>13</v>
+      </c>
+      <c r="AE80">
+        <v>1.2</v>
+      </c>
+      <c r="AF80">
+        <v>4.2</v>
+      </c>
+      <c r="AG80">
+        <v>1.55</v>
+      </c>
+      <c r="AH80">
+        <v>2.2</v>
+      </c>
+      <c r="AI80">
+        <v>1.65</v>
+      </c>
+      <c r="AJ80">
+        <v>2.15</v>
+      </c>
+      <c r="AK80">
+        <v>1.25</v>
+      </c>
+      <c r="AL80">
+        <v>1.25</v>
+      </c>
+      <c r="AM80">
+        <v>2.15</v>
+      </c>
+      <c r="AN80">
+        <v>1.86</v>
+      </c>
+      <c r="AO80">
+        <v>2.29</v>
+      </c>
+      <c r="AP80">
+        <v>2.11</v>
+      </c>
+      <c r="AQ80">
+        <v>2</v>
+      </c>
+      <c r="AR80">
+        <v>1.99</v>
+      </c>
+      <c r="AS80">
+        <v>1.82</v>
+      </c>
+      <c r="AT80">
+        <v>3.81</v>
+      </c>
+      <c r="AU80">
+        <v>7</v>
+      </c>
+      <c r="AV80">
+        <v>6</v>
+      </c>
+      <c r="AW80">
         <v>3</v>
       </c>
-      <c r="L80">
-        <v>1</v>
-      </c>
-      <c r="M80">
-        <v>2</v>
-      </c>
-      <c r="N80">
-        <v>3</v>
-      </c>
-      <c r="O80" t="s">
-        <v>106</v>
-      </c>
-      <c r="P80" t="s">
-        <v>198</v>
-      </c>
-      <c r="Q80">
-        <v>4.33</v>
-      </c>
-      <c r="R80">
-        <v>2.08</v>
-      </c>
-      <c r="S80">
-        <v>2.05</v>
-      </c>
-      <c r="T80">
-        <v>1.32</v>
-      </c>
-      <c r="U80">
-        <v>2.88</v>
-      </c>
-      <c r="V80">
-        <v>2.7</v>
-      </c>
-      <c r="W80">
-        <v>1.38</v>
-      </c>
-      <c r="X80">
-        <v>7.2</v>
-      </c>
-      <c r="Y80">
-        <v>1.05</v>
-      </c>
-      <c r="Z80">
-        <v>3.8</v>
-      </c>
-      <c r="AA80">
-        <v>3.3</v>
-      </c>
-      <c r="AB80">
-        <v>1.86</v>
-      </c>
-      <c r="AC80">
-        <v>1.02</v>
-      </c>
-      <c r="AD80">
+      <c r="AX80">
+        <v>4</v>
+      </c>
+      <c r="AY80">
         <v>10</v>
-      </c>
-      <c r="AE80">
-        <v>1.29</v>
-      </c>
-      <c r="AF80">
-        <v>3.4</v>
-      </c>
-      <c r="AG80">
-        <v>1.91</v>
-      </c>
-      <c r="AH80">
-        <v>1.83</v>
-      </c>
-      <c r="AI80">
-        <v>1.84</v>
-      </c>
-      <c r="AJ80">
-        <v>1.95</v>
-      </c>
-      <c r="AK80">
-        <v>1.96</v>
-      </c>
-      <c r="AL80">
-        <v>0</v>
-      </c>
-      <c r="AM80">
-        <v>1.12</v>
-      </c>
-      <c r="AN80">
-        <v>2.13</v>
-      </c>
-      <c r="AO80">
-        <v>2.71</v>
-      </c>
-      <c r="AP80">
-        <v>1.89</v>
-      </c>
-      <c r="AQ80">
-        <v>2.78</v>
-      </c>
-      <c r="AR80">
-        <v>2.07</v>
-      </c>
-      <c r="AS80">
-        <v>2.16</v>
-      </c>
-      <c r="AT80">
-        <v>4.23</v>
-      </c>
-      <c r="AU80">
-        <v>11</v>
-      </c>
-      <c r="AV80">
-        <v>5</v>
-      </c>
-      <c r="AW80">
-        <v>7</v>
-      </c>
-      <c r="AX80">
-        <v>5</v>
-      </c>
-      <c r="AY80">
-        <v>18</v>
       </c>
       <c r="AZ80">
         <v>10</v>
       </c>
       <c r="BA80">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BB80">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="BC80">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="BD80">
         <v>0</v>
@@ -17469,7 +17478,7 @@
         <v>80</v>
       </c>
       <c r="B81">
-        <v>7828537</v>
+        <v>7828538</v>
       </c>
       <c r="C81" t="s">
         <v>68</v>
@@ -17478,157 +17487,157 @@
         <v>69</v>
       </c>
       <c r="E81" s="2">
-        <v>45823.45833333334</v>
+        <v>45825.5</v>
       </c>
       <c r="F81">
         <v>0</v>
       </c>
       <c r="G81" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="H81" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I81">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J81">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K81">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L81">
         <v>2</v>
       </c>
       <c r="M81">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N81">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O81" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P81" t="s">
-        <v>81</v>
+        <v>200</v>
       </c>
       <c r="Q81">
-        <v>2.2</v>
+        <v>2.54</v>
       </c>
       <c r="R81">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="S81">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="T81">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="U81">
-        <v>3.34</v>
+        <v>3.8</v>
       </c>
       <c r="V81">
-        <v>2.44</v>
+        <v>2.19</v>
       </c>
       <c r="W81">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="X81">
-        <v>5.5</v>
+        <v>4.1</v>
       </c>
       <c r="Y81">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="Z81">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="AA81">
-        <v>3.76</v>
+        <v>3.5</v>
       </c>
       <c r="AB81">
-        <v>3.23</v>
+        <v>2.75</v>
       </c>
       <c r="AC81">
         <v>1.01</v>
       </c>
       <c r="AD81">
-        <v>13</v>
+        <v>14.7</v>
       </c>
       <c r="AE81">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AF81">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AG81">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="AH81">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="AI81">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AJ81">
-        <v>2.15</v>
+        <v>2.7</v>
       </c>
       <c r="AK81">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AL81">
         <v>1.25</v>
       </c>
       <c r="AM81">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="AN81">
-        <v>1.86</v>
+        <v>1.13</v>
       </c>
       <c r="AO81">
-        <v>2.29</v>
+        <v>0.5</v>
       </c>
       <c r="AP81">
-        <v>2.11</v>
+        <v>1</v>
       </c>
       <c r="AQ81">
-        <v>2</v>
+        <v>0.78</v>
       </c>
       <c r="AR81">
-        <v>1.99</v>
+        <v>1.51</v>
       </c>
       <c r="AS81">
-        <v>1.82</v>
+        <v>1.22</v>
       </c>
       <c r="AT81">
-        <v>3.81</v>
+        <v>2.73</v>
       </c>
       <c r="AU81">
         <v>7</v>
       </c>
       <c r="AV81">
+        <v>12</v>
+      </c>
+      <c r="AW81">
+        <v>11</v>
+      </c>
+      <c r="AX81">
+        <v>9</v>
+      </c>
+      <c r="AY81">
+        <v>18</v>
+      </c>
+      <c r="AZ81">
+        <v>21</v>
+      </c>
+      <c r="BA81">
+        <v>13</v>
+      </c>
+      <c r="BB81">
         <v>6</v>
       </c>
-      <c r="AW81">
-        <v>3</v>
-      </c>
-      <c r="AX81">
-        <v>4</v>
-      </c>
-      <c r="AY81">
-        <v>10</v>
-      </c>
-      <c r="AZ81">
-        <v>10</v>
-      </c>
-      <c r="BA81">
-        <v>9</v>
-      </c>
-      <c r="BB81">
-        <v>11</v>
-      </c>
       <c r="BC81">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BD81">
         <v>0</v>
@@ -17675,7 +17684,7 @@
         <v>81</v>
       </c>
       <c r="B82">
-        <v>7828538</v>
+        <v>7828540</v>
       </c>
       <c r="C82" t="s">
         <v>68</v>
@@ -17684,157 +17693,157 @@
         <v>69</v>
       </c>
       <c r="E82" s="2">
-        <v>45825.5</v>
+        <v>45826.5</v>
       </c>
       <c r="F82">
         <v>0</v>
       </c>
       <c r="G82" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H82" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I82">
         <v>2</v>
       </c>
       <c r="J82">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K82">
+        <v>2</v>
+      </c>
+      <c r="L82">
         <v>4</v>
       </c>
-      <c r="L82">
-        <v>2</v>
-      </c>
       <c r="M82">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N82">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O82" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P82" t="s">
-        <v>199</v>
+        <v>81</v>
       </c>
       <c r="Q82">
-        <v>2.54</v>
+        <v>1.25</v>
       </c>
       <c r="R82">
-        <v>2.34</v>
+        <v>4.75</v>
       </c>
       <c r="S82">
-        <v>3.3</v>
+        <v>17</v>
       </c>
       <c r="T82">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="U82">
-        <v>3.8</v>
+        <v>5.35</v>
       </c>
       <c r="V82">
-        <v>2.19</v>
+        <v>1.51</v>
       </c>
       <c r="W82">
-        <v>1.65</v>
+        <v>2.37</v>
       </c>
       <c r="X82">
-        <v>4.1</v>
+        <v>2.55</v>
       </c>
       <c r="Y82">
-        <v>1.17</v>
+        <v>1.46</v>
       </c>
       <c r="Z82">
-        <v>2.1</v>
+        <v>1.02</v>
       </c>
       <c r="AA82">
-        <v>3.5</v>
+        <v>21.03</v>
       </c>
       <c r="AB82">
-        <v>2.75</v>
+        <v>51</v>
       </c>
       <c r="AC82">
         <v>1.01</v>
       </c>
       <c r="AD82">
-        <v>14.7</v>
+        <v>41</v>
       </c>
       <c r="AE82">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
       <c r="AF82">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AG82">
-        <v>1.45</v>
+        <v>1.13</v>
       </c>
       <c r="AH82">
-        <v>2.45</v>
+        <v>4.8</v>
       </c>
       <c r="AI82">
-        <v>1.4</v>
+        <v>2.23</v>
       </c>
       <c r="AJ82">
-        <v>2.7</v>
+        <v>1.51</v>
       </c>
       <c r="AK82">
-        <v>1.29</v>
+        <v>1.02</v>
       </c>
       <c r="AL82">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="AM82">
-        <v>1.67</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AN82">
-        <v>1.13</v>
+        <v>2.43</v>
       </c>
       <c r="AO82">
-        <v>0.5</v>
+        <v>0.14</v>
       </c>
       <c r="AP82">
-        <v>1</v>
+        <v>2.56</v>
       </c>
       <c r="AQ82">
-        <v>0.78</v>
+        <v>0.13</v>
       </c>
       <c r="AR82">
-        <v>1.51</v>
+        <v>2.37</v>
       </c>
       <c r="AS82">
-        <v>1.22</v>
+        <v>1.59</v>
       </c>
       <c r="AT82">
-        <v>2.73</v>
+        <v>3.96</v>
       </c>
       <c r="AU82">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AV82">
+        <v>4</v>
+      </c>
+      <c r="AW82">
+        <v>9</v>
+      </c>
+      <c r="AX82">
+        <v>4</v>
+      </c>
+      <c r="AY82">
+        <v>23</v>
+      </c>
+      <c r="AZ82">
+        <v>8</v>
+      </c>
+      <c r="BA82">
+        <v>10</v>
+      </c>
+      <c r="BB82">
+        <v>2</v>
+      </c>
+      <c r="BC82">
         <v>12</v>
-      </c>
-      <c r="AW82">
-        <v>11</v>
-      </c>
-      <c r="AX82">
-        <v>9</v>
-      </c>
-      <c r="AY82">
-        <v>18</v>
-      </c>
-      <c r="AZ82">
-        <v>21</v>
-      </c>
-      <c r="BA82">
-        <v>13</v>
-      </c>
-      <c r="BB82">
-        <v>6</v>
-      </c>
-      <c r="BC82">
-        <v>19</v>
       </c>
       <c r="BD82">
         <v>0</v>
@@ -17920,10 +17929,10 @@
         <v>3</v>
       </c>
       <c r="O83" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P83" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q83">
         <v>3.8</v>
@@ -17998,22 +18007,22 @@
         <v>1.88</v>
       </c>
       <c r="AO83">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="AP83">
         <v>1.67</v>
       </c>
       <c r="AQ83">
-        <v>2.78</v>
+        <v>2.44</v>
       </c>
       <c r="AR83">
         <v>1.83</v>
       </c>
       <c r="AS83">
-        <v>2.07</v>
+        <v>2.16</v>
       </c>
       <c r="AT83">
-        <v>3.9</v>
+        <v>3.99</v>
       </c>
       <c r="AU83">
         <v>5</v>
@@ -18087,7 +18096,7 @@
         <v>83</v>
       </c>
       <c r="B84">
-        <v>7828540</v>
+        <v>7828541</v>
       </c>
       <c r="C84" t="s">
         <v>68</v>
@@ -18096,157 +18105,157 @@
         <v>69</v>
       </c>
       <c r="E84" s="2">
-        <v>45826.5</v>
+        <v>45826.54166666666</v>
       </c>
       <c r="F84">
         <v>0</v>
       </c>
       <c r="G84" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H84" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="I84">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J84">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K84">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L84">
+        <v>1</v>
+      </c>
+      <c r="M84">
+        <v>2</v>
+      </c>
+      <c r="N84">
+        <v>3</v>
+      </c>
+      <c r="O84" t="s">
+        <v>108</v>
+      </c>
+      <c r="P84" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q84">
+        <v>4.37</v>
+      </c>
+      <c r="R84">
+        <v>2.35</v>
+      </c>
+      <c r="S84">
+        <v>2.17</v>
+      </c>
+      <c r="T84">
+        <v>1.32</v>
+      </c>
+      <c r="U84">
+        <v>3.12</v>
+      </c>
+      <c r="V84">
+        <v>2.4</v>
+      </c>
+      <c r="W84">
+        <v>1.51</v>
+      </c>
+      <c r="X84">
+        <v>5.95</v>
+      </c>
+      <c r="Y84">
+        <v>1.12</v>
+      </c>
+      <c r="Z84">
+        <v>4.55</v>
+      </c>
+      <c r="AA84">
+        <v>3.98</v>
+      </c>
+      <c r="AB84">
+        <v>1.55</v>
+      </c>
+      <c r="AC84">
+        <v>1.03</v>
+      </c>
+      <c r="AD84">
+        <v>11</v>
+      </c>
+      <c r="AE84">
+        <v>1.22</v>
+      </c>
+      <c r="AF84">
+        <v>4.4</v>
+      </c>
+      <c r="AG84">
+        <v>1.68</v>
+      </c>
+      <c r="AH84">
+        <v>2.1</v>
+      </c>
+      <c r="AI84">
+        <v>1.78</v>
+      </c>
+      <c r="AJ84">
+        <v>1.89</v>
+      </c>
+      <c r="AK84">
+        <v>2.4</v>
+      </c>
+      <c r="AL84">
+        <v>1.22</v>
+      </c>
+      <c r="AM84">
+        <v>1.11</v>
+      </c>
+      <c r="AN84">
+        <v>1</v>
+      </c>
+      <c r="AO84">
+        <v>1.29</v>
+      </c>
+      <c r="AP84">
+        <v>0.89</v>
+      </c>
+      <c r="AQ84">
+        <v>1.5</v>
+      </c>
+      <c r="AR84">
+        <v>1.4</v>
+      </c>
+      <c r="AS84">
+        <v>1.95</v>
+      </c>
+      <c r="AT84">
+        <v>3.35</v>
+      </c>
+      <c r="AU84">
+        <v>6</v>
+      </c>
+      <c r="AV84">
+        <v>7</v>
+      </c>
+      <c r="AW84">
+        <v>2</v>
+      </c>
+      <c r="AX84">
+        <v>7</v>
+      </c>
+      <c r="AY84">
+        <v>8</v>
+      </c>
+      <c r="AZ84">
+        <v>14</v>
+      </c>
+      <c r="BA84">
         <v>4</v>
       </c>
-      <c r="M84">
-        <v>0</v>
-      </c>
-      <c r="N84">
-        <v>4</v>
-      </c>
-      <c r="O84" t="s">
-        <v>142</v>
-      </c>
-      <c r="P84" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q84">
-        <v>1.25</v>
-      </c>
-      <c r="R84">
-        <v>4.75</v>
-      </c>
-      <c r="S84">
-        <v>17</v>
-      </c>
-      <c r="T84">
-        <v>1.08</v>
-      </c>
-      <c r="U84">
-        <v>5.35</v>
-      </c>
-      <c r="V84">
-        <v>1.51</v>
-      </c>
-      <c r="W84">
-        <v>2.37</v>
-      </c>
-      <c r="X84">
-        <v>2.55</v>
-      </c>
-      <c r="Y84">
-        <v>1.46</v>
-      </c>
-      <c r="Z84">
-        <v>1.02</v>
-      </c>
-      <c r="AA84">
-        <v>21.03</v>
-      </c>
-      <c r="AB84">
-        <v>51</v>
-      </c>
-      <c r="AC84">
-        <v>1.01</v>
-      </c>
-      <c r="AD84">
-        <v>41</v>
-      </c>
-      <c r="AE84">
-        <v>1.02</v>
-      </c>
-      <c r="AF84">
-        <v>10</v>
-      </c>
-      <c r="AG84">
-        <v>1.13</v>
-      </c>
-      <c r="AH84">
-        <v>4.8</v>
-      </c>
-      <c r="AI84">
-        <v>2.23</v>
-      </c>
-      <c r="AJ84">
-        <v>1.51</v>
-      </c>
-      <c r="AK84">
-        <v>1.02</v>
-      </c>
-      <c r="AL84">
-        <v>1.01</v>
-      </c>
-      <c r="AM84">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="AN84">
-        <v>2.43</v>
-      </c>
-      <c r="AO84">
-        <v>0.14</v>
-      </c>
-      <c r="AP84">
-        <v>2.5</v>
-      </c>
-      <c r="AQ84">
-        <v>0.13</v>
-      </c>
-      <c r="AR84">
-        <v>2.37</v>
-      </c>
-      <c r="AS84">
-        <v>1.59</v>
-      </c>
-      <c r="AT84">
-        <v>3.96</v>
-      </c>
-      <c r="AU84">
-        <v>14</v>
-      </c>
-      <c r="AV84">
-        <v>4</v>
-      </c>
-      <c r="AW84">
+      <c r="BB84">
         <v>9</v>
       </c>
-      <c r="AX84">
-        <v>4</v>
-      </c>
-      <c r="AY84">
-        <v>23</v>
-      </c>
-      <c r="AZ84">
-        <v>8</v>
-      </c>
-      <c r="BA84">
-        <v>10</v>
-      </c>
-      <c r="BB84">
-        <v>2</v>
-      </c>
       <c r="BC84">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD84">
         <v>0</v>
@@ -18293,7 +18302,7 @@
         <v>84</v>
       </c>
       <c r="B85">
-        <v>7828541</v>
+        <v>7828542</v>
       </c>
       <c r="C85" t="s">
         <v>68</v>
@@ -18302,157 +18311,157 @@
         <v>69</v>
       </c>
       <c r="E85" s="2">
-        <v>45826.54166666666</v>
+        <v>45826.58333333334</v>
       </c>
       <c r="F85">
         <v>0</v>
       </c>
       <c r="G85" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="H85" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I85">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J85">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K85">
+        <v>0</v>
+      </c>
+      <c r="L85">
+        <v>1</v>
+      </c>
+      <c r="M85">
+        <v>0</v>
+      </c>
+      <c r="N85">
+        <v>1</v>
+      </c>
+      <c r="O85" t="s">
+        <v>143</v>
+      </c>
+      <c r="P85" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q85">
+        <v>1.77</v>
+      </c>
+      <c r="R85">
+        <v>2.64</v>
+      </c>
+      <c r="S85">
+        <v>6.74</v>
+      </c>
+      <c r="T85">
+        <v>1.16</v>
+      </c>
+      <c r="U85">
+        <v>4</v>
+      </c>
+      <c r="V85">
+        <v>1.95</v>
+      </c>
+      <c r="W85">
+        <v>1.73</v>
+      </c>
+      <c r="X85">
+        <v>4.2</v>
+      </c>
+      <c r="Y85">
+        <v>1.22</v>
+      </c>
+      <c r="Z85">
+        <v>1.29</v>
+      </c>
+      <c r="AA85">
+        <v>5</v>
+      </c>
+      <c r="AB85">
+        <v>6.5</v>
+      </c>
+      <c r="AC85">
+        <v>1.02</v>
+      </c>
+      <c r="AD85">
+        <v>19</v>
+      </c>
+      <c r="AE85">
+        <v>1.11</v>
+      </c>
+      <c r="AF85">
+        <v>5.8</v>
+      </c>
+      <c r="AG85">
+        <v>1.36</v>
+      </c>
+      <c r="AH85">
+        <v>2.76</v>
+      </c>
+      <c r="AI85">
+        <v>1.62</v>
+      </c>
+      <c r="AJ85">
+        <v>1.97</v>
+      </c>
+      <c r="AK85">
+        <v>1.02</v>
+      </c>
+      <c r="AL85">
+        <v>1.21</v>
+      </c>
+      <c r="AM85">
+        <v>3.2</v>
+      </c>
+      <c r="AN85">
+        <v>2</v>
+      </c>
+      <c r="AO85">
+        <v>0.89</v>
+      </c>
+      <c r="AP85">
+        <v>2.11</v>
+      </c>
+      <c r="AQ85">
+        <v>0.8</v>
+      </c>
+      <c r="AR85">
+        <v>1.93</v>
+      </c>
+      <c r="AS85">
+        <v>1.38</v>
+      </c>
+      <c r="AT85">
+        <v>3.31</v>
+      </c>
+      <c r="AU85">
+        <v>8</v>
+      </c>
+      <c r="AV85">
         <v>3</v>
       </c>
-      <c r="L85">
-        <v>1</v>
-      </c>
-      <c r="M85">
-        <v>2</v>
-      </c>
-      <c r="N85">
-        <v>3</v>
-      </c>
-      <c r="O85" t="s">
-        <v>108</v>
-      </c>
-      <c r="P85" t="s">
-        <v>201</v>
-      </c>
-      <c r="Q85">
-        <v>4.37</v>
-      </c>
-      <c r="R85">
-        <v>2.35</v>
-      </c>
-      <c r="S85">
-        <v>2.17</v>
-      </c>
-      <c r="T85">
-        <v>1.32</v>
-      </c>
-      <c r="U85">
-        <v>3.12</v>
-      </c>
-      <c r="V85">
-        <v>2.4</v>
-      </c>
-      <c r="W85">
-        <v>1.51</v>
-      </c>
-      <c r="X85">
-        <v>5.95</v>
-      </c>
-      <c r="Y85">
-        <v>1.12</v>
-      </c>
-      <c r="Z85">
-        <v>4.55</v>
-      </c>
-      <c r="AA85">
-        <v>3.98</v>
-      </c>
-      <c r="AB85">
-        <v>1.55</v>
-      </c>
-      <c r="AC85">
-        <v>1.03</v>
-      </c>
-      <c r="AD85">
-        <v>11</v>
-      </c>
-      <c r="AE85">
-        <v>1.22</v>
-      </c>
-      <c r="AF85">
-        <v>4.4</v>
-      </c>
-      <c r="AG85">
-        <v>1.68</v>
-      </c>
-      <c r="AH85">
-        <v>2.1</v>
-      </c>
-      <c r="AI85">
-        <v>1.78</v>
-      </c>
-      <c r="AJ85">
-        <v>1.89</v>
-      </c>
-      <c r="AK85">
-        <v>2.4</v>
-      </c>
-      <c r="AL85">
-        <v>1.22</v>
-      </c>
-      <c r="AM85">
-        <v>1.11</v>
-      </c>
-      <c r="AN85">
-        <v>1</v>
-      </c>
-      <c r="AO85">
-        <v>1.29</v>
-      </c>
-      <c r="AP85">
-        <v>0.89</v>
-      </c>
-      <c r="AQ85">
-        <v>1.5</v>
-      </c>
-      <c r="AR85">
-        <v>1.4</v>
-      </c>
-      <c r="AS85">
-        <v>1.95</v>
-      </c>
-      <c r="AT85">
-        <v>3.35</v>
-      </c>
-      <c r="AU85">
-        <v>6</v>
-      </c>
-      <c r="AV85">
-        <v>7</v>
-      </c>
       <c r="AW85">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="AX85">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AY85">
+        <v>25</v>
+      </c>
+      <c r="AZ85">
         <v>8</v>
       </c>
-      <c r="AZ85">
-        <v>14</v>
-      </c>
       <c r="BA85">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="BB85">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="BC85">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BD85">
         <v>0</v>
@@ -18499,7 +18508,7 @@
         <v>85</v>
       </c>
       <c r="B86">
-        <v>7828542</v>
+        <v>7828553</v>
       </c>
       <c r="C86" t="s">
         <v>68</v>
@@ -18508,195 +18517,401 @@
         <v>69</v>
       </c>
       <c r="E86" s="2">
-        <v>45826.58333333334</v>
+        <v>45829.35416666666</v>
       </c>
       <c r="F86">
         <v>0</v>
       </c>
       <c r="G86" t="s">
+        <v>70</v>
+      </c>
+      <c r="H86" t="s">
         <v>79</v>
       </c>
-      <c r="H86" t="s">
-        <v>77</v>
-      </c>
       <c r="I86">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J86">
         <v>0</v>
       </c>
       <c r="K86">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L86">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N86">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O86" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P86" t="s">
-        <v>81</v>
+        <v>203</v>
       </c>
       <c r="Q86">
-        <v>1.77</v>
+        <v>2.25</v>
       </c>
       <c r="R86">
-        <v>2.64</v>
+        <v>2.08</v>
       </c>
       <c r="S86">
-        <v>6.74</v>
+        <v>3.9</v>
       </c>
       <c r="T86">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="U86">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="V86">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="W86">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="X86">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="Y86">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="Z86">
-        <v>1.29</v>
+        <v>1.75</v>
       </c>
       <c r="AA86">
-        <v>5</v>
+        <v>3.42</v>
       </c>
       <c r="AB86">
-        <v>6.5</v>
+        <v>4.39</v>
       </c>
       <c r="AC86">
         <v>1.02</v>
       </c>
       <c r="AD86">
-        <v>19</v>
+        <v>10.4</v>
       </c>
       <c r="AE86">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AF86">
-        <v>5.8</v>
+        <v>3.9</v>
       </c>
       <c r="AG86">
-        <v>1.36</v>
+        <v>1.69</v>
       </c>
       <c r="AH86">
-        <v>2.76</v>
+        <v>2</v>
       </c>
       <c r="AI86">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AJ86">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="AK86">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="AL86">
         <v>1.21</v>
       </c>
       <c r="AM86">
-        <v>3.2</v>
+        <v>1.95</v>
       </c>
       <c r="AN86">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AO86">
-        <v>0.89</v>
+        <v>2.25</v>
       </c>
       <c r="AP86">
-        <v>2.11</v>
+        <v>2.56</v>
       </c>
       <c r="AQ86">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="AR86">
-        <v>1.93</v>
+        <v>2.42</v>
       </c>
       <c r="AS86">
-        <v>1.38</v>
+        <v>2.27</v>
       </c>
       <c r="AT86">
-        <v>3.31</v>
+        <v>4.69</v>
       </c>
       <c r="AU86">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AV86">
+        <v>5</v>
+      </c>
+      <c r="AW86">
+        <v>9</v>
+      </c>
+      <c r="AX86">
+        <v>2</v>
+      </c>
+      <c r="AY86">
+        <v>21</v>
+      </c>
+      <c r="AZ86">
+        <v>7</v>
+      </c>
+      <c r="BA86">
+        <v>9</v>
+      </c>
+      <c r="BB86">
+        <v>2</v>
+      </c>
+      <c r="BC86">
+        <v>11</v>
+      </c>
+      <c r="BD86">
+        <v>0</v>
+      </c>
+      <c r="BE86">
+        <v>0</v>
+      </c>
+      <c r="BF86">
+        <v>0</v>
+      </c>
+      <c r="BG86">
+        <v>0</v>
+      </c>
+      <c r="BH86">
+        <v>0</v>
+      </c>
+      <c r="BI86">
+        <v>0</v>
+      </c>
+      <c r="BJ86">
+        <v>0</v>
+      </c>
+      <c r="BK86">
+        <v>0</v>
+      </c>
+      <c r="BL86">
+        <v>0</v>
+      </c>
+      <c r="BM86">
+        <v>0</v>
+      </c>
+      <c r="BN86">
+        <v>0</v>
+      </c>
+      <c r="BO86">
+        <v>0</v>
+      </c>
+      <c r="BP86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:68">
+      <c r="A87" s="1">
+        <v>86</v>
+      </c>
+      <c r="B87">
+        <v>7828554</v>
+      </c>
+      <c r="C87" t="s">
+        <v>68</v>
+      </c>
+      <c r="D87" t="s">
+        <v>69</v>
+      </c>
+      <c r="E87" s="2">
+        <v>45829.54166666666</v>
+      </c>
+      <c r="F87">
+        <v>0</v>
+      </c>
+      <c r="G87" t="s">
+        <v>78</v>
+      </c>
+      <c r="H87" t="s">
+        <v>72</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>0</v>
+      </c>
+      <c r="K87">
+        <v>0</v>
+      </c>
+      <c r="L87">
+        <v>2</v>
+      </c>
+      <c r="M87">
+        <v>1</v>
+      </c>
+      <c r="N87">
         <v>3</v>
       </c>
-      <c r="AW86">
-        <v>17</v>
-      </c>
-      <c r="AX86">
+      <c r="O87" t="s">
+        <v>145</v>
+      </c>
+      <c r="P87" t="s">
+        <v>204</v>
+      </c>
+      <c r="Q87">
+        <v>3.3</v>
+      </c>
+      <c r="R87">
+        <v>2.19</v>
+      </c>
+      <c r="S87">
+        <v>2.69</v>
+      </c>
+      <c r="T87">
+        <v>1.3</v>
+      </c>
+      <c r="U87">
+        <v>3.1</v>
+      </c>
+      <c r="V87">
+        <v>2.55</v>
+      </c>
+      <c r="W87">
+        <v>1.46</v>
+      </c>
+      <c r="X87">
+        <v>5.75</v>
+      </c>
+      <c r="Y87">
+        <v>1.12</v>
+      </c>
+      <c r="Z87">
+        <v>2.93</v>
+      </c>
+      <c r="AA87">
+        <v>3.4</v>
+      </c>
+      <c r="AB87">
+        <v>2.15</v>
+      </c>
+      <c r="AC87">
+        <v>1.04</v>
+      </c>
+      <c r="AD87">
+        <v>12</v>
+      </c>
+      <c r="AE87">
+        <v>1.25</v>
+      </c>
+      <c r="AF87">
+        <v>3.8</v>
+      </c>
+      <c r="AG87">
+        <v>1.73</v>
+      </c>
+      <c r="AH87">
+        <v>2</v>
+      </c>
+      <c r="AI87">
+        <v>1.62</v>
+      </c>
+      <c r="AJ87">
+        <v>2.2</v>
+      </c>
+      <c r="AK87">
+        <v>1.59</v>
+      </c>
+      <c r="AL87">
+        <v>0</v>
+      </c>
+      <c r="AM87">
+        <v>1.35</v>
+      </c>
+      <c r="AN87">
+        <v>2.13</v>
+      </c>
+      <c r="AO87">
+        <v>2.75</v>
+      </c>
+      <c r="AP87">
+        <v>2.22</v>
+      </c>
+      <c r="AQ87">
+        <v>2.44</v>
+      </c>
+      <c r="AR87">
+        <v>2.07</v>
+      </c>
+      <c r="AS87">
+        <v>2.12</v>
+      </c>
+      <c r="AT87">
+        <v>4.19</v>
+      </c>
+      <c r="AU87">
         <v>5</v>
       </c>
-      <c r="AY86">
-        <v>25</v>
-      </c>
-      <c r="AZ86">
-        <v>8</v>
-      </c>
-      <c r="BA86">
-        <v>15</v>
-      </c>
-      <c r="BB86">
-        <v>1</v>
-      </c>
-      <c r="BC86">
-        <v>16</v>
-      </c>
-      <c r="BD86">
-        <v>0</v>
-      </c>
-      <c r="BE86">
-        <v>0</v>
-      </c>
-      <c r="BF86">
-        <v>0</v>
-      </c>
-      <c r="BG86">
-        <v>0</v>
-      </c>
-      <c r="BH86">
-        <v>0</v>
-      </c>
-      <c r="BI86">
-        <v>0</v>
-      </c>
-      <c r="BJ86">
-        <v>0</v>
-      </c>
-      <c r="BK86">
-        <v>0</v>
-      </c>
-      <c r="BL86">
-        <v>0</v>
-      </c>
-      <c r="BM86">
-        <v>0</v>
-      </c>
-      <c r="BN86">
-        <v>0</v>
-      </c>
-      <c r="BO86">
-        <v>0</v>
-      </c>
-      <c r="BP86">
+      <c r="AV87">
+        <v>5</v>
+      </c>
+      <c r="AW87">
+        <v>4</v>
+      </c>
+      <c r="AX87">
+        <v>5</v>
+      </c>
+      <c r="AY87">
+        <v>9</v>
+      </c>
+      <c r="AZ87">
+        <v>10</v>
+      </c>
+      <c r="BA87">
+        <v>3</v>
+      </c>
+      <c r="BB87">
+        <v>7</v>
+      </c>
+      <c r="BC87">
+        <v>10</v>
+      </c>
+      <c r="BD87">
+        <v>0</v>
+      </c>
+      <c r="BE87">
+        <v>0</v>
+      </c>
+      <c r="BF87">
+        <v>0</v>
+      </c>
+      <c r="BG87">
+        <v>0</v>
+      </c>
+      <c r="BH87">
+        <v>0</v>
+      </c>
+      <c r="BI87">
+        <v>0</v>
+      </c>
+      <c r="BJ87">
+        <v>0</v>
+      </c>
+      <c r="BK87">
+        <v>0</v>
+      </c>
+      <c r="BL87">
+        <v>0</v>
+      </c>
+      <c r="BM87">
+        <v>0</v>
+      </c>
+      <c r="BN87">
+        <v>0</v>
+      </c>
+      <c r="BO87">
+        <v>0</v>
+      </c>
+      <c r="BP87">
         <v>0</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
@@ -448,7 +448,7 @@
     <t>['80']</t>
   </si>
   <si>
-    <t>['16', '39', '58']</t>
+    <t>['16', '39', '57']</t>
   </si>
   <si>
     <t>['50', '68']</t>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="206">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -433,18 +433,21 @@
     <t>['53']</t>
   </si>
   <si>
+    <t>['84']</t>
+  </si>
+  <si>
     <t>['68', '72']</t>
   </si>
   <si>
     <t>['31', '8']</t>
   </si>
   <si>
+    <t>['16']</t>
+  </si>
+  <si>
     <t>['25', '21', '88', '84']</t>
   </si>
   <si>
-    <t>['16']</t>
-  </si>
-  <si>
     <t>['80']</t>
   </si>
   <si>
@@ -493,10 +496,10 @@
     <t>['86']</t>
   </si>
   <si>
+    <t>['84', '90+3']</t>
+  </si>
+  <si>
     <t>['74']</t>
-  </si>
-  <si>
-    <t>['84', '90+3']</t>
   </si>
   <si>
     <t>['68']</t>
@@ -990,7 +993,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP87"/>
+  <dimension ref="A1:BP88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1452,7 +1455,7 @@
         <v>81</v>
       </c>
       <c r="P3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -1658,7 +1661,7 @@
         <v>82</v>
       </c>
       <c r="P4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -1736,7 +1739,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ4">
         <v>2</v>
@@ -1864,7 +1867,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q5">
         <v>7</v>
@@ -1945,7 +1948,7 @@
         <v>1</v>
       </c>
       <c r="AQ5">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2070,7 +2073,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2354,7 +2357,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ7">
         <v>1.63</v>
@@ -2482,7 +2485,7 @@
         <v>85</v>
       </c>
       <c r="P8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q8">
         <v>8.5</v>
@@ -2688,7 +2691,7 @@
         <v>81</v>
       </c>
       <c r="P9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -3306,7 +3309,7 @@
         <v>88</v>
       </c>
       <c r="P12" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q12">
         <v>8</v>
@@ -3593,7 +3596,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ13">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR13">
         <v>1.59</v>
@@ -3718,7 +3721,7 @@
         <v>81</v>
       </c>
       <c r="P14" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q14">
         <v>5.5</v>
@@ -3924,7 +3927,7 @@
         <v>90</v>
       </c>
       <c r="P15" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q15">
         <v>2.5</v>
@@ -4130,7 +4133,7 @@
         <v>91</v>
       </c>
       <c r="P16" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q16">
         <v>2.1</v>
@@ -4336,7 +4339,7 @@
         <v>81</v>
       </c>
       <c r="P17" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q17">
         <v>2.38</v>
@@ -4542,7 +4545,7 @@
         <v>81</v>
       </c>
       <c r="P18" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q18">
         <v>3.4</v>
@@ -4826,7 +4829,7 @@
         <v>3</v>
       </c>
       <c r="AP19">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ19">
         <v>0.5</v>
@@ -5160,7 +5163,7 @@
         <v>94</v>
       </c>
       <c r="P21" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q21">
         <v>1.91</v>
@@ -5530,7 +5533,7 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>7828480</v>
+        <v>7828479</v>
       </c>
       <c r="C23" t="s">
         <v>68</v>
@@ -5545,10 +5548,10 @@
         <v>5</v>
       </c>
       <c r="G23" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H23" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -5560,136 +5563,136 @@
         <v>0</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O23" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="P23" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q23">
-        <v>5.5</v>
+        <v>3.1</v>
       </c>
       <c r="R23">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S23">
-        <v>1.95</v>
+        <v>2.75</v>
       </c>
       <c r="T23">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="U23">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="V23">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="W23">
+        <v>1.52</v>
+      </c>
+      <c r="X23">
+        <v>5.8</v>
+      </c>
+      <c r="Y23">
+        <v>1.12</v>
+      </c>
+      <c r="Z23">
+        <v>2.74</v>
+      </c>
+      <c r="AA23">
+        <v>3.73</v>
+      </c>
+      <c r="AB23">
+        <v>2.29</v>
+      </c>
+      <c r="AC23">
+        <v>1.03</v>
+      </c>
+      <c r="AD23">
+        <v>12</v>
+      </c>
+      <c r="AE23">
+        <v>1.2</v>
+      </c>
+      <c r="AF23">
+        <v>4.2</v>
+      </c>
+      <c r="AG23">
         <v>1.55</v>
       </c>
-      <c r="X23">
-        <v>5</v>
-      </c>
-      <c r="Y23">
-        <v>1.15</v>
-      </c>
-      <c r="Z23">
-        <v>6.6</v>
-      </c>
-      <c r="AA23">
-        <v>4.3</v>
-      </c>
-      <c r="AB23">
-        <v>1.46</v>
-      </c>
-      <c r="AC23">
-        <v>1.02</v>
-      </c>
-      <c r="AD23">
-        <v>13</v>
-      </c>
-      <c r="AE23">
-        <v>1.22</v>
-      </c>
-      <c r="AF23">
-        <v>4</v>
-      </c>
-      <c r="AG23">
-        <v>1.65</v>
-      </c>
       <c r="AH23">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AI23">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AJ23">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AK23">
-        <v>2.45</v>
+        <v>1.57</v>
       </c>
       <c r="AL23">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AM23">
-        <v>1.12</v>
+        <v>1.43</v>
       </c>
       <c r="AN23">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AO23">
         <v>3</v>
       </c>
       <c r="AP23">
-        <v>1.67</v>
+        <v>2.11</v>
       </c>
       <c r="AQ23">
-        <v>2</v>
+        <v>2.44</v>
       </c>
       <c r="AR23">
-        <v>1.34</v>
+        <v>3.56</v>
       </c>
       <c r="AS23">
-        <v>2.41</v>
+        <v>2.95</v>
       </c>
       <c r="AT23">
-        <v>3.75</v>
+        <v>6.51</v>
       </c>
       <c r="AU23">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AV23">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AW23">
         <v>4</v>
       </c>
       <c r="AX23">
+        <v>6</v>
+      </c>
+      <c r="AY23">
+        <v>13</v>
+      </c>
+      <c r="AZ23">
+        <v>17</v>
+      </c>
+      <c r="BA23">
         <v>5</v>
       </c>
-      <c r="AY23">
-        <v>10</v>
-      </c>
-      <c r="AZ23">
-        <v>10</v>
-      </c>
-      <c r="BA23">
-        <v>2</v>
-      </c>
       <c r="BB23">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="BC23">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="BD23">
         <v>0</v>
@@ -5736,7 +5739,7 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>7828479</v>
+        <v>7828480</v>
       </c>
       <c r="C24" t="s">
         <v>68</v>
@@ -5751,10 +5754,10 @@
         <v>5</v>
       </c>
       <c r="G24" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H24" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -5766,136 +5769,136 @@
         <v>0</v>
       </c>
       <c r="L24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O24" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="P24" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q24">
+        <v>5.5</v>
+      </c>
+      <c r="R24">
+        <v>2.4</v>
+      </c>
+      <c r="S24">
+        <v>1.95</v>
+      </c>
+      <c r="T24">
+        <v>1.31</v>
+      </c>
+      <c r="U24">
         <v>3.1</v>
       </c>
-      <c r="R24">
-        <v>2.38</v>
-      </c>
-      <c r="S24">
-        <v>2.75</v>
-      </c>
-      <c r="T24">
-        <v>1.29</v>
-      </c>
-      <c r="U24">
-        <v>3.25</v>
-      </c>
       <c r="V24">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="W24">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="X24">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="Y24">
+        <v>1.15</v>
+      </c>
+      <c r="Z24">
+        <v>6.6</v>
+      </c>
+      <c r="AA24">
+        <v>4.3</v>
+      </c>
+      <c r="AB24">
+        <v>1.46</v>
+      </c>
+      <c r="AC24">
+        <v>1.02</v>
+      </c>
+      <c r="AD24">
+        <v>13</v>
+      </c>
+      <c r="AE24">
+        <v>1.22</v>
+      </c>
+      <c r="AF24">
+        <v>4</v>
+      </c>
+      <c r="AG24">
+        <v>1.65</v>
+      </c>
+      <c r="AH24">
+        <v>2.05</v>
+      </c>
+      <c r="AI24">
+        <v>1.7</v>
+      </c>
+      <c r="AJ24">
+        <v>2</v>
+      </c>
+      <c r="AK24">
+        <v>2.45</v>
+      </c>
+      <c r="AL24">
+        <v>1.23</v>
+      </c>
+      <c r="AM24">
         <v>1.12</v>
       </c>
-      <c r="Z24">
-        <v>2.74</v>
-      </c>
-      <c r="AA24">
-        <v>3.73</v>
-      </c>
-      <c r="AB24">
-        <v>2.29</v>
-      </c>
-      <c r="AC24">
-        <v>1.03</v>
-      </c>
-      <c r="AD24">
-        <v>12</v>
-      </c>
-      <c r="AE24">
-        <v>1.2</v>
-      </c>
-      <c r="AF24">
-        <v>4.2</v>
-      </c>
-      <c r="AG24">
-        <v>1.55</v>
-      </c>
-      <c r="AH24">
-        <v>2.2</v>
-      </c>
-      <c r="AI24">
-        <v>1.55</v>
-      </c>
-      <c r="AJ24">
-        <v>2.25</v>
-      </c>
-      <c r="AK24">
-        <v>1.57</v>
-      </c>
-      <c r="AL24">
-        <v>1.27</v>
-      </c>
-      <c r="AM24">
-        <v>1.43</v>
-      </c>
       <c r="AN24">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AO24">
         <v>3</v>
       </c>
       <c r="AP24">
-        <v>2.11</v>
+        <v>1.67</v>
       </c>
       <c r="AQ24">
-        <v>2.44</v>
+        <v>2</v>
       </c>
       <c r="AR24">
-        <v>3.56</v>
+        <v>1.34</v>
       </c>
       <c r="AS24">
-        <v>2.95</v>
+        <v>2.41</v>
       </c>
       <c r="AT24">
-        <v>6.51</v>
+        <v>3.75</v>
       </c>
       <c r="AU24">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AV24">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AW24">
         <v>4</v>
       </c>
       <c r="AX24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY24">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AZ24">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="BA24">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BB24">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="BC24">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="BD24">
         <v>0</v>
@@ -5984,7 +5987,7 @@
         <v>97</v>
       </c>
       <c r="P25" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q25">
         <v>2.38</v>
@@ -6190,7 +6193,7 @@
         <v>98</v>
       </c>
       <c r="P26" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q26">
         <v>3.1</v>
@@ -6602,7 +6605,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q28">
         <v>1.3</v>
@@ -6808,7 +6811,7 @@
         <v>101</v>
       </c>
       <c r="P29" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q29">
         <v>5</v>
@@ -7426,7 +7429,7 @@
         <v>81</v>
       </c>
       <c r="P32" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q32">
         <v>6</v>
@@ -7632,7 +7635,7 @@
         <v>104</v>
       </c>
       <c r="P33" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q33">
         <v>8.449999999999999</v>
@@ -7713,7 +7716,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ33">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR33">
         <v>1.28</v>
@@ -8044,7 +8047,7 @@
         <v>105</v>
       </c>
       <c r="P35" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q35">
         <v>2.2</v>
@@ -8250,7 +8253,7 @@
         <v>106</v>
       </c>
       <c r="P36" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q36">
         <v>4.25</v>
@@ -8534,10 +8537,10 @@
         <v>2</v>
       </c>
       <c r="AP37">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ37">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR37">
         <v>1.88</v>
@@ -8868,7 +8871,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q39">
         <v>3.2</v>
@@ -9074,7 +9077,7 @@
         <v>81</v>
       </c>
       <c r="P40" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q40">
         <v>12</v>
@@ -9280,7 +9283,7 @@
         <v>110</v>
       </c>
       <c r="P41" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q41">
         <v>3.77</v>
@@ -9692,7 +9695,7 @@
         <v>112</v>
       </c>
       <c r="P43" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q43">
         <v>1.35</v>
@@ -9898,7 +9901,7 @@
         <v>113</v>
       </c>
       <c r="P44" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q44">
         <v>1.66</v>
@@ -9976,7 +9979,7 @@
         <v>1</v>
       </c>
       <c r="AP44">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ44">
         <v>0.8</v>
@@ -10104,7 +10107,7 @@
         <v>114</v>
       </c>
       <c r="P45" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q45">
         <v>4.75</v>
@@ -10310,7 +10313,7 @@
         <v>115</v>
       </c>
       <c r="P46" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q46">
         <v>5.2</v>
@@ -10516,7 +10519,7 @@
         <v>81</v>
       </c>
       <c r="P47" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q47">
         <v>2.35</v>
@@ -10803,7 +10806,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ48">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR48">
         <v>1.68</v>
@@ -11134,7 +11137,7 @@
         <v>117</v>
       </c>
       <c r="P50" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q50">
         <v>2.62</v>
@@ -11212,7 +11215,7 @@
         <v>1.8</v>
       </c>
       <c r="AP50">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ50">
         <v>2</v>
@@ -11340,7 +11343,7 @@
         <v>118</v>
       </c>
       <c r="P51" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q51">
         <v>4.55</v>
@@ -11546,7 +11549,7 @@
         <v>81</v>
       </c>
       <c r="P52" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q52">
         <v>6.5</v>
@@ -11752,7 +11755,7 @@
         <v>119</v>
       </c>
       <c r="P53" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q53">
         <v>3.35</v>
@@ -12370,7 +12373,7 @@
         <v>122</v>
       </c>
       <c r="P56" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q56">
         <v>1.56</v>
@@ -12576,7 +12579,7 @@
         <v>81</v>
       </c>
       <c r="P57" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q57">
         <v>5.25</v>
@@ -12988,7 +12991,7 @@
         <v>81</v>
       </c>
       <c r="P59" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -13194,7 +13197,7 @@
         <v>124</v>
       </c>
       <c r="P60" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q60">
         <v>2.25</v>
@@ -13275,7 +13278,7 @@
         <v>2.56</v>
       </c>
       <c r="AQ60">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR60">
         <v>2.68</v>
@@ -13400,7 +13403,7 @@
         <v>125</v>
       </c>
       <c r="P61" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q61">
         <v>2.27</v>
@@ -13606,7 +13609,7 @@
         <v>126</v>
       </c>
       <c r="P62" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q62">
         <v>2.4</v>
@@ -13812,7 +13815,7 @@
         <v>127</v>
       </c>
       <c r="P63" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q63">
         <v>1.64</v>
@@ -14096,7 +14099,7 @@
         <v>2</v>
       </c>
       <c r="AP64">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ64">
         <v>2</v>
@@ -14430,7 +14433,7 @@
         <v>130</v>
       </c>
       <c r="P66" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q66">
         <v>4.35</v>
@@ -14842,7 +14845,7 @@
         <v>132</v>
       </c>
       <c r="P68" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q68">
         <v>9</v>
@@ -15048,7 +15051,7 @@
         <v>133</v>
       </c>
       <c r="P69" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q69">
         <v>1.91</v>
@@ -15254,7 +15257,7 @@
         <v>81</v>
       </c>
       <c r="P70" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q70">
         <v>2.35</v>
@@ -15335,7 +15338,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ70">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR70">
         <v>2.19</v>
@@ -15460,7 +15463,7 @@
         <v>134</v>
       </c>
       <c r="P71" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q71">
         <v>1.55</v>
@@ -15666,7 +15669,7 @@
         <v>135</v>
       </c>
       <c r="P72" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q72">
         <v>1.46</v>
@@ -15744,7 +15747,7 @@
         <v>0.57</v>
       </c>
       <c r="AP72">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ72">
         <v>0.78</v>
@@ -15872,7 +15875,7 @@
         <v>81</v>
       </c>
       <c r="P73" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q73">
         <v>8.5</v>
@@ -16078,7 +16081,7 @@
         <v>81</v>
       </c>
       <c r="P74" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q74">
         <v>2.2</v>
@@ -16284,7 +16287,7 @@
         <v>136</v>
       </c>
       <c r="P75" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q75">
         <v>2.3</v>
@@ -16490,7 +16493,7 @@
         <v>81</v>
       </c>
       <c r="P76" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q76">
         <v>8.949999999999999</v>
@@ -16696,7 +16699,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q77">
         <v>2.94</v>
@@ -16902,7 +16905,7 @@
         <v>81</v>
       </c>
       <c r="P78" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q78">
         <v>4.83</v>
@@ -17108,7 +17111,7 @@
         <v>138</v>
       </c>
       <c r="P79" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q79">
         <v>10</v>
@@ -17272,7 +17275,7 @@
         <v>79</v>
       </c>
       <c r="B80">
-        <v>7828537</v>
+        <v>7931423</v>
       </c>
       <c r="C80" t="s">
         <v>68</v>
@@ -17281,16 +17284,16 @@
         <v>69</v>
       </c>
       <c r="E80" s="2">
-        <v>45823.45833333334</v>
+        <v>45823.35416666666</v>
       </c>
       <c r="F80">
         <v>0</v>
       </c>
       <c r="G80" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="H80" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I80">
         <v>0</v>
@@ -17302,136 +17305,136 @@
         <v>0</v>
       </c>
       <c r="L80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M80">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N80">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O80" t="s">
         <v>139</v>
       </c>
       <c r="P80" t="s">
-        <v>81</v>
+        <v>146</v>
       </c>
       <c r="Q80">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R80">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="S80">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="T80">
+        <v>0</v>
+      </c>
+      <c r="U80">
+        <v>0</v>
+      </c>
+      <c r="V80">
+        <v>0</v>
+      </c>
+      <c r="W80">
+        <v>0</v>
+      </c>
+      <c r="X80">
+        <v>0</v>
+      </c>
+      <c r="Y80">
+        <v>0</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+      <c r="AA80">
+        <v>0</v>
+      </c>
+      <c r="AB80">
+        <v>0</v>
+      </c>
+      <c r="AC80">
+        <v>0</v>
+      </c>
+      <c r="AD80">
+        <v>0</v>
+      </c>
+      <c r="AE80">
+        <v>0</v>
+      </c>
+      <c r="AF80">
+        <v>0</v>
+      </c>
+      <c r="AG80">
+        <v>0</v>
+      </c>
+      <c r="AH80">
+        <v>0</v>
+      </c>
+      <c r="AI80">
+        <v>0</v>
+      </c>
+      <c r="AJ80">
+        <v>0</v>
+      </c>
+      <c r="AK80">
+        <v>0</v>
+      </c>
+      <c r="AL80">
+        <v>0</v>
+      </c>
+      <c r="AM80">
+        <v>0</v>
+      </c>
+      <c r="AN80">
+        <v>2</v>
+      </c>
+      <c r="AO80">
         <v>1.29</v>
       </c>
-      <c r="U80">
-        <v>3.34</v>
-      </c>
-      <c r="V80">
-        <v>2.44</v>
-      </c>
-      <c r="W80">
-        <v>1.55</v>
-      </c>
-      <c r="X80">
-        <v>5.5</v>
-      </c>
-      <c r="Y80">
-        <v>1.09</v>
-      </c>
-      <c r="Z80">
-        <v>1.84</v>
-      </c>
-      <c r="AA80">
-        <v>3.76</v>
-      </c>
-      <c r="AB80">
-        <v>3.23</v>
-      </c>
-      <c r="AC80">
-        <v>1.01</v>
-      </c>
-      <c r="AD80">
-        <v>13</v>
-      </c>
-      <c r="AE80">
-        <v>1.2</v>
-      </c>
-      <c r="AF80">
-        <v>4.2</v>
-      </c>
-      <c r="AG80">
-        <v>1.55</v>
-      </c>
-      <c r="AH80">
-        <v>2.2</v>
-      </c>
-      <c r="AI80">
-        <v>1.65</v>
-      </c>
-      <c r="AJ80">
-        <v>2.15</v>
-      </c>
-      <c r="AK80">
-        <v>1.25</v>
-      </c>
-      <c r="AL80">
-        <v>1.25</v>
-      </c>
-      <c r="AM80">
-        <v>2.15</v>
-      </c>
-      <c r="AN80">
-        <v>1.86</v>
-      </c>
-      <c r="AO80">
-        <v>2.29</v>
-      </c>
       <c r="AP80">
-        <v>2.11</v>
+        <v>1.78</v>
       </c>
       <c r="AQ80">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AR80">
-        <v>1.99</v>
+        <v>1.85</v>
       </c>
       <c r="AS80">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="AT80">
-        <v>3.81</v>
+        <v>3.8</v>
       </c>
       <c r="AU80">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AV80">
+        <v>5</v>
+      </c>
+      <c r="AW80">
+        <v>1</v>
+      </c>
+      <c r="AX80">
+        <v>5</v>
+      </c>
+      <c r="AY80">
         <v>6</v>
-      </c>
-      <c r="AW80">
-        <v>3</v>
-      </c>
-      <c r="AX80">
-        <v>4</v>
-      </c>
-      <c r="AY80">
-        <v>10</v>
       </c>
       <c r="AZ80">
         <v>10</v>
       </c>
       <c r="BA80">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="BB80">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="BC80">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="BD80">
         <v>0</v>
@@ -17478,7 +17481,7 @@
         <v>80</v>
       </c>
       <c r="B81">
-        <v>7828538</v>
+        <v>7828537</v>
       </c>
       <c r="C81" t="s">
         <v>68</v>
@@ -17487,157 +17490,157 @@
         <v>69</v>
       </c>
       <c r="E81" s="2">
-        <v>45825.5</v>
+        <v>45823.45833333334</v>
       </c>
       <c r="F81">
         <v>0</v>
       </c>
       <c r="G81" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="H81" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I81">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J81">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K81">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L81">
         <v>2</v>
       </c>
       <c r="M81">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N81">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O81" t="s">
         <v>140</v>
       </c>
       <c r="P81" t="s">
-        <v>200</v>
+        <v>81</v>
       </c>
       <c r="Q81">
-        <v>2.54</v>
+        <v>2.2</v>
       </c>
       <c r="R81">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="S81">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="T81">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="U81">
-        <v>3.8</v>
+        <v>3.34</v>
       </c>
       <c r="V81">
-        <v>2.19</v>
+        <v>2.44</v>
       </c>
       <c r="W81">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="X81">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="Y81">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="Z81">
-        <v>2.1</v>
+        <v>1.84</v>
       </c>
       <c r="AA81">
-        <v>3.5</v>
+        <v>3.76</v>
       </c>
       <c r="AB81">
-        <v>2.75</v>
+        <v>3.23</v>
       </c>
       <c r="AC81">
         <v>1.01</v>
       </c>
       <c r="AD81">
-        <v>14.7</v>
+        <v>13</v>
       </c>
       <c r="AE81">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AF81">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="AG81">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="AH81">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="AI81">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AJ81">
-        <v>2.7</v>
+        <v>2.15</v>
       </c>
       <c r="AK81">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AL81">
         <v>1.25</v>
       </c>
       <c r="AM81">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="AN81">
-        <v>1.13</v>
+        <v>1.86</v>
       </c>
       <c r="AO81">
-        <v>0.5</v>
+        <v>2.29</v>
       </c>
       <c r="AP81">
-        <v>1</v>
+        <v>2.11</v>
       </c>
       <c r="AQ81">
-        <v>0.78</v>
+        <v>2</v>
       </c>
       <c r="AR81">
-        <v>1.51</v>
+        <v>1.99</v>
       </c>
       <c r="AS81">
-        <v>1.22</v>
+        <v>1.82</v>
       </c>
       <c r="AT81">
-        <v>2.73</v>
+        <v>3.81</v>
       </c>
       <c r="AU81">
         <v>7</v>
       </c>
       <c r="AV81">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="AW81">
+        <v>3</v>
+      </c>
+      <c r="AX81">
+        <v>4</v>
+      </c>
+      <c r="AY81">
+        <v>10</v>
+      </c>
+      <c r="AZ81">
+        <v>10</v>
+      </c>
+      <c r="BA81">
+        <v>9</v>
+      </c>
+      <c r="BB81">
         <v>11</v>
       </c>
-      <c r="AX81">
-        <v>9</v>
-      </c>
-      <c r="AY81">
-        <v>18</v>
-      </c>
-      <c r="AZ81">
-        <v>21</v>
-      </c>
-      <c r="BA81">
-        <v>13</v>
-      </c>
-      <c r="BB81">
-        <v>6</v>
-      </c>
       <c r="BC81">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD81">
         <v>0</v>
@@ -17684,7 +17687,7 @@
         <v>81</v>
       </c>
       <c r="B82">
-        <v>7828540</v>
+        <v>7828538</v>
       </c>
       <c r="C82" t="s">
         <v>68</v>
@@ -17693,157 +17696,157 @@
         <v>69</v>
       </c>
       <c r="E82" s="2">
-        <v>45826.5</v>
+        <v>45825.5</v>
       </c>
       <c r="F82">
         <v>0</v>
       </c>
       <c r="G82" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H82" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I82">
         <v>2</v>
       </c>
       <c r="J82">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K82">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L82">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M82">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N82">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O82" t="s">
         <v>141</v>
       </c>
       <c r="P82" t="s">
-        <v>81</v>
+        <v>201</v>
       </c>
       <c r="Q82">
-        <v>1.25</v>
+        <v>2.54</v>
       </c>
       <c r="R82">
-        <v>4.75</v>
+        <v>2.34</v>
       </c>
       <c r="S82">
-        <v>17</v>
+        <v>3.3</v>
       </c>
       <c r="T82">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="U82">
-        <v>5.35</v>
+        <v>3.8</v>
       </c>
       <c r="V82">
-        <v>1.51</v>
+        <v>2.19</v>
       </c>
       <c r="W82">
-        <v>2.37</v>
+        <v>1.65</v>
       </c>
       <c r="X82">
-        <v>2.55</v>
+        <v>4.1</v>
       </c>
       <c r="Y82">
-        <v>1.46</v>
+        <v>1.17</v>
       </c>
       <c r="Z82">
-        <v>1.02</v>
+        <v>2.1</v>
       </c>
       <c r="AA82">
-        <v>21.03</v>
+        <v>3.5</v>
       </c>
       <c r="AB82">
-        <v>51</v>
+        <v>2.75</v>
       </c>
       <c r="AC82">
         <v>1.01</v>
       </c>
       <c r="AD82">
-        <v>41</v>
+        <v>14.7</v>
       </c>
       <c r="AE82">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="AF82">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AG82">
+        <v>1.45</v>
+      </c>
+      <c r="AH82">
+        <v>2.45</v>
+      </c>
+      <c r="AI82">
+        <v>1.4</v>
+      </c>
+      <c r="AJ82">
+        <v>2.7</v>
+      </c>
+      <c r="AK82">
+        <v>1.29</v>
+      </c>
+      <c r="AL82">
+        <v>1.25</v>
+      </c>
+      <c r="AM82">
+        <v>1.67</v>
+      </c>
+      <c r="AN82">
         <v>1.13</v>
       </c>
-      <c r="AH82">
-        <v>4.8</v>
-      </c>
-      <c r="AI82">
-        <v>2.23</v>
-      </c>
-      <c r="AJ82">
+      <c r="AO82">
+        <v>0.5</v>
+      </c>
+      <c r="AP82">
+        <v>1</v>
+      </c>
+      <c r="AQ82">
+        <v>0.78</v>
+      </c>
+      <c r="AR82">
         <v>1.51</v>
       </c>
-      <c r="AK82">
-        <v>1.02</v>
-      </c>
-      <c r="AL82">
-        <v>1.01</v>
-      </c>
-      <c r="AM82">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="AN82">
-        <v>2.43</v>
-      </c>
-      <c r="AO82">
-        <v>0.14</v>
-      </c>
-      <c r="AP82">
-        <v>2.56</v>
-      </c>
-      <c r="AQ82">
-        <v>0.13</v>
-      </c>
-      <c r="AR82">
-        <v>2.37</v>
-      </c>
       <c r="AS82">
-        <v>1.59</v>
+        <v>1.22</v>
       </c>
       <c r="AT82">
-        <v>3.96</v>
+        <v>2.73</v>
       </c>
       <c r="AU82">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="AV82">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AW82">
+        <v>11</v>
+      </c>
+      <c r="AX82">
         <v>9</v>
       </c>
-      <c r="AX82">
-        <v>4</v>
-      </c>
       <c r="AY82">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AZ82">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="BA82">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BB82">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BC82">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="BD82">
         <v>0</v>
@@ -17932,7 +17935,7 @@
         <v>142</v>
       </c>
       <c r="P83" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q83">
         <v>3.8</v>
@@ -18096,7 +18099,7 @@
         <v>83</v>
       </c>
       <c r="B84">
-        <v>7828541</v>
+        <v>7828540</v>
       </c>
       <c r="C84" t="s">
         <v>68</v>
@@ -18105,157 +18108,157 @@
         <v>69</v>
       </c>
       <c r="E84" s="2">
-        <v>45826.54166666666</v>
+        <v>45826.5</v>
       </c>
       <c r="F84">
         <v>0</v>
       </c>
       <c r="G84" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H84" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="I84">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J84">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K84">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L84">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M84">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N84">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O84" t="s">
-        <v>108</v>
+        <v>143</v>
       </c>
       <c r="P84" t="s">
-        <v>202</v>
+        <v>81</v>
       </c>
       <c r="Q84">
-        <v>4.37</v>
+        <v>1.25</v>
       </c>
       <c r="R84">
-        <v>2.35</v>
+        <v>4.75</v>
       </c>
       <c r="S84">
-        <v>2.17</v>
+        <v>17</v>
       </c>
       <c r="T84">
-        <v>1.32</v>
+        <v>1.08</v>
       </c>
       <c r="U84">
-        <v>3.12</v>
+        <v>5.35</v>
       </c>
       <c r="V84">
-        <v>2.4</v>
+        <v>1.51</v>
       </c>
       <c r="W84">
+        <v>2.37</v>
+      </c>
+      <c r="X84">
+        <v>2.55</v>
+      </c>
+      <c r="Y84">
+        <v>1.46</v>
+      </c>
+      <c r="Z84">
+        <v>1.02</v>
+      </c>
+      <c r="AA84">
+        <v>21.03</v>
+      </c>
+      <c r="AB84">
+        <v>51</v>
+      </c>
+      <c r="AC84">
+        <v>1.01</v>
+      </c>
+      <c r="AD84">
+        <v>41</v>
+      </c>
+      <c r="AE84">
+        <v>1.02</v>
+      </c>
+      <c r="AF84">
+        <v>10</v>
+      </c>
+      <c r="AG84">
+        <v>1.13</v>
+      </c>
+      <c r="AH84">
+        <v>4.8</v>
+      </c>
+      <c r="AI84">
+        <v>2.23</v>
+      </c>
+      <c r="AJ84">
         <v>1.51</v>
       </c>
-      <c r="X84">
-        <v>5.95</v>
-      </c>
-      <c r="Y84">
-        <v>1.12</v>
-      </c>
-      <c r="Z84">
-        <v>4.55</v>
-      </c>
-      <c r="AA84">
-        <v>3.98</v>
-      </c>
-      <c r="AB84">
-        <v>1.55</v>
-      </c>
-      <c r="AC84">
-        <v>1.03</v>
-      </c>
-      <c r="AD84">
-        <v>11</v>
-      </c>
-      <c r="AE84">
-        <v>1.22</v>
-      </c>
-      <c r="AF84">
-        <v>4.4</v>
-      </c>
-      <c r="AG84">
-        <v>1.68</v>
-      </c>
-      <c r="AH84">
-        <v>2.1</v>
-      </c>
-      <c r="AI84">
-        <v>1.78</v>
-      </c>
-      <c r="AJ84">
-        <v>1.89</v>
-      </c>
       <c r="AK84">
-        <v>2.4</v>
+        <v>1.02</v>
       </c>
       <c r="AL84">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="AM84">
-        <v>1.11</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AN84">
-        <v>1</v>
+        <v>2.43</v>
       </c>
       <c r="AO84">
-        <v>1.29</v>
+        <v>0.14</v>
       </c>
       <c r="AP84">
-        <v>0.89</v>
+        <v>2.56</v>
       </c>
       <c r="AQ84">
-        <v>1.5</v>
+        <v>0.13</v>
       </c>
       <c r="AR84">
-        <v>1.4</v>
+        <v>2.37</v>
       </c>
       <c r="AS84">
-        <v>1.95</v>
+        <v>1.59</v>
       </c>
       <c r="AT84">
-        <v>3.35</v>
+        <v>3.96</v>
       </c>
       <c r="AU84">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="AV84">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AW84">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AX84">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AY84">
+        <v>23</v>
+      </c>
+      <c r="AZ84">
         <v>8</v>
       </c>
-      <c r="AZ84">
-        <v>14</v>
-      </c>
       <c r="BA84">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="BB84">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="BC84">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD84">
         <v>0</v>
@@ -18302,7 +18305,7 @@
         <v>84</v>
       </c>
       <c r="B85">
-        <v>7828542</v>
+        <v>7828541</v>
       </c>
       <c r="C85" t="s">
         <v>68</v>
@@ -18311,157 +18314,157 @@
         <v>69</v>
       </c>
       <c r="E85" s="2">
-        <v>45826.58333333334</v>
+        <v>45826.54166666666</v>
       </c>
       <c r="F85">
         <v>0</v>
       </c>
       <c r="G85" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="H85" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J85">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K85">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L85">
         <v>1</v>
       </c>
       <c r="M85">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N85">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O85" t="s">
-        <v>143</v>
+        <v>108</v>
       </c>
       <c r="P85" t="s">
-        <v>81</v>
+        <v>203</v>
       </c>
       <c r="Q85">
-        <v>1.77</v>
+        <v>4.37</v>
       </c>
       <c r="R85">
-        <v>2.64</v>
+        <v>2.35</v>
       </c>
       <c r="S85">
-        <v>6.74</v>
+        <v>2.17</v>
       </c>
       <c r="T85">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="U85">
+        <v>3.12</v>
+      </c>
+      <c r="V85">
+        <v>2.4</v>
+      </c>
+      <c r="W85">
+        <v>1.51</v>
+      </c>
+      <c r="X85">
+        <v>5.95</v>
+      </c>
+      <c r="Y85">
+        <v>1.12</v>
+      </c>
+      <c r="Z85">
+        <v>4.55</v>
+      </c>
+      <c r="AA85">
+        <v>3.98</v>
+      </c>
+      <c r="AB85">
+        <v>1.55</v>
+      </c>
+      <c r="AC85">
+        <v>1.03</v>
+      </c>
+      <c r="AD85">
+        <v>11</v>
+      </c>
+      <c r="AE85">
+        <v>1.22</v>
+      </c>
+      <c r="AF85">
+        <v>4.4</v>
+      </c>
+      <c r="AG85">
+        <v>1.68</v>
+      </c>
+      <c r="AH85">
+        <v>2.1</v>
+      </c>
+      <c r="AI85">
+        <v>1.78</v>
+      </c>
+      <c r="AJ85">
+        <v>1.89</v>
+      </c>
+      <c r="AK85">
+        <v>2.4</v>
+      </c>
+      <c r="AL85">
+        <v>1.22</v>
+      </c>
+      <c r="AM85">
+        <v>1.11</v>
+      </c>
+      <c r="AN85">
+        <v>1</v>
+      </c>
+      <c r="AO85">
+        <v>1.5</v>
+      </c>
+      <c r="AP85">
+        <v>0.89</v>
+      </c>
+      <c r="AQ85">
+        <v>1.67</v>
+      </c>
+      <c r="AR85">
+        <v>1.4</v>
+      </c>
+      <c r="AS85">
+        <v>1.88</v>
+      </c>
+      <c r="AT85">
+        <v>3.28</v>
+      </c>
+      <c r="AU85">
+        <v>6</v>
+      </c>
+      <c r="AV85">
+        <v>7</v>
+      </c>
+      <c r="AW85">
+        <v>2</v>
+      </c>
+      <c r="AX85">
+        <v>7</v>
+      </c>
+      <c r="AY85">
+        <v>8</v>
+      </c>
+      <c r="AZ85">
+        <v>14</v>
+      </c>
+      <c r="BA85">
         <v>4</v>
       </c>
-      <c r="V85">
-        <v>1.95</v>
-      </c>
-      <c r="W85">
-        <v>1.73</v>
-      </c>
-      <c r="X85">
-        <v>4.2</v>
-      </c>
-      <c r="Y85">
-        <v>1.22</v>
-      </c>
-      <c r="Z85">
-        <v>1.29</v>
-      </c>
-      <c r="AA85">
-        <v>5</v>
-      </c>
-      <c r="AB85">
-        <v>6.5</v>
-      </c>
-      <c r="AC85">
-        <v>1.02</v>
-      </c>
-      <c r="AD85">
-        <v>19</v>
-      </c>
-      <c r="AE85">
-        <v>1.11</v>
-      </c>
-      <c r="AF85">
-        <v>5.8</v>
-      </c>
-      <c r="AG85">
-        <v>1.36</v>
-      </c>
-      <c r="AH85">
-        <v>2.76</v>
-      </c>
-      <c r="AI85">
-        <v>1.62</v>
-      </c>
-      <c r="AJ85">
-        <v>1.97</v>
-      </c>
-      <c r="AK85">
-        <v>1.02</v>
-      </c>
-      <c r="AL85">
-        <v>1.21</v>
-      </c>
-      <c r="AM85">
-        <v>3.2</v>
-      </c>
-      <c r="AN85">
-        <v>2</v>
-      </c>
-      <c r="AO85">
-        <v>0.89</v>
-      </c>
-      <c r="AP85">
-        <v>2.11</v>
-      </c>
-      <c r="AQ85">
-        <v>0.8</v>
-      </c>
-      <c r="AR85">
-        <v>1.93</v>
-      </c>
-      <c r="AS85">
-        <v>1.38</v>
-      </c>
-      <c r="AT85">
-        <v>3.31</v>
-      </c>
-      <c r="AU85">
-        <v>8</v>
-      </c>
-      <c r="AV85">
-        <v>3</v>
-      </c>
-      <c r="AW85">
-        <v>17</v>
-      </c>
-      <c r="AX85">
-        <v>5</v>
-      </c>
-      <c r="AY85">
-        <v>25</v>
-      </c>
-      <c r="AZ85">
-        <v>8</v>
-      </c>
-      <c r="BA85">
-        <v>15</v>
-      </c>
       <c r="BB85">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="BC85">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BD85">
         <v>0</v>
@@ -18508,7 +18511,7 @@
         <v>85</v>
       </c>
       <c r="B86">
-        <v>7828553</v>
+        <v>7828542</v>
       </c>
       <c r="C86" t="s">
         <v>68</v>
@@ -18517,157 +18520,157 @@
         <v>69</v>
       </c>
       <c r="E86" s="2">
-        <v>45829.35416666666</v>
+        <v>45826.58333333334</v>
       </c>
       <c r="F86">
         <v>0</v>
       </c>
       <c r="G86" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="H86" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="I86">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J86">
         <v>0</v>
       </c>
       <c r="K86">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L86">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M86">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N86">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O86" t="s">
         <v>144</v>
       </c>
       <c r="P86" t="s">
-        <v>203</v>
+        <v>81</v>
       </c>
       <c r="Q86">
-        <v>2.25</v>
+        <v>1.77</v>
       </c>
       <c r="R86">
-        <v>2.08</v>
+        <v>2.64</v>
       </c>
       <c r="S86">
-        <v>3.9</v>
+        <v>6.74</v>
       </c>
       <c r="T86">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="U86">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="V86">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="W86">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="X86">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="Y86">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="Z86">
-        <v>1.75</v>
+        <v>1.29</v>
       </c>
       <c r="AA86">
-        <v>3.42</v>
+        <v>5</v>
       </c>
       <c r="AB86">
-        <v>4.39</v>
+        <v>6.5</v>
       </c>
       <c r="AC86">
         <v>1.02</v>
       </c>
       <c r="AD86">
-        <v>10.4</v>
+        <v>19</v>
       </c>
       <c r="AE86">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AF86">
-        <v>3.9</v>
+        <v>5.8</v>
       </c>
       <c r="AG86">
-        <v>1.69</v>
+        <v>1.36</v>
       </c>
       <c r="AH86">
-        <v>2</v>
+        <v>2.76</v>
       </c>
       <c r="AI86">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AJ86">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="AK86">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
       <c r="AL86">
         <v>1.21</v>
       </c>
       <c r="AM86">
-        <v>1.95</v>
+        <v>3.2</v>
       </c>
       <c r="AN86">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AO86">
-        <v>2.25</v>
+        <v>0.89</v>
       </c>
       <c r="AP86">
-        <v>2.56</v>
+        <v>2.11</v>
       </c>
       <c r="AQ86">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="AR86">
-        <v>2.42</v>
+        <v>1.93</v>
       </c>
       <c r="AS86">
-        <v>2.27</v>
+        <v>1.38</v>
       </c>
       <c r="AT86">
-        <v>4.69</v>
+        <v>3.31</v>
       </c>
       <c r="AU86">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AV86">
+        <v>3</v>
+      </c>
+      <c r="AW86">
+        <v>17</v>
+      </c>
+      <c r="AX86">
         <v>5</v>
       </c>
-      <c r="AW86">
-        <v>9</v>
-      </c>
-      <c r="AX86">
-        <v>2</v>
-      </c>
       <c r="AY86">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AZ86">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA86">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="BB86">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BC86">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="BD86">
         <v>0</v>
@@ -18714,7 +18717,7 @@
         <v>86</v>
       </c>
       <c r="B87">
-        <v>7828554</v>
+        <v>7828553</v>
       </c>
       <c r="C87" t="s">
         <v>68</v>
@@ -18723,34 +18726,34 @@
         <v>69</v>
       </c>
       <c r="E87" s="2">
-        <v>45829.54166666666</v>
+        <v>45829.35416666666</v>
       </c>
       <c r="F87">
         <v>0</v>
       </c>
       <c r="G87" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="H87" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="I87">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J87">
         <v>0</v>
       </c>
       <c r="K87">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L87">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M87">
         <v>1</v>
       </c>
       <c r="N87">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O87" t="s">
         <v>145</v>
@@ -18759,13 +18762,13 @@
         <v>204</v>
       </c>
       <c r="Q87">
-        <v>3.3</v>
+        <v>2.25</v>
       </c>
       <c r="R87">
-        <v>2.19</v>
+        <v>2.08</v>
       </c>
       <c r="S87">
-        <v>2.69</v>
+        <v>3.9</v>
       </c>
       <c r="T87">
         <v>1.3</v>
@@ -18774,144 +18777,350 @@
         <v>3.1</v>
       </c>
       <c r="V87">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="W87">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="X87">
-        <v>5.75</v>
+        <v>5.8</v>
       </c>
       <c r="Y87">
         <v>1.12</v>
       </c>
       <c r="Z87">
-        <v>2.93</v>
+        <v>1.75</v>
       </c>
       <c r="AA87">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="AB87">
-        <v>2.15</v>
+        <v>4.39</v>
       </c>
       <c r="AC87">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AD87">
+        <v>10.4</v>
+      </c>
+      <c r="AE87">
+        <v>1.2</v>
+      </c>
+      <c r="AF87">
+        <v>3.9</v>
+      </c>
+      <c r="AG87">
+        <v>1.69</v>
+      </c>
+      <c r="AH87">
+        <v>2</v>
+      </c>
+      <c r="AI87">
+        <v>1.67</v>
+      </c>
+      <c r="AJ87">
+        <v>2.1</v>
+      </c>
+      <c r="AK87">
+        <v>1.15</v>
+      </c>
+      <c r="AL87">
+        <v>1.21</v>
+      </c>
+      <c r="AM87">
+        <v>1.95</v>
+      </c>
+      <c r="AN87">
+        <v>2.5</v>
+      </c>
+      <c r="AO87">
+        <v>2.25</v>
+      </c>
+      <c r="AP87">
+        <v>2.56</v>
+      </c>
+      <c r="AQ87">
+        <v>2</v>
+      </c>
+      <c r="AR87">
+        <v>2.42</v>
+      </c>
+      <c r="AS87">
+        <v>2.27</v>
+      </c>
+      <c r="AT87">
+        <v>4.69</v>
+      </c>
+      <c r="AU87">
         <v>12</v>
-      </c>
-      <c r="AE87">
-        <v>1.25</v>
-      </c>
-      <c r="AF87">
-        <v>3.8</v>
-      </c>
-      <c r="AG87">
-        <v>1.73</v>
-      </c>
-      <c r="AH87">
-        <v>2</v>
-      </c>
-      <c r="AI87">
-        <v>1.62</v>
-      </c>
-      <c r="AJ87">
-        <v>2.2</v>
-      </c>
-      <c r="AK87">
-        <v>1.59</v>
-      </c>
-      <c r="AL87">
-        <v>0</v>
-      </c>
-      <c r="AM87">
-        <v>1.35</v>
-      </c>
-      <c r="AN87">
-        <v>2.13</v>
-      </c>
-      <c r="AO87">
-        <v>2.75</v>
-      </c>
-      <c r="AP87">
-        <v>2.22</v>
-      </c>
-      <c r="AQ87">
-        <v>2.44</v>
-      </c>
-      <c r="AR87">
-        <v>2.07</v>
-      </c>
-      <c r="AS87">
-        <v>2.12</v>
-      </c>
-      <c r="AT87">
-        <v>4.19</v>
-      </c>
-      <c r="AU87">
-        <v>5</v>
       </c>
       <c r="AV87">
         <v>5</v>
       </c>
       <c r="AW87">
+        <v>9</v>
+      </c>
+      <c r="AX87">
+        <v>2</v>
+      </c>
+      <c r="AY87">
+        <v>21</v>
+      </c>
+      <c r="AZ87">
+        <v>7</v>
+      </c>
+      <c r="BA87">
+        <v>9</v>
+      </c>
+      <c r="BB87">
+        <v>2</v>
+      </c>
+      <c r="BC87">
+        <v>11</v>
+      </c>
+      <c r="BD87">
+        <v>0</v>
+      </c>
+      <c r="BE87">
+        <v>0</v>
+      </c>
+      <c r="BF87">
+        <v>0</v>
+      </c>
+      <c r="BG87">
+        <v>0</v>
+      </c>
+      <c r="BH87">
+        <v>0</v>
+      </c>
+      <c r="BI87">
+        <v>0</v>
+      </c>
+      <c r="BJ87">
+        <v>0</v>
+      </c>
+      <c r="BK87">
+        <v>0</v>
+      </c>
+      <c r="BL87">
+        <v>0</v>
+      </c>
+      <c r="BM87">
+        <v>0</v>
+      </c>
+      <c r="BN87">
+        <v>0</v>
+      </c>
+      <c r="BO87">
+        <v>0</v>
+      </c>
+      <c r="BP87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:68">
+      <c r="A88" s="1">
+        <v>87</v>
+      </c>
+      <c r="B88">
+        <v>7828554</v>
+      </c>
+      <c r="C88" t="s">
+        <v>68</v>
+      </c>
+      <c r="D88" t="s">
+        <v>69</v>
+      </c>
+      <c r="E88" s="2">
+        <v>45829.54166666666</v>
+      </c>
+      <c r="F88">
+        <v>0</v>
+      </c>
+      <c r="G88" t="s">
+        <v>78</v>
+      </c>
+      <c r="H88" t="s">
+        <v>72</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>0</v>
+      </c>
+      <c r="K88">
+        <v>0</v>
+      </c>
+      <c r="L88">
+        <v>2</v>
+      </c>
+      <c r="M88">
+        <v>1</v>
+      </c>
+      <c r="N88">
+        <v>3</v>
+      </c>
+      <c r="O88" t="s">
+        <v>146</v>
+      </c>
+      <c r="P88" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q88">
+        <v>3.3</v>
+      </c>
+      <c r="R88">
+        <v>2.19</v>
+      </c>
+      <c r="S88">
+        <v>2.69</v>
+      </c>
+      <c r="T88">
+        <v>1.3</v>
+      </c>
+      <c r="U88">
+        <v>3.1</v>
+      </c>
+      <c r="V88">
+        <v>2.55</v>
+      </c>
+      <c r="W88">
+        <v>1.46</v>
+      </c>
+      <c r="X88">
+        <v>5.75</v>
+      </c>
+      <c r="Y88">
+        <v>1.12</v>
+      </c>
+      <c r="Z88">
+        <v>2.93</v>
+      </c>
+      <c r="AA88">
+        <v>3.4</v>
+      </c>
+      <c r="AB88">
+        <v>2.15</v>
+      </c>
+      <c r="AC88">
+        <v>1.04</v>
+      </c>
+      <c r="AD88">
+        <v>12</v>
+      </c>
+      <c r="AE88">
+        <v>1.25</v>
+      </c>
+      <c r="AF88">
+        <v>3.8</v>
+      </c>
+      <c r="AG88">
+        <v>1.73</v>
+      </c>
+      <c r="AH88">
+        <v>2</v>
+      </c>
+      <c r="AI88">
+        <v>1.62</v>
+      </c>
+      <c r="AJ88">
+        <v>2.2</v>
+      </c>
+      <c r="AK88">
+        <v>1.59</v>
+      </c>
+      <c r="AL88">
+        <v>0</v>
+      </c>
+      <c r="AM88">
+        <v>1.35</v>
+      </c>
+      <c r="AN88">
+        <v>2.13</v>
+      </c>
+      <c r="AO88">
+        <v>2.75</v>
+      </c>
+      <c r="AP88">
+        <v>2.22</v>
+      </c>
+      <c r="AQ88">
+        <v>2.44</v>
+      </c>
+      <c r="AR88">
+        <v>2.07</v>
+      </c>
+      <c r="AS88">
+        <v>2.12</v>
+      </c>
+      <c r="AT88">
+        <v>4.19</v>
+      </c>
+      <c r="AU88">
+        <v>5</v>
+      </c>
+      <c r="AV88">
+        <v>5</v>
+      </c>
+      <c r="AW88">
         <v>4</v>
       </c>
-      <c r="AX87">
+      <c r="AX88">
         <v>5</v>
       </c>
-      <c r="AY87">
+      <c r="AY88">
         <v>9</v>
       </c>
-      <c r="AZ87">
+      <c r="AZ88">
         <v>10</v>
       </c>
-      <c r="BA87">
+      <c r="BA88">
         <v>3</v>
       </c>
-      <c r="BB87">
+      <c r="BB88">
         <v>7</v>
       </c>
-      <c r="BC87">
+      <c r="BC88">
         <v>10</v>
       </c>
-      <c r="BD87">
-        <v>0</v>
-      </c>
-      <c r="BE87">
-        <v>0</v>
-      </c>
-      <c r="BF87">
-        <v>0</v>
-      </c>
-      <c r="BG87">
-        <v>0</v>
-      </c>
-      <c r="BH87">
-        <v>0</v>
-      </c>
-      <c r="BI87">
-        <v>0</v>
-      </c>
-      <c r="BJ87">
-        <v>0</v>
-      </c>
-      <c r="BK87">
-        <v>0</v>
-      </c>
-      <c r="BL87">
-        <v>0</v>
-      </c>
-      <c r="BM87">
-        <v>0</v>
-      </c>
-      <c r="BN87">
-        <v>0</v>
-      </c>
-      <c r="BO87">
-        <v>0</v>
-      </c>
-      <c r="BP87">
+      <c r="BD88">
+        <v>0</v>
+      </c>
+      <c r="BE88">
+        <v>0</v>
+      </c>
+      <c r="BF88">
+        <v>0</v>
+      </c>
+      <c r="BG88">
+        <v>0</v>
+      </c>
+      <c r="BH88">
+        <v>0</v>
+      </c>
+      <c r="BI88">
+        <v>0</v>
+      </c>
+      <c r="BJ88">
+        <v>0</v>
+      </c>
+      <c r="BK88">
+        <v>0</v>
+      </c>
+      <c r="BL88">
+        <v>0</v>
+      </c>
+      <c r="BM88">
+        <v>0</v>
+      </c>
+      <c r="BN88">
+        <v>0</v>
+      </c>
+      <c r="BO88">
+        <v>0</v>
+      </c>
+      <c r="BP88">
         <v>0</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
@@ -17428,10 +17428,10 @@
         <v>10</v>
       </c>
       <c r="BA80">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB80">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BC80">
         <v>10</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="209">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -457,6 +457,12 @@
     <t>['50', '68']</t>
   </si>
   <si>
+    <t>['9', '90+2']</t>
+  </si>
+  <si>
+    <t>['14', '58']</t>
+  </si>
+  <si>
     <t>['34', '59', '86']</t>
   </si>
   <si>
@@ -632,6 +638,9 @@
   </si>
   <si>
     <t>['83']</t>
+  </si>
+  <si>
+    <t>['8', '27']</t>
   </si>
 </sst>
 </file>
@@ -993,7 +1002,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP88"/>
+  <dimension ref="A1:BP90"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1327,7 +1336,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AQ2">
         <v>0.8</v>
@@ -1455,7 +1464,7 @@
         <v>81</v>
       </c>
       <c r="P3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -1533,10 +1542,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AQ3">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1661,7 +1670,7 @@
         <v>82</v>
       </c>
       <c r="P4" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -1742,7 +1751,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ4">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1867,7 +1876,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="Q5">
         <v>7</v>
@@ -2073,7 +2082,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2485,7 +2494,7 @@
         <v>85</v>
       </c>
       <c r="P8" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="Q8">
         <v>8.5</v>
@@ -2691,7 +2700,7 @@
         <v>81</v>
       </c>
       <c r="P9" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -3184,7 +3193,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ11">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3309,7 +3318,7 @@
         <v>88</v>
       </c>
       <c r="P12" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="Q12">
         <v>8</v>
@@ -3387,7 +3396,7 @@
         <v>3</v>
       </c>
       <c r="AP12">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AQ12">
         <v>2</v>
@@ -3721,7 +3730,7 @@
         <v>81</v>
       </c>
       <c r="P14" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="Q14">
         <v>5.5</v>
@@ -3927,7 +3936,7 @@
         <v>90</v>
       </c>
       <c r="P15" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="Q15">
         <v>2.5</v>
@@ -4133,7 +4142,7 @@
         <v>91</v>
       </c>
       <c r="P16" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="Q16">
         <v>2.1</v>
@@ -4339,7 +4348,7 @@
         <v>81</v>
       </c>
       <c r="P17" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q17">
         <v>2.38</v>
@@ -4545,7 +4554,7 @@
         <v>81</v>
       </c>
       <c r="P18" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Q18">
         <v>3.4</v>
@@ -4626,7 +4635,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ18">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AR18">
         <v>1.67</v>
@@ -5163,7 +5172,7 @@
         <v>94</v>
       </c>
       <c r="P21" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q21">
         <v>1.91</v>
@@ -5241,10 +5250,10 @@
         <v>1.5</v>
       </c>
       <c r="AP21">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AQ21">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AR21">
         <v>2.18</v>
@@ -5575,7 +5584,7 @@
         <v>96</v>
       </c>
       <c r="P23" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -5781,7 +5790,7 @@
         <v>81</v>
       </c>
       <c r="P24" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q24">
         <v>5.5</v>
@@ -5987,7 +5996,7 @@
         <v>97</v>
       </c>
       <c r="P25" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q25">
         <v>2.38</v>
@@ -6065,7 +6074,7 @@
         <v>1.5</v>
       </c>
       <c r="AP25">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AQ25">
         <v>0.8</v>
@@ -6193,7 +6202,7 @@
         <v>98</v>
       </c>
       <c r="P26" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q26">
         <v>3.1</v>
@@ -6605,7 +6614,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q28">
         <v>1.3</v>
@@ -6683,7 +6692,7 @@
         <v>1</v>
       </c>
       <c r="AP28">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AQ28">
         <v>0.5</v>
@@ -6811,7 +6820,7 @@
         <v>101</v>
       </c>
       <c r="P29" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q29">
         <v>5</v>
@@ -7429,7 +7438,7 @@
         <v>81</v>
       </c>
       <c r="P32" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q32">
         <v>6</v>
@@ -7510,7 +7519,7 @@
         <v>1</v>
       </c>
       <c r="AQ32">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AR32">
         <v>1.48</v>
@@ -7635,7 +7644,7 @@
         <v>104</v>
       </c>
       <c r="P33" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q33">
         <v>8.449999999999999</v>
@@ -7919,7 +7928,7 @@
         <v>3</v>
       </c>
       <c r="AP34">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AQ34">
         <v>2.44</v>
@@ -8047,7 +8056,7 @@
         <v>105</v>
       </c>
       <c r="P35" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q35">
         <v>2.2</v>
@@ -8125,7 +8134,7 @@
         <v>0</v>
       </c>
       <c r="AP35">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AQ35">
         <v>0.13</v>
@@ -8253,7 +8262,7 @@
         <v>106</v>
       </c>
       <c r="P36" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q36">
         <v>4.25</v>
@@ -8334,7 +8343,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ36">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AR36">
         <v>0.99</v>
@@ -8871,7 +8880,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q39">
         <v>3.2</v>
@@ -9077,7 +9086,7 @@
         <v>81</v>
       </c>
       <c r="P40" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q40">
         <v>12</v>
@@ -9283,7 +9292,7 @@
         <v>110</v>
       </c>
       <c r="P41" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q41">
         <v>3.77</v>
@@ -9364,7 +9373,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ41">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AR41">
         <v>1.43</v>
@@ -9695,7 +9704,7 @@
         <v>112</v>
       </c>
       <c r="P43" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q43">
         <v>1.35</v>
@@ -9901,7 +9910,7 @@
         <v>113</v>
       </c>
       <c r="P44" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q44">
         <v>1.66</v>
@@ -10107,7 +10116,7 @@
         <v>114</v>
       </c>
       <c r="P45" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q45">
         <v>4.75</v>
@@ -10185,10 +10194,10 @@
         <v>2.33</v>
       </c>
       <c r="AP45">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AQ45">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AR45">
         <v>1.06</v>
@@ -10313,7 +10322,7 @@
         <v>115</v>
       </c>
       <c r="P46" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q46">
         <v>5.2</v>
@@ -10519,7 +10528,7 @@
         <v>81</v>
       </c>
       <c r="P47" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q47">
         <v>2.35</v>
@@ -11009,7 +11018,7 @@
         <v>1</v>
       </c>
       <c r="AP49">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AQ49">
         <v>0.78</v>
@@ -11137,7 +11146,7 @@
         <v>117</v>
       </c>
       <c r="P50" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q50">
         <v>2.62</v>
@@ -11218,7 +11227,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ50">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AR50">
         <v>1.94</v>
@@ -11343,7 +11352,7 @@
         <v>118</v>
       </c>
       <c r="P51" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q51">
         <v>4.55</v>
@@ -11424,7 +11433,7 @@
         <v>1</v>
       </c>
       <c r="AQ51">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AR51">
         <v>1.64</v>
@@ -11549,7 +11558,7 @@
         <v>81</v>
       </c>
       <c r="P52" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q52">
         <v>6.5</v>
@@ -11627,7 +11636,7 @@
         <v>2.5</v>
       </c>
       <c r="AP52">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AQ52">
         <v>2.44</v>
@@ -11755,7 +11764,7 @@
         <v>119</v>
       </c>
       <c r="P53" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q53">
         <v>3.35</v>
@@ -12373,7 +12382,7 @@
         <v>122</v>
       </c>
       <c r="P56" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q56">
         <v>1.56</v>
@@ -12579,7 +12588,7 @@
         <v>81</v>
       </c>
       <c r="P57" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q57">
         <v>5.25</v>
@@ -12991,7 +13000,7 @@
         <v>81</v>
       </c>
       <c r="P59" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -13072,7 +13081,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ59">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AR59">
         <v>1.1</v>
@@ -13197,7 +13206,7 @@
         <v>124</v>
       </c>
       <c r="P60" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q60">
         <v>2.25</v>
@@ -13275,7 +13284,7 @@
         <v>1.2</v>
       </c>
       <c r="AP60">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AQ60">
         <v>1.67</v>
@@ -13403,7 +13412,7 @@
         <v>125</v>
       </c>
       <c r="P61" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q61">
         <v>2.27</v>
@@ -13609,7 +13618,7 @@
         <v>126</v>
       </c>
       <c r="P62" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q62">
         <v>2.4</v>
@@ -13687,7 +13696,7 @@
         <v>0.67</v>
       </c>
       <c r="AP62">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AQ62">
         <v>0.78</v>
@@ -13815,7 +13824,7 @@
         <v>127</v>
       </c>
       <c r="P63" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q63">
         <v>1.64</v>
@@ -14433,7 +14442,7 @@
         <v>130</v>
       </c>
       <c r="P66" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q66">
         <v>4.35</v>
@@ -14514,7 +14523,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ66">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AR66">
         <v>1.52</v>
@@ -14845,7 +14854,7 @@
         <v>132</v>
       </c>
       <c r="P68" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q68">
         <v>9</v>
@@ -15051,7 +15060,7 @@
         <v>133</v>
       </c>
       <c r="P69" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q69">
         <v>1.91</v>
@@ -15257,7 +15266,7 @@
         <v>81</v>
       </c>
       <c r="P70" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q70">
         <v>2.35</v>
@@ -15463,7 +15472,7 @@
         <v>134</v>
       </c>
       <c r="P71" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q71">
         <v>1.55</v>
@@ -15541,7 +15550,7 @@
         <v>1.5</v>
       </c>
       <c r="AP71">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AQ71">
         <v>1.63</v>
@@ -15669,7 +15678,7 @@
         <v>135</v>
       </c>
       <c r="P72" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q72">
         <v>1.46</v>
@@ -15875,7 +15884,7 @@
         <v>81</v>
       </c>
       <c r="P73" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q73">
         <v>8.5</v>
@@ -16081,7 +16090,7 @@
         <v>81</v>
       </c>
       <c r="P74" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q74">
         <v>2.2</v>
@@ -16162,7 +16171,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ74">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AR74">
         <v>2.22</v>
@@ -16287,7 +16296,7 @@
         <v>136</v>
       </c>
       <c r="P75" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q75">
         <v>2.3</v>
@@ -16365,7 +16374,7 @@
         <v>0.57</v>
       </c>
       <c r="AP75">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AQ75">
         <v>0.5</v>
@@ -16493,7 +16502,7 @@
         <v>81</v>
       </c>
       <c r="P76" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q76">
         <v>8.949999999999999</v>
@@ -16574,7 +16583,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ76">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AR76">
         <v>1.51</v>
@@ -16699,7 +16708,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q77">
         <v>2.94</v>
@@ -16905,7 +16914,7 @@
         <v>81</v>
       </c>
       <c r="P78" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q78">
         <v>4.83</v>
@@ -17111,7 +17120,7 @@
         <v>138</v>
       </c>
       <c r="P79" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q79">
         <v>10</v>
@@ -17604,7 +17613,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ81">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AR81">
         <v>1.99</v>
@@ -17729,7 +17738,7 @@
         <v>141</v>
       </c>
       <c r="P82" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q82">
         <v>2.54</v>
@@ -17935,7 +17944,7 @@
         <v>142</v>
       </c>
       <c r="P83" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q83">
         <v>3.8</v>
@@ -18219,7 +18228,7 @@
         <v>0.14</v>
       </c>
       <c r="AP84">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AQ84">
         <v>0.13</v>
@@ -18347,7 +18356,7 @@
         <v>108</v>
       </c>
       <c r="P85" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q85">
         <v>4.37</v>
@@ -18425,7 +18434,7 @@
         <v>1.5</v>
       </c>
       <c r="AP85">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AQ85">
         <v>1.67</v>
@@ -18759,7 +18768,7 @@
         <v>145</v>
       </c>
       <c r="P87" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q87">
         <v>2.25</v>
@@ -18837,10 +18846,10 @@
         <v>2.25</v>
       </c>
       <c r="AP87">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AQ87">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AR87">
         <v>2.42</v>
@@ -18965,7 +18974,7 @@
         <v>146</v>
       </c>
       <c r="P88" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q88">
         <v>3.3</v>
@@ -19121,6 +19130,418 @@
         <v>0</v>
       </c>
       <c r="BP88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:68">
+      <c r="A89" s="1">
+        <v>88</v>
+      </c>
+      <c r="B89">
+        <v>7828543</v>
+      </c>
+      <c r="C89" t="s">
+        <v>68</v>
+      </c>
+      <c r="D89" t="s">
+        <v>69</v>
+      </c>
+      <c r="E89" s="2">
+        <v>45835.54166666666</v>
+      </c>
+      <c r="F89">
+        <v>0</v>
+      </c>
+      <c r="G89" t="s">
+        <v>70</v>
+      </c>
+      <c r="H89" t="s">
+        <v>76</v>
+      </c>
+      <c r="I89">
+        <v>1</v>
+      </c>
+      <c r="J89">
+        <v>0</v>
+      </c>
+      <c r="K89">
+        <v>1</v>
+      </c>
+      <c r="L89">
+        <v>2</v>
+      </c>
+      <c r="M89">
+        <v>1</v>
+      </c>
+      <c r="N89">
+        <v>3</v>
+      </c>
+      <c r="O89" t="s">
+        <v>147</v>
+      </c>
+      <c r="P89" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q89">
+        <v>1.88</v>
+      </c>
+      <c r="R89">
+        <v>2.53</v>
+      </c>
+      <c r="S89">
+        <v>5.2</v>
+      </c>
+      <c r="T89">
+        <v>1.22</v>
+      </c>
+      <c r="U89">
+        <v>3.6</v>
+      </c>
+      <c r="V89">
+        <v>2.2</v>
+      </c>
+      <c r="W89">
+        <v>1.62</v>
+      </c>
+      <c r="X89">
+        <v>4.3</v>
+      </c>
+      <c r="Y89">
+        <v>1.16</v>
+      </c>
+      <c r="Z89">
+        <v>1.4</v>
+      </c>
+      <c r="AA89">
+        <v>4.65</v>
+      </c>
+      <c r="AB89">
+        <v>6</v>
+      </c>
+      <c r="AC89">
+        <v>1</v>
+      </c>
+      <c r="AD89">
+        <v>13.9</v>
+      </c>
+      <c r="AE89">
+        <v>1.17</v>
+      </c>
+      <c r="AF89">
+        <v>4.75</v>
+      </c>
+      <c r="AG89">
+        <v>1.5</v>
+      </c>
+      <c r="AH89">
+        <v>2.45</v>
+      </c>
+      <c r="AI89">
+        <v>1.73</v>
+      </c>
+      <c r="AJ89">
+        <v>2</v>
+      </c>
+      <c r="AK89">
+        <v>1.2</v>
+      </c>
+      <c r="AL89">
+        <v>1.17</v>
+      </c>
+      <c r="AM89">
+        <v>2.8</v>
+      </c>
+      <c r="AN89">
+        <v>2.56</v>
+      </c>
+      <c r="AO89">
+        <v>2</v>
+      </c>
+      <c r="AP89">
+        <v>2.6</v>
+      </c>
+      <c r="AQ89">
+        <v>1.78</v>
+      </c>
+      <c r="AR89">
+        <v>2.46</v>
+      </c>
+      <c r="AS89">
+        <v>1.77</v>
+      </c>
+      <c r="AT89">
+        <v>4.23</v>
+      </c>
+      <c r="AU89">
+        <v>8</v>
+      </c>
+      <c r="AV89">
+        <v>3</v>
+      </c>
+      <c r="AW89">
+        <v>8</v>
+      </c>
+      <c r="AX89">
+        <v>5</v>
+      </c>
+      <c r="AY89">
+        <v>16</v>
+      </c>
+      <c r="AZ89">
+        <v>8</v>
+      </c>
+      <c r="BA89">
+        <v>2</v>
+      </c>
+      <c r="BB89">
+        <v>3</v>
+      </c>
+      <c r="BC89">
+        <v>5</v>
+      </c>
+      <c r="BD89">
+        <v>0</v>
+      </c>
+      <c r="BE89">
+        <v>0</v>
+      </c>
+      <c r="BF89">
+        <v>0</v>
+      </c>
+      <c r="BG89">
+        <v>0</v>
+      </c>
+      <c r="BH89">
+        <v>0</v>
+      </c>
+      <c r="BI89">
+        <v>0</v>
+      </c>
+      <c r="BJ89">
+        <v>0</v>
+      </c>
+      <c r="BK89">
+        <v>0</v>
+      </c>
+      <c r="BL89">
+        <v>0</v>
+      </c>
+      <c r="BM89">
+        <v>0</v>
+      </c>
+      <c r="BN89">
+        <v>0</v>
+      </c>
+      <c r="BO89">
+        <v>0</v>
+      </c>
+      <c r="BP89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:68">
+      <c r="A90" s="1">
+        <v>89</v>
+      </c>
+      <c r="B90">
+        <v>7828544</v>
+      </c>
+      <c r="C90" t="s">
+        <v>68</v>
+      </c>
+      <c r="D90" t="s">
+        <v>69</v>
+      </c>
+      <c r="E90" s="2">
+        <v>45835.58333333334</v>
+      </c>
+      <c r="F90">
+        <v>0</v>
+      </c>
+      <c r="G90" t="s">
+        <v>71</v>
+      </c>
+      <c r="H90" t="s">
+        <v>79</v>
+      </c>
+      <c r="I90">
+        <v>1</v>
+      </c>
+      <c r="J90">
+        <v>2</v>
+      </c>
+      <c r="K90">
+        <v>3</v>
+      </c>
+      <c r="L90">
+        <v>2</v>
+      </c>
+      <c r="M90">
+        <v>2</v>
+      </c>
+      <c r="N90">
+        <v>4</v>
+      </c>
+      <c r="O90" t="s">
+        <v>148</v>
+      </c>
+      <c r="P90" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q90">
+        <v>5.6</v>
+      </c>
+      <c r="R90">
+        <v>2.5</v>
+      </c>
+      <c r="S90">
+        <v>1.92</v>
+      </c>
+      <c r="T90">
+        <v>1.29</v>
+      </c>
+      <c r="U90">
+        <v>3.5</v>
+      </c>
+      <c r="V90">
+        <v>2.3</v>
+      </c>
+      <c r="W90">
+        <v>1.53</v>
+      </c>
+      <c r="X90">
+        <v>4.9</v>
+      </c>
+      <c r="Y90">
+        <v>1.13</v>
+      </c>
+      <c r="Z90">
+        <v>5.5</v>
+      </c>
+      <c r="AA90">
+        <v>4.3</v>
+      </c>
+      <c r="AB90">
+        <v>1.44</v>
+      </c>
+      <c r="AC90">
+        <v>1.01</v>
+      </c>
+      <c r="AD90">
+        <v>11</v>
+      </c>
+      <c r="AE90">
+        <v>1.12</v>
+      </c>
+      <c r="AF90">
+        <v>4.4</v>
+      </c>
+      <c r="AG90">
+        <v>1.66</v>
+      </c>
+      <c r="AH90">
+        <v>2.2</v>
+      </c>
+      <c r="AI90">
+        <v>1.72</v>
+      </c>
+      <c r="AJ90">
+        <v>2.05</v>
+      </c>
+      <c r="AK90">
+        <v>1.2</v>
+      </c>
+      <c r="AL90">
+        <v>1.17</v>
+      </c>
+      <c r="AM90">
+        <v>1.06</v>
+      </c>
+      <c r="AN90">
+        <v>0.89</v>
+      </c>
+      <c r="AO90">
+        <v>2</v>
+      </c>
+      <c r="AP90">
+        <v>0.9</v>
+      </c>
+      <c r="AQ90">
+        <v>1.9</v>
+      </c>
+      <c r="AR90">
+        <v>1.38</v>
+      </c>
+      <c r="AS90">
+        <v>2.14</v>
+      </c>
+      <c r="AT90">
+        <v>3.52</v>
+      </c>
+      <c r="AU90">
+        <v>6</v>
+      </c>
+      <c r="AV90">
+        <v>8</v>
+      </c>
+      <c r="AW90">
+        <v>6</v>
+      </c>
+      <c r="AX90">
+        <v>10</v>
+      </c>
+      <c r="AY90">
+        <v>12</v>
+      </c>
+      <c r="AZ90">
+        <v>18</v>
+      </c>
+      <c r="BA90">
+        <v>7</v>
+      </c>
+      <c r="BB90">
+        <v>7</v>
+      </c>
+      <c r="BC90">
+        <v>14</v>
+      </c>
+      <c r="BD90">
+        <v>0</v>
+      </c>
+      <c r="BE90">
+        <v>0</v>
+      </c>
+      <c r="BF90">
+        <v>0</v>
+      </c>
+      <c r="BG90">
+        <v>0</v>
+      </c>
+      <c r="BH90">
+        <v>0</v>
+      </c>
+      <c r="BI90">
+        <v>0</v>
+      </c>
+      <c r="BJ90">
+        <v>0</v>
+      </c>
+      <c r="BK90">
+        <v>0</v>
+      </c>
+      <c r="BL90">
+        <v>0</v>
+      </c>
+      <c r="BM90">
+        <v>0</v>
+      </c>
+      <c r="BN90">
+        <v>0</v>
+      </c>
+      <c r="BO90">
+        <v>0</v>
+      </c>
+      <c r="BP90">
         <v>0</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="210">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -641,6 +641,9 @@
   </si>
   <si>
     <t>['8', '27']</t>
+  </si>
+  <si>
+    <t>['22', '55']</t>
   </si>
 </sst>
 </file>
@@ -1002,7 +1005,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP90"/>
+  <dimension ref="A1:BP91"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1957,7 +1960,7 @@
         <v>1</v>
       </c>
       <c r="AQ5">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2572,7 +2575,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ8">
         <v>2</v>
@@ -3605,7 +3608,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ13">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AR13">
         <v>1.59</v>
@@ -4426,7 +4429,7 @@
         <v>3</v>
       </c>
       <c r="AP17">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ17">
         <v>1.63</v>
@@ -6898,7 +6901,7 @@
         <v>3</v>
       </c>
       <c r="AP29">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ29">
         <v>2.44</v>
@@ -7725,7 +7728,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ33">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AR33">
         <v>1.28</v>
@@ -8340,7 +8343,7 @@
         <v>2</v>
       </c>
       <c r="AP36">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ36">
         <v>1.78</v>
@@ -8549,7 +8552,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ37">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AR37">
         <v>1.88</v>
@@ -9576,7 +9579,7 @@
         <v>0.75</v>
       </c>
       <c r="AP42">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ42">
         <v>0.5</v>
@@ -10815,7 +10818,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ48">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AR48">
         <v>1.68</v>
@@ -13078,7 +13081,7 @@
         <v>2</v>
       </c>
       <c r="AP59">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ59">
         <v>1.9</v>
@@ -13287,7 +13290,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ60">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AR60">
         <v>2.68</v>
@@ -14726,7 +14729,7 @@
         <v>0.17</v>
       </c>
       <c r="AP67">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ67">
         <v>0.13</v>
@@ -15347,7 +15350,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ70">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AR70">
         <v>2.19</v>
@@ -16786,7 +16789,7 @@
         <v>1</v>
       </c>
       <c r="AP77">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ77">
         <v>0.8</v>
@@ -17407,7 +17410,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ80">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AR80">
         <v>1.85</v>
@@ -18437,7 +18440,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ85">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AR85">
         <v>1.4</v>
@@ -19542,6 +19545,212 @@
         <v>0</v>
       </c>
       <c r="BP90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:68">
+      <c r="A91" s="1">
+        <v>90</v>
+      </c>
+      <c r="B91">
+        <v>7828545</v>
+      </c>
+      <c r="C91" t="s">
+        <v>68</v>
+      </c>
+      <c r="D91" t="s">
+        <v>69</v>
+      </c>
+      <c r="E91" s="2">
+        <v>45836.54166666666</v>
+      </c>
+      <c r="F91">
+        <v>0</v>
+      </c>
+      <c r="G91" t="s">
+        <v>75</v>
+      </c>
+      <c r="H91" t="s">
+        <v>78</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>1</v>
+      </c>
+      <c r="K91">
+        <v>1</v>
+      </c>
+      <c r="L91">
+        <v>0</v>
+      </c>
+      <c r="M91">
+        <v>2</v>
+      </c>
+      <c r="N91">
+        <v>2</v>
+      </c>
+      <c r="O91" t="s">
+        <v>81</v>
+      </c>
+      <c r="P91" t="s">
+        <v>209</v>
+      </c>
+      <c r="Q91">
+        <v>5.7</v>
+      </c>
+      <c r="R91">
+        <v>2.55</v>
+      </c>
+      <c r="S91">
+        <v>1.7</v>
+      </c>
+      <c r="T91">
+        <v>1.22</v>
+      </c>
+      <c r="U91">
+        <v>3.8</v>
+      </c>
+      <c r="V91">
+        <v>2.1</v>
+      </c>
+      <c r="W91">
+        <v>1.7</v>
+      </c>
+      <c r="X91">
+        <v>4.5</v>
+      </c>
+      <c r="Y91">
+        <v>1.14</v>
+      </c>
+      <c r="Z91">
+        <v>6</v>
+      </c>
+      <c r="AA91">
+        <v>4.6</v>
+      </c>
+      <c r="AB91">
+        <v>1.4</v>
+      </c>
+      <c r="AC91">
+        <v>1.02</v>
+      </c>
+      <c r="AD91">
+        <v>19</v>
+      </c>
+      <c r="AE91">
+        <v>1.09</v>
+      </c>
+      <c r="AF91">
+        <v>5.5</v>
+      </c>
+      <c r="AG91">
+        <v>1.44</v>
+      </c>
+      <c r="AH91">
+        <v>2.63</v>
+      </c>
+      <c r="AI91">
+        <v>1.62</v>
+      </c>
+      <c r="AJ91">
+        <v>2.1</v>
+      </c>
+      <c r="AK91">
+        <v>1.18</v>
+      </c>
+      <c r="AL91">
+        <v>1.14</v>
+      </c>
+      <c r="AM91">
+        <v>1.11</v>
+      </c>
+      <c r="AN91">
+        <v>1.13</v>
+      </c>
+      <c r="AO91">
+        <v>1.67</v>
+      </c>
+      <c r="AP91">
+        <v>1</v>
+      </c>
+      <c r="AQ91">
+        <v>1.8</v>
+      </c>
+      <c r="AR91">
+        <v>1.5</v>
+      </c>
+      <c r="AS91">
+        <v>1.87</v>
+      </c>
+      <c r="AT91">
+        <v>3.37</v>
+      </c>
+      <c r="AU91">
+        <v>5</v>
+      </c>
+      <c r="AV91">
+        <v>10</v>
+      </c>
+      <c r="AW91">
+        <v>6</v>
+      </c>
+      <c r="AX91">
+        <v>15</v>
+      </c>
+      <c r="AY91">
+        <v>11</v>
+      </c>
+      <c r="AZ91">
+        <v>25</v>
+      </c>
+      <c r="BA91">
+        <v>3</v>
+      </c>
+      <c r="BB91">
+        <v>7</v>
+      </c>
+      <c r="BC91">
+        <v>10</v>
+      </c>
+      <c r="BD91">
+        <v>0</v>
+      </c>
+      <c r="BE91">
+        <v>0</v>
+      </c>
+      <c r="BF91">
+        <v>0</v>
+      </c>
+      <c r="BG91">
+        <v>0</v>
+      </c>
+      <c r="BH91">
+        <v>0</v>
+      </c>
+      <c r="BI91">
+        <v>0</v>
+      </c>
+      <c r="BJ91">
+        <v>0</v>
+      </c>
+      <c r="BK91">
+        <v>0</v>
+      </c>
+      <c r="BL91">
+        <v>0</v>
+      </c>
+      <c r="BM91">
+        <v>0</v>
+      </c>
+      <c r="BN91">
+        <v>0</v>
+      </c>
+      <c r="BO91">
+        <v>0</v>
+      </c>
+      <c r="BP91">
         <v>0</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="213">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -463,6 +463,12 @@
     <t>['14', '58']</t>
   </si>
   <si>
+    <t>['56']</t>
+  </si>
+  <si>
+    <t>['50', '76', '84']</t>
+  </si>
+  <si>
     <t>['34', '59', '86']</t>
   </si>
   <si>
@@ -634,16 +640,19 @@
     <t>['33', '45+1']</t>
   </si>
   <si>
-    <t>['56']</t>
-  </si>
-  <si>
     <t>['83']</t>
   </si>
   <si>
     <t>['8', '27']</t>
   </si>
   <si>
-    <t>['22', '55']</t>
+    <t>['21', '56']</t>
+  </si>
+  <si>
+    <t>['6']</t>
+  </si>
+  <si>
+    <t>['65']</t>
   </si>
 </sst>
 </file>
@@ -1005,7 +1014,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP91"/>
+  <dimension ref="A1:BP93"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1467,7 +1476,7 @@
         <v>81</v>
       </c>
       <c r="P3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -1673,7 +1682,7 @@
         <v>82</v>
       </c>
       <c r="P4" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -1751,7 +1760,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ4">
         <v>1.78</v>
@@ -1879,7 +1888,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="Q5">
         <v>7</v>
@@ -2085,7 +2094,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2369,7 +2378,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ7">
         <v>1.63</v>
@@ -2497,7 +2506,7 @@
         <v>85</v>
       </c>
       <c r="P8" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="Q8">
         <v>8.5</v>
@@ -2703,7 +2712,7 @@
         <v>81</v>
       </c>
       <c r="P9" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -2784,7 +2793,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ9">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -2987,10 +2996,10 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AQ10">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3321,7 +3330,7 @@
         <v>88</v>
       </c>
       <c r="P12" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="Q12">
         <v>8</v>
@@ -3733,7 +3742,7 @@
         <v>81</v>
       </c>
       <c r="P14" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="Q14">
         <v>5.5</v>
@@ -3939,7 +3948,7 @@
         <v>90</v>
       </c>
       <c r="P15" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q15">
         <v>2.5</v>
@@ -4145,7 +4154,7 @@
         <v>91</v>
       </c>
       <c r="P16" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Q16">
         <v>2.1</v>
@@ -4351,7 +4360,7 @@
         <v>81</v>
       </c>
       <c r="P17" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q17">
         <v>2.38</v>
@@ -4557,7 +4566,7 @@
         <v>81</v>
       </c>
       <c r="P18" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q18">
         <v>3.4</v>
@@ -4635,7 +4644,7 @@
         <v>1</v>
       </c>
       <c r="AP18">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AQ18">
         <v>1.78</v>
@@ -4841,10 +4850,10 @@
         <v>3</v>
       </c>
       <c r="AP19">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ19">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR19">
         <v>1.56</v>
@@ -5050,7 +5059,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ20">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="AR20">
         <v>2.45</v>
@@ -5175,7 +5184,7 @@
         <v>94</v>
       </c>
       <c r="P21" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q21">
         <v>1.91</v>
@@ -5587,7 +5596,7 @@
         <v>96</v>
       </c>
       <c r="P23" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -5793,7 +5802,7 @@
         <v>81</v>
       </c>
       <c r="P24" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q24">
         <v>5.5</v>
@@ -5999,7 +6008,7 @@
         <v>97</v>
       </c>
       <c r="P25" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q25">
         <v>2.38</v>
@@ -6205,7 +6214,7 @@
         <v>98</v>
       </c>
       <c r="P26" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q26">
         <v>3.1</v>
@@ -6286,7 +6295,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ26">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR26">
         <v>1.15</v>
@@ -6492,7 +6501,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ27">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="AR27">
         <v>1.38</v>
@@ -6617,7 +6626,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q28">
         <v>1.3</v>
@@ -6698,7 +6707,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ28">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR28">
         <v>2.38</v>
@@ -6823,7 +6832,7 @@
         <v>101</v>
       </c>
       <c r="P29" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q29">
         <v>5</v>
@@ -7441,7 +7450,7 @@
         <v>81</v>
       </c>
       <c r="P32" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q32">
         <v>6</v>
@@ -7647,7 +7656,7 @@
         <v>104</v>
       </c>
       <c r="P33" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q33">
         <v>8.449999999999999</v>
@@ -7725,7 +7734,7 @@
         <v>1.5</v>
       </c>
       <c r="AP33">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AQ33">
         <v>1.8</v>
@@ -8059,7 +8068,7 @@
         <v>105</v>
       </c>
       <c r="P35" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q35">
         <v>2.2</v>
@@ -8140,7 +8149,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ35">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="AR35">
         <v>0.88</v>
@@ -8265,7 +8274,7 @@
         <v>106</v>
       </c>
       <c r="P36" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q36">
         <v>4.25</v>
@@ -8549,7 +8558,7 @@
         <v>2</v>
       </c>
       <c r="AP37">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ37">
         <v>1.8</v>
@@ -8883,7 +8892,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q39">
         <v>3.2</v>
@@ -8961,7 +8970,7 @@
         <v>1.33</v>
       </c>
       <c r="AP39">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AQ39">
         <v>0.78</v>
@@ -9089,7 +9098,7 @@
         <v>81</v>
       </c>
       <c r="P40" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q40">
         <v>12</v>
@@ -9295,7 +9304,7 @@
         <v>110</v>
       </c>
       <c r="P41" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q41">
         <v>3.77</v>
@@ -9582,7 +9591,7 @@
         <v>1</v>
       </c>
       <c r="AQ42">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR42">
         <v>1.17</v>
@@ -9707,7 +9716,7 @@
         <v>112</v>
       </c>
       <c r="P43" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q43">
         <v>1.35</v>
@@ -9788,7 +9797,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ43">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="AR43">
         <v>2.31</v>
@@ -9913,7 +9922,7 @@
         <v>113</v>
       </c>
       <c r="P44" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q44">
         <v>1.66</v>
@@ -9991,7 +10000,7 @@
         <v>1</v>
       </c>
       <c r="AP44">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ44">
         <v>0.8</v>
@@ -10119,7 +10128,7 @@
         <v>114</v>
       </c>
       <c r="P45" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q45">
         <v>4.75</v>
@@ -10325,7 +10334,7 @@
         <v>115</v>
       </c>
       <c r="P46" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q46">
         <v>5.2</v>
@@ -10531,7 +10540,7 @@
         <v>81</v>
       </c>
       <c r="P47" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q47">
         <v>2.35</v>
@@ -10609,7 +10618,7 @@
         <v>1.5</v>
       </c>
       <c r="AP47">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AQ47">
         <v>1.63</v>
@@ -11149,7 +11158,7 @@
         <v>117</v>
       </c>
       <c r="P50" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q50">
         <v>2.62</v>
@@ -11227,7 +11236,7 @@
         <v>1.8</v>
       </c>
       <c r="AP50">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ50">
         <v>1.9</v>
@@ -11355,7 +11364,7 @@
         <v>118</v>
       </c>
       <c r="P51" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q51">
         <v>4.55</v>
@@ -11561,7 +11570,7 @@
         <v>81</v>
       </c>
       <c r="P52" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q52">
         <v>6.5</v>
@@ -11767,7 +11776,7 @@
         <v>119</v>
       </c>
       <c r="P53" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q53">
         <v>3.35</v>
@@ -12385,7 +12394,7 @@
         <v>122</v>
       </c>
       <c r="P56" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q56">
         <v>1.56</v>
@@ -12466,7 +12475,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ56">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR56">
         <v>2.2</v>
@@ -12591,7 +12600,7 @@
         <v>81</v>
       </c>
       <c r="P57" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q57">
         <v>5.25</v>
@@ -12669,7 +12678,7 @@
         <v>2.6</v>
       </c>
       <c r="AP57">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AQ57">
         <v>2.44</v>
@@ -12878,7 +12887,7 @@
         <v>1</v>
       </c>
       <c r="AQ58">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="AR58">
         <v>1.57</v>
@@ -13003,7 +13012,7 @@
         <v>81</v>
       </c>
       <c r="P59" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -13209,7 +13218,7 @@
         <v>124</v>
       </c>
       <c r="P60" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q60">
         <v>2.25</v>
@@ -13415,7 +13424,7 @@
         <v>125</v>
       </c>
       <c r="P61" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q61">
         <v>2.27</v>
@@ -13621,7 +13630,7 @@
         <v>126</v>
       </c>
       <c r="P62" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q62">
         <v>2.4</v>
@@ -13827,7 +13836,7 @@
         <v>127</v>
       </c>
       <c r="P63" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q63">
         <v>1.64</v>
@@ -14111,7 +14120,7 @@
         <v>2</v>
       </c>
       <c r="AP64">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ64">
         <v>2</v>
@@ -14320,7 +14329,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ65">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR65">
         <v>2.11</v>
@@ -14445,7 +14454,7 @@
         <v>130</v>
       </c>
       <c r="P66" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q66">
         <v>4.35</v>
@@ -14732,7 +14741,7 @@
         <v>1</v>
       </c>
       <c r="AQ67">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="AR67">
         <v>1.07</v>
@@ -14857,7 +14866,7 @@
         <v>132</v>
       </c>
       <c r="P68" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q68">
         <v>9</v>
@@ -15063,7 +15072,7 @@
         <v>133</v>
       </c>
       <c r="P69" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q69">
         <v>1.91</v>
@@ -15269,7 +15278,7 @@
         <v>81</v>
       </c>
       <c r="P70" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q70">
         <v>2.35</v>
@@ -15475,7 +15484,7 @@
         <v>134</v>
       </c>
       <c r="P71" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q71">
         <v>1.55</v>
@@ -15681,7 +15690,7 @@
         <v>135</v>
       </c>
       <c r="P72" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q72">
         <v>1.46</v>
@@ -15759,7 +15768,7 @@
         <v>0.57</v>
       </c>
       <c r="AP72">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ72">
         <v>0.78</v>
@@ -15887,7 +15896,7 @@
         <v>81</v>
       </c>
       <c r="P73" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q73">
         <v>8.5</v>
@@ -15965,7 +15974,7 @@
         <v>1.71</v>
       </c>
       <c r="AP73">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AQ73">
         <v>2</v>
@@ -16093,7 +16102,7 @@
         <v>81</v>
       </c>
       <c r="P74" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q74">
         <v>2.2</v>
@@ -16299,7 +16308,7 @@
         <v>136</v>
       </c>
       <c r="P75" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q75">
         <v>2.3</v>
@@ -16380,7 +16389,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ75">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR75">
         <v>1.34</v>
@@ -16505,7 +16514,7 @@
         <v>81</v>
       </c>
       <c r="P76" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q76">
         <v>8.949999999999999</v>
@@ -16711,7 +16720,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q77">
         <v>2.94</v>
@@ -16917,7 +16926,7 @@
         <v>81</v>
       </c>
       <c r="P78" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q78">
         <v>4.83</v>
@@ -17123,7 +17132,7 @@
         <v>138</v>
       </c>
       <c r="P79" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q79">
         <v>10</v>
@@ -17407,7 +17416,7 @@
         <v>1.29</v>
       </c>
       <c r="AP80">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ80">
         <v>1.8</v>
@@ -17741,7 +17750,7 @@
         <v>141</v>
       </c>
       <c r="P82" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q82">
         <v>2.54</v>
@@ -17947,7 +17956,7 @@
         <v>142</v>
       </c>
       <c r="P83" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q83">
         <v>3.8</v>
@@ -18234,7 +18243,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ84">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="AR84">
         <v>2.37</v>
@@ -18359,7 +18368,7 @@
         <v>108</v>
       </c>
       <c r="P85" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q85">
         <v>4.37</v>
@@ -18771,7 +18780,7 @@
         <v>145</v>
       </c>
       <c r="P87" t="s">
-        <v>206</v>
+        <v>149</v>
       </c>
       <c r="Q87">
         <v>2.25</v>
@@ -18977,7 +18986,7 @@
         <v>146</v>
       </c>
       <c r="P88" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q88">
         <v>3.3</v>
@@ -19183,7 +19192,7 @@
         <v>147</v>
       </c>
       <c r="P89" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q89">
         <v>1.88</v>
@@ -19389,7 +19398,7 @@
         <v>148</v>
       </c>
       <c r="P90" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q90">
         <v>5.6</v>
@@ -19595,7 +19604,7 @@
         <v>81</v>
       </c>
       <c r="P91" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q91">
         <v>5.7</v>
@@ -19751,6 +19760,418 @@
         <v>0</v>
       </c>
       <c r="BP91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:68">
+      <c r="A92" s="1">
+        <v>91</v>
+      </c>
+      <c r="B92">
+        <v>7828546</v>
+      </c>
+      <c r="C92" t="s">
+        <v>68</v>
+      </c>
+      <c r="D92" t="s">
+        <v>69</v>
+      </c>
+      <c r="E92" s="2">
+        <v>45837.45833333334</v>
+      </c>
+      <c r="F92">
+        <v>0</v>
+      </c>
+      <c r="G92" t="s">
+        <v>77</v>
+      </c>
+      <c r="H92" t="s">
+        <v>73</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>1</v>
+      </c>
+      <c r="K92">
+        <v>1</v>
+      </c>
+      <c r="L92">
+        <v>1</v>
+      </c>
+      <c r="M92">
+        <v>1</v>
+      </c>
+      <c r="N92">
+        <v>2</v>
+      </c>
+      <c r="O92" t="s">
+        <v>149</v>
+      </c>
+      <c r="P92" t="s">
+        <v>211</v>
+      </c>
+      <c r="Q92">
+        <v>2.28</v>
+      </c>
+      <c r="R92">
+        <v>2.25</v>
+      </c>
+      <c r="S92">
+        <v>4.33</v>
+      </c>
+      <c r="T92">
+        <v>1.29</v>
+      </c>
+      <c r="U92">
+        <v>3.3</v>
+      </c>
+      <c r="V92">
+        <v>2.3</v>
+      </c>
+      <c r="W92">
+        <v>1.55</v>
+      </c>
+      <c r="X92">
+        <v>5.05</v>
+      </c>
+      <c r="Y92">
+        <v>1.12</v>
+      </c>
+      <c r="Z92">
+        <v>1.94</v>
+      </c>
+      <c r="AA92">
+        <v>3.57</v>
+      </c>
+      <c r="AB92">
+        <v>3.08</v>
+      </c>
+      <c r="AC92">
+        <v>1.03</v>
+      </c>
+      <c r="AD92">
+        <v>12</v>
+      </c>
+      <c r="AE92">
+        <v>1.15</v>
+      </c>
+      <c r="AF92">
+        <v>4.3</v>
+      </c>
+      <c r="AG92">
+        <v>1.57</v>
+      </c>
+      <c r="AH92">
+        <v>2.15</v>
+      </c>
+      <c r="AI92">
+        <v>1.6</v>
+      </c>
+      <c r="AJ92">
+        <v>2.2</v>
+      </c>
+      <c r="AK92">
+        <v>1.2</v>
+      </c>
+      <c r="AL92">
+        <v>1.23</v>
+      </c>
+      <c r="AM92">
+        <v>2</v>
+      </c>
+      <c r="AN92">
+        <v>0.86</v>
+      </c>
+      <c r="AO92">
+        <v>0.5</v>
+      </c>
+      <c r="AP92">
+        <v>0.88</v>
+      </c>
+      <c r="AQ92">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AR92">
+        <v>1.32</v>
+      </c>
+      <c r="AS92">
+        <v>1.05</v>
+      </c>
+      <c r="AT92">
+        <v>2.37</v>
+      </c>
+      <c r="AU92">
+        <v>4</v>
+      </c>
+      <c r="AV92">
+        <v>3</v>
+      </c>
+      <c r="AW92">
+        <v>12</v>
+      </c>
+      <c r="AX92">
+        <v>3</v>
+      </c>
+      <c r="AY92">
+        <v>16</v>
+      </c>
+      <c r="AZ92">
+        <v>6</v>
+      </c>
+      <c r="BA92">
+        <v>9</v>
+      </c>
+      <c r="BB92">
+        <v>4</v>
+      </c>
+      <c r="BC92">
+        <v>13</v>
+      </c>
+      <c r="BD92">
+        <v>0</v>
+      </c>
+      <c r="BE92">
+        <v>0</v>
+      </c>
+      <c r="BF92">
+        <v>0</v>
+      </c>
+      <c r="BG92">
+        <v>0</v>
+      </c>
+      <c r="BH92">
+        <v>0</v>
+      </c>
+      <c r="BI92">
+        <v>0</v>
+      </c>
+      <c r="BJ92">
+        <v>0</v>
+      </c>
+      <c r="BK92">
+        <v>0</v>
+      </c>
+      <c r="BL92">
+        <v>0</v>
+      </c>
+      <c r="BM92">
+        <v>0</v>
+      </c>
+      <c r="BN92">
+        <v>0</v>
+      </c>
+      <c r="BO92">
+        <v>0</v>
+      </c>
+      <c r="BP92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:68">
+      <c r="A93" s="1">
+        <v>92</v>
+      </c>
+      <c r="B93">
+        <v>7828547</v>
+      </c>
+      <c r="C93" t="s">
+        <v>68</v>
+      </c>
+      <c r="D93" t="s">
+        <v>69</v>
+      </c>
+      <c r="E93" s="2">
+        <v>45837.54166666666</v>
+      </c>
+      <c r="F93">
+        <v>0</v>
+      </c>
+      <c r="G93" t="s">
+        <v>72</v>
+      </c>
+      <c r="H93" t="s">
+        <v>74</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>0</v>
+      </c>
+      <c r="K93">
+        <v>0</v>
+      </c>
+      <c r="L93">
+        <v>3</v>
+      </c>
+      <c r="M93">
+        <v>1</v>
+      </c>
+      <c r="N93">
+        <v>4</v>
+      </c>
+      <c r="O93" t="s">
+        <v>150</v>
+      </c>
+      <c r="P93" t="s">
+        <v>212</v>
+      </c>
+      <c r="Q93">
+        <v>1.36</v>
+      </c>
+      <c r="R93">
+        <v>3.96</v>
+      </c>
+      <c r="S93">
+        <v>10.5</v>
+      </c>
+      <c r="T93">
+        <v>1.12</v>
+      </c>
+      <c r="U93">
+        <v>5</v>
+      </c>
+      <c r="V93">
+        <v>1.72</v>
+      </c>
+      <c r="W93">
+        <v>2</v>
+      </c>
+      <c r="X93">
+        <v>3.25</v>
+      </c>
+      <c r="Y93">
+        <v>1.31</v>
+      </c>
+      <c r="Z93">
+        <v>1.08</v>
+      </c>
+      <c r="AA93">
+        <v>10</v>
+      </c>
+      <c r="AB93">
+        <v>18</v>
+      </c>
+      <c r="AC93">
+        <v>1.01</v>
+      </c>
+      <c r="AD93">
+        <v>24</v>
+      </c>
+      <c r="AE93">
+        <v>1.01</v>
+      </c>
+      <c r="AF93">
+        <v>8.5</v>
+      </c>
+      <c r="AG93">
+        <v>1.22</v>
+      </c>
+      <c r="AH93">
+        <v>4.4</v>
+      </c>
+      <c r="AI93">
+        <v>1.9</v>
+      </c>
+      <c r="AJ93">
+        <v>1.75</v>
+      </c>
+      <c r="AK93">
+        <v>1.01</v>
+      </c>
+      <c r="AL93">
+        <v>1.01</v>
+      </c>
+      <c r="AM93">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AN93">
+        <v>1.78</v>
+      </c>
+      <c r="AO93">
+        <v>0.13</v>
+      </c>
+      <c r="AP93">
+        <v>1.9</v>
+      </c>
+      <c r="AQ93">
+        <v>0.11</v>
+      </c>
+      <c r="AR93">
+        <v>1.77</v>
+      </c>
+      <c r="AS93">
+        <v>1.51</v>
+      </c>
+      <c r="AT93">
+        <v>3.28</v>
+      </c>
+      <c r="AU93">
+        <v>8</v>
+      </c>
+      <c r="AV93">
+        <v>4</v>
+      </c>
+      <c r="AW93">
+        <v>4</v>
+      </c>
+      <c r="AX93">
+        <v>2</v>
+      </c>
+      <c r="AY93">
+        <v>12</v>
+      </c>
+      <c r="AZ93">
+        <v>6</v>
+      </c>
+      <c r="BA93">
+        <v>3</v>
+      </c>
+      <c r="BB93">
+        <v>3</v>
+      </c>
+      <c r="BC93">
+        <v>6</v>
+      </c>
+      <c r="BD93">
+        <v>0</v>
+      </c>
+      <c r="BE93">
+        <v>0</v>
+      </c>
+      <c r="BF93">
+        <v>0</v>
+      </c>
+      <c r="BG93">
+        <v>0</v>
+      </c>
+      <c r="BH93">
+        <v>0</v>
+      </c>
+      <c r="BI93">
+        <v>0</v>
+      </c>
+      <c r="BJ93">
+        <v>0</v>
+      </c>
+      <c r="BK93">
+        <v>0</v>
+      </c>
+      <c r="BL93">
+        <v>0</v>
+      </c>
+      <c r="BM93">
+        <v>0</v>
+      </c>
+      <c r="BN93">
+        <v>0</v>
+      </c>
+      <c r="BO93">
+        <v>0</v>
+      </c>
+      <c r="BP93">
         <v>0</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="212">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -463,183 +463,183 @@
     <t>['14', '58']</t>
   </si>
   <si>
+    <t>['50', '77', '85']</t>
+  </si>
+  <si>
+    <t>['34', '59', '86']</t>
+  </si>
+  <si>
+    <t>['55', '57']</t>
+  </si>
+  <si>
+    <t>['72', '90+4']</t>
+  </si>
+  <si>
+    <t>['36', '63']</t>
+  </si>
+  <si>
+    <t>['18', '44', '89']</t>
+  </si>
+  <si>
+    <t>['8', '90+6']</t>
+  </si>
+  <si>
+    <t>['67', '90+1']</t>
+  </si>
+  <si>
+    <t>['25', '45+1', '47', '78']</t>
+  </si>
+  <si>
+    <t>['6', '90+1']</t>
+  </si>
+  <si>
+    <t>['42', '46']</t>
+  </si>
+  <si>
+    <t>['1', '34', '36', '47', '90']</t>
+  </si>
+  <si>
+    <t>['17', '37', '90']</t>
+  </si>
+  <si>
+    <t>['86']</t>
+  </si>
+  <si>
+    <t>['84', '90+3']</t>
+  </si>
+  <si>
+    <t>['74']</t>
+  </si>
+  <si>
+    <t>['68']</t>
+  </si>
+  <si>
+    <t>['2']</t>
+  </si>
+  <si>
+    <t>['29']</t>
+  </si>
+  <si>
+    <t>['42', '47']</t>
+  </si>
+  <si>
+    <t>['53', '69']</t>
+  </si>
+  <si>
+    <t>['34', '90+7']</t>
+  </si>
+  <si>
+    <t>['29', '58']</t>
+  </si>
+  <si>
+    <t>['25', '70']</t>
+  </si>
+  <si>
+    <t>['7']</t>
+  </si>
+  <si>
+    <t>['12', '24', '37', '54', '56', '59', '65', '75', '89']</t>
+  </si>
+  <si>
+    <t>['18', '47']</t>
+  </si>
+  <si>
+    <t>['37']</t>
+  </si>
+  <si>
+    <t>['39']</t>
+  </si>
+  <si>
+    <t>['6', '24']</t>
+  </si>
+  <si>
+    <t>['31']</t>
+  </si>
+  <si>
+    <t>['88']</t>
+  </si>
+  <si>
+    <t>['20', '58', '79']</t>
+  </si>
+  <si>
+    <t>['63']</t>
+  </si>
+  <si>
+    <t>['26', '45', '71']</t>
+  </si>
+  <si>
+    <t>['25', '60', '84']</t>
+  </si>
+  <si>
+    <t>['43', '82', '90+1']</t>
+  </si>
+  <si>
+    <t>['41']</t>
+  </si>
+  <si>
+    <t>['70']</t>
+  </si>
+  <si>
+    <t>['45+2', '90+4']</t>
+  </si>
+  <si>
+    <t>['71']</t>
+  </si>
+  <si>
+    <t>['31', '55']</t>
+  </si>
+  <si>
+    <t>['3', '16', '29', '32', '39']</t>
+  </si>
+  <si>
+    <t>['34', '60', '90']</t>
+  </si>
+  <si>
+    <t>['74', '79']</t>
+  </si>
+  <si>
+    <t>['53', '66']</t>
+  </si>
+  <si>
+    <t>['15', '79']</t>
+  </si>
+  <si>
+    <t>['33']</t>
+  </si>
+  <si>
+    <t>['12']</t>
+  </si>
+  <si>
+    <t>['34']</t>
+  </si>
+  <si>
+    <t>['72']</t>
+  </si>
+  <si>
+    <t>['24']</t>
+  </si>
+  <si>
+    <t>['90+4']</t>
+  </si>
+  <si>
+    <t>['3', '41', '69']</t>
+  </si>
+  <si>
+    <t>['45+5', '59']</t>
+  </si>
+  <si>
+    <t>['45', '38', '90+9']</t>
+  </si>
+  <si>
+    <t>['88', '48']</t>
+  </si>
+  <si>
+    <t>['33', '45+1']</t>
+  </si>
+  <si>
     <t>['56']</t>
   </si>
   <si>
-    <t>['50', '76', '84']</t>
-  </si>
-  <si>
-    <t>['34', '59', '86']</t>
-  </si>
-  <si>
-    <t>['55', '57']</t>
-  </si>
-  <si>
-    <t>['72', '90+4']</t>
-  </si>
-  <si>
-    <t>['36', '63']</t>
-  </si>
-  <si>
-    <t>['18', '44', '89']</t>
-  </si>
-  <si>
-    <t>['8', '90+6']</t>
-  </si>
-  <si>
-    <t>['67', '90+1']</t>
-  </si>
-  <si>
-    <t>['25', '45+1', '47', '78']</t>
-  </si>
-  <si>
-    <t>['6', '90+1']</t>
-  </si>
-  <si>
-    <t>['42', '46']</t>
-  </si>
-  <si>
-    <t>['1', '34', '36', '47', '90']</t>
-  </si>
-  <si>
-    <t>['17', '37', '90']</t>
-  </si>
-  <si>
-    <t>['86']</t>
-  </si>
-  <si>
-    <t>['84', '90+3']</t>
-  </si>
-  <si>
-    <t>['74']</t>
-  </si>
-  <si>
-    <t>['68']</t>
-  </si>
-  <si>
-    <t>['2']</t>
-  </si>
-  <si>
-    <t>['29']</t>
-  </si>
-  <si>
-    <t>['42', '47']</t>
-  </si>
-  <si>
-    <t>['53', '69']</t>
-  </si>
-  <si>
-    <t>['34', '90+7']</t>
-  </si>
-  <si>
-    <t>['29', '58']</t>
-  </si>
-  <si>
-    <t>['25', '70']</t>
-  </si>
-  <si>
-    <t>['7']</t>
-  </si>
-  <si>
-    <t>['12', '24', '37', '54', '56', '59', '65', '75', '89']</t>
-  </si>
-  <si>
-    <t>['18', '47']</t>
-  </si>
-  <si>
-    <t>['37']</t>
-  </si>
-  <si>
-    <t>['39']</t>
-  </si>
-  <si>
-    <t>['6', '24']</t>
-  </si>
-  <si>
-    <t>['31']</t>
-  </si>
-  <si>
-    <t>['88']</t>
-  </si>
-  <si>
-    <t>['20', '58', '79']</t>
-  </si>
-  <si>
-    <t>['63']</t>
-  </si>
-  <si>
-    <t>['26', '45', '71']</t>
-  </si>
-  <si>
-    <t>['25', '60', '84']</t>
-  </si>
-  <si>
-    <t>['43', '82', '90+1']</t>
-  </si>
-  <si>
-    <t>['41']</t>
-  </si>
-  <si>
-    <t>['70']</t>
-  </si>
-  <si>
-    <t>['45+2', '90+4']</t>
-  </si>
-  <si>
-    <t>['71']</t>
-  </si>
-  <si>
-    <t>['31', '55']</t>
-  </si>
-  <si>
-    <t>['3', '16', '29', '32', '39']</t>
-  </si>
-  <si>
-    <t>['34', '60', '90']</t>
-  </si>
-  <si>
-    <t>['74', '79']</t>
-  </si>
-  <si>
-    <t>['53', '66']</t>
-  </si>
-  <si>
-    <t>['15', '79']</t>
-  </si>
-  <si>
-    <t>['33']</t>
-  </si>
-  <si>
-    <t>['12']</t>
-  </si>
-  <si>
-    <t>['34']</t>
-  </si>
-  <si>
-    <t>['72']</t>
-  </si>
-  <si>
-    <t>['24']</t>
-  </si>
-  <si>
-    <t>['90+4']</t>
-  </si>
-  <si>
-    <t>['3', '41', '69']</t>
-  </si>
-  <si>
-    <t>['45+5', '59']</t>
-  </si>
-  <si>
-    <t>['45', '38', '90+9']</t>
-  </si>
-  <si>
-    <t>['88', '48']</t>
-  </si>
-  <si>
-    <t>['33', '45+1']</t>
-  </si>
-  <si>
     <t>['83']</t>
   </si>
   <si>
@@ -647,9 +647,6 @@
   </si>
   <si>
     <t>['21', '56']</t>
-  </si>
-  <si>
-    <t>['6']</t>
   </si>
   <si>
     <t>['65']</t>
@@ -1476,7 +1473,7 @@
         <v>81</v>
       </c>
       <c r="P3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -1682,7 +1679,7 @@
         <v>82</v>
       </c>
       <c r="P4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -1888,7 +1885,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q5">
         <v>7</v>
@@ -2094,7 +2091,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2506,7 +2503,7 @@
         <v>85</v>
       </c>
       <c r="P8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="Q8">
         <v>8.5</v>
@@ -2712,7 +2709,7 @@
         <v>81</v>
       </c>
       <c r="P9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -3330,7 +3327,7 @@
         <v>88</v>
       </c>
       <c r="P12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Q12">
         <v>8</v>
@@ -3742,7 +3739,7 @@
         <v>81</v>
       </c>
       <c r="P14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Q14">
         <v>5.5</v>
@@ -3948,7 +3945,7 @@
         <v>90</v>
       </c>
       <c r="P15" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="Q15">
         <v>2.5</v>
@@ -4154,7 +4151,7 @@
         <v>91</v>
       </c>
       <c r="P16" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q16">
         <v>2.1</v>
@@ -4360,7 +4357,7 @@
         <v>81</v>
       </c>
       <c r="P17" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q17">
         <v>2.38</v>
@@ -4566,7 +4563,7 @@
         <v>81</v>
       </c>
       <c r="P18" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Q18">
         <v>3.4</v>
@@ -5184,7 +5181,7 @@
         <v>94</v>
       </c>
       <c r="P21" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="Q21">
         <v>1.91</v>
@@ -5596,7 +5593,7 @@
         <v>96</v>
       </c>
       <c r="P23" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -5802,7 +5799,7 @@
         <v>81</v>
       </c>
       <c r="P24" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Q24">
         <v>5.5</v>
@@ -6008,7 +6005,7 @@
         <v>97</v>
       </c>
       <c r="P25" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q25">
         <v>2.38</v>
@@ -6214,7 +6211,7 @@
         <v>98</v>
       </c>
       <c r="P26" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Q26">
         <v>3.1</v>
@@ -6626,7 +6623,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q28">
         <v>1.3</v>
@@ -6832,7 +6829,7 @@
         <v>101</v>
       </c>
       <c r="P29" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="Q29">
         <v>5</v>
@@ -7450,7 +7447,7 @@
         <v>81</v>
       </c>
       <c r="P32" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="Q32">
         <v>6</v>
@@ -7656,7 +7653,7 @@
         <v>104</v>
       </c>
       <c r="P33" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Q33">
         <v>8.449999999999999</v>
@@ -8068,7 +8065,7 @@
         <v>105</v>
       </c>
       <c r="P35" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q35">
         <v>2.2</v>
@@ -8274,7 +8271,7 @@
         <v>106</v>
       </c>
       <c r="P36" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q36">
         <v>4.25</v>
@@ -8892,7 +8889,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q39">
         <v>3.2</v>
@@ -9098,7 +9095,7 @@
         <v>81</v>
       </c>
       <c r="P40" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q40">
         <v>12</v>
@@ -9304,7 +9301,7 @@
         <v>110</v>
       </c>
       <c r="P41" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q41">
         <v>3.77</v>
@@ -9716,7 +9713,7 @@
         <v>112</v>
       </c>
       <c r="P43" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q43">
         <v>1.35</v>
@@ -9922,7 +9919,7 @@
         <v>113</v>
       </c>
       <c r="P44" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q44">
         <v>1.66</v>
@@ -10128,7 +10125,7 @@
         <v>114</v>
       </c>
       <c r="P45" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q45">
         <v>4.75</v>
@@ -10334,7 +10331,7 @@
         <v>115</v>
       </c>
       <c r="P46" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q46">
         <v>5.2</v>
@@ -10540,7 +10537,7 @@
         <v>81</v>
       </c>
       <c r="P47" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q47">
         <v>2.35</v>
@@ -11158,7 +11155,7 @@
         <v>117</v>
       </c>
       <c r="P50" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q50">
         <v>2.62</v>
@@ -11364,7 +11361,7 @@
         <v>118</v>
       </c>
       <c r="P51" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q51">
         <v>4.55</v>
@@ -11570,7 +11567,7 @@
         <v>81</v>
       </c>
       <c r="P52" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q52">
         <v>6.5</v>
@@ -11776,7 +11773,7 @@
         <v>119</v>
       </c>
       <c r="P53" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q53">
         <v>3.35</v>
@@ -12394,7 +12391,7 @@
         <v>122</v>
       </c>
       <c r="P56" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q56">
         <v>1.56</v>
@@ -12600,7 +12597,7 @@
         <v>81</v>
       </c>
       <c r="P57" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q57">
         <v>5.25</v>
@@ -13012,7 +13009,7 @@
         <v>81</v>
       </c>
       <c r="P59" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -13218,7 +13215,7 @@
         <v>124</v>
       </c>
       <c r="P60" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Q60">
         <v>2.25</v>
@@ -13424,7 +13421,7 @@
         <v>125</v>
       </c>
       <c r="P61" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q61">
         <v>2.27</v>
@@ -13630,7 +13627,7 @@
         <v>126</v>
       </c>
       <c r="P62" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q62">
         <v>2.4</v>
@@ -13836,7 +13833,7 @@
         <v>127</v>
       </c>
       <c r="P63" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q63">
         <v>1.64</v>
@@ -14454,7 +14451,7 @@
         <v>130</v>
       </c>
       <c r="P66" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Q66">
         <v>4.35</v>
@@ -14866,7 +14863,7 @@
         <v>132</v>
       </c>
       <c r="P68" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q68">
         <v>9</v>
@@ -15072,7 +15069,7 @@
         <v>133</v>
       </c>
       <c r="P69" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Q69">
         <v>1.91</v>
@@ -15278,7 +15275,7 @@
         <v>81</v>
       </c>
       <c r="P70" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q70">
         <v>2.35</v>
@@ -15484,7 +15481,7 @@
         <v>134</v>
       </c>
       <c r="P71" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Q71">
         <v>1.55</v>
@@ -15690,7 +15687,7 @@
         <v>135</v>
       </c>
       <c r="P72" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q72">
         <v>1.46</v>
@@ -15896,7 +15893,7 @@
         <v>81</v>
       </c>
       <c r="P73" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q73">
         <v>8.5</v>
@@ -16102,7 +16099,7 @@
         <v>81</v>
       </c>
       <c r="P74" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q74">
         <v>2.2</v>
@@ -16308,7 +16305,7 @@
         <v>136</v>
       </c>
       <c r="P75" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q75">
         <v>2.3</v>
@@ -16514,7 +16511,7 @@
         <v>81</v>
       </c>
       <c r="P76" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Q76">
         <v>8.949999999999999</v>
@@ -16720,7 +16717,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="Q77">
         <v>2.94</v>
@@ -16926,7 +16923,7 @@
         <v>81</v>
       </c>
       <c r="P78" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Q78">
         <v>4.83</v>
@@ -17132,7 +17129,7 @@
         <v>138</v>
       </c>
       <c r="P79" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q79">
         <v>10</v>
@@ -17750,7 +17747,7 @@
         <v>141</v>
       </c>
       <c r="P82" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q82">
         <v>2.54</v>
@@ -17956,7 +17953,7 @@
         <v>142</v>
       </c>
       <c r="P83" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="Q83">
         <v>3.8</v>
@@ -18368,7 +18365,7 @@
         <v>108</v>
       </c>
       <c r="P85" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q85">
         <v>4.37</v>
@@ -18780,7 +18777,7 @@
         <v>145</v>
       </c>
       <c r="P87" t="s">
-        <v>149</v>
+        <v>207</v>
       </c>
       <c r="Q87">
         <v>2.25</v>
@@ -19807,10 +19804,10 @@
         <v>2</v>
       </c>
       <c r="O92" t="s">
-        <v>149</v>
+        <v>96</v>
       </c>
       <c r="P92" t="s">
-        <v>211</v>
+        <v>103</v>
       </c>
       <c r="Q92">
         <v>2.28</v>
@@ -20013,10 +20010,10 @@
         <v>4</v>
       </c>
       <c r="O93" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P93" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Q93">
         <v>1.36</v>
@@ -20109,22 +20106,22 @@
         <v>3.28</v>
       </c>
       <c r="AU93">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AV93">
         <v>4</v>
       </c>
       <c r="AW93">
+        <v>3</v>
+      </c>
+      <c r="AX93">
         <v>4</v>
       </c>
-      <c r="AX93">
-        <v>2</v>
-      </c>
       <c r="AY93">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AZ93">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BA93">
         <v>3</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
@@ -20106,22 +20106,22 @@
         <v>3.28</v>
       </c>
       <c r="AU93">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AV93">
         <v>4</v>
       </c>
       <c r="AW93">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX93">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AY93">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AZ93">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA93">
         <v>3</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="213">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -650,6 +650,9 @@
   </si>
   <si>
     <t>['65']</t>
+  </si>
+  <si>
+    <t>['23', '59', '45+3']</t>
   </si>
 </sst>
 </file>
@@ -1011,7 +1014,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP93"/>
+  <dimension ref="A1:BP94"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2584,7 +2587,7 @@
         <v>1</v>
       </c>
       <c r="AQ8">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3199,7 +3202,7 @@
         <v>3</v>
       </c>
       <c r="AP11">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AQ11">
         <v>1.9</v>
@@ -3408,7 +3411,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ12">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AR12">
         <v>0.79</v>
@@ -5053,7 +5056,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AQ20">
         <v>0.11</v>
@@ -5465,7 +5468,7 @@
         <v>2</v>
       </c>
       <c r="AP22">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AQ22">
         <v>0.78</v>
@@ -5880,7 +5883,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ24">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AR24">
         <v>1.34</v>
@@ -7319,7 +7322,7 @@
         <v>3</v>
       </c>
       <c r="AP31">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AQ31">
         <v>1.63</v>
@@ -9176,7 +9179,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ40">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AR40">
         <v>1.8</v>
@@ -10409,10 +10412,10 @@
         <v>3</v>
       </c>
       <c r="AP46">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AQ46">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AR46">
         <v>2.34</v>
@@ -12266,7 +12269,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ55">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AR55">
         <v>2.3</v>
@@ -12469,7 +12472,7 @@
         <v>0.6</v>
       </c>
       <c r="AP56">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AQ56">
         <v>0.5600000000000001</v>
@@ -13911,7 +13914,7 @@
         <v>1.17</v>
       </c>
       <c r="AP63">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AQ63">
         <v>0.8</v>
@@ -14120,7 +14123,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ64">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AR64">
         <v>1.9</v>
@@ -15974,7 +15977,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ73">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AR73">
         <v>1.33</v>
@@ -16177,7 +16180,7 @@
         <v>2.17</v>
       </c>
       <c r="AP74">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AQ74">
         <v>1.78</v>
@@ -17210,7 +17213,7 @@
         <v>1</v>
       </c>
       <c r="AQ79">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AR79">
         <v>1.48</v>
@@ -19061,7 +19064,7 @@
         <v>2.75</v>
       </c>
       <c r="AP88">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AQ88">
         <v>2.44</v>
@@ -20169,6 +20172,212 @@
         <v>0</v>
       </c>
       <c r="BP93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:68">
+      <c r="A94" s="1">
+        <v>93</v>
+      </c>
+      <c r="B94">
+        <v>7828548</v>
+      </c>
+      <c r="C94" t="s">
+        <v>68</v>
+      </c>
+      <c r="D94" t="s">
+        <v>69</v>
+      </c>
+      <c r="E94" s="2">
+        <v>45842.54166666666</v>
+      </c>
+      <c r="F94">
+        <v>0</v>
+      </c>
+      <c r="G94" t="s">
+        <v>78</v>
+      </c>
+      <c r="H94" t="s">
+        <v>70</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>2</v>
+      </c>
+      <c r="K94">
+        <v>2</v>
+      </c>
+      <c r="L94">
+        <v>0</v>
+      </c>
+      <c r="M94">
+        <v>3</v>
+      </c>
+      <c r="N94">
+        <v>3</v>
+      </c>
+      <c r="O94" t="s">
+        <v>81</v>
+      </c>
+      <c r="P94" t="s">
+        <v>212</v>
+      </c>
+      <c r="Q94">
+        <v>3.94</v>
+      </c>
+      <c r="R94">
+        <v>2.37</v>
+      </c>
+      <c r="S94">
+        <v>2.38</v>
+      </c>
+      <c r="T94">
+        <v>1.27</v>
+      </c>
+      <c r="U94">
+        <v>3.2</v>
+      </c>
+      <c r="V94">
+        <v>2.37</v>
+      </c>
+      <c r="W94">
+        <v>1.5</v>
+      </c>
+      <c r="X94">
+        <v>6</v>
+      </c>
+      <c r="Y94">
+        <v>1.12</v>
+      </c>
+      <c r="Z94">
+        <v>3.54</v>
+      </c>
+      <c r="AA94">
+        <v>3.61</v>
+      </c>
+      <c r="AB94">
+        <v>1.93</v>
+      </c>
+      <c r="AC94">
+        <v>1.04</v>
+      </c>
+      <c r="AD94">
+        <v>12</v>
+      </c>
+      <c r="AE94">
+        <v>1.22</v>
+      </c>
+      <c r="AF94">
+        <v>4.3</v>
+      </c>
+      <c r="AG94">
+        <v>1.73</v>
+      </c>
+      <c r="AH94">
+        <v>2.08</v>
+      </c>
+      <c r="AI94">
+        <v>1.6</v>
+      </c>
+      <c r="AJ94">
+        <v>2.06</v>
+      </c>
+      <c r="AK94">
+        <v>1.29</v>
+      </c>
+      <c r="AL94">
+        <v>1.26</v>
+      </c>
+      <c r="AM94">
+        <v>1.25</v>
+      </c>
+      <c r="AN94">
+        <v>2.22</v>
+      </c>
+      <c r="AO94">
+        <v>2</v>
+      </c>
+      <c r="AP94">
+        <v>2</v>
+      </c>
+      <c r="AQ94">
+        <v>2.1</v>
+      </c>
+      <c r="AR94">
+        <v>2</v>
+      </c>
+      <c r="AS94">
+        <v>2.42</v>
+      </c>
+      <c r="AT94">
+        <v>4.42</v>
+      </c>
+      <c r="AU94">
+        <v>4</v>
+      </c>
+      <c r="AV94">
+        <v>6</v>
+      </c>
+      <c r="AW94">
+        <v>4</v>
+      </c>
+      <c r="AX94">
+        <v>8</v>
+      </c>
+      <c r="AY94">
+        <v>8</v>
+      </c>
+      <c r="AZ94">
+        <v>14</v>
+      </c>
+      <c r="BA94">
+        <v>8</v>
+      </c>
+      <c r="BB94">
+        <v>4</v>
+      </c>
+      <c r="BC94">
+        <v>12</v>
+      </c>
+      <c r="BD94">
+        <v>0</v>
+      </c>
+      <c r="BE94">
+        <v>0</v>
+      </c>
+      <c r="BF94">
+        <v>0</v>
+      </c>
+      <c r="BG94">
+        <v>0</v>
+      </c>
+      <c r="BH94">
+        <v>0</v>
+      </c>
+      <c r="BI94">
+        <v>0</v>
+      </c>
+      <c r="BJ94">
+        <v>0</v>
+      </c>
+      <c r="BK94">
+        <v>0</v>
+      </c>
+      <c r="BL94">
+        <v>0</v>
+      </c>
+      <c r="BM94">
+        <v>0</v>
+      </c>
+      <c r="BN94">
+        <v>0</v>
+      </c>
+      <c r="BO94">
+        <v>0</v>
+      </c>
+      <c r="BP94">
         <v>0</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="215">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -466,6 +466,9 @@
     <t>['50', '77', '85']</t>
   </si>
   <si>
+    <t>['22', '38', '79']</t>
+  </si>
+  <si>
     <t>['34', '59', '86']</t>
   </si>
   <si>
@@ -653,6 +656,9 @@
   </si>
   <si>
     <t>['23', '59', '45+3']</t>
+  </si>
+  <si>
+    <t>['12', '30']</t>
   </si>
 </sst>
 </file>
@@ -1014,7 +1020,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP94"/>
+  <dimension ref="A1:BP95"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1476,7 +1482,7 @@
         <v>81</v>
       </c>
       <c r="P3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -1682,7 +1688,7 @@
         <v>82</v>
       </c>
       <c r="P4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -1888,7 +1894,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q5">
         <v>7</v>
@@ -2094,7 +2100,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2506,7 +2512,7 @@
         <v>85</v>
       </c>
       <c r="P8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q8">
         <v>8.5</v>
@@ -2712,7 +2718,7 @@
         <v>81</v>
       </c>
       <c r="P9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -2790,10 +2796,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ9">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3330,7 +3336,7 @@
         <v>88</v>
       </c>
       <c r="P12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q12">
         <v>8</v>
@@ -3614,7 +3620,7 @@
         <v>3</v>
       </c>
       <c r="AP13">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ13">
         <v>1.8</v>
@@ -3742,7 +3748,7 @@
         <v>81</v>
       </c>
       <c r="P14" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q14">
         <v>5.5</v>
@@ -3948,7 +3954,7 @@
         <v>90</v>
       </c>
       <c r="P15" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q15">
         <v>2.5</v>
@@ -4154,7 +4160,7 @@
         <v>91</v>
       </c>
       <c r="P16" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q16">
         <v>2.1</v>
@@ -4360,7 +4366,7 @@
         <v>81</v>
       </c>
       <c r="P17" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q17">
         <v>2.38</v>
@@ -4566,7 +4572,7 @@
         <v>81</v>
       </c>
       <c r="P18" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q18">
         <v>3.4</v>
@@ -4853,7 +4859,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ19">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR19">
         <v>1.56</v>
@@ -5184,7 +5190,7 @@
         <v>94</v>
       </c>
       <c r="P21" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q21">
         <v>1.91</v>
@@ -5596,7 +5602,7 @@
         <v>96</v>
       </c>
       <c r="P23" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -5802,7 +5808,7 @@
         <v>81</v>
       </c>
       <c r="P24" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q24">
         <v>5.5</v>
@@ -5880,7 +5886,7 @@
         <v>3</v>
       </c>
       <c r="AP24">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ24">
         <v>2.1</v>
@@ -6008,7 +6014,7 @@
         <v>97</v>
       </c>
       <c r="P25" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q25">
         <v>2.38</v>
@@ -6214,7 +6220,7 @@
         <v>98</v>
       </c>
       <c r="P26" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q26">
         <v>3.1</v>
@@ -6295,7 +6301,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ26">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR26">
         <v>1.15</v>
@@ -6498,7 +6504,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ27">
         <v>0.11</v>
@@ -6626,7 +6632,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q28">
         <v>1.3</v>
@@ -6707,7 +6713,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ28">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR28">
         <v>2.38</v>
@@ -6832,7 +6838,7 @@
         <v>101</v>
       </c>
       <c r="P29" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q29">
         <v>5</v>
@@ -7450,7 +7456,7 @@
         <v>81</v>
       </c>
       <c r="P32" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q32">
         <v>6</v>
@@ -7656,7 +7662,7 @@
         <v>104</v>
       </c>
       <c r="P33" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q33">
         <v>8.449999999999999</v>
@@ -8068,7 +8074,7 @@
         <v>105</v>
       </c>
       <c r="P35" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q35">
         <v>2.2</v>
@@ -8274,7 +8280,7 @@
         <v>106</v>
       </c>
       <c r="P36" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q36">
         <v>4.25</v>
@@ -8892,7 +8898,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q39">
         <v>3.2</v>
@@ -9098,7 +9104,7 @@
         <v>81</v>
       </c>
       <c r="P40" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q40">
         <v>12</v>
@@ -9304,7 +9310,7 @@
         <v>110</v>
       </c>
       <c r="P41" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q41">
         <v>3.77</v>
@@ -9382,7 +9388,7 @@
         <v>1.5</v>
       </c>
       <c r="AP41">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ41">
         <v>1.9</v>
@@ -9591,7 +9597,7 @@
         <v>1</v>
       </c>
       <c r="AQ42">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR42">
         <v>1.17</v>
@@ -9716,7 +9722,7 @@
         <v>112</v>
       </c>
       <c r="P43" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q43">
         <v>1.35</v>
@@ -9922,7 +9928,7 @@
         <v>113</v>
       </c>
       <c r="P44" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q44">
         <v>1.66</v>
@@ -10128,7 +10134,7 @@
         <v>114</v>
       </c>
       <c r="P45" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q45">
         <v>4.75</v>
@@ -10334,7 +10340,7 @@
         <v>115</v>
       </c>
       <c r="P46" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q46">
         <v>5.2</v>
@@ -10540,7 +10546,7 @@
         <v>81</v>
       </c>
       <c r="P47" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q47">
         <v>2.35</v>
@@ -11158,7 +11164,7 @@
         <v>117</v>
       </c>
       <c r="P50" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q50">
         <v>2.62</v>
@@ -11364,7 +11370,7 @@
         <v>118</v>
       </c>
       <c r="P51" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q51">
         <v>4.55</v>
@@ -11570,7 +11576,7 @@
         <v>81</v>
       </c>
       <c r="P52" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q52">
         <v>6.5</v>
@@ -11776,7 +11782,7 @@
         <v>119</v>
       </c>
       <c r="P53" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q53">
         <v>3.35</v>
@@ -12060,7 +12066,7 @@
         <v>0.8</v>
       </c>
       <c r="AP54">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ54">
         <v>0.78</v>
@@ -12394,7 +12400,7 @@
         <v>122</v>
       </c>
       <c r="P56" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q56">
         <v>1.56</v>
@@ -12475,7 +12481,7 @@
         <v>2</v>
       </c>
       <c r="AQ56">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR56">
         <v>2.2</v>
@@ -12600,7 +12606,7 @@
         <v>81</v>
       </c>
       <c r="P57" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q57">
         <v>5.25</v>
@@ -13012,7 +13018,7 @@
         <v>81</v>
       </c>
       <c r="P59" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -13218,7 +13224,7 @@
         <v>124</v>
       </c>
       <c r="P60" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q60">
         <v>2.25</v>
@@ -13424,7 +13430,7 @@
         <v>125</v>
       </c>
       <c r="P61" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q61">
         <v>2.27</v>
@@ -13502,7 +13508,7 @@
         <v>1.8</v>
       </c>
       <c r="AP61">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ61">
         <v>1.63</v>
@@ -13630,7 +13636,7 @@
         <v>126</v>
       </c>
       <c r="P62" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q62">
         <v>2.4</v>
@@ -13836,7 +13842,7 @@
         <v>127</v>
       </c>
       <c r="P63" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q63">
         <v>1.64</v>
@@ -14329,7 +14335,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ65">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR65">
         <v>2.11</v>
@@ -14454,7 +14460,7 @@
         <v>130</v>
       </c>
       <c r="P66" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q66">
         <v>4.35</v>
@@ -14866,7 +14872,7 @@
         <v>132</v>
       </c>
       <c r="P68" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q68">
         <v>9</v>
@@ -15072,7 +15078,7 @@
         <v>133</v>
       </c>
       <c r="P69" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q69">
         <v>1.91</v>
@@ -15150,7 +15156,7 @@
         <v>1.14</v>
       </c>
       <c r="AP69">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ69">
         <v>0.8</v>
@@ -15278,7 +15284,7 @@
         <v>81</v>
       </c>
       <c r="P70" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q70">
         <v>2.35</v>
@@ -15484,7 +15490,7 @@
         <v>134</v>
       </c>
       <c r="P71" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q71">
         <v>1.55</v>
@@ -15690,7 +15696,7 @@
         <v>135</v>
       </c>
       <c r="P72" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q72">
         <v>1.46</v>
@@ -15896,7 +15902,7 @@
         <v>81</v>
       </c>
       <c r="P73" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q73">
         <v>8.5</v>
@@ -16102,7 +16108,7 @@
         <v>81</v>
       </c>
       <c r="P74" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q74">
         <v>2.2</v>
@@ -16308,7 +16314,7 @@
         <v>136</v>
       </c>
       <c r="P75" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q75">
         <v>2.3</v>
@@ -16389,7 +16395,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ75">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR75">
         <v>1.34</v>
@@ -16514,7 +16520,7 @@
         <v>81</v>
       </c>
       <c r="P76" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q76">
         <v>8.949999999999999</v>
@@ -16720,7 +16726,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q77">
         <v>2.94</v>
@@ -16926,7 +16932,7 @@
         <v>81</v>
       </c>
       <c r="P78" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q78">
         <v>4.83</v>
@@ -17132,7 +17138,7 @@
         <v>138</v>
       </c>
       <c r="P79" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q79">
         <v>10</v>
@@ -17750,7 +17756,7 @@
         <v>141</v>
       </c>
       <c r="P82" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q82">
         <v>2.54</v>
@@ -17956,7 +17962,7 @@
         <v>142</v>
       </c>
       <c r="P83" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q83">
         <v>3.8</v>
@@ -18034,7 +18040,7 @@
         <v>2.71</v>
       </c>
       <c r="AP83">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ83">
         <v>2.44</v>
@@ -18368,7 +18374,7 @@
         <v>108</v>
       </c>
       <c r="P85" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q85">
         <v>4.37</v>
@@ -18780,7 +18786,7 @@
         <v>145</v>
       </c>
       <c r="P87" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q87">
         <v>2.25</v>
@@ -18986,7 +18992,7 @@
         <v>146</v>
       </c>
       <c r="P88" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q88">
         <v>3.3</v>
@@ -19192,7 +19198,7 @@
         <v>147</v>
       </c>
       <c r="P89" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q89">
         <v>1.88</v>
@@ -19398,7 +19404,7 @@
         <v>148</v>
       </c>
       <c r="P90" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q90">
         <v>5.6</v>
@@ -19604,7 +19610,7 @@
         <v>81</v>
       </c>
       <c r="P91" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q91">
         <v>5.7</v>
@@ -19891,7 +19897,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ92">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR92">
         <v>1.32</v>
@@ -20016,7 +20022,7 @@
         <v>149</v>
       </c>
       <c r="P93" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q93">
         <v>1.36</v>
@@ -20222,7 +20228,7 @@
         <v>81</v>
       </c>
       <c r="P94" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q94">
         <v>3.94</v>
@@ -20378,6 +20384,212 @@
         <v>0</v>
       </c>
       <c r="BP94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:68">
+      <c r="A95" s="1">
+        <v>94</v>
+      </c>
+      <c r="B95">
+        <v>7828549</v>
+      </c>
+      <c r="C95" t="s">
+        <v>68</v>
+      </c>
+      <c r="D95" t="s">
+        <v>69</v>
+      </c>
+      <c r="E95" s="2">
+        <v>45843.45833333334</v>
+      </c>
+      <c r="F95">
+        <v>0</v>
+      </c>
+      <c r="G95" t="s">
+        <v>76</v>
+      </c>
+      <c r="H95" t="s">
+        <v>73</v>
+      </c>
+      <c r="I95">
+        <v>2</v>
+      </c>
+      <c r="J95">
+        <v>2</v>
+      </c>
+      <c r="K95">
+        <v>4</v>
+      </c>
+      <c r="L95">
+        <v>3</v>
+      </c>
+      <c r="M95">
+        <v>2</v>
+      </c>
+      <c r="N95">
+        <v>5</v>
+      </c>
+      <c r="O95" t="s">
+        <v>150</v>
+      </c>
+      <c r="P95" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q95">
+        <v>2.05</v>
+      </c>
+      <c r="R95">
+        <v>2.34</v>
+      </c>
+      <c r="S95">
+        <v>4.8</v>
+      </c>
+      <c r="T95">
+        <v>1.25</v>
+      </c>
+      <c r="U95">
+        <v>3.3</v>
+      </c>
+      <c r="V95">
+        <v>2.36</v>
+      </c>
+      <c r="W95">
+        <v>1.52</v>
+      </c>
+      <c r="X95">
+        <v>5.5</v>
+      </c>
+      <c r="Y95">
+        <v>1.11</v>
+      </c>
+      <c r="Z95">
+        <v>1.42</v>
+      </c>
+      <c r="AA95">
+        <v>4.5</v>
+      </c>
+      <c r="AB95">
+        <v>5.2</v>
+      </c>
+      <c r="AC95">
+        <v>1.01</v>
+      </c>
+      <c r="AD95">
+        <v>11</v>
+      </c>
+      <c r="AE95">
+        <v>1.15</v>
+      </c>
+      <c r="AF95">
+        <v>4.2</v>
+      </c>
+      <c r="AG95">
+        <v>1.55</v>
+      </c>
+      <c r="AH95">
+        <v>2.29</v>
+      </c>
+      <c r="AI95">
+        <v>1.58</v>
+      </c>
+      <c r="AJ95">
+        <v>2.05</v>
+      </c>
+      <c r="AK95">
+        <v>1.22</v>
+      </c>
+      <c r="AL95">
+        <v>1.14</v>
+      </c>
+      <c r="AM95">
+        <v>2.25</v>
+      </c>
+      <c r="AN95">
+        <v>1.67</v>
+      </c>
+      <c r="AO95">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AP95">
+        <v>1.8</v>
+      </c>
+      <c r="AQ95">
+        <v>0.5</v>
+      </c>
+      <c r="AR95">
+        <v>1.8</v>
+      </c>
+      <c r="AS95">
+        <v>1.02</v>
+      </c>
+      <c r="AT95">
+        <v>2.82</v>
+      </c>
+      <c r="AU95">
+        <v>9</v>
+      </c>
+      <c r="AV95">
+        <v>7</v>
+      </c>
+      <c r="AW95">
+        <v>3</v>
+      </c>
+      <c r="AX95">
+        <v>0</v>
+      </c>
+      <c r="AY95">
+        <v>12</v>
+      </c>
+      <c r="AZ95">
+        <v>7</v>
+      </c>
+      <c r="BA95">
+        <v>3</v>
+      </c>
+      <c r="BB95">
+        <v>2</v>
+      </c>
+      <c r="BC95">
+        <v>5</v>
+      </c>
+      <c r="BD95">
+        <v>0</v>
+      </c>
+      <c r="BE95">
+        <v>0</v>
+      </c>
+      <c r="BF95">
+        <v>0</v>
+      </c>
+      <c r="BG95">
+        <v>0</v>
+      </c>
+      <c r="BH95">
+        <v>0</v>
+      </c>
+      <c r="BI95">
+        <v>0</v>
+      </c>
+      <c r="BJ95">
+        <v>0</v>
+      </c>
+      <c r="BK95">
+        <v>0</v>
+      </c>
+      <c r="BL95">
+        <v>0</v>
+      </c>
+      <c r="BM95">
+        <v>0</v>
+      </c>
+      <c r="BN95">
+        <v>0</v>
+      </c>
+      <c r="BO95">
+        <v>0</v>
+      </c>
+      <c r="BP95">
         <v>0</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="218">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -469,6 +469,12 @@
     <t>['22', '38', '79']</t>
   </si>
   <si>
+    <t>['41', '76', '49']</t>
+  </si>
+  <si>
+    <t>['90+1']</t>
+  </si>
+  <si>
     <t>['34', '59', '86']</t>
   </si>
   <si>
@@ -659,6 +665,9 @@
   </si>
   <si>
     <t>['12', '30']</t>
+  </si>
+  <si>
+    <t>['6', '9']</t>
   </si>
 </sst>
 </file>
@@ -1020,7 +1029,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP95"/>
+  <dimension ref="A1:BP97"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1482,7 +1491,7 @@
         <v>81</v>
       </c>
       <c r="P3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -1563,7 +1572,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ3">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1688,7 +1697,7 @@
         <v>82</v>
       </c>
       <c r="P4" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -1766,7 +1775,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ4">
         <v>1.78</v>
@@ -1894,7 +1903,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="Q5">
         <v>7</v>
@@ -2100,7 +2109,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2178,10 +2187,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="AQ6">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2384,7 +2393,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ7">
         <v>1.63</v>
@@ -2512,7 +2521,7 @@
         <v>85</v>
       </c>
       <c r="P8" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="Q8">
         <v>8.5</v>
@@ -2718,7 +2727,7 @@
         <v>81</v>
       </c>
       <c r="P9" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -3211,7 +3220,7 @@
         <v>2</v>
       </c>
       <c r="AQ11">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3336,7 +3345,7 @@
         <v>88</v>
       </c>
       <c r="P12" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q12">
         <v>8</v>
@@ -3748,7 +3757,7 @@
         <v>81</v>
       </c>
       <c r="P14" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Q14">
         <v>5.5</v>
@@ -3826,7 +3835,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="AQ14">
         <v>2.44</v>
@@ -3954,7 +3963,7 @@
         <v>90</v>
       </c>
       <c r="P15" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q15">
         <v>2.5</v>
@@ -4160,7 +4169,7 @@
         <v>91</v>
       </c>
       <c r="P16" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q16">
         <v>2.1</v>
@@ -4241,7 +4250,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ16">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4366,7 +4375,7 @@
         <v>81</v>
       </c>
       <c r="P17" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q17">
         <v>2.38</v>
@@ -4572,7 +4581,7 @@
         <v>81</v>
       </c>
       <c r="P18" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q18">
         <v>3.4</v>
@@ -4856,7 +4865,7 @@
         <v>3</v>
       </c>
       <c r="AP19">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ19">
         <v>0.5</v>
@@ -5190,7 +5199,7 @@
         <v>94</v>
       </c>
       <c r="P21" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q21">
         <v>1.91</v>
@@ -5271,7 +5280,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ21">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR21">
         <v>2.18</v>
@@ -5477,7 +5486,7 @@
         <v>2</v>
       </c>
       <c r="AQ22">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR22">
         <v>3.01</v>
@@ -5602,7 +5611,7 @@
         <v>96</v>
       </c>
       <c r="P23" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -5808,7 +5817,7 @@
         <v>81</v>
       </c>
       <c r="P24" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q24">
         <v>5.5</v>
@@ -6014,7 +6023,7 @@
         <v>97</v>
       </c>
       <c r="P25" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q25">
         <v>2.38</v>
@@ -6220,7 +6229,7 @@
         <v>98</v>
       </c>
       <c r="P26" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q26">
         <v>3.1</v>
@@ -6298,7 +6307,7 @@
         <v>1.5</v>
       </c>
       <c r="AP26">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="AQ26">
         <v>0.5</v>
@@ -6632,7 +6641,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q28">
         <v>1.3</v>
@@ -6838,7 +6847,7 @@
         <v>101</v>
       </c>
       <c r="P29" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q29">
         <v>5</v>
@@ -7456,7 +7465,7 @@
         <v>81</v>
       </c>
       <c r="P32" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q32">
         <v>6</v>
@@ -7537,7 +7546,7 @@
         <v>1</v>
       </c>
       <c r="AQ32">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR32">
         <v>1.48</v>
@@ -7662,7 +7671,7 @@
         <v>104</v>
       </c>
       <c r="P33" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q33">
         <v>8.449999999999999</v>
@@ -8074,7 +8083,7 @@
         <v>105</v>
       </c>
       <c r="P35" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q35">
         <v>2.2</v>
@@ -8280,7 +8289,7 @@
         <v>106</v>
       </c>
       <c r="P36" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q36">
         <v>4.25</v>
@@ -8564,7 +8573,7 @@
         <v>2</v>
       </c>
       <c r="AP37">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ37">
         <v>1.8</v>
@@ -8898,7 +8907,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q39">
         <v>3.2</v>
@@ -8979,7 +8988,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ39">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR39">
         <v>1.2</v>
@@ -9104,7 +9113,7 @@
         <v>81</v>
       </c>
       <c r="P40" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q40">
         <v>12</v>
@@ -9182,7 +9191,7 @@
         <v>3</v>
       </c>
       <c r="AP40">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="AQ40">
         <v>2.1</v>
@@ -9310,7 +9319,7 @@
         <v>110</v>
       </c>
       <c r="P41" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q41">
         <v>3.77</v>
@@ -9391,7 +9400,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ41">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR41">
         <v>1.43</v>
@@ -9722,7 +9731,7 @@
         <v>112</v>
       </c>
       <c r="P43" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q43">
         <v>1.35</v>
@@ -9928,7 +9937,7 @@
         <v>113</v>
       </c>
       <c r="P44" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q44">
         <v>1.66</v>
@@ -10006,7 +10015,7 @@
         <v>1</v>
       </c>
       <c r="AP44">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ44">
         <v>0.8</v>
@@ -10134,7 +10143,7 @@
         <v>114</v>
       </c>
       <c r="P45" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q45">
         <v>4.75</v>
@@ -10340,7 +10349,7 @@
         <v>115</v>
       </c>
       <c r="P46" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q46">
         <v>5.2</v>
@@ -10546,7 +10555,7 @@
         <v>81</v>
       </c>
       <c r="P47" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q47">
         <v>2.35</v>
@@ -10830,7 +10839,7 @@
         <v>1.5</v>
       </c>
       <c r="AP48">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="AQ48">
         <v>1.8</v>
@@ -11039,7 +11048,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ49">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR49">
         <v>2.61</v>
@@ -11164,7 +11173,7 @@
         <v>117</v>
       </c>
       <c r="P50" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q50">
         <v>2.62</v>
@@ -11242,10 +11251,10 @@
         <v>1.8</v>
       </c>
       <c r="AP50">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ50">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR50">
         <v>1.94</v>
@@ -11370,7 +11379,7 @@
         <v>118</v>
       </c>
       <c r="P51" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q51">
         <v>4.55</v>
@@ -11576,7 +11585,7 @@
         <v>81</v>
       </c>
       <c r="P52" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q52">
         <v>6.5</v>
@@ -11782,7 +11791,7 @@
         <v>119</v>
       </c>
       <c r="P53" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q53">
         <v>3.35</v>
@@ -11860,7 +11869,7 @@
         <v>0.8</v>
       </c>
       <c r="AP53">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="AQ53">
         <v>0.8</v>
@@ -12069,7 +12078,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ54">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR54">
         <v>1.43</v>
@@ -12400,7 +12409,7 @@
         <v>122</v>
       </c>
       <c r="P56" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q56">
         <v>1.56</v>
@@ -12606,7 +12615,7 @@
         <v>81</v>
       </c>
       <c r="P57" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q57">
         <v>5.25</v>
@@ -13018,7 +13027,7 @@
         <v>81</v>
       </c>
       <c r="P59" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -13099,7 +13108,7 @@
         <v>1</v>
       </c>
       <c r="AQ59">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR59">
         <v>1.1</v>
@@ -13224,7 +13233,7 @@
         <v>124</v>
       </c>
       <c r="P60" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q60">
         <v>2.25</v>
@@ -13430,7 +13439,7 @@
         <v>125</v>
       </c>
       <c r="P61" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q61">
         <v>2.27</v>
@@ -13636,7 +13645,7 @@
         <v>126</v>
       </c>
       <c r="P62" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q62">
         <v>2.4</v>
@@ -13717,7 +13726,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ62">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR62">
         <v>1.18</v>
@@ -13842,7 +13851,7 @@
         <v>127</v>
       </c>
       <c r="P63" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q63">
         <v>1.64</v>
@@ -14126,7 +14135,7 @@
         <v>2</v>
       </c>
       <c r="AP64">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ64">
         <v>2.1</v>
@@ -14460,7 +14469,7 @@
         <v>130</v>
       </c>
       <c r="P66" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q66">
         <v>4.35</v>
@@ -14538,7 +14547,7 @@
         <v>2</v>
       </c>
       <c r="AP66">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="AQ66">
         <v>1.78</v>
@@ -14872,7 +14881,7 @@
         <v>132</v>
       </c>
       <c r="P68" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q68">
         <v>9</v>
@@ -15078,7 +15087,7 @@
         <v>133</v>
       </c>
       <c r="P69" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q69">
         <v>1.91</v>
@@ -15284,7 +15293,7 @@
         <v>81</v>
       </c>
       <c r="P70" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q70">
         <v>2.35</v>
@@ -15490,7 +15499,7 @@
         <v>134</v>
       </c>
       <c r="P71" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q71">
         <v>1.55</v>
@@ -15696,7 +15705,7 @@
         <v>135</v>
       </c>
       <c r="P72" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q72">
         <v>1.46</v>
@@ -15774,10 +15783,10 @@
         <v>0.57</v>
       </c>
       <c r="AP72">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ72">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR72">
         <v>1.73</v>
@@ -15902,7 +15911,7 @@
         <v>81</v>
       </c>
       <c r="P73" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q73">
         <v>8.5</v>
@@ -16108,7 +16117,7 @@
         <v>81</v>
       </c>
       <c r="P74" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q74">
         <v>2.2</v>
@@ -16314,7 +16323,7 @@
         <v>136</v>
       </c>
       <c r="P75" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q75">
         <v>2.3</v>
@@ -16520,7 +16529,7 @@
         <v>81</v>
       </c>
       <c r="P76" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q76">
         <v>8.949999999999999</v>
@@ -16598,10 +16607,10 @@
         <v>2.14</v>
       </c>
       <c r="AP76">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="AQ76">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR76">
         <v>1.51</v>
@@ -16726,7 +16735,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q77">
         <v>2.94</v>
@@ -16932,7 +16941,7 @@
         <v>81</v>
       </c>
       <c r="P78" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q78">
         <v>4.83</v>
@@ -17010,7 +17019,7 @@
         <v>1.43</v>
       </c>
       <c r="AP78">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="AQ78">
         <v>1.63</v>
@@ -17138,7 +17147,7 @@
         <v>138</v>
       </c>
       <c r="P79" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q79">
         <v>10</v>
@@ -17422,7 +17431,7 @@
         <v>1.29</v>
       </c>
       <c r="AP80">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ80">
         <v>1.8</v>
@@ -17756,7 +17765,7 @@
         <v>141</v>
       </c>
       <c r="P82" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q82">
         <v>2.54</v>
@@ -17837,7 +17846,7 @@
         <v>1</v>
       </c>
       <c r="AQ82">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR82">
         <v>1.51</v>
@@ -17962,7 +17971,7 @@
         <v>142</v>
       </c>
       <c r="P83" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q83">
         <v>3.8</v>
@@ -18374,7 +18383,7 @@
         <v>108</v>
       </c>
       <c r="P85" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q85">
         <v>4.37</v>
@@ -18786,7 +18795,7 @@
         <v>145</v>
       </c>
       <c r="P87" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q87">
         <v>2.25</v>
@@ -18867,7 +18876,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ87">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR87">
         <v>2.42</v>
@@ -18992,7 +19001,7 @@
         <v>146</v>
       </c>
       <c r="P88" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q88">
         <v>3.3</v>
@@ -19198,7 +19207,7 @@
         <v>147</v>
       </c>
       <c r="P89" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q89">
         <v>1.88</v>
@@ -19404,7 +19413,7 @@
         <v>148</v>
       </c>
       <c r="P90" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q90">
         <v>5.6</v>
@@ -19485,7 +19494,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ90">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR90">
         <v>1.38</v>
@@ -19610,7 +19619,7 @@
         <v>81</v>
       </c>
       <c r="P91" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q91">
         <v>5.7</v>
@@ -20022,7 +20031,7 @@
         <v>149</v>
       </c>
       <c r="P93" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q93">
         <v>1.36</v>
@@ -20100,7 +20109,7 @@
         <v>0.13</v>
       </c>
       <c r="AP93">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ93">
         <v>0.11</v>
@@ -20228,7 +20237,7 @@
         <v>81</v>
       </c>
       <c r="P94" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q94">
         <v>3.94</v>
@@ -20434,7 +20443,7 @@
         <v>150</v>
       </c>
       <c r="P95" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q95">
         <v>2.05</v>
@@ -20590,6 +20599,418 @@
         <v>0</v>
       </c>
       <c r="BP95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:68">
+      <c r="A96" s="1">
+        <v>95</v>
+      </c>
+      <c r="B96">
+        <v>7828551</v>
+      </c>
+      <c r="C96" t="s">
+        <v>68</v>
+      </c>
+      <c r="D96" t="s">
+        <v>69</v>
+      </c>
+      <c r="E96" s="2">
+        <v>45844.45833333334</v>
+      </c>
+      <c r="F96">
+        <v>0</v>
+      </c>
+      <c r="G96" t="s">
+        <v>74</v>
+      </c>
+      <c r="H96" t="s">
+        <v>75</v>
+      </c>
+      <c r="I96">
+        <v>1</v>
+      </c>
+      <c r="J96">
+        <v>2</v>
+      </c>
+      <c r="K96">
+        <v>3</v>
+      </c>
+      <c r="L96">
+        <v>3</v>
+      </c>
+      <c r="M96">
+        <v>2</v>
+      </c>
+      <c r="N96">
+        <v>5</v>
+      </c>
+      <c r="O96" t="s">
+        <v>151</v>
+      </c>
+      <c r="P96" t="s">
+        <v>217</v>
+      </c>
+      <c r="Q96">
+        <v>3.73</v>
+      </c>
+      <c r="R96">
+        <v>2.32</v>
+      </c>
+      <c r="S96">
+        <v>2.21</v>
+      </c>
+      <c r="T96">
+        <v>1.28</v>
+      </c>
+      <c r="U96">
+        <v>3.3</v>
+      </c>
+      <c r="V96">
+        <v>2.25</v>
+      </c>
+      <c r="W96">
+        <v>1.57</v>
+      </c>
+      <c r="X96">
+        <v>5.5</v>
+      </c>
+      <c r="Y96">
+        <v>1.08</v>
+      </c>
+      <c r="Z96">
+        <v>3.94</v>
+      </c>
+      <c r="AA96">
+        <v>3.45</v>
+      </c>
+      <c r="AB96">
+        <v>1.74</v>
+      </c>
+      <c r="AC96">
+        <v>1</v>
+      </c>
+      <c r="AD96">
+        <v>12</v>
+      </c>
+      <c r="AE96">
+        <v>1.18</v>
+      </c>
+      <c r="AF96">
+        <v>4.5</v>
+      </c>
+      <c r="AG96">
+        <v>1.53</v>
+      </c>
+      <c r="AH96">
+        <v>2.38</v>
+      </c>
+      <c r="AI96">
+        <v>1.53</v>
+      </c>
+      <c r="AJ96">
+        <v>2.4</v>
+      </c>
+      <c r="AK96">
+        <v>1.15</v>
+      </c>
+      <c r="AL96">
+        <v>1.22</v>
+      </c>
+      <c r="AM96">
+        <v>1.14</v>
+      </c>
+      <c r="AN96">
+        <v>0.67</v>
+      </c>
+      <c r="AO96">
+        <v>0.78</v>
+      </c>
+      <c r="AP96">
+        <v>0.9</v>
+      </c>
+      <c r="AQ96">
+        <v>0.7</v>
+      </c>
+      <c r="AR96">
+        <v>1.5</v>
+      </c>
+      <c r="AS96">
+        <v>1.37</v>
+      </c>
+      <c r="AT96">
+        <v>2.87</v>
+      </c>
+      <c r="AU96">
+        <v>10</v>
+      </c>
+      <c r="AV96">
+        <v>8</v>
+      </c>
+      <c r="AW96">
+        <v>7</v>
+      </c>
+      <c r="AX96">
+        <v>6</v>
+      </c>
+      <c r="AY96">
+        <v>17</v>
+      </c>
+      <c r="AZ96">
+        <v>14</v>
+      </c>
+      <c r="BA96">
+        <v>3</v>
+      </c>
+      <c r="BB96">
+        <v>5</v>
+      </c>
+      <c r="BC96">
+        <v>8</v>
+      </c>
+      <c r="BD96">
+        <v>0</v>
+      </c>
+      <c r="BE96">
+        <v>0</v>
+      </c>
+      <c r="BF96">
+        <v>0</v>
+      </c>
+      <c r="BG96">
+        <v>0</v>
+      </c>
+      <c r="BH96">
+        <v>0</v>
+      </c>
+      <c r="BI96">
+        <v>0</v>
+      </c>
+      <c r="BJ96">
+        <v>0</v>
+      </c>
+      <c r="BK96">
+        <v>0</v>
+      </c>
+      <c r="BL96">
+        <v>0</v>
+      </c>
+      <c r="BM96">
+        <v>0</v>
+      </c>
+      <c r="BN96">
+        <v>0</v>
+      </c>
+      <c r="BO96">
+        <v>0</v>
+      </c>
+      <c r="BP96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:68">
+      <c r="A97" s="1">
+        <v>96</v>
+      </c>
+      <c r="B97">
+        <v>7828552</v>
+      </c>
+      <c r="C97" t="s">
+        <v>68</v>
+      </c>
+      <c r="D97" t="s">
+        <v>69</v>
+      </c>
+      <c r="E97" s="2">
+        <v>45844.64583333334</v>
+      </c>
+      <c r="F97">
+        <v>0</v>
+      </c>
+      <c r="G97" t="s">
+        <v>72</v>
+      </c>
+      <c r="H97" t="s">
+        <v>79</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>0</v>
+      </c>
+      <c r="K97">
+        <v>0</v>
+      </c>
+      <c r="L97">
+        <v>1</v>
+      </c>
+      <c r="M97">
+        <v>0</v>
+      </c>
+      <c r="N97">
+        <v>1</v>
+      </c>
+      <c r="O97" t="s">
+        <v>152</v>
+      </c>
+      <c r="P97" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q97">
+        <v>2.29</v>
+      </c>
+      <c r="R97">
+        <v>2.3</v>
+      </c>
+      <c r="S97">
+        <v>3.95</v>
+      </c>
+      <c r="T97">
+        <v>1.22</v>
+      </c>
+      <c r="U97">
+        <v>3.6</v>
+      </c>
+      <c r="V97">
+        <v>2.15</v>
+      </c>
+      <c r="W97">
+        <v>1.6</v>
+      </c>
+      <c r="X97">
+        <v>5</v>
+      </c>
+      <c r="Y97">
+        <v>1.14</v>
+      </c>
+      <c r="Z97">
+        <v>1.75</v>
+      </c>
+      <c r="AA97">
+        <v>3.73</v>
+      </c>
+      <c r="AB97">
+        <v>3.58</v>
+      </c>
+      <c r="AC97">
+        <v>1.03</v>
+      </c>
+      <c r="AD97">
+        <v>15</v>
+      </c>
+      <c r="AE97">
+        <v>1.18</v>
+      </c>
+      <c r="AF97">
+        <v>4.75</v>
+      </c>
+      <c r="AG97">
+        <v>1.57</v>
+      </c>
+      <c r="AH97">
+        <v>2.3</v>
+      </c>
+      <c r="AI97">
+        <v>1.5</v>
+      </c>
+      <c r="AJ97">
+        <v>2.51</v>
+      </c>
+      <c r="AK97">
+        <v>1.29</v>
+      </c>
+      <c r="AL97">
+        <v>1.26</v>
+      </c>
+      <c r="AM97">
+        <v>1.85</v>
+      </c>
+      <c r="AN97">
+        <v>1.9</v>
+      </c>
+      <c r="AO97">
+        <v>1.9</v>
+      </c>
+      <c r="AP97">
+        <v>2</v>
+      </c>
+      <c r="AQ97">
+        <v>1.73</v>
+      </c>
+      <c r="AR97">
+        <v>1.77</v>
+      </c>
+      <c r="AS97">
+        <v>2.16</v>
+      </c>
+      <c r="AT97">
+        <v>3.93</v>
+      </c>
+      <c r="AU97">
+        <v>7</v>
+      </c>
+      <c r="AV97">
+        <v>8</v>
+      </c>
+      <c r="AW97">
+        <v>6</v>
+      </c>
+      <c r="AX97">
+        <v>8</v>
+      </c>
+      <c r="AY97">
+        <v>13</v>
+      </c>
+      <c r="AZ97">
+        <v>16</v>
+      </c>
+      <c r="BA97">
+        <v>8</v>
+      </c>
+      <c r="BB97">
+        <v>3</v>
+      </c>
+      <c r="BC97">
+        <v>11</v>
+      </c>
+      <c r="BD97">
+        <v>0</v>
+      </c>
+      <c r="BE97">
+        <v>0</v>
+      </c>
+      <c r="BF97">
+        <v>0</v>
+      </c>
+      <c r="BG97">
+        <v>0</v>
+      </c>
+      <c r="BH97">
+        <v>0</v>
+      </c>
+      <c r="BI97">
+        <v>0</v>
+      </c>
+      <c r="BJ97">
+        <v>0</v>
+      </c>
+      <c r="BK97">
+        <v>0</v>
+      </c>
+      <c r="BL97">
+        <v>0</v>
+      </c>
+      <c r="BM97">
+        <v>0</v>
+      </c>
+      <c r="BN97">
+        <v>0</v>
+      </c>
+      <c r="BO97">
+        <v>0</v>
+      </c>
+      <c r="BP97">
         <v>0</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="217">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -469,10 +469,7 @@
     <t>['22', '38', '79']</t>
   </si>
   <si>
-    <t>['41', '76', '49']</t>
-  </si>
-  <si>
-    <t>['90+1']</t>
+    <t>['41', '76', '48']</t>
   </si>
   <si>
     <t>['34', '59', '86']</t>
@@ -1491,7 +1488,7 @@
         <v>81</v>
       </c>
       <c r="P3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -1697,7 +1694,7 @@
         <v>82</v>
       </c>
       <c r="P4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -1903,7 +1900,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="Q5">
         <v>7</v>
@@ -2109,7 +2106,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2521,7 +2518,7 @@
         <v>85</v>
       </c>
       <c r="P8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Q8">
         <v>8.5</v>
@@ -2727,7 +2724,7 @@
         <v>81</v>
       </c>
       <c r="P9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -3345,7 +3342,7 @@
         <v>88</v>
       </c>
       <c r="P12" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="Q12">
         <v>8</v>
@@ -3757,7 +3754,7 @@
         <v>81</v>
       </c>
       <c r="P14" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q14">
         <v>5.5</v>
@@ -3963,7 +3960,7 @@
         <v>90</v>
       </c>
       <c r="P15" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q15">
         <v>2.5</v>
@@ -4169,7 +4166,7 @@
         <v>91</v>
       </c>
       <c r="P16" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Q16">
         <v>2.1</v>
@@ -4375,7 +4372,7 @@
         <v>81</v>
       </c>
       <c r="P17" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="Q17">
         <v>2.38</v>
@@ -4581,7 +4578,7 @@
         <v>81</v>
       </c>
       <c r="P18" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q18">
         <v>3.4</v>
@@ -5199,7 +5196,7 @@
         <v>94</v>
       </c>
       <c r="P21" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Q21">
         <v>1.91</v>
@@ -5611,7 +5608,7 @@
         <v>96</v>
       </c>
       <c r="P23" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -5817,7 +5814,7 @@
         <v>81</v>
       </c>
       <c r="P24" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Q24">
         <v>5.5</v>
@@ -6023,7 +6020,7 @@
         <v>97</v>
       </c>
       <c r="P25" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q25">
         <v>2.38</v>
@@ -6229,7 +6226,7 @@
         <v>98</v>
       </c>
       <c r="P26" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="Q26">
         <v>3.1</v>
@@ -6641,7 +6638,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="Q28">
         <v>1.3</v>
@@ -6847,7 +6844,7 @@
         <v>101</v>
       </c>
       <c r="P29" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Q29">
         <v>5</v>
@@ -7465,7 +7462,7 @@
         <v>81</v>
       </c>
       <c r="P32" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q32">
         <v>6</v>
@@ -7671,7 +7668,7 @@
         <v>104</v>
       </c>
       <c r="P33" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q33">
         <v>8.449999999999999</v>
@@ -8083,7 +8080,7 @@
         <v>105</v>
       </c>
       <c r="P35" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q35">
         <v>2.2</v>
@@ -8289,7 +8286,7 @@
         <v>106</v>
       </c>
       <c r="P36" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q36">
         <v>4.25</v>
@@ -8907,7 +8904,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q39">
         <v>3.2</v>
@@ -9113,7 +9110,7 @@
         <v>81</v>
       </c>
       <c r="P40" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q40">
         <v>12</v>
@@ -9319,7 +9316,7 @@
         <v>110</v>
       </c>
       <c r="P41" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q41">
         <v>3.77</v>
@@ -9731,7 +9728,7 @@
         <v>112</v>
       </c>
       <c r="P43" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q43">
         <v>1.35</v>
@@ -9937,7 +9934,7 @@
         <v>113</v>
       </c>
       <c r="P44" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q44">
         <v>1.66</v>
@@ -10143,7 +10140,7 @@
         <v>114</v>
       </c>
       <c r="P45" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q45">
         <v>4.75</v>
@@ -10349,7 +10346,7 @@
         <v>115</v>
       </c>
       <c r="P46" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q46">
         <v>5.2</v>
@@ -10555,7 +10552,7 @@
         <v>81</v>
       </c>
       <c r="P47" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q47">
         <v>2.35</v>
@@ -11173,7 +11170,7 @@
         <v>117</v>
       </c>
       <c r="P50" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q50">
         <v>2.62</v>
@@ -11379,7 +11376,7 @@
         <v>118</v>
       </c>
       <c r="P51" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q51">
         <v>4.55</v>
@@ -11585,7 +11582,7 @@
         <v>81</v>
       </c>
       <c r="P52" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q52">
         <v>6.5</v>
@@ -11791,7 +11788,7 @@
         <v>119</v>
       </c>
       <c r="P53" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q53">
         <v>3.35</v>
@@ -12409,7 +12406,7 @@
         <v>122</v>
       </c>
       <c r="P56" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q56">
         <v>1.56</v>
@@ -12615,7 +12612,7 @@
         <v>81</v>
       </c>
       <c r="P57" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Q57">
         <v>5.25</v>
@@ -13027,7 +13024,7 @@
         <v>81</v>
       </c>
       <c r="P59" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -13233,7 +13230,7 @@
         <v>124</v>
       </c>
       <c r="P60" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q60">
         <v>2.25</v>
@@ -13439,7 +13436,7 @@
         <v>125</v>
       </c>
       <c r="P61" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q61">
         <v>2.27</v>
@@ -13645,7 +13642,7 @@
         <v>126</v>
       </c>
       <c r="P62" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Q62">
         <v>2.4</v>
@@ -13851,7 +13848,7 @@
         <v>127</v>
       </c>
       <c r="P63" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q63">
         <v>1.64</v>
@@ -14469,7 +14466,7 @@
         <v>130</v>
       </c>
       <c r="P66" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Q66">
         <v>4.35</v>
@@ -14881,7 +14878,7 @@
         <v>132</v>
       </c>
       <c r="P68" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q68">
         <v>9</v>
@@ -15087,7 +15084,7 @@
         <v>133</v>
       </c>
       <c r="P69" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Q69">
         <v>1.91</v>
@@ -15293,7 +15290,7 @@
         <v>81</v>
       </c>
       <c r="P70" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q70">
         <v>2.35</v>
@@ -15499,7 +15496,7 @@
         <v>134</v>
       </c>
       <c r="P71" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q71">
         <v>1.55</v>
@@ -15705,7 +15702,7 @@
         <v>135</v>
       </c>
       <c r="P72" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q72">
         <v>1.46</v>
@@ -15911,7 +15908,7 @@
         <v>81</v>
       </c>
       <c r="P73" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q73">
         <v>8.5</v>
@@ -16117,7 +16114,7 @@
         <v>81</v>
       </c>
       <c r="P74" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Q74">
         <v>2.2</v>
@@ -16323,7 +16320,7 @@
         <v>136</v>
       </c>
       <c r="P75" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="Q75">
         <v>2.3</v>
@@ -16529,7 +16526,7 @@
         <v>81</v>
       </c>
       <c r="P76" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Q76">
         <v>8.949999999999999</v>
@@ -16735,7 +16732,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q77">
         <v>2.94</v>
@@ -16941,7 +16938,7 @@
         <v>81</v>
       </c>
       <c r="P78" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q78">
         <v>4.83</v>
@@ -17147,7 +17144,7 @@
         <v>138</v>
       </c>
       <c r="P79" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="Q79">
         <v>10</v>
@@ -17765,7 +17762,7 @@
         <v>141</v>
       </c>
       <c r="P82" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q82">
         <v>2.54</v>
@@ -17971,7 +17968,7 @@
         <v>142</v>
       </c>
       <c r="P83" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Q83">
         <v>3.8</v>
@@ -18383,7 +18380,7 @@
         <v>108</v>
       </c>
       <c r="P85" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Q85">
         <v>4.37</v>
@@ -18795,7 +18792,7 @@
         <v>145</v>
       </c>
       <c r="P87" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Q87">
         <v>2.25</v>
@@ -19001,7 +18998,7 @@
         <v>146</v>
       </c>
       <c r="P88" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q88">
         <v>3.3</v>
@@ -19207,7 +19204,7 @@
         <v>147</v>
       </c>
       <c r="P89" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q89">
         <v>1.88</v>
@@ -19413,7 +19410,7 @@
         <v>148</v>
       </c>
       <c r="P90" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Q90">
         <v>5.6</v>
@@ -19619,7 +19616,7 @@
         <v>81</v>
       </c>
       <c r="P91" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q91">
         <v>5.7</v>
@@ -20031,7 +20028,7 @@
         <v>149</v>
       </c>
       <c r="P93" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q93">
         <v>1.36</v>
@@ -20237,7 +20234,7 @@
         <v>81</v>
       </c>
       <c r="P94" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q94">
         <v>3.94</v>
@@ -20443,7 +20440,7 @@
         <v>150</v>
       </c>
       <c r="P95" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="Q95">
         <v>2.05</v>
@@ -20649,7 +20646,7 @@
         <v>151</v>
       </c>
       <c r="P96" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="Q96">
         <v>3.73</v>
@@ -20852,7 +20849,7 @@
         <v>1</v>
       </c>
       <c r="O97" t="s">
-        <v>152</v>
+        <v>83</v>
       </c>
       <c r="P97" t="s">
         <v>81</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="218">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -665,6 +665,9 @@
   </si>
   <si>
     <t>['6', '9']</t>
+  </si>
+  <si>
+    <t>['4', '49']</t>
   </si>
 </sst>
 </file>
@@ -1026,7 +1029,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP97"/>
+  <dimension ref="A1:BP99"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1566,7 +1569,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AQ3">
         <v>1.73</v>
@@ -1775,7 +1778,7 @@
         <v>2</v>
       </c>
       <c r="AQ4">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1978,7 +1981,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ5">
         <v>1.8</v>
@@ -2187,7 +2190,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ6">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -3420,7 +3423,7 @@
         <v>3</v>
       </c>
       <c r="AP12">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AQ12">
         <v>2.1</v>
@@ -4038,7 +4041,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ15">
         <v>0.8</v>
@@ -4247,7 +4250,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ16">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4659,7 +4662,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ18">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR18">
         <v>1.67</v>
@@ -5483,7 +5486,7 @@
         <v>2</v>
       </c>
       <c r="AQ22">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR22">
         <v>3.01</v>
@@ -6098,7 +6101,7 @@
         <v>1.5</v>
       </c>
       <c r="AP25">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AQ25">
         <v>0.8</v>
@@ -7540,7 +7543,7 @@
         <v>1</v>
       </c>
       <c r="AP32">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ32">
         <v>1.73</v>
@@ -8158,7 +8161,7 @@
         <v>0</v>
       </c>
       <c r="AP35">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AQ35">
         <v>0.11</v>
@@ -8367,7 +8370,7 @@
         <v>1</v>
       </c>
       <c r="AQ36">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR36">
         <v>0.99</v>
@@ -8776,7 +8779,7 @@
         <v>2</v>
       </c>
       <c r="AP38">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ38">
         <v>1.63</v>
@@ -8985,7 +8988,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ39">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR39">
         <v>1.2</v>
@@ -10218,10 +10221,10 @@
         <v>2.33</v>
       </c>
       <c r="AP45">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AQ45">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR45">
         <v>1.06</v>
@@ -11045,7 +11048,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ49">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR49">
         <v>2.61</v>
@@ -11454,10 +11457,10 @@
         <v>2.5</v>
       </c>
       <c r="AP51">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ51">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR51">
         <v>1.64</v>
@@ -11660,7 +11663,7 @@
         <v>2.5</v>
       </c>
       <c r="AP52">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AQ52">
         <v>2.44</v>
@@ -12075,7 +12078,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ54">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR54">
         <v>1.43</v>
@@ -12896,7 +12899,7 @@
         <v>0.2</v>
       </c>
       <c r="AP58">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ58">
         <v>0.11</v>
@@ -13720,10 +13723,10 @@
         <v>0.67</v>
       </c>
       <c r="AP62">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AQ62">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR62">
         <v>1.18</v>
@@ -14547,7 +14550,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ66">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR66">
         <v>1.52</v>
@@ -14956,7 +14959,7 @@
         <v>2.67</v>
       </c>
       <c r="AP68">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ68">
         <v>2.44</v>
@@ -15783,7 +15786,7 @@
         <v>2</v>
       </c>
       <c r="AQ72">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR72">
         <v>1.73</v>
@@ -16195,7 +16198,7 @@
         <v>2</v>
       </c>
       <c r="AQ74">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR74">
         <v>2.22</v>
@@ -16398,7 +16401,7 @@
         <v>0.57</v>
       </c>
       <c r="AP75">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AQ75">
         <v>0.5</v>
@@ -17222,7 +17225,7 @@
         <v>1.88</v>
       </c>
       <c r="AP79">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ79">
         <v>2.1</v>
@@ -17637,7 +17640,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ81">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR81">
         <v>1.99</v>
@@ -17840,10 +17843,10 @@
         <v>0.5</v>
       </c>
       <c r="AP82">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ82">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR82">
         <v>1.51</v>
@@ -18458,7 +18461,7 @@
         <v>1.5</v>
       </c>
       <c r="AP85">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AQ85">
         <v>1.8</v>
@@ -19285,7 +19288,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ89">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR89">
         <v>2.46</v>
@@ -19488,7 +19491,7 @@
         <v>2</v>
       </c>
       <c r="AP90">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AQ90">
         <v>1.73</v>
@@ -20727,7 +20730,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ96">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR96">
         <v>1.5</v>
@@ -21008,6 +21011,418 @@
         <v>0</v>
       </c>
       <c r="BP97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:68">
+      <c r="A98" s="1">
+        <v>97</v>
+      </c>
+      <c r="B98">
+        <v>7828556</v>
+      </c>
+      <c r="C98" t="s">
+        <v>68</v>
+      </c>
+      <c r="D98" t="s">
+        <v>69</v>
+      </c>
+      <c r="E98" s="2">
+        <v>45849.54166666666</v>
+      </c>
+      <c r="F98">
+        <v>0</v>
+      </c>
+      <c r="G98" t="s">
+        <v>73</v>
+      </c>
+      <c r="H98" t="s">
+        <v>75</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>1</v>
+      </c>
+      <c r="K98">
+        <v>1</v>
+      </c>
+      <c r="L98">
+        <v>0</v>
+      </c>
+      <c r="M98">
+        <v>2</v>
+      </c>
+      <c r="N98">
+        <v>2</v>
+      </c>
+      <c r="O98" t="s">
+        <v>81</v>
+      </c>
+      <c r="P98" t="s">
+        <v>217</v>
+      </c>
+      <c r="Q98">
+        <v>2.85</v>
+      </c>
+      <c r="R98">
+        <v>2.25</v>
+      </c>
+      <c r="S98">
+        <v>3.24</v>
+      </c>
+      <c r="T98">
+        <v>1.29</v>
+      </c>
+      <c r="U98">
+        <v>3.5</v>
+      </c>
+      <c r="V98">
+        <v>2.29</v>
+      </c>
+      <c r="W98">
+        <v>1.58</v>
+      </c>
+      <c r="X98">
+        <v>4.75</v>
+      </c>
+      <c r="Y98">
+        <v>1.14</v>
+      </c>
+      <c r="Z98">
+        <v>2.03</v>
+      </c>
+      <c r="AA98">
+        <v>3.45</v>
+      </c>
+      <c r="AB98">
+        <v>2.82</v>
+      </c>
+      <c r="AC98">
+        <v>1.03</v>
+      </c>
+      <c r="AD98">
+        <v>15</v>
+      </c>
+      <c r="AE98">
+        <v>1.12</v>
+      </c>
+      <c r="AF98">
+        <v>4.5</v>
+      </c>
+      <c r="AG98">
+        <v>1.5</v>
+      </c>
+      <c r="AH98">
+        <v>2.38</v>
+      </c>
+      <c r="AI98">
+        <v>1.48</v>
+      </c>
+      <c r="AJ98">
+        <v>2.5</v>
+      </c>
+      <c r="AK98">
+        <v>1.48</v>
+      </c>
+      <c r="AL98">
+        <v>1.23</v>
+      </c>
+      <c r="AM98">
+        <v>1.54</v>
+      </c>
+      <c r="AN98">
+        <v>1</v>
+      </c>
+      <c r="AO98">
+        <v>0.7</v>
+      </c>
+      <c r="AP98">
+        <v>0.9</v>
+      </c>
+      <c r="AQ98">
+        <v>0.91</v>
+      </c>
+      <c r="AR98">
+        <v>1.58</v>
+      </c>
+      <c r="AS98">
+        <v>1.42</v>
+      </c>
+      <c r="AT98">
+        <v>3</v>
+      </c>
+      <c r="AU98">
+        <v>6</v>
+      </c>
+      <c r="AV98">
+        <v>11</v>
+      </c>
+      <c r="AW98">
+        <v>11</v>
+      </c>
+      <c r="AX98">
+        <v>14</v>
+      </c>
+      <c r="AY98">
+        <v>17</v>
+      </c>
+      <c r="AZ98">
+        <v>25</v>
+      </c>
+      <c r="BA98">
+        <v>10</v>
+      </c>
+      <c r="BB98">
+        <v>6</v>
+      </c>
+      <c r="BC98">
+        <v>16</v>
+      </c>
+      <c r="BD98">
+        <v>0</v>
+      </c>
+      <c r="BE98">
+        <v>0</v>
+      </c>
+      <c r="BF98">
+        <v>0</v>
+      </c>
+      <c r="BG98">
+        <v>0</v>
+      </c>
+      <c r="BH98">
+        <v>0</v>
+      </c>
+      <c r="BI98">
+        <v>0</v>
+      </c>
+      <c r="BJ98">
+        <v>0</v>
+      </c>
+      <c r="BK98">
+        <v>0</v>
+      </c>
+      <c r="BL98">
+        <v>0</v>
+      </c>
+      <c r="BM98">
+        <v>0</v>
+      </c>
+      <c r="BN98">
+        <v>0</v>
+      </c>
+      <c r="BO98">
+        <v>0</v>
+      </c>
+      <c r="BP98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:68">
+      <c r="A99" s="1">
+        <v>98</v>
+      </c>
+      <c r="B99">
+        <v>7828555</v>
+      </c>
+      <c r="C99" t="s">
+        <v>68</v>
+      </c>
+      <c r="D99" t="s">
+        <v>69</v>
+      </c>
+      <c r="E99" s="2">
+        <v>45850.35416666666</v>
+      </c>
+      <c r="F99">
+        <v>0</v>
+      </c>
+      <c r="G99" t="s">
+        <v>71</v>
+      </c>
+      <c r="H99" t="s">
+        <v>76</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>0</v>
+      </c>
+      <c r="K99">
+        <v>0</v>
+      </c>
+      <c r="L99">
+        <v>0</v>
+      </c>
+      <c r="M99">
+        <v>0</v>
+      </c>
+      <c r="N99">
+        <v>0</v>
+      </c>
+      <c r="O99" t="s">
+        <v>81</v>
+      </c>
+      <c r="P99" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q99">
+        <v>3.2</v>
+      </c>
+      <c r="R99">
+        <v>2.17</v>
+      </c>
+      <c r="S99">
+        <v>2.44</v>
+      </c>
+      <c r="T99">
+        <v>1.33</v>
+      </c>
+      <c r="U99">
+        <v>3.1</v>
+      </c>
+      <c r="V99">
+        <v>2.5</v>
+      </c>
+      <c r="W99">
+        <v>1.44</v>
+      </c>
+      <c r="X99">
+        <v>6.5</v>
+      </c>
+      <c r="Y99">
+        <v>1.11</v>
+      </c>
+      <c r="Z99">
+        <v>3.55</v>
+      </c>
+      <c r="AA99">
+        <v>3.3</v>
+      </c>
+      <c r="AB99">
+        <v>1.91</v>
+      </c>
+      <c r="AC99">
+        <v>1.05</v>
+      </c>
+      <c r="AD99">
+        <v>9.9</v>
+      </c>
+      <c r="AE99">
+        <v>1.25</v>
+      </c>
+      <c r="AF99">
+        <v>3.7</v>
+      </c>
+      <c r="AG99">
+        <v>1.7</v>
+      </c>
+      <c r="AH99">
+        <v>2</v>
+      </c>
+      <c r="AI99">
+        <v>1.6</v>
+      </c>
+      <c r="AJ99">
+        <v>2.14</v>
+      </c>
+      <c r="AK99">
+        <v>1.3</v>
+      </c>
+      <c r="AL99">
+        <v>1.22</v>
+      </c>
+      <c r="AM99">
+        <v>1.29</v>
+      </c>
+      <c r="AN99">
+        <v>0.9</v>
+      </c>
+      <c r="AO99">
+        <v>1.78</v>
+      </c>
+      <c r="AP99">
+        <v>0.91</v>
+      </c>
+      <c r="AQ99">
+        <v>1.7</v>
+      </c>
+      <c r="AR99">
+        <v>1.39</v>
+      </c>
+      <c r="AS99">
+        <v>1.68</v>
+      </c>
+      <c r="AT99">
+        <v>3.07</v>
+      </c>
+      <c r="AU99">
+        <v>6</v>
+      </c>
+      <c r="AV99">
+        <v>2</v>
+      </c>
+      <c r="AW99">
+        <v>10</v>
+      </c>
+      <c r="AX99">
+        <v>8</v>
+      </c>
+      <c r="AY99">
+        <v>16</v>
+      </c>
+      <c r="AZ99">
+        <v>10</v>
+      </c>
+      <c r="BA99">
+        <v>4</v>
+      </c>
+      <c r="BB99">
+        <v>5</v>
+      </c>
+      <c r="BC99">
+        <v>9</v>
+      </c>
+      <c r="BD99">
+        <v>0</v>
+      </c>
+      <c r="BE99">
+        <v>0</v>
+      </c>
+      <c r="BF99">
+        <v>0</v>
+      </c>
+      <c r="BG99">
+        <v>0</v>
+      </c>
+      <c r="BH99">
+        <v>0</v>
+      </c>
+      <c r="BI99">
+        <v>0</v>
+      </c>
+      <c r="BJ99">
+        <v>0</v>
+      </c>
+      <c r="BK99">
+        <v>0</v>
+      </c>
+      <c r="BL99">
+        <v>0</v>
+      </c>
+      <c r="BM99">
+        <v>0</v>
+      </c>
+      <c r="BN99">
+        <v>0</v>
+      </c>
+      <c r="BO99">
+        <v>0</v>
+      </c>
+      <c r="BP99">
         <v>0</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
@@ -21366,16 +21366,16 @@
         <v>2</v>
       </c>
       <c r="AW99">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX99">
+        <v>6</v>
+      </c>
+      <c r="AY99">
+        <v>15</v>
+      </c>
+      <c r="AZ99">
         <v>8</v>
-      </c>
-      <c r="AY99">
-        <v>16</v>
-      </c>
-      <c r="AZ99">
-        <v>10</v>
       </c>
       <c r="BA99">
         <v>4</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="219">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -470,6 +470,9 @@
   </si>
   <si>
     <t>['41', '76', '48']</t>
+  </si>
+  <si>
+    <t>['4', '43', '69']</t>
   </si>
   <si>
     <t>['34', '59', '86']</t>
@@ -1029,7 +1032,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP99"/>
+  <dimension ref="A1:BP100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1366,7 +1369,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ2">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1491,7 +1494,7 @@
         <v>81</v>
       </c>
       <c r="P3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -1697,7 +1700,7 @@
         <v>82</v>
       </c>
       <c r="P4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -1903,7 +1906,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q5">
         <v>7</v>
@@ -2109,7 +2112,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2187,7 +2190,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ6">
         <v>0.91</v>
@@ -2521,7 +2524,7 @@
         <v>85</v>
       </c>
       <c r="P8" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q8">
         <v>8.5</v>
@@ -2727,7 +2730,7 @@
         <v>81</v>
       </c>
       <c r="P9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -3345,7 +3348,7 @@
         <v>88</v>
       </c>
       <c r="P12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q12">
         <v>8</v>
@@ -3757,7 +3760,7 @@
         <v>81</v>
       </c>
       <c r="P14" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q14">
         <v>5.5</v>
@@ -3835,7 +3838,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ14">
         <v>2.44</v>
@@ -3963,7 +3966,7 @@
         <v>90</v>
       </c>
       <c r="P15" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q15">
         <v>2.5</v>
@@ -4044,7 +4047,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ15">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR15">
         <v>1.37</v>
@@ -4169,7 +4172,7 @@
         <v>91</v>
       </c>
       <c r="P16" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q16">
         <v>2.1</v>
@@ -4375,7 +4378,7 @@
         <v>81</v>
       </c>
       <c r="P17" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q17">
         <v>2.38</v>
@@ -4581,7 +4584,7 @@
         <v>81</v>
       </c>
       <c r="P18" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q18">
         <v>3.4</v>
@@ -5199,7 +5202,7 @@
         <v>94</v>
       </c>
       <c r="P21" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q21">
         <v>1.91</v>
@@ -5611,7 +5614,7 @@
         <v>96</v>
       </c>
       <c r="P23" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -5817,7 +5820,7 @@
         <v>81</v>
       </c>
       <c r="P24" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q24">
         <v>5.5</v>
@@ -6023,7 +6026,7 @@
         <v>97</v>
       </c>
       <c r="P25" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q25">
         <v>2.38</v>
@@ -6104,7 +6107,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ25">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR25">
         <v>0.71</v>
@@ -6229,7 +6232,7 @@
         <v>98</v>
       </c>
       <c r="P26" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q26">
         <v>3.1</v>
@@ -6307,7 +6310,7 @@
         <v>1.5</v>
       </c>
       <c r="AP26">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ26">
         <v>0.5</v>
@@ -6641,7 +6644,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q28">
         <v>1.3</v>
@@ -6847,7 +6850,7 @@
         <v>101</v>
       </c>
       <c r="P29" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q29">
         <v>5</v>
@@ -7134,7 +7137,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ30">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR30">
         <v>2.7</v>
@@ -7465,7 +7468,7 @@
         <v>81</v>
       </c>
       <c r="P32" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q32">
         <v>6</v>
@@ -7671,7 +7674,7 @@
         <v>104</v>
       </c>
       <c r="P33" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q33">
         <v>8.449999999999999</v>
@@ -8083,7 +8086,7 @@
         <v>105</v>
       </c>
       <c r="P35" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q35">
         <v>2.2</v>
@@ -8289,7 +8292,7 @@
         <v>106</v>
       </c>
       <c r="P36" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q36">
         <v>4.25</v>
@@ -8907,7 +8910,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q39">
         <v>3.2</v>
@@ -9113,7 +9116,7 @@
         <v>81</v>
       </c>
       <c r="P40" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q40">
         <v>12</v>
@@ -9191,7 +9194,7 @@
         <v>3</v>
       </c>
       <c r="AP40">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ40">
         <v>2.1</v>
@@ -9319,7 +9322,7 @@
         <v>110</v>
       </c>
       <c r="P41" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q41">
         <v>3.77</v>
@@ -9731,7 +9734,7 @@
         <v>112</v>
       </c>
       <c r="P43" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q43">
         <v>1.35</v>
@@ -9937,7 +9940,7 @@
         <v>113</v>
       </c>
       <c r="P44" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q44">
         <v>1.66</v>
@@ -10018,7 +10021,7 @@
         <v>2</v>
       </c>
       <c r="AQ44">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR44">
         <v>1.77</v>
@@ -10143,7 +10146,7 @@
         <v>114</v>
       </c>
       <c r="P45" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q45">
         <v>4.75</v>
@@ -10349,7 +10352,7 @@
         <v>115</v>
       </c>
       <c r="P46" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q46">
         <v>5.2</v>
@@ -10555,7 +10558,7 @@
         <v>81</v>
       </c>
       <c r="P47" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q47">
         <v>2.35</v>
@@ -10839,7 +10842,7 @@
         <v>1.5</v>
       </c>
       <c r="AP48">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ48">
         <v>1.8</v>
@@ -11173,7 +11176,7 @@
         <v>117</v>
       </c>
       <c r="P50" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q50">
         <v>2.62</v>
@@ -11379,7 +11382,7 @@
         <v>118</v>
       </c>
       <c r="P51" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q51">
         <v>4.55</v>
@@ -11585,7 +11588,7 @@
         <v>81</v>
       </c>
       <c r="P52" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q52">
         <v>6.5</v>
@@ -11791,7 +11794,7 @@
         <v>119</v>
       </c>
       <c r="P53" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q53">
         <v>3.35</v>
@@ -11869,10 +11872,10 @@
         <v>0.8</v>
       </c>
       <c r="AP53">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ53">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR53">
         <v>1.56</v>
@@ -12409,7 +12412,7 @@
         <v>122</v>
       </c>
       <c r="P56" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q56">
         <v>1.56</v>
@@ -12615,7 +12618,7 @@
         <v>81</v>
       </c>
       <c r="P57" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q57">
         <v>5.25</v>
@@ -13027,7 +13030,7 @@
         <v>81</v>
       </c>
       <c r="P59" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -13233,7 +13236,7 @@
         <v>124</v>
       </c>
       <c r="P60" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q60">
         <v>2.25</v>
@@ -13439,7 +13442,7 @@
         <v>125</v>
       </c>
       <c r="P61" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q61">
         <v>2.27</v>
@@ -13645,7 +13648,7 @@
         <v>126</v>
       </c>
       <c r="P62" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q62">
         <v>2.4</v>
@@ -13851,7 +13854,7 @@
         <v>127</v>
       </c>
       <c r="P63" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q63">
         <v>1.64</v>
@@ -13932,7 +13935,7 @@
         <v>2</v>
       </c>
       <c r="AQ63">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR63">
         <v>2.27</v>
@@ -14469,7 +14472,7 @@
         <v>130</v>
       </c>
       <c r="P66" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q66">
         <v>4.35</v>
@@ -14547,7 +14550,7 @@
         <v>2</v>
       </c>
       <c r="AP66">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ66">
         <v>1.7</v>
@@ -14881,7 +14884,7 @@
         <v>132</v>
       </c>
       <c r="P68" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q68">
         <v>9</v>
@@ -15087,7 +15090,7 @@
         <v>133</v>
       </c>
       <c r="P69" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q69">
         <v>1.91</v>
@@ -15168,7 +15171,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ69">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR69">
         <v>1.66</v>
@@ -15293,7 +15296,7 @@
         <v>81</v>
       </c>
       <c r="P70" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q70">
         <v>2.35</v>
@@ -15499,7 +15502,7 @@
         <v>134</v>
       </c>
       <c r="P71" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q71">
         <v>1.55</v>
@@ -15705,7 +15708,7 @@
         <v>135</v>
       </c>
       <c r="P72" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q72">
         <v>1.46</v>
@@ -15911,7 +15914,7 @@
         <v>81</v>
       </c>
       <c r="P73" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q73">
         <v>8.5</v>
@@ -16117,7 +16120,7 @@
         <v>81</v>
       </c>
       <c r="P74" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q74">
         <v>2.2</v>
@@ -16323,7 +16326,7 @@
         <v>136</v>
       </c>
       <c r="P75" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q75">
         <v>2.3</v>
@@ -16529,7 +16532,7 @@
         <v>81</v>
       </c>
       <c r="P76" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q76">
         <v>8.949999999999999</v>
@@ -16607,7 +16610,7 @@
         <v>2.14</v>
       </c>
       <c r="AP76">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ76">
         <v>1.73</v>
@@ -16735,7 +16738,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q77">
         <v>2.94</v>
@@ -16816,7 +16819,7 @@
         <v>1</v>
       </c>
       <c r="AQ77">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR77">
         <v>1.36</v>
@@ -16941,7 +16944,7 @@
         <v>81</v>
       </c>
       <c r="P78" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q78">
         <v>4.83</v>
@@ -17019,7 +17022,7 @@
         <v>1.43</v>
       </c>
       <c r="AP78">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ78">
         <v>1.63</v>
@@ -17147,7 +17150,7 @@
         <v>138</v>
       </c>
       <c r="P79" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q79">
         <v>10</v>
@@ -17765,7 +17768,7 @@
         <v>141</v>
       </c>
       <c r="P82" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q82">
         <v>2.54</v>
@@ -17971,7 +17974,7 @@
         <v>142</v>
       </c>
       <c r="P83" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q83">
         <v>3.8</v>
@@ -18383,7 +18386,7 @@
         <v>108</v>
       </c>
       <c r="P85" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q85">
         <v>4.37</v>
@@ -18670,7 +18673,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ86">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR86">
         <v>1.93</v>
@@ -18795,7 +18798,7 @@
         <v>145</v>
       </c>
       <c r="P87" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q87">
         <v>2.25</v>
@@ -19001,7 +19004,7 @@
         <v>146</v>
       </c>
       <c r="P88" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q88">
         <v>3.3</v>
@@ -19207,7 +19210,7 @@
         <v>147</v>
       </c>
       <c r="P89" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q89">
         <v>1.88</v>
@@ -19413,7 +19416,7 @@
         <v>148</v>
       </c>
       <c r="P90" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q90">
         <v>5.6</v>
@@ -19619,7 +19622,7 @@
         <v>81</v>
       </c>
       <c r="P91" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q91">
         <v>5.7</v>
@@ -20031,7 +20034,7 @@
         <v>149</v>
       </c>
       <c r="P93" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q93">
         <v>1.36</v>
@@ -20237,7 +20240,7 @@
         <v>81</v>
       </c>
       <c r="P94" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q94">
         <v>3.94</v>
@@ -20443,7 +20446,7 @@
         <v>150</v>
       </c>
       <c r="P95" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q95">
         <v>2.05</v>
@@ -20649,7 +20652,7 @@
         <v>151</v>
       </c>
       <c r="P96" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q96">
         <v>3.73</v>
@@ -20727,7 +20730,7 @@
         <v>0.78</v>
       </c>
       <c r="AP96">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ96">
         <v>0.91</v>
@@ -21061,7 +21064,7 @@
         <v>81</v>
       </c>
       <c r="P98" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q98">
         <v>2.85</v>
@@ -21423,6 +21426,212 @@
         <v>0</v>
       </c>
       <c r="BP99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:68">
+      <c r="A100" s="1">
+        <v>99</v>
+      </c>
+      <c r="B100">
+        <v>7828557</v>
+      </c>
+      <c r="C100" t="s">
+        <v>68</v>
+      </c>
+      <c r="D100" t="s">
+        <v>69</v>
+      </c>
+      <c r="E100" s="2">
+        <v>45851.35416666666</v>
+      </c>
+      <c r="F100">
+        <v>0</v>
+      </c>
+      <c r="G100" t="s">
+        <v>74</v>
+      </c>
+      <c r="H100" t="s">
+        <v>77</v>
+      </c>
+      <c r="I100">
+        <v>2</v>
+      </c>
+      <c r="J100">
+        <v>0</v>
+      </c>
+      <c r="K100">
+        <v>2</v>
+      </c>
+      <c r="L100">
+        <v>3</v>
+      </c>
+      <c r="M100">
+        <v>1</v>
+      </c>
+      <c r="N100">
+        <v>4</v>
+      </c>
+      <c r="O100" t="s">
+        <v>152</v>
+      </c>
+      <c r="P100" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q100">
+        <v>3.8</v>
+      </c>
+      <c r="R100">
+        <v>2.6</v>
+      </c>
+      <c r="S100">
+        <v>2.38</v>
+      </c>
+      <c r="T100">
+        <v>1.23</v>
+      </c>
+      <c r="U100">
+        <v>3.9</v>
+      </c>
+      <c r="V100">
+        <v>2.1</v>
+      </c>
+      <c r="W100">
+        <v>1.65</v>
+      </c>
+      <c r="X100">
+        <v>4.6</v>
+      </c>
+      <c r="Y100">
+        <v>1.17</v>
+      </c>
+      <c r="Z100">
+        <v>3.1</v>
+      </c>
+      <c r="AA100">
+        <v>3.78</v>
+      </c>
+      <c r="AB100">
+        <v>1.97</v>
+      </c>
+      <c r="AC100">
+        <v>1.03</v>
+      </c>
+      <c r="AD100">
+        <v>17</v>
+      </c>
+      <c r="AE100">
+        <v>1.11</v>
+      </c>
+      <c r="AF100">
+        <v>5</v>
+      </c>
+      <c r="AG100">
+        <v>1.5</v>
+      </c>
+      <c r="AH100">
+        <v>2.45</v>
+      </c>
+      <c r="AI100">
+        <v>1.4</v>
+      </c>
+      <c r="AJ100">
+        <v>2.5</v>
+      </c>
+      <c r="AK100">
+        <v>1.77</v>
+      </c>
+      <c r="AL100">
+        <v>1.22</v>
+      </c>
+      <c r="AM100">
+        <v>1.3</v>
+      </c>
+      <c r="AN100">
+        <v>0.9</v>
+      </c>
+      <c r="AO100">
+        <v>0.8</v>
+      </c>
+      <c r="AP100">
+        <v>1.09</v>
+      </c>
+      <c r="AQ100">
+        <v>0.73</v>
+      </c>
+      <c r="AR100">
+        <v>1.58</v>
+      </c>
+      <c r="AS100">
+        <v>1.33</v>
+      </c>
+      <c r="AT100">
+        <v>2.91</v>
+      </c>
+      <c r="AU100">
+        <v>7</v>
+      </c>
+      <c r="AV100">
+        <v>4</v>
+      </c>
+      <c r="AW100">
+        <v>7</v>
+      </c>
+      <c r="AX100">
+        <v>5</v>
+      </c>
+      <c r="AY100">
+        <v>14</v>
+      </c>
+      <c r="AZ100">
+        <v>9</v>
+      </c>
+      <c r="BA100">
+        <v>1</v>
+      </c>
+      <c r="BB100">
+        <v>4</v>
+      </c>
+      <c r="BC100">
+        <v>5</v>
+      </c>
+      <c r="BD100">
+        <v>0</v>
+      </c>
+      <c r="BE100">
+        <v>0</v>
+      </c>
+      <c r="BF100">
+        <v>0</v>
+      </c>
+      <c r="BG100">
+        <v>0</v>
+      </c>
+      <c r="BH100">
+        <v>0</v>
+      </c>
+      <c r="BI100">
+        <v>0</v>
+      </c>
+      <c r="BJ100">
+        <v>0</v>
+      </c>
+      <c r="BK100">
+        <v>0</v>
+      </c>
+      <c r="BL100">
+        <v>0</v>
+      </c>
+      <c r="BM100">
+        <v>0</v>
+      </c>
+      <c r="BN100">
+        <v>0</v>
+      </c>
+      <c r="BO100">
+        <v>0</v>
+      </c>
+      <c r="BP100">
         <v>0</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
@@ -21369,16 +21369,16 @@
         <v>2</v>
       </c>
       <c r="AW99">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX99">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AY99">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ99">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BA99">
         <v>4</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
@@ -472,7 +472,7 @@
     <t>['41', '76', '48']</t>
   </si>
   <si>
-    <t>['4', '43', '69']</t>
+    <t>['4', '43', '71']</t>
   </si>
   <si>
     <t>['34', '59', '86']</t>
@@ -21476,7 +21476,7 @@
         <v>152</v>
       </c>
       <c r="P100" t="s">
-        <v>138</v>
+        <v>96</v>
       </c>
       <c r="Q100">
         <v>3.8</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="220">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -473,6 +473,9 @@
   </si>
   <si>
     <t>['4', '43', '71']</t>
+  </si>
+  <si>
+    <t>['30', '34', '87']</t>
   </si>
   <si>
     <t>['34', '59', '86']</t>
@@ -1032,7 +1035,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP100"/>
+  <dimension ref="A1:BP101"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1366,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="AQ2">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1494,7 +1497,7 @@
         <v>81</v>
       </c>
       <c r="P3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -1700,7 +1703,7 @@
         <v>82</v>
       </c>
       <c r="P4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -1906,7 +1909,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q5">
         <v>7</v>
@@ -2112,7 +2115,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2524,7 +2527,7 @@
         <v>85</v>
       </c>
       <c r="P8" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q8">
         <v>8.5</v>
@@ -2730,7 +2733,7 @@
         <v>81</v>
       </c>
       <c r="P9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -3348,7 +3351,7 @@
         <v>88</v>
       </c>
       <c r="P12" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q12">
         <v>8</v>
@@ -3760,7 +3763,7 @@
         <v>81</v>
       </c>
       <c r="P14" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q14">
         <v>5.5</v>
@@ -3966,7 +3969,7 @@
         <v>90</v>
       </c>
       <c r="P15" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q15">
         <v>2.5</v>
@@ -4047,7 +4050,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ15">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR15">
         <v>1.37</v>
@@ -4172,7 +4175,7 @@
         <v>91</v>
       </c>
       <c r="P16" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q16">
         <v>2.1</v>
@@ -4378,7 +4381,7 @@
         <v>81</v>
       </c>
       <c r="P17" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q17">
         <v>2.38</v>
@@ -4584,7 +4587,7 @@
         <v>81</v>
       </c>
       <c r="P18" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q18">
         <v>3.4</v>
@@ -5202,7 +5205,7 @@
         <v>94</v>
       </c>
       <c r="P21" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q21">
         <v>1.91</v>
@@ -5280,7 +5283,7 @@
         <v>1.5</v>
       </c>
       <c r="AP21">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="AQ21">
         <v>1.73</v>
@@ -5614,7 +5617,7 @@
         <v>96</v>
       </c>
       <c r="P23" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -5820,7 +5823,7 @@
         <v>81</v>
       </c>
       <c r="P24" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q24">
         <v>5.5</v>
@@ -6026,7 +6029,7 @@
         <v>97</v>
       </c>
       <c r="P25" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q25">
         <v>2.38</v>
@@ -6107,7 +6110,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ25">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR25">
         <v>0.71</v>
@@ -6232,7 +6235,7 @@
         <v>98</v>
       </c>
       <c r="P26" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q26">
         <v>3.1</v>
@@ -6644,7 +6647,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q28">
         <v>1.3</v>
@@ -6722,7 +6725,7 @@
         <v>1</v>
       </c>
       <c r="AP28">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="AQ28">
         <v>0.5</v>
@@ -6850,7 +6853,7 @@
         <v>101</v>
       </c>
       <c r="P29" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q29">
         <v>5</v>
@@ -7137,7 +7140,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ30">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR30">
         <v>2.7</v>
@@ -7468,7 +7471,7 @@
         <v>81</v>
       </c>
       <c r="P32" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q32">
         <v>6</v>
@@ -7674,7 +7677,7 @@
         <v>104</v>
       </c>
       <c r="P33" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q33">
         <v>8.449999999999999</v>
@@ -7958,7 +7961,7 @@
         <v>3</v>
       </c>
       <c r="AP34">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="AQ34">
         <v>2.44</v>
@@ -8086,7 +8089,7 @@
         <v>105</v>
       </c>
       <c r="P35" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q35">
         <v>2.2</v>
@@ -8292,7 +8295,7 @@
         <v>106</v>
       </c>
       <c r="P36" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q36">
         <v>4.25</v>
@@ -8910,7 +8913,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q39">
         <v>3.2</v>
@@ -9116,7 +9119,7 @@
         <v>81</v>
       </c>
       <c r="P40" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q40">
         <v>12</v>
@@ -9322,7 +9325,7 @@
         <v>110</v>
       </c>
       <c r="P41" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q41">
         <v>3.77</v>
@@ -9734,7 +9737,7 @@
         <v>112</v>
       </c>
       <c r="P43" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q43">
         <v>1.35</v>
@@ -9940,7 +9943,7 @@
         <v>113</v>
       </c>
       <c r="P44" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q44">
         <v>1.66</v>
@@ -10021,7 +10024,7 @@
         <v>2</v>
       </c>
       <c r="AQ44">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR44">
         <v>1.77</v>
@@ -10146,7 +10149,7 @@
         <v>114</v>
       </c>
       <c r="P45" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q45">
         <v>4.75</v>
@@ -10352,7 +10355,7 @@
         <v>115</v>
       </c>
       <c r="P46" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q46">
         <v>5.2</v>
@@ -10558,7 +10561,7 @@
         <v>81</v>
       </c>
       <c r="P47" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q47">
         <v>2.35</v>
@@ -11048,7 +11051,7 @@
         <v>1</v>
       </c>
       <c r="AP49">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="AQ49">
         <v>0.91</v>
@@ -11176,7 +11179,7 @@
         <v>117</v>
       </c>
       <c r="P50" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q50">
         <v>2.62</v>
@@ -11382,7 +11385,7 @@
         <v>118</v>
       </c>
       <c r="P51" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q51">
         <v>4.55</v>
@@ -11588,7 +11591,7 @@
         <v>81</v>
       </c>
       <c r="P52" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q52">
         <v>6.5</v>
@@ -11794,7 +11797,7 @@
         <v>119</v>
       </c>
       <c r="P53" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q53">
         <v>3.35</v>
@@ -11875,7 +11878,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ53">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR53">
         <v>1.56</v>
@@ -12412,7 +12415,7 @@
         <v>122</v>
       </c>
       <c r="P56" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q56">
         <v>1.56</v>
@@ -12618,7 +12621,7 @@
         <v>81</v>
       </c>
       <c r="P57" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q57">
         <v>5.25</v>
@@ -13030,7 +13033,7 @@
         <v>81</v>
       </c>
       <c r="P59" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -13236,7 +13239,7 @@
         <v>124</v>
       </c>
       <c r="P60" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q60">
         <v>2.25</v>
@@ -13314,7 +13317,7 @@
         <v>1.2</v>
       </c>
       <c r="AP60">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="AQ60">
         <v>1.8</v>
@@ -13442,7 +13445,7 @@
         <v>125</v>
       </c>
       <c r="P61" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q61">
         <v>2.27</v>
@@ -13648,7 +13651,7 @@
         <v>126</v>
       </c>
       <c r="P62" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q62">
         <v>2.4</v>
@@ -13854,7 +13857,7 @@
         <v>127</v>
       </c>
       <c r="P63" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q63">
         <v>1.64</v>
@@ -13935,7 +13938,7 @@
         <v>2</v>
       </c>
       <c r="AQ63">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR63">
         <v>2.27</v>
@@ -14472,7 +14475,7 @@
         <v>130</v>
       </c>
       <c r="P66" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q66">
         <v>4.35</v>
@@ -14884,7 +14887,7 @@
         <v>132</v>
       </c>
       <c r="P68" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q68">
         <v>9</v>
@@ -15090,7 +15093,7 @@
         <v>133</v>
       </c>
       <c r="P69" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q69">
         <v>1.91</v>
@@ -15171,7 +15174,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ69">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR69">
         <v>1.66</v>
@@ -15296,7 +15299,7 @@
         <v>81</v>
       </c>
       <c r="P70" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q70">
         <v>2.35</v>
@@ -15502,7 +15505,7 @@
         <v>134</v>
       </c>
       <c r="P71" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q71">
         <v>1.55</v>
@@ -15580,7 +15583,7 @@
         <v>1.5</v>
       </c>
       <c r="AP71">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="AQ71">
         <v>1.63</v>
@@ -15708,7 +15711,7 @@
         <v>135</v>
       </c>
       <c r="P72" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q72">
         <v>1.46</v>
@@ -15914,7 +15917,7 @@
         <v>81</v>
       </c>
       <c r="P73" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q73">
         <v>8.5</v>
@@ -16120,7 +16123,7 @@
         <v>81</v>
       </c>
       <c r="P74" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q74">
         <v>2.2</v>
@@ -16326,7 +16329,7 @@
         <v>136</v>
       </c>
       <c r="P75" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q75">
         <v>2.3</v>
@@ -16532,7 +16535,7 @@
         <v>81</v>
       </c>
       <c r="P76" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q76">
         <v>8.949999999999999</v>
@@ -16738,7 +16741,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q77">
         <v>2.94</v>
@@ -16819,7 +16822,7 @@
         <v>1</v>
       </c>
       <c r="AQ77">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR77">
         <v>1.36</v>
@@ -16944,7 +16947,7 @@
         <v>81</v>
       </c>
       <c r="P78" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q78">
         <v>4.83</v>
@@ -17150,7 +17153,7 @@
         <v>138</v>
       </c>
       <c r="P79" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q79">
         <v>10</v>
@@ -17768,7 +17771,7 @@
         <v>141</v>
       </c>
       <c r="P82" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q82">
         <v>2.54</v>
@@ -17974,7 +17977,7 @@
         <v>142</v>
       </c>
       <c r="P83" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q83">
         <v>3.8</v>
@@ -18258,7 +18261,7 @@
         <v>0.14</v>
       </c>
       <c r="AP84">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="AQ84">
         <v>0.11</v>
@@ -18386,7 +18389,7 @@
         <v>108</v>
       </c>
       <c r="P85" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q85">
         <v>4.37</v>
@@ -18673,7 +18676,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ86">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR86">
         <v>1.93</v>
@@ -18798,7 +18801,7 @@
         <v>145</v>
       </c>
       <c r="P87" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q87">
         <v>2.25</v>
@@ -18876,7 +18879,7 @@
         <v>2.25</v>
       </c>
       <c r="AP87">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="AQ87">
         <v>1.73</v>
@@ -19004,7 +19007,7 @@
         <v>146</v>
       </c>
       <c r="P88" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q88">
         <v>3.3</v>
@@ -19210,7 +19213,7 @@
         <v>147</v>
       </c>
       <c r="P89" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q89">
         <v>1.88</v>
@@ -19288,7 +19291,7 @@
         <v>2</v>
       </c>
       <c r="AP89">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="AQ89">
         <v>1.7</v>
@@ -19416,7 +19419,7 @@
         <v>148</v>
       </c>
       <c r="P90" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q90">
         <v>5.6</v>
@@ -19622,7 +19625,7 @@
         <v>81</v>
       </c>
       <c r="P91" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q91">
         <v>5.7</v>
@@ -20034,7 +20037,7 @@
         <v>149</v>
       </c>
       <c r="P93" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q93">
         <v>1.36</v>
@@ -20240,7 +20243,7 @@
         <v>81</v>
       </c>
       <c r="P94" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q94">
         <v>3.94</v>
@@ -20446,7 +20449,7 @@
         <v>150</v>
       </c>
       <c r="P95" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q95">
         <v>2.05</v>
@@ -20652,7 +20655,7 @@
         <v>151</v>
       </c>
       <c r="P96" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q96">
         <v>3.73</v>
@@ -21064,7 +21067,7 @@
         <v>81</v>
       </c>
       <c r="P98" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q98">
         <v>2.85</v>
@@ -21557,7 +21560,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ100">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR100">
         <v>1.58</v>
@@ -21632,6 +21635,212 @@
         <v>0</v>
       </c>
       <c r="BP100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:68">
+      <c r="A101" s="1">
+        <v>100</v>
+      </c>
+      <c r="B101">
+        <v>7828633</v>
+      </c>
+      <c r="C101" t="s">
+        <v>68</v>
+      </c>
+      <c r="D101" t="s">
+        <v>69</v>
+      </c>
+      <c r="E101" s="2">
+        <v>45857.54166666666</v>
+      </c>
+      <c r="F101">
+        <v>0</v>
+      </c>
+      <c r="G101" t="s">
+        <v>70</v>
+      </c>
+      <c r="H101" t="s">
+        <v>77</v>
+      </c>
+      <c r="I101">
+        <v>2</v>
+      </c>
+      <c r="J101">
+        <v>0</v>
+      </c>
+      <c r="K101">
+        <v>2</v>
+      </c>
+      <c r="L101">
+        <v>3</v>
+      </c>
+      <c r="M101">
+        <v>0</v>
+      </c>
+      <c r="N101">
+        <v>3</v>
+      </c>
+      <c r="O101" t="s">
+        <v>153</v>
+      </c>
+      <c r="P101" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q101">
+        <v>1.5</v>
+      </c>
+      <c r="R101">
+        <v>3</v>
+      </c>
+      <c r="S101">
+        <v>7.5</v>
+      </c>
+      <c r="T101">
+        <v>1.2</v>
+      </c>
+      <c r="U101">
+        <v>4.33</v>
+      </c>
+      <c r="V101">
+        <v>1.9</v>
+      </c>
+      <c r="W101">
+        <v>1.79</v>
+      </c>
+      <c r="X101">
+        <v>3.6</v>
+      </c>
+      <c r="Y101">
+        <v>1.2</v>
+      </c>
+      <c r="Z101">
+        <v>1.22</v>
+      </c>
+      <c r="AA101">
+        <v>6.4</v>
+      </c>
+      <c r="AB101">
+        <v>6.9</v>
+      </c>
+      <c r="AC101">
+        <v>1.01</v>
+      </c>
+      <c r="AD101">
+        <v>23</v>
+      </c>
+      <c r="AE101">
+        <v>1.11</v>
+      </c>
+      <c r="AF101">
+        <v>6</v>
+      </c>
+      <c r="AG101">
+        <v>1.32</v>
+      </c>
+      <c r="AH101">
+        <v>3.1</v>
+      </c>
+      <c r="AI101">
+        <v>2</v>
+      </c>
+      <c r="AJ101">
+        <v>1.87</v>
+      </c>
+      <c r="AK101">
+        <v>1.04</v>
+      </c>
+      <c r="AL101">
+        <v>0</v>
+      </c>
+      <c r="AM101">
+        <v>4.33</v>
+      </c>
+      <c r="AN101">
+        <v>2.6</v>
+      </c>
+      <c r="AO101">
+        <v>0.73</v>
+      </c>
+      <c r="AP101">
+        <v>2.64</v>
+      </c>
+      <c r="AQ101">
+        <v>0.67</v>
+      </c>
+      <c r="AR101">
+        <v>2.42</v>
+      </c>
+      <c r="AS101">
+        <v>1.33</v>
+      </c>
+      <c r="AT101">
+        <v>3.75</v>
+      </c>
+      <c r="AU101">
+        <v>8</v>
+      </c>
+      <c r="AV101">
+        <v>3</v>
+      </c>
+      <c r="AW101">
+        <v>22</v>
+      </c>
+      <c r="AX101">
+        <v>3</v>
+      </c>
+      <c r="AY101">
+        <v>30</v>
+      </c>
+      <c r="AZ101">
+        <v>6</v>
+      </c>
+      <c r="BA101">
+        <v>6</v>
+      </c>
+      <c r="BB101">
+        <v>2</v>
+      </c>
+      <c r="BC101">
+        <v>8</v>
+      </c>
+      <c r="BD101">
+        <v>0</v>
+      </c>
+      <c r="BE101">
+        <v>0</v>
+      </c>
+      <c r="BF101">
+        <v>0</v>
+      </c>
+      <c r="BG101">
+        <v>0</v>
+      </c>
+      <c r="BH101">
+        <v>0</v>
+      </c>
+      <c r="BI101">
+        <v>0</v>
+      </c>
+      <c r="BJ101">
+        <v>0</v>
+      </c>
+      <c r="BK101">
+        <v>0</v>
+      </c>
+      <c r="BL101">
+        <v>0</v>
+      </c>
+      <c r="BM101">
+        <v>0</v>
+      </c>
+      <c r="BN101">
+        <v>0</v>
+      </c>
+      <c r="BO101">
+        <v>0</v>
+      </c>
+      <c r="BP101">
         <v>0</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="225">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -478,6 +478,15 @@
     <t>['30', '34', '87']</t>
   </si>
   <si>
+    <t>['45', '7', '24', '60', '72', '88']</t>
+  </si>
+  <si>
+    <t>['58', '80']</t>
+  </si>
+  <si>
+    <t>['27', '90+6']</t>
+  </si>
+  <si>
     <t>['34', '59', '86']</t>
   </si>
   <si>
@@ -674,6 +683,12 @@
   </si>
   <si>
     <t>['4', '49']</t>
+  </si>
+  <si>
+    <t>['23', '16']</t>
+  </si>
+  <si>
+    <t>['77', '85']</t>
   </si>
 </sst>
 </file>
@@ -1035,7 +1050,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP101"/>
+  <dimension ref="A1:BP105"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1497,7 +1512,7 @@
         <v>81</v>
       </c>
       <c r="P3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -1703,7 +1718,7 @@
         <v>82</v>
       </c>
       <c r="P4" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -1784,7 +1799,7 @@
         <v>2</v>
       </c>
       <c r="AQ4">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1909,7 +1924,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="Q5">
         <v>7</v>
@@ -1987,7 +2002,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ5">
         <v>1.8</v>
@@ -2115,7 +2130,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2402,7 +2417,7 @@
         <v>2</v>
       </c>
       <c r="AQ7">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR7">
         <v>1.43</v>
@@ -2527,7 +2542,7 @@
         <v>85</v>
       </c>
       <c r="P8" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="Q8">
         <v>8.5</v>
@@ -2605,7 +2620,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ8">
         <v>2.1</v>
@@ -2733,7 +2748,7 @@
         <v>81</v>
       </c>
       <c r="P9" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -3020,7 +3035,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ10">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3223,7 +3238,7 @@
         <v>3</v>
       </c>
       <c r="AP11">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ11">
         <v>1.73</v>
@@ -3351,7 +3366,7 @@
         <v>88</v>
       </c>
       <c r="P12" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="Q12">
         <v>8</v>
@@ -3763,7 +3778,7 @@
         <v>81</v>
       </c>
       <c r="P14" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="Q14">
         <v>5.5</v>
@@ -3844,7 +3859,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ14">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AR14">
         <v>1.42</v>
@@ -3969,7 +3984,7 @@
         <v>90</v>
       </c>
       <c r="P15" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="Q15">
         <v>2.5</v>
@@ -4047,7 +4062,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ15">
         <v>0.67</v>
@@ -4175,7 +4190,7 @@
         <v>91</v>
       </c>
       <c r="P16" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="Q16">
         <v>2.1</v>
@@ -4253,7 +4268,7 @@
         <v>3</v>
       </c>
       <c r="AP16">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ16">
         <v>0.91</v>
@@ -4381,7 +4396,7 @@
         <v>81</v>
       </c>
       <c r="P17" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="Q17">
         <v>2.38</v>
@@ -4459,10 +4474,10 @@
         <v>3</v>
       </c>
       <c r="AP17">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ17">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR17">
         <v>1.11</v>
@@ -4587,7 +4602,7 @@
         <v>81</v>
       </c>
       <c r="P18" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="Q18">
         <v>3.4</v>
@@ -4668,7 +4683,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ18">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR18">
         <v>1.67</v>
@@ -5077,10 +5092,10 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ20">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AR20">
         <v>2.45</v>
@@ -5205,7 +5220,7 @@
         <v>94</v>
       </c>
       <c r="P21" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="Q21">
         <v>1.91</v>
@@ -5489,7 +5504,7 @@
         <v>2</v>
       </c>
       <c r="AP22">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ22">
         <v>0.91</v>
@@ -5617,7 +5632,7 @@
         <v>96</v>
       </c>
       <c r="P23" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -5695,10 +5710,10 @@
         <v>3</v>
       </c>
       <c r="AP23">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ23">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AR23">
         <v>3.56</v>
@@ -5823,7 +5838,7 @@
         <v>81</v>
       </c>
       <c r="P24" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="Q24">
         <v>5.5</v>
@@ -6029,7 +6044,7 @@
         <v>97</v>
       </c>
       <c r="P25" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="Q25">
         <v>2.38</v>
@@ -6235,7 +6250,7 @@
         <v>98</v>
       </c>
       <c r="P26" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="Q26">
         <v>3.1</v>
@@ -6522,7 +6537,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ27">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AR27">
         <v>1.38</v>
@@ -6647,7 +6662,7 @@
         <v>100</v>
       </c>
       <c r="P28" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="Q28">
         <v>1.3</v>
@@ -6853,7 +6868,7 @@
         <v>101</v>
       </c>
       <c r="P29" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="Q29">
         <v>5</v>
@@ -6931,10 +6946,10 @@
         <v>3</v>
       </c>
       <c r="AP29">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ29">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AR29">
         <v>1.01</v>
@@ -7137,7 +7152,7 @@
         <v>1.33</v>
       </c>
       <c r="AP30">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ30">
         <v>0.67</v>
@@ -7343,10 +7358,10 @@
         <v>3</v>
       </c>
       <c r="AP31">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ31">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR31">
         <v>2.69</v>
@@ -7471,7 +7486,7 @@
         <v>81</v>
       </c>
       <c r="P32" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="Q32">
         <v>6</v>
@@ -7549,7 +7564,7 @@
         <v>1</v>
       </c>
       <c r="AP32">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ32">
         <v>1.73</v>
@@ -7677,7 +7692,7 @@
         <v>104</v>
       </c>
       <c r="P33" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="Q33">
         <v>8.449999999999999</v>
@@ -7964,7 +7979,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ34">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AR34">
         <v>2.81</v>
@@ -8089,7 +8104,7 @@
         <v>105</v>
       </c>
       <c r="P35" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="Q35">
         <v>2.2</v>
@@ -8170,7 +8185,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ35">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AR35">
         <v>0.88</v>
@@ -8295,7 +8310,7 @@
         <v>106</v>
       </c>
       <c r="P36" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="Q36">
         <v>4.25</v>
@@ -8373,10 +8388,10 @@
         <v>2</v>
       </c>
       <c r="AP36">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ36">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR36">
         <v>0.99</v>
@@ -8785,10 +8800,10 @@
         <v>2</v>
       </c>
       <c r="AP38">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ38">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR38">
         <v>1.47</v>
@@ -8913,7 +8928,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Q39">
         <v>3.2</v>
@@ -9119,7 +9134,7 @@
         <v>81</v>
       </c>
       <c r="P40" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="Q40">
         <v>12</v>
@@ -9325,7 +9340,7 @@
         <v>110</v>
       </c>
       <c r="P41" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="Q41">
         <v>3.77</v>
@@ -9609,7 +9624,7 @@
         <v>0.75</v>
       </c>
       <c r="AP42">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ42">
         <v>0.5</v>
@@ -9737,7 +9752,7 @@
         <v>112</v>
       </c>
       <c r="P43" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="Q43">
         <v>1.35</v>
@@ -9815,10 +9830,10 @@
         <v>0.25</v>
       </c>
       <c r="AP43">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ43">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AR43">
         <v>2.31</v>
@@ -9943,7 +9958,7 @@
         <v>113</v>
       </c>
       <c r="P44" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="Q44">
         <v>1.66</v>
@@ -10149,7 +10164,7 @@
         <v>114</v>
       </c>
       <c r="P45" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Q45">
         <v>4.75</v>
@@ -10230,7 +10245,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ45">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR45">
         <v>1.06</v>
@@ -10355,7 +10370,7 @@
         <v>115</v>
       </c>
       <c r="P46" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="Q46">
         <v>5.2</v>
@@ -10433,7 +10448,7 @@
         <v>3</v>
       </c>
       <c r="AP46">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ46">
         <v>2.1</v>
@@ -10561,7 +10576,7 @@
         <v>81</v>
       </c>
       <c r="P47" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="Q47">
         <v>2.35</v>
@@ -10642,7 +10657,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ47">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR47">
         <v>1.51</v>
@@ -11179,7 +11194,7 @@
         <v>117</v>
       </c>
       <c r="P50" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Q50">
         <v>2.62</v>
@@ -11385,7 +11400,7 @@
         <v>118</v>
       </c>
       <c r="P51" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="Q51">
         <v>4.55</v>
@@ -11463,10 +11478,10 @@
         <v>2.5</v>
       </c>
       <c r="AP51">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ51">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR51">
         <v>1.64</v>
@@ -11591,7 +11606,7 @@
         <v>81</v>
       </c>
       <c r="P52" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q52">
         <v>6.5</v>
@@ -11672,7 +11687,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ52">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AR52">
         <v>1.16</v>
@@ -11797,7 +11812,7 @@
         <v>119</v>
       </c>
       <c r="P53" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q53">
         <v>3.35</v>
@@ -12287,7 +12302,7 @@
         <v>2.4</v>
       </c>
       <c r="AP55">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ55">
         <v>2.1</v>
@@ -12415,7 +12430,7 @@
         <v>122</v>
       </c>
       <c r="P56" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Q56">
         <v>1.56</v>
@@ -12493,7 +12508,7 @@
         <v>0.6</v>
       </c>
       <c r="AP56">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ56">
         <v>0.5</v>
@@ -12621,7 +12636,7 @@
         <v>81</v>
       </c>
       <c r="P57" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q57">
         <v>5.25</v>
@@ -12702,7 +12717,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ57">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AR57">
         <v>1.43</v>
@@ -12905,10 +12920,10 @@
         <v>0.2</v>
       </c>
       <c r="AP58">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ58">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AR58">
         <v>1.57</v>
@@ -13033,7 +13048,7 @@
         <v>81</v>
       </c>
       <c r="P59" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -13111,7 +13126,7 @@
         <v>2</v>
       </c>
       <c r="AP59">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ59">
         <v>1.73</v>
@@ -13239,7 +13254,7 @@
         <v>124</v>
       </c>
       <c r="P60" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q60">
         <v>2.25</v>
@@ -13445,7 +13460,7 @@
         <v>125</v>
       </c>
       <c r="P61" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q61">
         <v>2.27</v>
@@ -13526,7 +13541,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ61">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR61">
         <v>1.64</v>
@@ -13651,7 +13666,7 @@
         <v>126</v>
       </c>
       <c r="P62" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q62">
         <v>2.4</v>
@@ -13857,7 +13872,7 @@
         <v>127</v>
       </c>
       <c r="P63" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q63">
         <v>1.64</v>
@@ -13935,7 +13950,7 @@
         <v>1.17</v>
       </c>
       <c r="AP63">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ63">
         <v>0.67</v>
@@ -14347,7 +14362,7 @@
         <v>0.67</v>
       </c>
       <c r="AP65">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ65">
         <v>0.5</v>
@@ -14475,7 +14490,7 @@
         <v>130</v>
       </c>
       <c r="P66" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q66">
         <v>4.35</v>
@@ -14556,7 +14571,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ66">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR66">
         <v>1.52</v>
@@ -14759,10 +14774,10 @@
         <v>0.17</v>
       </c>
       <c r="AP67">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ67">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AR67">
         <v>1.07</v>
@@ -14887,7 +14902,7 @@
         <v>132</v>
       </c>
       <c r="P68" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q68">
         <v>9</v>
@@ -14965,10 +14980,10 @@
         <v>2.67</v>
       </c>
       <c r="AP68">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ68">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AR68">
         <v>1.52</v>
@@ -15093,7 +15108,7 @@
         <v>133</v>
       </c>
       <c r="P69" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Q69">
         <v>1.91</v>
@@ -15299,7 +15314,7 @@
         <v>81</v>
       </c>
       <c r="P70" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q70">
         <v>2.35</v>
@@ -15377,7 +15392,7 @@
         <v>1</v>
       </c>
       <c r="AP70">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ70">
         <v>1.8</v>
@@ -15505,7 +15520,7 @@
         <v>134</v>
       </c>
       <c r="P71" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q71">
         <v>1.55</v>
@@ -15586,7 +15601,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ71">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR71">
         <v>2.37</v>
@@ -15711,7 +15726,7 @@
         <v>135</v>
       </c>
       <c r="P72" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q72">
         <v>1.46</v>
@@ -15917,7 +15932,7 @@
         <v>81</v>
       </c>
       <c r="P73" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q73">
         <v>8.5</v>
@@ -16123,7 +16138,7 @@
         <v>81</v>
       </c>
       <c r="P74" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q74">
         <v>2.2</v>
@@ -16201,10 +16216,10 @@
         <v>2.17</v>
       </c>
       <c r="AP74">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ74">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR74">
         <v>2.22</v>
@@ -16329,7 +16344,7 @@
         <v>136</v>
       </c>
       <c r="P75" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q75">
         <v>2.3</v>
@@ -16535,7 +16550,7 @@
         <v>81</v>
       </c>
       <c r="P76" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q76">
         <v>8.949999999999999</v>
@@ -16741,7 +16756,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q77">
         <v>2.94</v>
@@ -16819,7 +16834,7 @@
         <v>1</v>
       </c>
       <c r="AP77">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ77">
         <v>0.67</v>
@@ -16947,7 +16962,7 @@
         <v>81</v>
       </c>
       <c r="P78" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q78">
         <v>4.83</v>
@@ -17028,7 +17043,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ78">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR78">
         <v>1.49</v>
@@ -17153,7 +17168,7 @@
         <v>138</v>
       </c>
       <c r="P79" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q79">
         <v>10</v>
@@ -17231,7 +17246,7 @@
         <v>1.88</v>
       </c>
       <c r="AP79">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ79">
         <v>2.1</v>
@@ -17643,10 +17658,10 @@
         <v>2.29</v>
       </c>
       <c r="AP81">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ81">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR81">
         <v>1.99</v>
@@ -17771,7 +17786,7 @@
         <v>141</v>
       </c>
       <c r="P82" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q82">
         <v>2.54</v>
@@ -17849,7 +17864,7 @@
         <v>0.5</v>
       </c>
       <c r="AP82">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ82">
         <v>0.91</v>
@@ -17977,7 +17992,7 @@
         <v>142</v>
       </c>
       <c r="P83" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q83">
         <v>3.8</v>
@@ -18058,7 +18073,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ83">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AR83">
         <v>1.83</v>
@@ -18264,7 +18279,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ84">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AR84">
         <v>2.37</v>
@@ -18389,7 +18404,7 @@
         <v>108</v>
       </c>
       <c r="P85" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q85">
         <v>4.37</v>
@@ -18673,7 +18688,7 @@
         <v>0.89</v>
       </c>
       <c r="AP86">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ86">
         <v>0.67</v>
@@ -18801,7 +18816,7 @@
         <v>145</v>
       </c>
       <c r="P87" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q87">
         <v>2.25</v>
@@ -19007,7 +19022,7 @@
         <v>146</v>
       </c>
       <c r="P88" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q88">
         <v>3.3</v>
@@ -19085,10 +19100,10 @@
         <v>2.75</v>
       </c>
       <c r="AP88">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ88">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AR88">
         <v>2.07</v>
@@ -19213,7 +19228,7 @@
         <v>147</v>
       </c>
       <c r="P89" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q89">
         <v>1.88</v>
@@ -19294,7 +19309,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ89">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR89">
         <v>2.46</v>
@@ -19419,7 +19434,7 @@
         <v>148</v>
       </c>
       <c r="P90" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q90">
         <v>5.6</v>
@@ -19625,7 +19640,7 @@
         <v>81</v>
       </c>
       <c r="P91" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q91">
         <v>5.7</v>
@@ -19703,7 +19718,7 @@
         <v>1.67</v>
       </c>
       <c r="AP91">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ91">
         <v>1.8</v>
@@ -20037,7 +20052,7 @@
         <v>149</v>
       </c>
       <c r="P93" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q93">
         <v>1.36</v>
@@ -20118,7 +20133,7 @@
         <v>2</v>
       </c>
       <c r="AQ93">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AR93">
         <v>1.77</v>
@@ -20243,7 +20258,7 @@
         <v>81</v>
       </c>
       <c r="P94" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q94">
         <v>3.94</v>
@@ -20321,7 +20336,7 @@
         <v>2</v>
       </c>
       <c r="AP94">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ94">
         <v>2.1</v>
@@ -20449,7 +20464,7 @@
         <v>150</v>
       </c>
       <c r="P95" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q95">
         <v>2.05</v>
@@ -20655,7 +20670,7 @@
         <v>151</v>
       </c>
       <c r="P96" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q96">
         <v>3.73</v>
@@ -21067,7 +21082,7 @@
         <v>81</v>
       </c>
       <c r="P98" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q98">
         <v>2.85</v>
@@ -21145,7 +21160,7 @@
         <v>0.7</v>
       </c>
       <c r="AP98">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ98">
         <v>0.91</v>
@@ -21354,7 +21369,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ99">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR99">
         <v>1.39</v>
@@ -21841,6 +21856,830 @@
         <v>0</v>
       </c>
       <c r="BP101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:68">
+      <c r="A102" s="1">
+        <v>101</v>
+      </c>
+      <c r="B102">
+        <v>7828560</v>
+      </c>
+      <c r="C102" t="s">
+        <v>68</v>
+      </c>
+      <c r="D102" t="s">
+        <v>69</v>
+      </c>
+      <c r="E102" s="2">
+        <v>45858.45833333334</v>
+      </c>
+      <c r="F102">
+        <v>0</v>
+      </c>
+      <c r="G102" t="s">
+        <v>75</v>
+      </c>
+      <c r="H102" t="s">
+        <v>72</v>
+      </c>
+      <c r="I102">
+        <v>1</v>
+      </c>
+      <c r="J102">
+        <v>2</v>
+      </c>
+      <c r="K102">
+        <v>3</v>
+      </c>
+      <c r="L102">
+        <v>1</v>
+      </c>
+      <c r="M102">
+        <v>2</v>
+      </c>
+      <c r="N102">
+        <v>3</v>
+      </c>
+      <c r="O102" t="s">
+        <v>107</v>
+      </c>
+      <c r="P102" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q102">
+        <v>6.05</v>
+      </c>
+      <c r="R102">
+        <v>2.74</v>
+      </c>
+      <c r="S102">
+        <v>1.81</v>
+      </c>
+      <c r="T102">
+        <v>1.2</v>
+      </c>
+      <c r="U102">
+        <v>3.75</v>
+      </c>
+      <c r="V102">
+        <v>2.1</v>
+      </c>
+      <c r="W102">
+        <v>1.68</v>
+      </c>
+      <c r="X102">
+        <v>4.6</v>
+      </c>
+      <c r="Y102">
+        <v>1.18</v>
+      </c>
+      <c r="Z102">
+        <v>7</v>
+      </c>
+      <c r="AA102">
+        <v>5.7</v>
+      </c>
+      <c r="AB102">
+        <v>1.25</v>
+      </c>
+      <c r="AC102">
+        <v>1.02</v>
+      </c>
+      <c r="AD102">
+        <v>16.5</v>
+      </c>
+      <c r="AE102">
+        <v>1.08</v>
+      </c>
+      <c r="AF102">
+        <v>5.65</v>
+      </c>
+      <c r="AG102">
+        <v>1.4</v>
+      </c>
+      <c r="AH102">
+        <v>2.75</v>
+      </c>
+      <c r="AI102">
+        <v>1.62</v>
+      </c>
+      <c r="AJ102">
+        <v>2.18</v>
+      </c>
+      <c r="AK102">
+        <v>1.16</v>
+      </c>
+      <c r="AL102">
+        <v>1.08</v>
+      </c>
+      <c r="AM102">
+        <v>1.11</v>
+      </c>
+      <c r="AN102">
+        <v>1</v>
+      </c>
+      <c r="AO102">
+        <v>2.44</v>
+      </c>
+      <c r="AP102">
+        <v>0.9</v>
+      </c>
+      <c r="AQ102">
+        <v>2.5</v>
+      </c>
+      <c r="AR102">
+        <v>1.47</v>
+      </c>
+      <c r="AS102">
+        <v>2.05</v>
+      </c>
+      <c r="AT102">
+        <v>3.52</v>
+      </c>
+      <c r="AU102">
+        <v>4</v>
+      </c>
+      <c r="AV102">
+        <v>5</v>
+      </c>
+      <c r="AW102">
+        <v>11</v>
+      </c>
+      <c r="AX102">
+        <v>9</v>
+      </c>
+      <c r="AY102">
+        <v>15</v>
+      </c>
+      <c r="AZ102">
+        <v>14</v>
+      </c>
+      <c r="BA102">
+        <v>6</v>
+      </c>
+      <c r="BB102">
+        <v>4</v>
+      </c>
+      <c r="BC102">
+        <v>10</v>
+      </c>
+      <c r="BD102">
+        <v>0</v>
+      </c>
+      <c r="BE102">
+        <v>0</v>
+      </c>
+      <c r="BF102">
+        <v>0</v>
+      </c>
+      <c r="BG102">
+        <v>0</v>
+      </c>
+      <c r="BH102">
+        <v>0</v>
+      </c>
+      <c r="BI102">
+        <v>0</v>
+      </c>
+      <c r="BJ102">
+        <v>0</v>
+      </c>
+      <c r="BK102">
+        <v>0</v>
+      </c>
+      <c r="BL102">
+        <v>0</v>
+      </c>
+      <c r="BM102">
+        <v>0</v>
+      </c>
+      <c r="BN102">
+        <v>0</v>
+      </c>
+      <c r="BO102">
+        <v>0</v>
+      </c>
+      <c r="BP102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:68">
+      <c r="A103" s="1">
+        <v>102</v>
+      </c>
+      <c r="B103">
+        <v>7828559</v>
+      </c>
+      <c r="C103" t="s">
+        <v>68</v>
+      </c>
+      <c r="D103" t="s">
+        <v>69</v>
+      </c>
+      <c r="E103" s="2">
+        <v>45858.45833333334</v>
+      </c>
+      <c r="F103">
+        <v>0</v>
+      </c>
+      <c r="G103" t="s">
+        <v>79</v>
+      </c>
+      <c r="H103" t="s">
+        <v>74</v>
+      </c>
+      <c r="I103">
+        <v>3</v>
+      </c>
+      <c r="J103">
+        <v>0</v>
+      </c>
+      <c r="K103">
+        <v>3</v>
+      </c>
+      <c r="L103">
+        <v>6</v>
+      </c>
+      <c r="M103">
+        <v>2</v>
+      </c>
+      <c r="N103">
+        <v>8</v>
+      </c>
+      <c r="O103" t="s">
+        <v>154</v>
+      </c>
+      <c r="P103" t="s">
+        <v>224</v>
+      </c>
+      <c r="Q103">
+        <v>1.8</v>
+      </c>
+      <c r="R103">
+        <v>2.62</v>
+      </c>
+      <c r="S103">
+        <v>7.5</v>
+      </c>
+      <c r="T103">
+        <v>1.2</v>
+      </c>
+      <c r="U103">
+        <v>4</v>
+      </c>
+      <c r="V103">
+        <v>1.7</v>
+      </c>
+      <c r="W103">
+        <v>2</v>
+      </c>
+      <c r="X103">
+        <v>3.3</v>
+      </c>
+      <c r="Y103">
+        <v>1.27</v>
+      </c>
+      <c r="Z103">
+        <v>1.16</v>
+      </c>
+      <c r="AA103">
+        <v>6.7</v>
+      </c>
+      <c r="AB103">
+        <v>9.5</v>
+      </c>
+      <c r="AC103">
+        <v>1.02</v>
+      </c>
+      <c r="AD103">
+        <v>21</v>
+      </c>
+      <c r="AE103">
+        <v>1.06</v>
+      </c>
+      <c r="AF103">
+        <v>5.75</v>
+      </c>
+      <c r="AG103">
+        <v>1.29</v>
+      </c>
+      <c r="AH103">
+        <v>3.5</v>
+      </c>
+      <c r="AI103">
+        <v>1.57</v>
+      </c>
+      <c r="AJ103">
+        <v>2.1</v>
+      </c>
+      <c r="AK103">
+        <v>1.08</v>
+      </c>
+      <c r="AL103">
+        <v>1.07</v>
+      </c>
+      <c r="AM103">
+        <v>3.25</v>
+      </c>
+      <c r="AN103">
+        <v>2.11</v>
+      </c>
+      <c r="AO103">
+        <v>0.11</v>
+      </c>
+      <c r="AP103">
+        <v>2.2</v>
+      </c>
+      <c r="AQ103">
+        <v>0.1</v>
+      </c>
+      <c r="AR103">
+        <v>2.02</v>
+      </c>
+      <c r="AS103">
+        <v>1.45</v>
+      </c>
+      <c r="AT103">
+        <v>3.47</v>
+      </c>
+      <c r="AU103">
+        <v>17</v>
+      </c>
+      <c r="AV103">
+        <v>5</v>
+      </c>
+      <c r="AW103">
+        <v>13</v>
+      </c>
+      <c r="AX103">
+        <v>4</v>
+      </c>
+      <c r="AY103">
+        <v>30</v>
+      </c>
+      <c r="AZ103">
+        <v>9</v>
+      </c>
+      <c r="BA103">
+        <v>7</v>
+      </c>
+      <c r="BB103">
+        <v>2</v>
+      </c>
+      <c r="BC103">
+        <v>9</v>
+      </c>
+      <c r="BD103">
+        <v>0</v>
+      </c>
+      <c r="BE103">
+        <v>0</v>
+      </c>
+      <c r="BF103">
+        <v>0</v>
+      </c>
+      <c r="BG103">
+        <v>0</v>
+      </c>
+      <c r="BH103">
+        <v>0</v>
+      </c>
+      <c r="BI103">
+        <v>0</v>
+      </c>
+      <c r="BJ103">
+        <v>0</v>
+      </c>
+      <c r="BK103">
+        <v>0</v>
+      </c>
+      <c r="BL103">
+        <v>0</v>
+      </c>
+      <c r="BM103">
+        <v>0</v>
+      </c>
+      <c r="BN103">
+        <v>0</v>
+      </c>
+      <c r="BO103">
+        <v>0</v>
+      </c>
+      <c r="BP103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:68">
+      <c r="A104" s="1">
+        <v>103</v>
+      </c>
+      <c r="B104">
+        <v>7828561</v>
+      </c>
+      <c r="C104" t="s">
+        <v>68</v>
+      </c>
+      <c r="D104" t="s">
+        <v>69</v>
+      </c>
+      <c r="E104" s="2">
+        <v>45858.54166666666</v>
+      </c>
+      <c r="F104">
+        <v>0</v>
+      </c>
+      <c r="G104" t="s">
+        <v>73</v>
+      </c>
+      <c r="H104" t="s">
+        <v>71</v>
+      </c>
+      <c r="I104">
+        <v>0</v>
+      </c>
+      <c r="J104">
+        <v>1</v>
+      </c>
+      <c r="K104">
+        <v>1</v>
+      </c>
+      <c r="L104">
+        <v>2</v>
+      </c>
+      <c r="M104">
+        <v>1</v>
+      </c>
+      <c r="N104">
+        <v>3</v>
+      </c>
+      <c r="O104" t="s">
+        <v>155</v>
+      </c>
+      <c r="P104" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q104">
+        <v>3.84</v>
+      </c>
+      <c r="R104">
+        <v>2.2</v>
+      </c>
+      <c r="S104">
+        <v>2.6</v>
+      </c>
+      <c r="T104">
+        <v>1.3</v>
+      </c>
+      <c r="U104">
+        <v>2.88</v>
+      </c>
+      <c r="V104">
+        <v>2.62</v>
+      </c>
+      <c r="W104">
+        <v>1.42</v>
+      </c>
+      <c r="X104">
+        <v>6.15</v>
+      </c>
+      <c r="Y104">
+        <v>1.06</v>
+      </c>
+      <c r="Z104">
+        <v>3.1</v>
+      </c>
+      <c r="AA104">
+        <v>3.3</v>
+      </c>
+      <c r="AB104">
+        <v>2.1</v>
+      </c>
+      <c r="AC104">
+        <v>1.01</v>
+      </c>
+      <c r="AD104">
+        <v>10</v>
+      </c>
+      <c r="AE104">
+        <v>1.21</v>
+      </c>
+      <c r="AF104">
+        <v>4.4</v>
+      </c>
+      <c r="AG104">
+        <v>1.65</v>
+      </c>
+      <c r="AH104">
+        <v>2.1</v>
+      </c>
+      <c r="AI104">
+        <v>1.5</v>
+      </c>
+      <c r="AJ104">
+        <v>2.1</v>
+      </c>
+      <c r="AK104">
+        <v>1.55</v>
+      </c>
+      <c r="AL104">
+        <v>1.22</v>
+      </c>
+      <c r="AM104">
+        <v>1.33</v>
+      </c>
+      <c r="AN104">
+        <v>0.9</v>
+      </c>
+      <c r="AO104">
+        <v>1.63</v>
+      </c>
+      <c r="AP104">
+        <v>1.09</v>
+      </c>
+      <c r="AQ104">
+        <v>1.44</v>
+      </c>
+      <c r="AR104">
+        <v>1.63</v>
+      </c>
+      <c r="AS104">
+        <v>1.51</v>
+      </c>
+      <c r="AT104">
+        <v>3.14</v>
+      </c>
+      <c r="AU104">
+        <v>12</v>
+      </c>
+      <c r="AV104">
+        <v>8</v>
+      </c>
+      <c r="AW104">
+        <v>5</v>
+      </c>
+      <c r="AX104">
+        <v>12</v>
+      </c>
+      <c r="AY104">
+        <v>17</v>
+      </c>
+      <c r="AZ104">
+        <v>20</v>
+      </c>
+      <c r="BA104">
+        <v>4</v>
+      </c>
+      <c r="BB104">
+        <v>9</v>
+      </c>
+      <c r="BC104">
+        <v>13</v>
+      </c>
+      <c r="BD104">
+        <v>0</v>
+      </c>
+      <c r="BE104">
+        <v>0</v>
+      </c>
+      <c r="BF104">
+        <v>0</v>
+      </c>
+      <c r="BG104">
+        <v>0</v>
+      </c>
+      <c r="BH104">
+        <v>0</v>
+      </c>
+      <c r="BI104">
+        <v>0</v>
+      </c>
+      <c r="BJ104">
+        <v>0</v>
+      </c>
+      <c r="BK104">
+        <v>0</v>
+      </c>
+      <c r="BL104">
+        <v>0</v>
+      </c>
+      <c r="BM104">
+        <v>0</v>
+      </c>
+      <c r="BN104">
+        <v>0</v>
+      </c>
+      <c r="BO104">
+        <v>0</v>
+      </c>
+      <c r="BP104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:68">
+      <c r="A105" s="1">
+        <v>104</v>
+      </c>
+      <c r="B105">
+        <v>7828562</v>
+      </c>
+      <c r="C105" t="s">
+        <v>68</v>
+      </c>
+      <c r="D105" t="s">
+        <v>69</v>
+      </c>
+      <c r="E105" s="2">
+        <v>45858.54166666666</v>
+      </c>
+      <c r="F105">
+        <v>0</v>
+      </c>
+      <c r="G105" t="s">
+        <v>78</v>
+      </c>
+      <c r="H105" t="s">
+        <v>76</v>
+      </c>
+      <c r="I105">
+        <v>1</v>
+      </c>
+      <c r="J105">
+        <v>0</v>
+      </c>
+      <c r="K105">
+        <v>1</v>
+      </c>
+      <c r="L105">
+        <v>2</v>
+      </c>
+      <c r="M105">
+        <v>0</v>
+      </c>
+      <c r="N105">
+        <v>2</v>
+      </c>
+      <c r="O105" t="s">
+        <v>156</v>
+      </c>
+      <c r="P105" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q105">
+        <v>2.25</v>
+      </c>
+      <c r="R105">
+        <v>2.25</v>
+      </c>
+      <c r="S105">
+        <v>5.21</v>
+      </c>
+      <c r="T105">
+        <v>1.27</v>
+      </c>
+      <c r="U105">
+        <v>3.3</v>
+      </c>
+      <c r="V105">
+        <v>2.15</v>
+      </c>
+      <c r="W105">
+        <v>1.6</v>
+      </c>
+      <c r="X105">
+        <v>4.5</v>
+      </c>
+      <c r="Y105">
+        <v>1.15</v>
+      </c>
+      <c r="Z105">
+        <v>1.7</v>
+      </c>
+      <c r="AA105">
+        <v>3.6</v>
+      </c>
+      <c r="AB105">
+        <v>4.3</v>
+      </c>
+      <c r="AC105">
+        <v>1</v>
+      </c>
+      <c r="AD105">
+        <v>10</v>
+      </c>
+      <c r="AE105">
+        <v>1.2</v>
+      </c>
+      <c r="AF105">
+        <v>4.6</v>
+      </c>
+      <c r="AG105">
+        <v>1.82</v>
+      </c>
+      <c r="AH105">
+        <v>2.3</v>
+      </c>
+      <c r="AI105">
+        <v>1.73</v>
+      </c>
+      <c r="AJ105">
+        <v>2</v>
+      </c>
+      <c r="AK105">
+        <v>1.3</v>
+      </c>
+      <c r="AL105">
+        <v>1.22</v>
+      </c>
+      <c r="AM105">
+        <v>1.95</v>
+      </c>
+      <c r="AN105">
+        <v>2</v>
+      </c>
+      <c r="AO105">
+        <v>1.7</v>
+      </c>
+      <c r="AP105">
+        <v>2.09</v>
+      </c>
+      <c r="AQ105">
+        <v>1.55</v>
+      </c>
+      <c r="AR105">
+        <v>1.92</v>
+      </c>
+      <c r="AS105">
+        <v>1.61</v>
+      </c>
+      <c r="AT105">
+        <v>3.53</v>
+      </c>
+      <c r="AU105">
+        <v>3</v>
+      </c>
+      <c r="AV105">
+        <v>6</v>
+      </c>
+      <c r="AW105">
+        <v>6</v>
+      </c>
+      <c r="AX105">
+        <v>7</v>
+      </c>
+      <c r="AY105">
+        <v>9</v>
+      </c>
+      <c r="AZ105">
+        <v>13</v>
+      </c>
+      <c r="BA105">
+        <v>3</v>
+      </c>
+      <c r="BB105">
+        <v>5</v>
+      </c>
+      <c r="BC105">
+        <v>8</v>
+      </c>
+      <c r="BD105">
+        <v>0</v>
+      </c>
+      <c r="BE105">
+        <v>0</v>
+      </c>
+      <c r="BF105">
+        <v>0</v>
+      </c>
+      <c r="BG105">
+        <v>0</v>
+      </c>
+      <c r="BH105">
+        <v>0</v>
+      </c>
+      <c r="BI105">
+        <v>0</v>
+      </c>
+      <c r="BJ105">
+        <v>0</v>
+      </c>
+      <c r="BK105">
+        <v>0</v>
+      </c>
+      <c r="BL105">
+        <v>0</v>
+      </c>
+      <c r="BM105">
+        <v>0</v>
+      </c>
+      <c r="BN105">
+        <v>0</v>
+      </c>
+      <c r="BO105">
+        <v>0</v>
+      </c>
+      <c r="BP105">
         <v>0</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
@@ -478,7 +478,7 @@
     <t>['30', '34', '87']</t>
   </si>
   <si>
-    <t>['45', '7', '24', '60', '72', '88']</t>
+    <t>['45+1', '7', '25', '60', '72', '88']</t>
   </si>
   <si>
     <t>['58', '80']</t>
@@ -685,10 +685,10 @@
     <t>['4', '49']</t>
   </si>
   <si>
-    <t>['23', '16']</t>
+    <t>['24', '17']</t>
   </si>
   <si>
-    <t>['77', '85']</t>
+    <t>['76', '85']</t>
   </si>
 </sst>
 </file>
@@ -21876,7 +21876,7 @@
         <v>45858.45833333334</v>
       </c>
       <c r="F102">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G102" t="s">
         <v>75</v>
@@ -21999,22 +21999,22 @@
         <v>3.52</v>
       </c>
       <c r="AU102">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV102">
         <v>5</v>
       </c>
       <c r="AW102">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AX102">
+        <v>7</v>
+      </c>
+      <c r="AY102">
         <v>9</v>
       </c>
-      <c r="AY102">
-        <v>15</v>
-      </c>
       <c r="AZ102">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA102">
         <v>6</v>
@@ -22082,7 +22082,7 @@
         <v>45858.45833333334</v>
       </c>
       <c r="F103">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G103" t="s">
         <v>79</v>
@@ -22205,22 +22205,22 @@
         <v>3.47</v>
       </c>
       <c r="AU103">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AV103">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW103">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AX103">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AY103">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="AZ103">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA103">
         <v>7</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Estonia Meistriliiga_2025.xlsx
@@ -21999,22 +21999,22 @@
         <v>3.52</v>
       </c>
       <c r="AU102">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV102">
         <v>5</v>
       </c>
       <c r="AW102">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AX102">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AY102">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AZ102">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BA102">
         <v>6</v>
@@ -22205,22 +22205,22 @@
         <v>3.47</v>
       </c>
       <c r="AU103">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AV103">
+        <v>5</v>
+      </c>
+      <c r="AW103">
+        <v>13</v>
+      </c>
+      <c r="AX103">
         <v>4</v>
       </c>
-      <c r="AW103">
-        <v>7</v>
-      </c>
-      <c r="AX103">
-        <v>6</v>
-      </c>
       <c r="AY103">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="AZ103">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA103">
         <v>7</v>
@@ -22288,7 +22288,7 @@
         <v>45858.54166666666</v>
       </c>
       <c r="F104">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G104" t="s">
         <v>73</v>
@@ -22494,7 +22494,7 @@
         <v>45858.54166666666</v>
       </c>
       <c r="F105">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G105" t="s">
         <v>78</v>
